--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,129 +476,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>290</v>
+        <v>86</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.69</v>
+        <v>-5.18</v>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>237</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5.243</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3650</v>
+        <v>293.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-9.99</v>
+        <v>1.21</v>
       </c>
       <c r="F3" t="n">
-        <v>250</v>
+        <v>139</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>8.134</v>
+        <v>5.408</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1620</v>
+        <v>6400</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.28</v>
+        <v>4.58</v>
       </c>
       <c r="F4" t="n">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>15.359</v>
+        <v>12.426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>169.5</v>
+        <v>2380</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.31</v>
+        <v>-1.24</v>
       </c>
       <c r="F5" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,67 +606,67 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.414</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.2</v>
+        <v>172.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="F6" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>27.45</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.92</v>
+        <v>0.92</v>
       </c>
       <c r="F7" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,101 +674,101 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10.8</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1315</v>
+        <v>713</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.31</v>
+        <v>1.28</v>
       </c>
       <c r="F8" t="n">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.539</v>
+        <v>1.765</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2410</v>
+        <v>556</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.63</v>
+        <v>1.65</v>
       </c>
       <c r="F9" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>41.482</v>
+        <v>1.853</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>90.7</v>
+        <v>3590</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2</v>
+        <v>-1.64</v>
       </c>
       <c r="F10" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.275</v>
+        <v>7.456</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1990</v>
+        <v>1620</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.63</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,67 +810,67 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8.255000000000001</v>
+        <v>14.883</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>51.7</v>
+        <v>18.8</v>
       </c>
       <c r="E12" t="n">
-        <v>3.61</v>
+        <v>-0.53</v>
       </c>
       <c r="F12" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.583</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>273</v>
+        <v>160</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7</v>
+        <v>-6.71</v>
       </c>
       <c r="F13" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3.329</v>
+        <v>21.318</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.9</v>
+        <v>1365</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.05</v>
+        <v>3.8</v>
       </c>
       <c r="F14" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,67 +912,67 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.494</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>86.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.62</v>
+        <v>1.49</v>
       </c>
       <c r="F15" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.896</v>
+        <v>2.092</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4585</v>
+        <v>154</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.86</v>
+        <v>3.7</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>34.854</v>
+        <v>3.144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59.4</v>
+        <v>2730</v>
       </c>
       <c r="E17" t="n">
-        <v>2.41</v>
+        <v>5.81</v>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.42</v>
+        <v>4.125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70.7</v>
+        <v>112.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.81</v>
+        <v>1.81</v>
       </c>
       <c r="F18" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10.72</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>263</v>
+        <v>4560</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.13</v>
+        <v>-0.55</v>
       </c>
       <c r="F19" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,101 +1082,101 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.459</v>
+        <v>33.649</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.35</v>
+        <v>237</v>
       </c>
       <c r="E20" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.86</v>
+        <v>3.825</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>232.5</v>
+        <v>142.5</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.49</v>
+        <v>1.42</v>
       </c>
       <c r="F21" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.316</v>
+        <v>24.041</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>185.5</v>
+        <v>52.5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.27</v>
+        <v>1.55</v>
       </c>
       <c r="F22" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,67 +1184,67 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>9.776</v>
+        <v>1.528</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>704</v>
+        <v>232</v>
       </c>
       <c r="E23" t="n">
-        <v>1.15</v>
+        <v>-0.22</v>
       </c>
       <c r="F23" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.738</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2580</v>
+        <v>62.9</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.49</v>
+        <v>-2.63</v>
       </c>
       <c r="F24" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,271 +1252,271 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.903</v>
+        <v>2.085</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>157.5</v>
+        <v>248.5</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.48</v>
+        <v>0.2</v>
       </c>
       <c r="F25" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.856</v>
+        <v>7.809</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>336.5</v>
+        <v>473</v>
       </c>
       <c r="E26" t="n">
-        <v>0.15</v>
+        <v>-4.06</v>
       </c>
       <c r="F26" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.889</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6120</v>
+        <v>181</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.69</v>
+        <v>-2.43</v>
       </c>
       <c r="F27" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>12.01</v>
+        <v>9.385</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>248</v>
+        <v>70.7</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7.952</v>
+        <v>10.126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67.09999999999999</v>
+        <v>332.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3</v>
+        <v>-1.19</v>
       </c>
       <c r="F29" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.056</v>
+        <v>4.473</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>140.5</v>
+        <v>273.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.4</v>
+        <v>-2.5</v>
       </c>
       <c r="F30" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>23.251</v>
+        <v>1.242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>547</v>
+        <v>116</v>
       </c>
       <c r="E31" t="n">
-        <v>0.37</v>
+        <v>-2.52</v>
       </c>
       <c r="F31" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.813</v>
+        <v>4.357</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>110.5</v>
+        <v>30.4</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="F32" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,67 +1524,67 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2.509</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>280.5</v>
+        <v>42.05</v>
       </c>
       <c r="E33" t="n">
-        <v>1.45</v>
+        <v>-0.71</v>
       </c>
       <c r="F33" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.288</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>277</v>
+        <v>271.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.81</v>
+        <v>-0.55</v>
       </c>
       <c r="F34" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8.863</v>
+        <v>3.297</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>20.4</v>
+        <v>159.5</v>
       </c>
       <c r="E35" t="n">
-        <v>0.99</v>
+        <v>1.27</v>
       </c>
       <c r="F35" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.423</v>
+        <v>1.864</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>112</v>
+        <v>1935</v>
       </c>
       <c r="E36" t="n">
-        <v>1.36</v>
+        <v>-2.76</v>
       </c>
       <c r="F36" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,101 +1660,101 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4.911</v>
+        <v>7.788</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>402.5</v>
+        <v>612</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.11</v>
+        <v>-0.97</v>
       </c>
       <c r="F37" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.597</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>119</v>
+        <v>261.5</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.86</v>
+        <v>-0.57</v>
       </c>
       <c r="F38" t="n">
         <v>56</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4.775</v>
+        <v>5.396</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>171.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>-4.46</v>
+        <v>-0.12</v>
       </c>
       <c r="F39" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>22.905</v>
+        <v>1.807</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>398</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.96</v>
+        <v>-1.12</v>
       </c>
       <c r="F40" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.114</v>
+        <v>3.549</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>106</v>
+        <v>61.7</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2</v>
+        <v>-0.48</v>
       </c>
       <c r="F41" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,41 +1830,41 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.475</v>
+        <v>1.021</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>493</v>
+        <v>444</v>
       </c>
       <c r="E42" t="n">
-        <v>-4.27</v>
+        <v>1.49</v>
       </c>
       <c r="F42" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>35.355</v>
+        <v>12.314</v>
       </c>
     </row>
     <row r="43">
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.64</v>
+        <v>-0.22</v>
       </c>
       <c r="F43" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,135 +1898,135 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8.035</v>
+        <v>7.717</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>148.5</v>
+        <v>176.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="F44" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.106</v>
+        <v>2.584</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>61.7</v>
+        <v>20.2</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.48</v>
+        <v>-0.98</v>
       </c>
       <c r="F45" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.82</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>437.5</v>
+        <v>277.5</v>
       </c>
       <c r="E46" t="n">
-        <v>-5.2</v>
+        <v>0.18</v>
       </c>
       <c r="F46" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>12.392</v>
+        <v>8.725</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>234.5</v>
+        <v>105.5</v>
       </c>
       <c r="E47" t="n">
-        <v>1.52</v>
+        <v>-0.47</v>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,41 +2034,41 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.07</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>176</v>
+        <v>61.5</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.68</v>
+        <v>-0.32</v>
       </c>
       <c r="F48" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.712</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>276.5</v>
+        <v>274</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.12</v>
+        <v>-0.9</v>
       </c>
       <c r="F49" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.287</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>64.59999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.52</v>
+        <v>-0.17</v>
       </c>
       <c r="F50" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,41 +2136,41 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.163</v>
+        <v>5.212</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.66</v>
+        <v>0.89</v>
       </c>
       <c r="F51" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.133</v>
+        <v>4.751</v>
       </c>
     </row>
     <row r="52">
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="E52" t="n">
-        <v>-3.2</v>
+        <v>3.88</v>
       </c>
       <c r="F52" t="n">
         <v>14</v>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>6.739</v>
+        <v>6.692</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38.1</v>
+        <v>39.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="G2" t="n">
-        <v>5.243</v>
+        <v>5.408</v>
       </c>
     </row>
     <row r="3">
@@ -2311,44 +2311,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35.7</v>
+        <v>28.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="G3" t="n">
-        <v>6.739</v>
+        <v>6.692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23.62</v>
+        <v>22.71</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="G4" t="n">
-        <v>4.911</v>
+        <v>3.144</v>
       </c>
     </row>
     <row r="5">
@@ -2373,122 +2373,122 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16.12</v>
+        <v>17.28</v>
       </c>
       <c r="F5" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
-        <v>23.251</v>
+        <v>24.041</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15.74</v>
+        <v>14.68</v>
       </c>
       <c r="F6" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="G6" t="n">
-        <v>12.392</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.12</v>
+        <v>14.23</v>
       </c>
       <c r="F7" t="n">
-        <v>0.41</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>5.42</v>
+        <v>4.125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14.67</v>
+        <v>13.45</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="G8" t="n">
-        <v>3.106</v>
+        <v>4.751</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2497,292 +2497,292 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12.4</v>
+        <v>12.66</v>
       </c>
       <c r="F9" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.528</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>11.99</v>
+        <v>12.59</v>
       </c>
       <c r="F10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>12.01</v>
+        <v>33.649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.19</v>
+        <v>11.56</v>
       </c>
       <c r="F11" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>1.583</v>
+        <v>12.314</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.91</v>
+        <v>10.24</v>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="G12" t="n">
-        <v>34.854</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.869999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="F13" t="n">
         <v>0.85</v>
       </c>
       <c r="G13" t="n">
-        <v>2.509</v>
+        <v>12.426</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8.44</v>
+        <v>9.23</v>
       </c>
       <c r="F14" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="G14" t="n">
-        <v>0.82</v>
+        <v>1.853</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.67</v>
+        <v>8.41</v>
       </c>
       <c r="F15" t="n">
-        <v>0.71</v>
+        <v>0.45</v>
       </c>
       <c r="G15" t="n">
-        <v>2.163</v>
+        <v>5.212</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.08</v>
+        <v>7.81</v>
       </c>
       <c r="F16" t="n">
-        <v>0.41</v>
+        <v>0.66</v>
       </c>
       <c r="G16" t="n">
-        <v>4.07</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.84</v>
+        <v>6.43</v>
       </c>
       <c r="F17" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.813</v>
+        <v>2.085</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.77</v>
+        <v>6.28</v>
       </c>
       <c r="F18" t="n">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="G18" t="n">
-        <v>0.133</v>
+        <v>8.725</v>
       </c>
     </row>
     <row r="19">
@@ -2807,44 +2807,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.48</v>
+        <v>5.23</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="G19" t="n">
-        <v>5.459</v>
+        <v>5.396</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.14</v>
+        <v>3.81</v>
       </c>
       <c r="F20" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="G20" t="n">
-        <v>0.86</v>
+        <v>2.092</v>
       </c>
     </row>
     <row r="21">
@@ -2869,463 +2869,463 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="F21" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="G21" t="n">
-        <v>1.288</v>
+        <v>1.242</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.7</v>
+        <v>3.02</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="G22" t="n">
-        <v>8.863</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="F23" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="G23" t="n">
-        <v>4.889</v>
+        <v>1.765</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="F24" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="G24" t="n">
-        <v>0.423</v>
+        <v>3.825</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.98</v>
+        <v>0.6</v>
       </c>
       <c r="F25" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="G25" t="n">
-        <v>2.056</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.11</v>
+        <v>-0.25</v>
       </c>
       <c r="F26" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="G26" t="n">
-        <v>1.738</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.63</v>
+        <v>-0.27</v>
       </c>
       <c r="F27" t="n">
-        <v>1.19</v>
+        <v>0.97</v>
       </c>
       <c r="G27" t="n">
-        <v>41.482</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="F28" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="G28" t="n">
-        <v>10.8</v>
+        <v>4.473</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.12</v>
+        <v>-0.49</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="G29" t="n">
-        <v>3.597</v>
+        <v>10.317</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="G30" t="n">
-        <v>0.494</v>
+        <v>3.549</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-1.8</v>
+        <v>-0.83</v>
       </c>
       <c r="F31" t="n">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="G31" t="n">
-        <v>3.329</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-1.87</v>
+        <v>-1.44</v>
       </c>
       <c r="F32" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G32" t="n">
-        <v>1.856</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-2.31</v>
+        <v>-1.54</v>
       </c>
       <c r="F33" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="G33" t="n">
-        <v>0.414</v>
+        <v>1.864</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-2.82</v>
+        <v>-2.34</v>
       </c>
       <c r="F34" t="n">
-        <v>1.17</v>
+        <v>0.98</v>
       </c>
       <c r="G34" t="n">
-        <v>3.903</v>
+        <v>3.297</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-3.71</v>
+        <v>-2.54</v>
       </c>
       <c r="F35" t="n">
-        <v>0.67</v>
+        <v>1.06</v>
       </c>
       <c r="G35" t="n">
-        <v>35.355</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3334,137 +3334,137 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-4.13</v>
+        <v>-2.55</v>
       </c>
       <c r="F36" t="n">
-        <v>1.46</v>
+        <v>0.9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.776</v>
+        <v>7.809</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-4.33</v>
+        <v>-3.21</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="G37" t="n">
-        <v>8.255000000000001</v>
+        <v>9.385</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-4.43</v>
+        <v>-4.72</v>
       </c>
       <c r="F38" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="G38" t="n">
-        <v>7.952</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-4.71</v>
+        <v>-4.92</v>
       </c>
       <c r="F39" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="G39" t="n">
-        <v>0.539</v>
+        <v>10.126</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-5.47</v>
+        <v>-5.36</v>
       </c>
       <c r="F40" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="G40" t="n">
-        <v>1.287</v>
+        <v>2.584</v>
       </c>
     </row>
     <row r="41">
@@ -3489,292 +3489,292 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-5.66</v>
+        <v>-5.36</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="G41" t="n">
-        <v>1.896</v>
+        <v>1.807</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-5.67</v>
+        <v>-5.52</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="G42" t="n">
-        <v>0.475</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-5.68</v>
+        <v>-7.19</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="G43" t="n">
-        <v>0.316</v>
+        <v>7.788</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-6.38</v>
+        <v>-7.5</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5</v>
+        <v>1.02</v>
       </c>
       <c r="G44" t="n">
-        <v>2.712</v>
+        <v>1.021</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-6.54</v>
+        <v>-9.73</v>
       </c>
       <c r="F45" t="n">
-        <v>0.92</v>
+        <v>0.66</v>
       </c>
       <c r="G45" t="n">
-        <v>22.905</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-9.529999999999999</v>
+        <v>-10.42</v>
       </c>
       <c r="F46" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="G46" t="n">
-        <v>10.72</v>
+        <v>4.357</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-10.69</v>
+        <v>-10.89</v>
       </c>
       <c r="F47" t="n">
-        <v>0.76</v>
+        <v>1.3</v>
       </c>
       <c r="G47" t="n">
-        <v>8.035</v>
+        <v>7.456</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-11.3</v>
+        <v>-11.18</v>
       </c>
       <c r="F48" t="n">
-        <v>1.13</v>
+        <v>0.51</v>
       </c>
       <c r="G48" t="n">
-        <v>1.114</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-12.62</v>
+        <v>-11.76</v>
       </c>
       <c r="F49" t="n">
-        <v>1.36</v>
+        <v>0.68</v>
       </c>
       <c r="G49" t="n">
-        <v>8.134</v>
+        <v>7.717</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-13.14</v>
+        <v>-11.85</v>
       </c>
       <c r="F50" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="G50" t="n">
-        <v>4.775</v>
+        <v>21.318</v>
       </c>
     </row>
     <row r="51">
@@ -3802,10 +3802,10 @@
         <v>-14.06</v>
       </c>
       <c r="F51" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="G51" t="n">
-        <v>15.359</v>
+        <v>14.883</v>
       </c>
     </row>
     <row r="52">
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-21.76</v>
+        <v>-24.19</v>
       </c>
       <c r="F52" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="G52" t="n">
         <v>0.275</v>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.1</v>
+        <v>39.1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="D2" t="n">
-        <v>5.243</v>
+        <v>5.408</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,93 +3902,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.27333333333333</v>
+        <v>14.23</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4399999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="D3" t="n">
-        <v>14.401</v>
+        <v>4.125</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.25666666666667</v>
+        <v>12.82</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4766666666666666</v>
+        <v>0.8240000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>19.606</v>
+        <v>9.783000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.422000000000001</v>
+        <v>12.59</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8019999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="D5" t="n">
-        <v>9.815</v>
+        <v>33.649</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.91</v>
+        <v>9.56</v>
       </c>
       <c r="C6" t="n">
-        <v>1.02</v>
+        <v>0.4633333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>34.854</v>
+        <v>19.461</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.44</v>
+        <v>9.23</v>
       </c>
       <c r="C7" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="D7" t="n">
-        <v>0.82</v>
+        <v>1.853</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.375</v>
+        <v>8.225000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1.285</v>
+        <v>1.115</v>
       </c>
       <c r="D8" t="n">
-        <v>64.733</v>
+        <v>65.73099999999999</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -4016,36 +4016,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.67</v>
+        <v>8.08</v>
       </c>
       <c r="C9" t="n">
-        <v>0.71</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>2.163</v>
+        <v>13.788</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.84</v>
+        <v>7.81</v>
       </c>
       <c r="C10" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="D10" t="n">
-        <v>1.813</v>
+        <v>0.136</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.77</v>
+        <v>6.43</v>
       </c>
       <c r="C11" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="D11" t="n">
-        <v>0.133</v>
+        <v>2.085</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.48</v>
+        <v>5.23</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="D12" t="n">
-        <v>5.459</v>
+        <v>5.396</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,20 +4092,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.324999999999999</v>
+        <v>3.02</v>
       </c>
       <c r="C13" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="D13" t="n">
-        <v>1.283</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.11</v>
+        <v>2.97</v>
       </c>
       <c r="C14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="D14" t="n">
-        <v>1.738</v>
+        <v>1.765</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,112 +4130,112 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.32</v>
+        <v>0.175</v>
       </c>
       <c r="C15" t="n">
-        <v>1.13</v>
+        <v>0.625</v>
       </c>
       <c r="D15" t="n">
-        <v>10.8</v>
+        <v>1.183</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.01666666666666661</v>
+        <v>-0.27</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.97</v>
       </c>
       <c r="D16" t="n">
-        <v>6.172</v>
+        <v>0.49</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3149999999999995</v>
+        <v>-0.49</v>
       </c>
       <c r="C17" t="n">
-        <v>1.075</v>
+        <v>0.97</v>
       </c>
       <c r="D17" t="n">
-        <v>20.144</v>
+        <v>10.317</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.53</v>
+        <v>-0.7399999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.91</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="D18" t="n">
-        <v>0.494</v>
+        <v>6.051</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.87</v>
+        <v>-0.7450000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1.18</v>
+        <v>1.075</v>
       </c>
       <c r="D19" t="n">
-        <v>1.856</v>
+        <v>19.882</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-2.82</v>
+        <v>-1.44</v>
       </c>
       <c r="C20" t="n">
-        <v>1.17</v>
+        <v>0.88</v>
       </c>
       <c r="D20" t="n">
-        <v>3.903</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-3.71</v>
+        <v>-1.54</v>
       </c>
       <c r="C21" t="n">
-        <v>0.67</v>
+        <v>1.07</v>
       </c>
       <c r="D21" t="n">
-        <v>35.355</v>
+        <v>1.864</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4263,93 +4263,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-3.73</v>
+        <v>-3.39</v>
       </c>
       <c r="C22" t="n">
-        <v>0.965</v>
+        <v>1.16</v>
       </c>
       <c r="D22" t="n">
-        <v>5.225</v>
+        <v>22.688</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-4.2775</v>
+        <v>-3.85</v>
       </c>
       <c r="C23" t="n">
-        <v>1.2225</v>
+        <v>0.95</v>
       </c>
       <c r="D23" t="n">
-        <v>23.731</v>
+        <v>5.104</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-4.33</v>
+        <v>-3.89</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="D24" t="n">
-        <v>8.255000000000001</v>
+        <v>23.608</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-4.68</v>
+        <v>-4.72</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="D25" t="n">
-        <v>24.222</v>
+        <v>0.318</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-4.71</v>
+        <v>-4.92</v>
       </c>
       <c r="C26" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="D26" t="n">
-        <v>0.539</v>
+        <v>10.126</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-5.68</v>
+        <v>-7.19</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="D27" t="n">
-        <v>0.316</v>
+        <v>7.788</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,55 +4377,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-6.54</v>
+        <v>-8.56</v>
       </c>
       <c r="C28" t="n">
-        <v>0.92</v>
+        <v>0.575</v>
       </c>
       <c r="D28" t="n">
-        <v>22.905</v>
+        <v>10.301</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-8.535</v>
+        <v>-9.73</v>
       </c>
       <c r="C29" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="D29" t="n">
-        <v>10.747</v>
+        <v>33.59</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-9.529999999999999</v>
+        <v>-10.42</v>
       </c>
       <c r="C30" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="D30" t="n">
-        <v>10.72</v>
+        <v>4.357</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4434,39 +4434,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-12.035</v>
+        <v>-11.85</v>
       </c>
       <c r="C31" t="n">
-        <v>1.115</v>
+        <v>0.93</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6890000000000001</v>
+        <v>21.318</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-13.14</v>
+        <v>-13.365</v>
       </c>
       <c r="C32" t="n">
-        <v>0.83</v>
+        <v>1.315</v>
       </c>
       <c r="D32" t="n">
-        <v>4.775</v>
+        <v>0.6990000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1990</v>
+        <v>1935</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.63</v>
+        <v>-2.76</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.33</v>
+        <v>-7.19</v>
       </c>
       <c r="G2" t="n">
-        <v>35.64</v>
+        <v>35.29</v>
       </c>
       <c r="H2" t="n">
-        <v>11.1356</v>
+        <v>6.4839</v>
       </c>
       <c r="I2" t="n">
-        <v>15.9</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>-43</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4585</v>
+        <v>4560</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.86</v>
+        <v>-0.55</v>
       </c>
       <c r="F3" t="n">
-        <v>8.91</v>
+        <v>12.59</v>
       </c>
       <c r="G3" t="n">
-        <v>73.03</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>221.3698</v>
+        <v>219.4805</v>
       </c>
       <c r="I3" t="n">
-        <v>78.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>82.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.61</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4</v>
+        <v>-17.2</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,38 +4676,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>90.7</v>
+        <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2</v>
+        <v>-5.18</v>
       </c>
       <c r="F4" t="n">
-        <v>-21.76</v>
+        <v>-24.19</v>
       </c>
       <c r="G4" t="n">
-        <v>25.13</v>
+        <v>18.14</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.5059</v>
+        <v>-7.6406</v>
       </c>
       <c r="I4" t="n">
-        <v>-12.6</v>
+        <v>-14.7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>6.47</v>
+        <v>6.77</v>
       </c>
       <c r="L4" t="n">
-        <v>20.5</v>
+        <v>137.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>❌ EXIT</t>
         </is>
       </c>
     </row>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>290</v>
+        <v>293.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.69</v>
+        <v>1.21</v>
       </c>
       <c r="F5" t="n">
-        <v>38.1</v>
+        <v>39.1</v>
       </c>
       <c r="G5" t="n">
-        <v>73.51000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="H5" t="n">
-        <v>22.9282</v>
+        <v>24.7926</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>94.8</v>
+        <v>98.5</v>
       </c>
       <c r="K5" t="n">
-        <v>7.4</v>
+        <v>7.74</v>
       </c>
       <c r="L5" t="n">
-        <v>230.7</v>
+        <v>39.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.2</v>
+        <v>3.88</v>
       </c>
       <c r="F6" t="n">
-        <v>35.7</v>
+        <v>28.3</v>
       </c>
       <c r="G6" t="n">
-        <v>75.72</v>
+        <v>73.91</v>
       </c>
       <c r="H6" t="n">
-        <v>43.1289</v>
+        <v>43.2575</v>
       </c>
       <c r="I6" t="n">
-        <v>71.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="J6" t="n">
-        <v>78</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>6.74</v>
+        <v>6.45</v>
       </c>
       <c r="L6" t="n">
-        <v>-86</v>
+        <v>-86.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>248</v>
+        <v>248.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.43</v>
+        <v>-2.55</v>
       </c>
       <c r="G7" t="n">
-        <v>54.95</v>
+        <v>56.04</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4066</v>
+        <v>-0.0515</v>
       </c>
       <c r="I7" t="n">
-        <v>38.5</v>
+        <v>43.2</v>
       </c>
       <c r="J7" t="n">
-        <v>38.5</v>
+        <v>21.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="L7" t="n">
-        <v>-24.9</v>
+        <v>-29.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,95 +476,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>69.7</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.18</v>
+        <v>2.35</v>
       </c>
       <c r="F2" t="n">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.275</v>
+        <v>2.255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>293.5</v>
+        <v>1670</v>
       </c>
       <c r="E3" t="n">
-        <v>1.21</v>
+        <v>3.09</v>
       </c>
       <c r="F3" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.408</v>
+        <v>15.774</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6400</v>
+        <v>294.5</v>
       </c>
       <c r="E4" t="n">
-        <v>4.58</v>
+        <v>0.34</v>
       </c>
       <c r="F4" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12.426</v>
+        <v>5.678</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2380</v>
+        <v>86</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.24</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>41.69</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>172.5</v>
+        <v>3355</v>
       </c>
       <c r="E6" t="n">
-        <v>1.77</v>
+        <v>-6.55</v>
       </c>
       <c r="F6" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.424</v>
+        <v>6.799</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.45</v>
+        <v>454</v>
       </c>
       <c r="E7" t="n">
-        <v>0.92</v>
+        <v>2.25</v>
       </c>
       <c r="F7" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.549</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>713</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>1.28</v>
+        <v>-1.64</v>
       </c>
       <c r="F8" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,67 +708,67 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.765</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>556</v>
+        <v>19.9</v>
       </c>
       <c r="E9" t="n">
-        <v>1.65</v>
+        <v>-1.49</v>
       </c>
       <c r="F9" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.853</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3590</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.64</v>
+        <v>-5.37</v>
       </c>
       <c r="F10" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.456</v>
+        <v>9.371</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1620</v>
+        <v>18.65</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F11" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,67 +810,67 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14.883</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>6035</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.53</v>
+        <v>-5.7</v>
       </c>
       <c r="F12" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.49</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>160</v>
+        <v>41.2</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.71</v>
+        <v>-2.02</v>
       </c>
       <c r="F13" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>21.318</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1365</v>
+        <v>541</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8</v>
+        <v>-2.7</v>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,132 +912,132 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.829</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>68.09999999999999</v>
+        <v>914</v>
       </c>
       <c r="E15" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="F15" t="n">
         <v>91</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.092</v>
+        <v>7.575</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7</v>
+        <v>-0.28</v>
       </c>
       <c r="F16" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.144</v>
+        <v>2.429</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2730</v>
+        <v>2385</v>
       </c>
       <c r="E17" t="n">
-        <v>5.81</v>
+        <v>0.21</v>
       </c>
       <c r="F17" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4.125</v>
+        <v>41.131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>112.5</v>
+        <v>4430</v>
       </c>
       <c r="E18" t="n">
-        <v>1.81</v>
+        <v>-2.85</v>
       </c>
       <c r="F18" t="n">
         <v>85</v>
@@ -1048,135 +1048,135 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.47</v>
+        <v>32.097</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4560</v>
+        <v>592</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.55</v>
+        <v>-3.27</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>33.649</v>
+        <v>9.811</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="E20" t="n">
-        <v>1.07</v>
+        <v>-1.95</v>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.825</v>
+        <v>3.033</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>142.5</v>
+        <v>153</v>
       </c>
       <c r="E21" t="n">
-        <v>1.42</v>
+        <v>-4.08</v>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>24.041</v>
+        <v>1.749</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52.5</v>
+        <v>703</v>
       </c>
       <c r="E22" t="n">
-        <v>1.55</v>
+        <v>-1.4</v>
       </c>
       <c r="F22" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,64 +1184,64 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.528</v>
+        <v>1.721</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.22</v>
+        <v>-2.22</v>
       </c>
       <c r="F23" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.318</v>
+        <v>2.423</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62.9</v>
+        <v>51.8</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.63</v>
+        <v>-1.33</v>
       </c>
       <c r="F24" t="n">
         <v>72</v>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.085</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>248.5</v>
+        <v>388.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2</v>
+        <v>-2.39</v>
       </c>
       <c r="F25" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7.809</v>
+        <v>3.402</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>473</v>
+        <v>1370</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.06</v>
+        <v>0.37</v>
       </c>
       <c r="F26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,30 +1320,30 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>33.59</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>181</v>
+        <v>268</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.43</v>
+        <v>-1.29</v>
       </c>
       <c r="F27" t="n">
         <v>66</v>
@@ -1354,75 +1354,75 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.385</v>
+        <v>3.213</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>70.7</v>
+        <v>29.65</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
       <c r="F28" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>10.126</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>332.5</v>
+        <v>2625</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.19</v>
+        <v>-3.85</v>
       </c>
       <c r="F29" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4.473</v>
+        <v>3.839</v>
       </c>
     </row>
     <row r="30">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>273.5</v>
+        <v>266</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.5</v>
+        <v>-2.74</v>
       </c>
       <c r="F30" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.242</v>
+        <v>1.198</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>116</v>
+        <v>333</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.52</v>
+        <v>0.15</v>
       </c>
       <c r="F31" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.357</v>
+        <v>4.381</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>30.4</v>
+        <v>138.5</v>
       </c>
       <c r="E32" t="n">
-        <v>1.33</v>
+        <v>-2.81</v>
       </c>
       <c r="F32" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.136</v>
+        <v>23.441</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>42.05</v>
+        <v>274</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.71</v>
+        <v>-1.26</v>
       </c>
       <c r="F33" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,30 +1558,30 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.781</v>
+        <v>8.308999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>271.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.55</v>
+        <v>-2.54</v>
       </c>
       <c r="F34" t="n">
         <v>58</v>
@@ -1592,41 +1592,41 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3.297</v>
+        <v>1.691</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>159.5</v>
+        <v>60.5</v>
       </c>
       <c r="E35" t="n">
-        <v>1.27</v>
+        <v>-1.94</v>
       </c>
       <c r="F35" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.864</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="36">
@@ -1646,13 +1646,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1935</v>
+        <v>1920</v>
       </c>
       <c r="E36" t="n">
-        <v>-2.76</v>
+        <v>-0.78</v>
       </c>
       <c r="F36" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,101 +1660,101 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7.788</v>
+        <v>7.477</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>612</v>
+        <v>159.5</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.97</v>
+        <v>-0.31</v>
       </c>
       <c r="F37" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>10.317</v>
+        <v>20.328</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>261.5</v>
+        <v>62</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.57</v>
+        <v>-1.43</v>
       </c>
       <c r="F38" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.396</v>
+        <v>2.046</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>86.59999999999999</v>
+        <v>170</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.12</v>
+        <v>-1.45</v>
       </c>
       <c r="F39" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.807</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>398</v>
+        <v>246.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.12</v>
+        <v>-0.8</v>
       </c>
       <c r="F40" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.549</v>
+        <v>7.341</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>61.7</v>
+        <v>114.5</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.48</v>
+        <v>-1.29</v>
       </c>
       <c r="F41" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,67 +1830,67 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.021</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>444</v>
+        <v>465.5</v>
       </c>
       <c r="E42" t="n">
-        <v>1.49</v>
+        <v>-1.59</v>
       </c>
       <c r="F42" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>12.314</v>
+        <v>31.839</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>900</v>
+        <v>106</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.22</v>
+        <v>0.47</v>
       </c>
       <c r="F43" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7.717</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>176.5</v>
+        <v>233.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.28</v>
+        <v>-1.48</v>
       </c>
       <c r="F44" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.584</v>
+        <v>3.501</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>20.2</v>
+        <v>224.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.98</v>
+        <v>-3.23</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.402</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>277.5</v>
+        <v>182.5</v>
       </c>
       <c r="E46" t="n">
-        <v>0.18</v>
+        <v>0.83</v>
       </c>
       <c r="F46" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,101 +2000,101 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.725</v>
+        <v>9.302</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>105.5</v>
+        <v>257</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.47</v>
+        <v>-1.72</v>
       </c>
       <c r="F47" t="n">
         <v>38</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.455</v>
+        <v>5.152</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>61.5</v>
+        <v>273</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
       <c r="F48" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>274</v>
+        <v>60.1</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.9</v>
+        <v>-2.28</v>
       </c>
       <c r="F49" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.26</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="50">
@@ -2122,21 +2122,21 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>59.3</v>
+        <v>58.8</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.17</v>
+        <v>-0.84</v>
       </c>
       <c r="F50" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5.212</v>
+        <v>4.979</v>
       </c>
     </row>
     <row r="51">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E51" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="F51" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>4.751</v>
+        <v>4.358</v>
       </c>
     </row>
     <row r="52">
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="E52" t="n">
-        <v>3.88</v>
+        <v>-2.8</v>
       </c>
       <c r="F52" t="n">
         <v>14</v>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>6.692</v>
+        <v>5.633</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>39.1</v>
+        <v>51.41</v>
       </c>
       <c r="F2" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="G2" t="n">
-        <v>5.408</v>
+        <v>5.678</v>
       </c>
     </row>
     <row r="3">
@@ -2311,184 +2311,184 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28.3</v>
+        <v>24.55</v>
       </c>
       <c r="F3" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="G3" t="n">
-        <v>6.692</v>
+        <v>5.633</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22.71</v>
+        <v>21.23</v>
       </c>
       <c r="F4" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>3.144</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17.28</v>
+        <v>16.6</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>0.73</v>
       </c>
       <c r="G5" t="n">
-        <v>24.041</v>
+        <v>3.033</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14.68</v>
+        <v>16.39</v>
       </c>
       <c r="F6" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2.47</v>
+        <v>23.441</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.23</v>
+        <v>14.03</v>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>4.125</v>
+        <v>32.097</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>13.45</v>
+        <v>12.18</v>
       </c>
       <c r="F8" t="n">
-        <v>0.54</v>
+        <v>0.88</v>
       </c>
       <c r="G8" t="n">
-        <v>4.751</v>
+        <v>3.839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2497,199 +2497,199 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12.66</v>
+        <v>10.89</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="G9" t="n">
-        <v>1.528</v>
+        <v>2.423</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12.59</v>
+        <v>10.45</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>33.649</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11.56</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="G11" t="n">
-        <v>12.314</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.24</v>
+        <v>8.9</v>
       </c>
       <c r="F12" t="n">
-        <v>0.98</v>
+        <v>0.61</v>
       </c>
       <c r="G12" t="n">
-        <v>0.549</v>
+        <v>5.152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.4</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="G13" t="n">
-        <v>12.426</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.23</v>
+        <v>7.32</v>
       </c>
       <c r="F14" t="n">
-        <v>0.84</v>
+        <v>0.55</v>
       </c>
       <c r="G14" t="n">
-        <v>1.853</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.41</v>
+        <v>7.13</v>
       </c>
       <c r="F15" t="n">
-        <v>0.45</v>
+        <v>0.92</v>
       </c>
       <c r="G15" t="n">
-        <v>5.212</v>
+        <v>1.829</v>
       </c>
     </row>
     <row r="16">
@@ -2714,106 +2714,106 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.81</v>
+        <v>7.02</v>
       </c>
       <c r="F16" t="n">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="G16" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.43</v>
+        <v>6.67</v>
       </c>
       <c r="F17" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>2.085</v>
+        <v>4.358</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.28</v>
+        <v>5.56</v>
       </c>
       <c r="F18" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>8.725</v>
+        <v>1.198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.23</v>
+        <v>5.26</v>
       </c>
       <c r="F19" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="G19" t="n">
-        <v>5.396</v>
+        <v>2.046</v>
       </c>
     </row>
     <row r="20">
@@ -2838,571 +2838,571 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.81</v>
+        <v>4.81</v>
       </c>
       <c r="F20" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="G20" t="n">
-        <v>2.092</v>
+        <v>2.255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.8</v>
+        <v>4.63</v>
       </c>
       <c r="F21" t="n">
-        <v>0.87</v>
+        <v>0.49</v>
       </c>
       <c r="G21" t="n">
-        <v>1.242</v>
+        <v>4.979</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="F22" t="n">
-        <v>0.66</v>
+        <v>0.99</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.721</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.97</v>
+        <v>1.83</v>
       </c>
       <c r="F23" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1.765</v>
+        <v>4.381</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.38</v>
+        <v>1.11</v>
       </c>
       <c r="F24" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="G24" t="n">
-        <v>3.825</v>
+        <v>8.308999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.6</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="G25" t="n">
-        <v>0.781</v>
+        <v>3.213</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-0.25</v>
+        <v>0.83</v>
       </c>
       <c r="F26" t="n">
-        <v>0.59</v>
+        <v>0.99</v>
       </c>
       <c r="G26" t="n">
-        <v>0.402</v>
+        <v>9.302</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-0.27</v>
+        <v>0.74</v>
       </c>
       <c r="F27" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.49</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-0.3</v>
+        <v>0.39</v>
       </c>
       <c r="F28" t="n">
-        <v>1.36</v>
+        <v>0.63</v>
       </c>
       <c r="G28" t="n">
-        <v>4.473</v>
+        <v>3.402</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-0.49</v>
+        <v>0.21</v>
       </c>
       <c r="F29" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="G29" t="n">
-        <v>10.317</v>
+        <v>41.131</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.5</v>
+        <v>-0.29</v>
       </c>
       <c r="F30" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="G30" t="n">
-        <v>3.549</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.83</v>
+        <v>-1</v>
       </c>
       <c r="F31" t="n">
-        <v>1.12</v>
+        <v>0.67</v>
       </c>
       <c r="G31" t="n">
-        <v>41.69</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-1.44</v>
+        <v>-1</v>
       </c>
       <c r="F32" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5649999999999999</v>
+        <v>7.341</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-1.54</v>
+        <v>-1.17</v>
       </c>
       <c r="F33" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="G33" t="n">
-        <v>1.864</v>
+        <v>9.811</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-2.34</v>
+        <v>-1.29</v>
       </c>
       <c r="F34" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="G34" t="n">
-        <v>3.297</v>
+        <v>1.749</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-2.54</v>
+        <v>-1.58</v>
       </c>
       <c r="F35" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="G35" t="n">
-        <v>0.424</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-2.55</v>
+        <v>-1.67</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="G36" t="n">
-        <v>7.809</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-3.21</v>
+        <v>-1.89</v>
       </c>
       <c r="F37" t="n">
-        <v>1.36</v>
+        <v>0.58</v>
       </c>
       <c r="G37" t="n">
-        <v>9.385</v>
+        <v>3.501</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-4.72</v>
+        <v>-2.5</v>
       </c>
       <c r="F38" t="n">
-        <v>0.73</v>
+        <v>0.38</v>
       </c>
       <c r="G38" t="n">
-        <v>0.318</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="39">
@@ -3427,323 +3427,323 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-4.92</v>
+        <v>-3.7</v>
       </c>
       <c r="F39" t="n">
         <v>0.91</v>
       </c>
       <c r="G39" t="n">
-        <v>10.126</v>
+        <v>9.371</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-5.36</v>
+        <v>-4</v>
       </c>
       <c r="F40" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="G40" t="n">
-        <v>2.584</v>
+        <v>7.477</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-5.36</v>
+        <v>-4.86</v>
       </c>
       <c r="F41" t="n">
-        <v>0.92</v>
+        <v>0.53</v>
       </c>
       <c r="G41" t="n">
-        <v>1.807</v>
+        <v>2.429</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-5.52</v>
+        <v>-5.27</v>
       </c>
       <c r="F42" t="n">
-        <v>0.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>1.26</v>
+        <v>1.691</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-7.19</v>
+        <v>-6.15</v>
       </c>
       <c r="F43" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="G43" t="n">
-        <v>7.788</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-7.5</v>
+        <v>-6.49</v>
       </c>
       <c r="F44" t="n">
-        <v>1.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>1.021</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-9.73</v>
+        <v>-6.78</v>
       </c>
       <c r="F45" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="G45" t="n">
-        <v>33.59</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-10.42</v>
+        <v>-8.24</v>
       </c>
       <c r="F46" t="n">
-        <v>0.85</v>
+        <v>1.29</v>
       </c>
       <c r="G46" t="n">
-        <v>4.357</v>
+        <v>15.774</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-10.89</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="G47" t="n">
-        <v>7.456</v>
+        <v>0.305</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-11.18</v>
+        <v>-8.99</v>
       </c>
       <c r="F48" t="n">
-        <v>0.51</v>
+        <v>1.43</v>
       </c>
       <c r="G48" t="n">
-        <v>0.455</v>
+        <v>6.799</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-11.76</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>0.68</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>7.717</v>
+        <v>31.839</v>
       </c>
     </row>
     <row r="50">
@@ -3768,44 +3768,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-11.85</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="G50" t="n">
-        <v>21.318</v>
+        <v>20.328</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-14.06</v>
+        <v>-13.77</v>
       </c>
       <c r="F51" t="n">
-        <v>1.15</v>
+        <v>0.66</v>
       </c>
       <c r="G51" t="n">
-        <v>14.883</v>
+        <v>7.575</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-24.19</v>
+        <v>-21.43</v>
       </c>
       <c r="F52" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="G52" t="n">
-        <v>0.275</v>
+        <v>0.276</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39.1</v>
+        <v>51.41</v>
       </c>
       <c r="C2" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="D2" t="n">
-        <v>5.408</v>
+        <v>5.678</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.23</v>
+        <v>14.03</v>
       </c>
       <c r="C3" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>4.125</v>
+        <v>32.097</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,36 +3921,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.82</v>
+        <v>13.09666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8240000000000001</v>
+        <v>0.5100000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>9.783000000000001</v>
+        <v>18.802</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.59</v>
+        <v>12.18</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="D5" t="n">
-        <v>33.649</v>
+        <v>3.839</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,36 +3959,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.56</v>
+        <v>10.194</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4633333333333333</v>
+        <v>0.866</v>
       </c>
       <c r="D6" t="n">
-        <v>19.461</v>
+        <v>9.698</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.23</v>
+        <v>8.9</v>
       </c>
       <c r="C7" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="D7" t="n">
-        <v>1.853</v>
+        <v>5.152</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.225000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1.115</v>
+        <v>0.975</v>
       </c>
       <c r="D8" t="n">
-        <v>65.73099999999999</v>
+        <v>64.572</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -4016,36 +4016,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.08</v>
+        <v>7.32</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5066666666666667</v>
+        <v>0.55</v>
       </c>
       <c r="D9" t="n">
-        <v>13.788</v>
+        <v>0.779</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.81</v>
+        <v>7.13</v>
       </c>
       <c r="C10" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="D10" t="n">
-        <v>0.136</v>
+        <v>1.829</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.43</v>
+        <v>7.02</v>
       </c>
       <c r="C11" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="D11" t="n">
-        <v>2.085</v>
+        <v>0.134</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,17 +4073,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.23</v>
+        <v>5.26</v>
       </c>
       <c r="C12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="D12" t="n">
-        <v>5.396</v>
+        <v>2.046</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,20 +4092,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.02</v>
+        <v>3.136666666666667</v>
       </c>
       <c r="C13" t="n">
-        <v>0.66</v>
+        <v>0.5433333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8070000000000001</v>
+        <v>12.838</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4118,10 +4118,10 @@
         <v>2.97</v>
       </c>
       <c r="C14" t="n">
-        <v>1.21</v>
+        <v>0.99</v>
       </c>
       <c r="D14" t="n">
-        <v>1.765</v>
+        <v>1.721</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,36 +4130,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.175</v>
+        <v>1.15</v>
       </c>
       <c r="C15" t="n">
-        <v>0.625</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>1.183</v>
+        <v>5.82</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.27</v>
+        <v>0.74</v>
       </c>
       <c r="C16" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="D16" t="n">
-        <v>0.49</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,74 +4168,74 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.49</v>
+        <v>0.01999999999999957</v>
       </c>
       <c r="C17" t="n">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="D17" t="n">
-        <v>10.317</v>
+        <v>18.429</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.7399999999999999</v>
+        <v>-1.17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.99</v>
       </c>
       <c r="D18" t="n">
-        <v>6.051</v>
+        <v>9.811</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.7450000000000001</v>
+        <v>-1.28</v>
       </c>
       <c r="C19" t="n">
-        <v>1.075</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>19.882</v>
+        <v>21.995</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.44</v>
+        <v>-1.29</v>
       </c>
       <c r="C20" t="n">
-        <v>0.88</v>
+        <v>1.02</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.749</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,39 +4244,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.54</v>
+        <v>-1.335</v>
       </c>
       <c r="C21" t="n">
-        <v>1.07</v>
+        <v>0.73</v>
       </c>
       <c r="D21" t="n">
-        <v>1.864</v>
+        <v>1.144</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-3.39</v>
+        <v>-1.58</v>
       </c>
       <c r="C22" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="D22" t="n">
-        <v>22.688</v>
+        <v>0.497</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-3.85</v>
+        <v>-2.165</v>
       </c>
       <c r="C23" t="n">
-        <v>0.95</v>
+        <v>0.915</v>
       </c>
       <c r="D23" t="n">
-        <v>5.104</v>
+        <v>4.904</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-3.89</v>
+        <v>-3.565</v>
       </c>
       <c r="C24" t="n">
-        <v>0.845</v>
+        <v>0.92</v>
       </c>
       <c r="D24" t="n">
-        <v>23.608</v>
+        <v>24.083</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -4320,17 +4320,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-4.72</v>
+        <v>-3.7</v>
       </c>
       <c r="C25" t="n">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="D25" t="n">
-        <v>0.318</v>
+        <v>9.371</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,17 +4339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-4.92</v>
+        <v>-4</v>
       </c>
       <c r="C26" t="n">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="D26" t="n">
-        <v>10.126</v>
+        <v>7.477</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-7.19</v>
+        <v>-6.15</v>
       </c>
       <c r="C27" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="D27" t="n">
-        <v>7.788</v>
+        <v>3.79</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,55 +4377,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-8.56</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.575</v>
+        <v>0.61</v>
       </c>
       <c r="D28" t="n">
-        <v>10.301</v>
+        <v>0.305</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-9.73</v>
+        <v>-9.315</v>
       </c>
       <c r="C29" t="n">
-        <v>0.66</v>
+        <v>0.595</v>
       </c>
       <c r="D29" t="n">
-        <v>33.59</v>
+        <v>10.004</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-10.42</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>0.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>4.357</v>
+        <v>31.839</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-11.85</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="D31" t="n">
-        <v>21.318</v>
+        <v>20.328</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-13.365</v>
+        <v>-10.86</v>
       </c>
       <c r="C32" t="n">
-        <v>1.315</v>
+        <v>1.325</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6990000000000001</v>
+        <v>0.6839999999999999</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1935</v>
+        <v>1920</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.76</v>
+        <v>-0.78</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.19</v>
+        <v>-4</v>
       </c>
       <c r="G2" t="n">
-        <v>35.29</v>
+        <v>28.87</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4839</v>
+        <v>3.1906</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4.32</v>
+        <v>4.37</v>
       </c>
       <c r="L2" t="n">
-        <v>-43</v>
+        <v>-45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.55</v>
+        <v>-2.85</v>
       </c>
       <c r="F3" t="n">
-        <v>12.59</v>
+        <v>14.03</v>
       </c>
       <c r="G3" t="n">
-        <v>73.23999999999999</v>
+        <v>64.31</v>
       </c>
       <c r="H3" t="n">
-        <v>219.4805</v>
+        <v>213.68</v>
       </c>
       <c r="I3" t="n">
-        <v>74.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="J3" t="n">
-        <v>77.7</v>
+        <v>63.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="L3" t="n">
-        <v>-17.2</v>
+        <v>-14.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4679,35 +4679,35 @@
         <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.18</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-24.19</v>
+        <v>-21.43</v>
       </c>
       <c r="G4" t="n">
-        <v>18.14</v>
+        <v>16.89</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.6406</v>
+        <v>-7.6276</v>
       </c>
       <c r="I4" t="n">
-        <v>-14.7</v>
+        <v>-3.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>6.77</v>
+        <v>6.79</v>
       </c>
       <c r="L4" t="n">
-        <v>137.4</v>
+        <v>42.9</v>
       </c>
       <c r="M4" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>❌ EXIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>293.5</v>
+        <v>294.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1.21</v>
+        <v>0.34</v>
       </c>
       <c r="F5" t="n">
-        <v>39.1</v>
+        <v>51.41</v>
       </c>
       <c r="G5" t="n">
-        <v>73.94</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>24.7926</v>
+        <v>25.9051</v>
       </c>
       <c r="I5" t="n">
-        <v>86.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="J5" t="n">
-        <v>98.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>7.74</v>
+        <v>7.96</v>
       </c>
       <c r="L5" t="n">
-        <v>39.3</v>
+        <v>51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="E6" t="n">
-        <v>3.88</v>
+        <v>-2.8</v>
       </c>
       <c r="F6" t="n">
-        <v>28.3</v>
+        <v>24.55</v>
       </c>
       <c r="G6" t="n">
-        <v>73.91</v>
+        <v>68.55</v>
       </c>
       <c r="H6" t="n">
-        <v>43.2575</v>
+        <v>42.3534</v>
       </c>
       <c r="I6" t="n">
-        <v>77.3</v>
+        <v>68.7</v>
       </c>
       <c r="J6" t="n">
-        <v>93.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K6" t="n">
-        <v>6.45</v>
+        <v>6.84</v>
       </c>
       <c r="L6" t="n">
-        <v>-86.3</v>
+        <v>-86.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.55</v>
+        <v>-1</v>
       </c>
       <c r="G7" t="n">
-        <v>56.04</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0515</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>43.2</v>
+        <v>31.7</v>
       </c>
       <c r="J7" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="L7" t="n">
-        <v>-29.4</v>
+        <v>-47.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69.7</v>
+        <v>1475</v>
       </c>
       <c r="E2" t="n">
-        <v>2.35</v>
+        <v>7.66</v>
       </c>
       <c r="F2" t="n">
-        <v>183</v>
+        <v>359</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,67 +504,67 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.255</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1670</v>
+        <v>515</v>
       </c>
       <c r="E3" t="n">
-        <v>3.09</v>
+        <v>-0.96</v>
       </c>
       <c r="F3" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>15.774</v>
+        <v>5.697</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>294.5</v>
+        <v>70.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.34</v>
+        <v>1.58</v>
       </c>
       <c r="F4" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,135 +572,135 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.678</v>
+        <v>2.348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>315</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>6.96</v>
       </c>
       <c r="F5" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.276</v>
+        <v>6.359</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3355</v>
+        <v>340.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.55</v>
+        <v>2.25</v>
       </c>
       <c r="F6" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6.799</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>454</v>
+        <v>2380</v>
       </c>
       <c r="E7" t="n">
-        <v>2.25</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>12.76</v>
+        <v>40.961</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>112.5</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.64</v>
+        <v>2.27</v>
       </c>
       <c r="F8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.535</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.9</v>
+        <v>1710</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.49</v>
+        <v>2.4</v>
       </c>
       <c r="F9" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.397</v>
+        <v>16.019</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.37</v>
+        <v>4.42</v>
       </c>
       <c r="F10" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,67 +776,67 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9.371</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.65</v>
+        <v>720</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8</v>
+        <v>2.42</v>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.497</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6035</v>
+        <v>27.35</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,101 +844,101 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>11.63</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41.2</v>
+        <v>472.5</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.02</v>
+        <v>4.07</v>
       </c>
       <c r="F13" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.747</v>
+        <v>13.541</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>541</v>
+        <v>153</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.7</v>
+        <v>1.32</v>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.829</v>
+        <v>3.135</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>914</v>
+        <v>18.65</v>
       </c>
       <c r="E15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7.575</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>176</v>
+        <v>3345</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.28</v>
+        <v>-0.3</v>
       </c>
       <c r="F16" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,67 +980,67 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2.429</v>
+        <v>6.748</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2385</v>
+        <v>50.9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.21</v>
+        <v>-1.74</v>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>41.131</v>
+        <v>1.429</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4430</v>
+        <v>548</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.85</v>
+        <v>1.29</v>
       </c>
       <c r="F18" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,67 +1048,67 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>32.097</v>
+        <v>1.808</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>592</v>
+        <v>4530</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.27</v>
+        <v>2.26</v>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.811</v>
+        <v>32.755</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.95</v>
+        <v>2.36</v>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.033</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>153</v>
+        <v>937</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.08</v>
+        <v>2.52</v>
       </c>
       <c r="F21" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.749</v>
+        <v>7.575</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>703</v>
+        <v>64.3</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4</v>
+        <v>6.99</v>
       </c>
       <c r="F22" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,67 +1184,67 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.721</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>110</v>
+        <v>1985</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.22</v>
+        <v>3.39</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.423</v>
+        <v>7.587</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>51.8</v>
+        <v>142</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.33</v>
+        <v>2.53</v>
       </c>
       <c r="F24" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.452</v>
+        <v>24.092</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>388.5</v>
+        <v>115</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.39</v>
+        <v>2.68</v>
       </c>
       <c r="F25" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,30 +1286,30 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3.402</v>
+        <v>4.387</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1370</v>
+        <v>248</v>
       </c>
       <c r="E26" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="F26" t="n">
         <v>68</v>
@@ -1320,33 +1320,33 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.5649999999999999</v>
+        <v>7.193</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>268</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.29</v>
+        <v>4.48</v>
       </c>
       <c r="F27" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,67 +1354,67 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3.213</v>
+        <v>9.497</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29.65</v>
+        <v>6170</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.47</v>
+        <v>2.24</v>
       </c>
       <c r="F28" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.134</v>
+        <v>11.512</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2625</v>
+        <v>183.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.85</v>
+        <v>4.26</v>
       </c>
       <c r="F29" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.839</v>
+        <v>2.451</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>266</v>
+        <v>119</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.74</v>
+        <v>3.93</v>
       </c>
       <c r="F30" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,101 +1456,101 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.198</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>333</v>
+        <v>158</v>
       </c>
       <c r="E31" t="n">
-        <v>0.15</v>
+        <v>3.27</v>
       </c>
       <c r="F31" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.381</v>
+        <v>1.699</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>138.5</v>
+        <v>169</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.81</v>
+        <v>5.96</v>
       </c>
       <c r="F32" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>23.441</v>
+        <v>21.302</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>274</v>
+        <v>282.5</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.26</v>
+        <v>3.48</v>
       </c>
       <c r="F33" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8.308999999999999</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>84.40000000000001</v>
+        <v>183</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.54</v>
+        <v>0.27</v>
       </c>
       <c r="F34" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.691</v>
+        <v>9.369</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>60.5</v>
+        <v>19.95</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.94</v>
+        <v>0.25</v>
       </c>
       <c r="F35" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.971</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1920</v>
+        <v>41.3</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.78</v>
+        <v>0.24</v>
       </c>
       <c r="F36" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7.477</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>159.5</v>
+        <v>274.5</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.31</v>
+        <v>2.43</v>
       </c>
       <c r="F37" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,67 +1694,67 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>20.328</v>
+        <v>3.252</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>62</v>
+        <v>605</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.43</v>
+        <v>2.2</v>
       </c>
       <c r="F38" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.046</v>
+        <v>9.627000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>170</v>
+        <v>62.4</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.45</v>
+        <v>0.65</v>
       </c>
       <c r="F39" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.408</v>
+        <v>2.044</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>246.5</v>
+        <v>61.7</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.8</v>
+        <v>1.98</v>
       </c>
       <c r="F40" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7.341</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>114.5</v>
+        <v>492.5</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.29</v>
+        <v>5.8</v>
       </c>
       <c r="F41" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.79</v>
+        <v>32.913</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>465.5</v>
+        <v>173.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.59</v>
+        <v>2.06</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>31.839</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="43">
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>106</v>
+        <v>107.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.47</v>
+        <v>1.42</v>
       </c>
       <c r="F43" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,67 +1898,67 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.409</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>233.5</v>
+        <v>60.2</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.48</v>
+        <v>2.38</v>
       </c>
       <c r="F44" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.501</v>
+        <v>4.879</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>224.5</v>
+        <v>29.85</v>
       </c>
       <c r="E45" t="n">
-        <v>-3.23</v>
+        <v>0.67</v>
       </c>
       <c r="F45" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.305</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>182.5</v>
+        <v>277</v>
       </c>
       <c r="E46" t="n">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="F46" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,67 +2000,67 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>9.302</v>
+        <v>8.103999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.72</v>
+        <v>3.38</v>
       </c>
       <c r="F47" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5.152</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>273</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.36</v>
+        <v>3.2</v>
       </c>
       <c r="F48" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,33 +2068,33 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.22</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>60.1</v>
+        <v>399.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.28</v>
+        <v>2.83</v>
       </c>
       <c r="F49" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,109 +2102,109 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.779</v>
+        <v>3.437</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>58.8</v>
+        <v>2700</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.84</v>
+        <v>2.86</v>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>4.979</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>112</v>
+        <v>261.5</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.88</v>
+        <v>1.75</v>
       </c>
       <c r="F51" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>4.358</v>
+        <v>5.143</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>520</v>
+        <v>229</v>
       </c>
       <c r="E52" t="n">
-        <v>-2.8</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5.633</v>
+        <v>0.306</v>
       </c>
     </row>
   </sheetData>
@@ -2280,29 +2280,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>51.41</v>
+        <v>47.54</v>
       </c>
       <c r="F2" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
-        <v>5.678</v>
+        <v>6.359</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2311,29 +2311,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>24.55</v>
+        <v>29.99</v>
       </c>
       <c r="F3" t="n">
-        <v>0.16</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>5.633</v>
+        <v>13.541</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2342,230 +2342,230 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21.23</v>
+        <v>29.89</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="G4" t="n">
-        <v>12.76</v>
+        <v>5.697</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16.6</v>
+        <v>22.94</v>
       </c>
       <c r="F5" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="G5" t="n">
-        <v>3.033</v>
+        <v>24.092</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>16.39</v>
+        <v>19.47</v>
       </c>
       <c r="F6" t="n">
-        <v>0.97</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
-        <v>23.441</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.03</v>
+        <v>19.07</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="G7" t="n">
-        <v>32.097</v>
+        <v>3.135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12.18</v>
+        <v>17.82</v>
       </c>
       <c r="F8" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="G8" t="n">
-        <v>3.839</v>
+        <v>32.755</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10.89</v>
+        <v>16.53</v>
       </c>
       <c r="F9" t="n">
-        <v>0.79</v>
+        <v>0.97</v>
       </c>
       <c r="G9" t="n">
-        <v>2.423</v>
+        <v>11.512</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>10.45</v>
+        <v>16.49</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="G10" t="n">
-        <v>1.452</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.029999999999999</v>
+        <v>14.45</v>
       </c>
       <c r="F11" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>11.63</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="12">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.9</v>
+        <v>11.28</v>
       </c>
       <c r="F12" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="G12" t="n">
-        <v>5.152</v>
+        <v>5.143</v>
       </c>
     </row>
     <row r="13">
@@ -2621,106 +2621,106 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.220000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="F13" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.535</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.32</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G14" t="n">
-        <v>0.779</v>
+        <v>2.044</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.13</v>
+        <v>9.09</v>
       </c>
       <c r="F15" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="G15" t="n">
-        <v>1.829</v>
+        <v>2.348</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.02</v>
+        <v>8.18</v>
       </c>
       <c r="F16" t="n">
-        <v>0.52</v>
+        <v>0.89</v>
       </c>
       <c r="G16" t="n">
-        <v>0.134</v>
+        <v>1.429</v>
       </c>
     </row>
     <row r="17">
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.67</v>
+        <v>7.98</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="G17" t="n">
-        <v>4.358</v>
+        <v>4.387</v>
       </c>
     </row>
     <row r="18">
@@ -2776,323 +2776,323 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.56</v>
+        <v>5.77</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="G18" t="n">
-        <v>1.198</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.26</v>
+        <v>5.68</v>
       </c>
       <c r="F19" t="n">
-        <v>0.62</v>
+        <v>0.52</v>
       </c>
       <c r="G19" t="n">
-        <v>2.046</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.81</v>
+        <v>5.3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="G20" t="n">
-        <v>2.255</v>
+        <v>9.497</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.63</v>
+        <v>4.57</v>
       </c>
       <c r="F21" t="n">
-        <v>0.49</v>
+        <v>0.8</v>
       </c>
       <c r="G21" t="n">
-        <v>4.979</v>
+        <v>3.252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.97</v>
+        <v>4.29</v>
       </c>
       <c r="F22" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="G22" t="n">
-        <v>1.721</v>
+        <v>1.699</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.83</v>
+        <v>3.97</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="G23" t="n">
-        <v>4.381</v>
+        <v>2.451</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.11</v>
+        <v>2.89</v>
       </c>
       <c r="F24" t="n">
-        <v>0.55</v>
+        <v>0.86</v>
       </c>
       <c r="G24" t="n">
-        <v>8.308999999999999</v>
+        <v>9.627000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.87</v>
       </c>
       <c r="F25" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="G25" t="n">
-        <v>3.213</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.83</v>
+        <v>2.62</v>
       </c>
       <c r="F26" t="n">
-        <v>0.99</v>
+        <v>0.9</v>
       </c>
       <c r="G26" t="n">
-        <v>9.302</v>
+        <v>1.808</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.74</v>
+        <v>2.39</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5649999999999999</v>
+        <v>32.913</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.39</v>
+        <v>2.03</v>
       </c>
       <c r="F28" t="n">
-        <v>0.63</v>
+        <v>0.53</v>
       </c>
       <c r="G28" t="n">
-        <v>3.402</v>
+        <v>4.879</v>
       </c>
     </row>
     <row r="29">
@@ -3117,385 +3117,385 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.21</v>
+        <v>1.57</v>
       </c>
       <c r="F29" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="G29" t="n">
-        <v>41.131</v>
+        <v>40.961</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.29</v>
+        <v>1.28</v>
       </c>
       <c r="F30" t="n">
-        <v>0.96</v>
+        <v>0.57</v>
       </c>
       <c r="G30" t="n">
-        <v>0.408</v>
+        <v>8.103999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-1</v>
+        <v>1.22</v>
       </c>
       <c r="F31" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="G31" t="n">
-        <v>0.397</v>
+        <v>7.193</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-1</v>
+        <v>1.14</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="G32" t="n">
-        <v>7.341</v>
+        <v>3.437</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-1.17</v>
+        <v>1.03</v>
       </c>
       <c r="F33" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="G33" t="n">
-        <v>9.811</v>
+        <v>1.714</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-1.29</v>
+        <v>1.03</v>
       </c>
       <c r="F34" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="G34" t="n">
-        <v>1.749</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-1.58</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="G35" t="n">
-        <v>0.497</v>
+        <v>7.587</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-1.67</v>
+        <v>0.6</v>
       </c>
       <c r="F36" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="G36" t="n">
-        <v>0.747</v>
+        <v>21.302</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-1.89</v>
+        <v>0.58</v>
       </c>
       <c r="F37" t="n">
-        <v>0.58</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>3.501</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-2.5</v>
+        <v>0.55</v>
       </c>
       <c r="F38" t="n">
-        <v>0.38</v>
+        <v>0.85</v>
       </c>
       <c r="G38" t="n">
-        <v>1.22</v>
+        <v>9.369</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-3.7</v>
+        <v>0.53</v>
       </c>
       <c r="F39" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="G39" t="n">
-        <v>9.371</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-4</v>
+        <v>0.25</v>
       </c>
       <c r="F40" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="G40" t="n">
-        <v>7.477</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-4.86</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="G41" t="n">
-        <v>2.429</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="42">
@@ -3520,106 +3520,106 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-5.27</v>
+        <v>-0.23</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="G42" t="n">
-        <v>1.691</v>
+        <v>1.702</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-6.15</v>
+        <v>-0.62</v>
       </c>
       <c r="F43" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="G43" t="n">
-        <v>3.79</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-6.49</v>
+        <v>-0.72</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G44" t="n">
-        <v>0.409</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-6.78</v>
+        <v>-1.58</v>
       </c>
       <c r="F45" t="n">
-        <v>0.72</v>
+        <v>0.98</v>
       </c>
       <c r="G45" t="n">
-        <v>0.971</v>
+        <v>0.493</v>
       </c>
     </row>
     <row r="46">
@@ -3644,168 +3644,168 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-8.24</v>
+        <v>-3.12</v>
       </c>
       <c r="F46" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="G46" t="n">
-        <v>15.774</v>
+        <v>16.019</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-8.369999999999999</v>
+        <v>-4.68</v>
       </c>
       <c r="F47" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="G47" t="n">
-        <v>0.305</v>
+        <v>7.575</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-8.99</v>
+        <v>-5.37</v>
       </c>
       <c r="F48" t="n">
-        <v>1.43</v>
+        <v>0.65</v>
       </c>
       <c r="G48" t="n">
-        <v>6.799</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-9.609999999999999</v>
+        <v>-5.58</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="G49" t="n">
-        <v>31.839</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-9.630000000000001</v>
+        <v>-7.13</v>
       </c>
       <c r="F50" t="n">
-        <v>0.73</v>
+        <v>1.3</v>
       </c>
       <c r="G50" t="n">
-        <v>20.328</v>
+        <v>6.748</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-13.77</v>
+        <v>-7.85</v>
       </c>
       <c r="F51" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="G51" t="n">
-        <v>7.575</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-21.43</v>
+        <v>-16.44</v>
       </c>
       <c r="F52" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="G52" t="n">
-        <v>0.276</v>
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.41</v>
+        <v>47.54</v>
       </c>
       <c r="C2" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="D2" t="n">
-        <v>5.678</v>
+        <v>6.359</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.03</v>
+        <v>19.47</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="D3" t="n">
-        <v>32.097</v>
+        <v>3.88</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.09666666666667</v>
+        <v>18.1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5100000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="D4" t="n">
-        <v>18.802</v>
+        <v>19.638</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3940,17 +3940,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.18</v>
+        <v>17.82</v>
       </c>
       <c r="C5" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="D5" t="n">
-        <v>3.839</v>
+        <v>32.755</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,74 +3959,74 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.194</v>
+        <v>16.49</v>
       </c>
       <c r="C6" t="n">
-        <v>0.866</v>
+        <v>0.48</v>
       </c>
       <c r="D6" t="n">
-        <v>9.698</v>
+        <v>0.858</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.9</v>
+        <v>12.255</v>
       </c>
       <c r="C7" t="n">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
       <c r="D7" t="n">
-        <v>5.152</v>
+        <v>65.053</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.300000000000001</v>
+        <v>12.17</v>
       </c>
       <c r="C8" t="n">
-        <v>0.975</v>
+        <v>0.924</v>
       </c>
       <c r="D8" t="n">
-        <v>64.572</v>
+        <v>10.004</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.32</v>
+        <v>11.28</v>
       </c>
       <c r="C9" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="D9" t="n">
-        <v>0.779</v>
+        <v>5.143</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -4035,17 +4035,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.13</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="D10" t="n">
-        <v>1.829</v>
+        <v>2.044</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7.02</v>
+        <v>5.68</v>
       </c>
       <c r="C11" t="n">
         <v>0.52</v>
       </c>
       <c r="D11" t="n">
-        <v>0.134</v>
+        <v>0.135</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,17 +4073,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="C12" t="n">
-        <v>0.62</v>
+        <v>0.91</v>
       </c>
       <c r="D12" t="n">
-        <v>2.046</v>
+        <v>9.497</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,36 +4092,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.136666666666667</v>
+        <v>4.700000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5433333333333333</v>
+        <v>1.135</v>
       </c>
       <c r="D13" t="n">
-        <v>12.838</v>
+        <v>18.26</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.97</v>
+        <v>4.29</v>
       </c>
       <c r="C14" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="D14" t="n">
-        <v>1.721</v>
+        <v>1.699</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,17 +4130,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.15</v>
+        <v>3.13</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>5.82</v>
+        <v>12.758</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
@@ -4149,17 +4149,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.74</v>
+        <v>2.89</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5649999999999999</v>
+        <v>9.627000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,112 +4168,112 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01999999999999957</v>
+        <v>2.62</v>
       </c>
       <c r="C17" t="n">
-        <v>1.17</v>
+        <v>0.9</v>
       </c>
       <c r="D17" t="n">
-        <v>18.429</v>
+        <v>1.808</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.17</v>
+        <v>2.48</v>
       </c>
       <c r="C18" t="n">
-        <v>0.99</v>
+        <v>0.5233333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>9.811</v>
+        <v>5.888999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.28</v>
+        <v>2.39</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="D19" t="n">
-        <v>21.995</v>
+        <v>32.913</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.29</v>
+        <v>2.17</v>
       </c>
       <c r="C20" t="n">
-        <v>1.02</v>
+        <v>0.7250000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>1.749</v>
+        <v>4.954</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.335</v>
+        <v>1.03</v>
       </c>
       <c r="C21" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="D21" t="n">
-        <v>1.144</v>
+        <v>1.714</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.58</v>
+        <v>1.03</v>
       </c>
       <c r="C22" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="D22" t="n">
-        <v>0.497</v>
+        <v>0.643</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,55 +4282,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-2.165</v>
+        <v>1.02</v>
       </c>
       <c r="C23" t="n">
-        <v>0.915</v>
+        <v>0.73</v>
       </c>
       <c r="D23" t="n">
-        <v>4.904</v>
+        <v>7.587</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-3.565</v>
+        <v>0.6</v>
       </c>
       <c r="C24" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="D24" t="n">
-        <v>24.083</v>
+        <v>21.302</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-3.7</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="D25" t="n">
-        <v>9.371</v>
+        <v>3.77</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,74 +4339,74 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-4</v>
+        <v>-0.1825000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.66</v>
+        <v>0.7949999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>7.477</v>
+        <v>22.022</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-6.15</v>
+        <v>-0.235</v>
       </c>
       <c r="C27" t="n">
-        <v>0.71</v>
+        <v>0.765</v>
       </c>
       <c r="D27" t="n">
-        <v>3.79</v>
+        <v>1.12</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-8.369999999999999</v>
+        <v>-0.3549999999999998</v>
       </c>
       <c r="C28" t="n">
-        <v>0.61</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.305</v>
+        <v>10.026</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-9.315</v>
+        <v>-0.92</v>
       </c>
       <c r="C29" t="n">
-        <v>0.595</v>
+        <v>0.9650000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>10.004</v>
+        <v>24.123</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -4415,17 +4415,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-9.609999999999999</v>
+        <v>-1.58</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="D30" t="n">
-        <v>31.839</v>
+        <v>0.493</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4434,17 +4434,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-9.630000000000001</v>
+        <v>-7.85</v>
       </c>
       <c r="C31" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="D31" t="n">
-        <v>20.328</v>
+        <v>0.306</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-10.86</v>
+        <v>-7.930000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>1.325</v>
+        <v>1.275</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1920</v>
+        <v>1985</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.78</v>
+        <v>3.39</v>
       </c>
       <c r="F2" t="n">
-        <v>-4</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>28.87</v>
+        <v>33.65</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1906</v>
+        <v>1.6562</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>23.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.37</v>
+        <v>4.26</v>
       </c>
       <c r="L2" t="n">
-        <v>-45</v>
+        <v>-20.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4430</v>
+        <v>4530</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.85</v>
+        <v>2.26</v>
       </c>
       <c r="F3" t="n">
-        <v>14.03</v>
+        <v>17.82</v>
       </c>
       <c r="G3" t="n">
-        <v>64.31</v>
+        <v>69.39</v>
       </c>
       <c r="H3" t="n">
-        <v>213.68</v>
+        <v>205.7796</v>
       </c>
       <c r="I3" t="n">
-        <v>64.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>63.1</v>
+        <v>72.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
       <c r="L3" t="n">
-        <v>-14.7</v>
+        <v>-11.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>89.8</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="F4" t="n">
-        <v>-21.43</v>
+        <v>-16.44</v>
       </c>
       <c r="G4" t="n">
-        <v>16.89</v>
+        <v>21.28</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.6276</v>
+        <v>-7.6482</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.3</v>
+        <v>13.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.79</v>
+        <v>6.13</v>
       </c>
       <c r="L4" t="n">
-        <v>42.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>294.5</v>
+        <v>315</v>
       </c>
       <c r="E5" t="n">
-        <v>0.34</v>
+        <v>6.96</v>
       </c>
       <c r="F5" t="n">
-        <v>51.41</v>
+        <v>47.54</v>
       </c>
       <c r="G5" t="n">
-        <v>76.29000000000001</v>
+        <v>76.42</v>
       </c>
       <c r="H5" t="n">
-        <v>25.9051</v>
+        <v>28.147</v>
       </c>
       <c r="I5" t="n">
-        <v>83.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
-        <v>7.96</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
-        <v>51</v>
+        <v>39.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8</v>
+        <v>-0.96</v>
       </c>
       <c r="F6" t="n">
-        <v>24.55</v>
+        <v>29.89</v>
       </c>
       <c r="G6" t="n">
-        <v>68.55</v>
+        <v>66.53</v>
       </c>
       <c r="H6" t="n">
-        <v>42.3534</v>
+        <v>40.0057</v>
       </c>
       <c r="I6" t="n">
-        <v>68.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>79.8</v>
+        <v>75</v>
       </c>
       <c r="K6" t="n">
-        <v>6.84</v>
+        <v>6.97</v>
       </c>
       <c r="L6" t="n">
-        <v>-86.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>246.5</v>
+        <v>248</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8</v>
+        <v>0.61</v>
       </c>
       <c r="F7" t="n">
-        <v>-1</v>
+        <v>1.22</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.2696</v>
       </c>
       <c r="I7" t="n">
-        <v>31.7</v>
+        <v>39.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="L7" t="n">
-        <v>-47.2</v>
+        <v>-32.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1475</v>
+        <v>165.5</v>
       </c>
       <c r="E2" t="n">
-        <v>7.66</v>
+        <v>4.75</v>
       </c>
       <c r="F2" t="n">
-        <v>359</v>
+        <v>262</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.643</v>
+        <v>1.961</v>
       </c>
     </row>
     <row r="3">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.96</v>
+        <v>3.69</v>
       </c>
       <c r="F3" t="n">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.697</v>
+        <v>6.229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>70.8</v>
+        <v>1480</v>
       </c>
       <c r="E4" t="n">
-        <v>1.58</v>
+        <v>0.34</v>
       </c>
       <c r="F4" t="n">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.348</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>315</v>
+        <v>471</v>
       </c>
       <c r="E5" t="n">
-        <v>6.96</v>
+        <v>-0.32</v>
       </c>
       <c r="F5" t="n">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,101 +606,101 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.359</v>
+        <v>14.244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>340.5</v>
+        <v>3295</v>
       </c>
       <c r="E6" t="n">
-        <v>2.25</v>
+        <v>-1.49</v>
       </c>
       <c r="F6" t="n">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.49</v>
+        <v>6.835</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2380</v>
+        <v>251.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08</v>
+        <v>9.83</v>
       </c>
       <c r="F7" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40.961</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>112.5</v>
+        <v>147.5</v>
       </c>
       <c r="E8" t="n">
-        <v>2.27</v>
+        <v>3.87</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,101 +708,101 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.57</v>
+        <v>26.172</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1710</v>
+        <v>179</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="F9" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>16.019</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>89.8</v>
+        <v>182</v>
       </c>
       <c r="E10" t="n">
-        <v>4.42</v>
+        <v>-0.82</v>
       </c>
       <c r="F10" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.29</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>720</v>
+        <v>303.5</v>
       </c>
       <c r="E11" t="n">
-        <v>2.42</v>
+        <v>-3.65</v>
       </c>
       <c r="F11" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.714</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27.35</v>
+        <v>715</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,67 +844,67 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.522</v>
+        <v>1.638</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>472.5</v>
+        <v>912</v>
       </c>
       <c r="E13" t="n">
-        <v>4.07</v>
+        <v>-2.67</v>
       </c>
       <c r="F13" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.541</v>
+        <v>7.428</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>153</v>
+        <v>6500</v>
       </c>
       <c r="E14" t="n">
-        <v>1.32</v>
+        <v>5.35</v>
       </c>
       <c r="F14" t="n">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,305 +912,305 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.135</v>
+        <v>12.045</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.65</v>
+        <v>344</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.493</v>
+        <v>4.606</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3345</v>
+        <v>65.5</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3</v>
+        <v>1.87</v>
       </c>
       <c r="F16" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6.748</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50.9</v>
+        <v>1685</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.74</v>
+        <v>-1.46</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.429</v>
+        <v>15.892</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>548</v>
+        <v>71.2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.808</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4530</v>
+        <v>274.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>32.755</v>
+        <v>3.332</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>239</v>
+        <v>88.2</v>
       </c>
       <c r="E20" t="n">
-        <v>2.36</v>
+        <v>-1.78</v>
       </c>
       <c r="F20" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.492</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>937</v>
+        <v>27.55</v>
       </c>
       <c r="E21" t="n">
-        <v>2.52</v>
+        <v>0.73</v>
       </c>
       <c r="F21" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7.575</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64.3</v>
+        <v>2425</v>
       </c>
       <c r="E22" t="n">
-        <v>6.99</v>
+        <v>1.89</v>
       </c>
       <c r="F22" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.858</v>
+        <v>41.669</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1985</v>
+        <v>170</v>
       </c>
       <c r="E23" t="n">
-        <v>3.39</v>
+        <v>0.59</v>
       </c>
       <c r="F23" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,75 +1218,75 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>7.587</v>
+        <v>21.175</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>142</v>
+        <v>116.5</v>
       </c>
       <c r="E24" t="n">
-        <v>2.53</v>
+        <v>-2.1</v>
       </c>
       <c r="F24" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>24.092</v>
+        <v>3.578</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>115</v>
+        <v>4500</v>
       </c>
       <c r="E25" t="n">
-        <v>2.68</v>
+        <v>-0.66</v>
       </c>
       <c r="F25" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.387</v>
+        <v>31.369</v>
       </c>
     </row>
     <row r="26">
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>248</v>
+        <v>250.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.61</v>
+        <v>1.01</v>
       </c>
       <c r="F26" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7.193</v>
+        <v>7.269</v>
       </c>
     </row>
     <row r="27">
@@ -1340,81 +1340,81 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>69.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.48</v>
+        <v>1.86</v>
       </c>
       <c r="F27" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.497</v>
+        <v>9.503</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6170</v>
+        <v>42.05</v>
       </c>
       <c r="E28" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="F28" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>11.512</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>183.5</v>
+        <v>112</v>
       </c>
       <c r="E29" t="n">
-        <v>4.26</v>
+        <v>-0.44</v>
       </c>
       <c r="F29" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.451</v>
+        <v>2.573</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E30" t="n">
-        <v>3.93</v>
+        <v>0.47</v>
       </c>
       <c r="F30" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3.77</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>158</v>
+        <v>51.9</v>
       </c>
       <c r="E31" t="n">
-        <v>3.27</v>
+        <v>1.96</v>
       </c>
       <c r="F31" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.699</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>169</v>
+        <v>86.7</v>
       </c>
       <c r="E32" t="n">
-        <v>5.96</v>
+        <v>-0.46</v>
       </c>
       <c r="F32" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,67 +1524,67 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>21.302</v>
+        <v>1.675</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>282.5</v>
+        <v>265</v>
       </c>
       <c r="E33" t="n">
-        <v>3.48</v>
+        <v>1.34</v>
       </c>
       <c r="F33" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.264</v>
+        <v>5.254</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>183</v>
+        <v>1970</v>
       </c>
       <c r="E34" t="n">
-        <v>0.27</v>
+        <v>-0.76</v>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,135 +1592,135 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9.369</v>
+        <v>7.417</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19.95</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.25</v>
+        <v>3.53</v>
       </c>
       <c r="F35" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.385</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>41.3</v>
+        <v>2710</v>
       </c>
       <c r="E36" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="F36" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.735</v>
+        <v>3.962</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>274.5</v>
+        <v>614</v>
       </c>
       <c r="E37" t="n">
-        <v>2.43</v>
+        <v>1.49</v>
       </c>
       <c r="F37" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3.252</v>
+        <v>9.483000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>605</v>
+        <v>545</v>
       </c>
       <c r="E38" t="n">
-        <v>2.2</v>
+        <v>-0.55</v>
       </c>
       <c r="F38" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>9.627000000000001</v>
+        <v>1.745</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>62.4</v>
+        <v>18.7</v>
       </c>
       <c r="E39" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
       <c r="F39" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.044</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>61.7</v>
+        <v>488</v>
       </c>
       <c r="E40" t="n">
-        <v>1.98</v>
+        <v>-0.91</v>
       </c>
       <c r="F40" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,67 +1796,67 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.97</v>
+        <v>31.578</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>492.5</v>
+        <v>151.5</v>
       </c>
       <c r="E41" t="n">
-        <v>5.8</v>
+        <v>-0.98</v>
       </c>
       <c r="F41" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>32.913</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>173.5</v>
+        <v>20.35</v>
       </c>
       <c r="E42" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="F42" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,67 +1864,67 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.4</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>107.5</v>
+        <v>242.5</v>
       </c>
       <c r="E43" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="F43" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.4</v>
+        <v>3.274</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>60.2</v>
+        <v>186.5</v>
       </c>
       <c r="E44" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="F44" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4.879</v>
+        <v>9.601000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1952,115 +1952,115 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>29.85</v>
+        <v>30.6</v>
       </c>
       <c r="E45" t="n">
-        <v>0.67</v>
+        <v>2.51</v>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.135</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>277</v>
+        <v>120.5</v>
       </c>
       <c r="E46" t="n">
-        <v>1.09</v>
+        <v>4.78</v>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.103999999999999</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>275</v>
+        <v>62</v>
       </c>
       <c r="E47" t="n">
-        <v>3.38</v>
+        <v>2.99</v>
       </c>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.188</v>
+        <v>4.676</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>87.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="E48" t="n">
-        <v>3.2</v>
+        <v>-0.32</v>
       </c>
       <c r="F48" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.702</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="49">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>399.5</v>
+        <v>395</v>
       </c>
       <c r="E49" t="n">
-        <v>2.83</v>
+        <v>-1.13</v>
       </c>
       <c r="F49" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,101 +2102,101 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.437</v>
+        <v>3.343</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2700</v>
+        <v>277</v>
       </c>
       <c r="E50" t="n">
-        <v>2.86</v>
+        <v>-1.95</v>
       </c>
       <c r="F50" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.88</v>
+        <v>1.225</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>261.5</v>
+        <v>271</v>
       </c>
       <c r="E51" t="n">
-        <v>1.75</v>
+        <v>-1.45</v>
       </c>
       <c r="F51" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5.143</v>
+        <v>1.138</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>0.36</v>
       </c>
       <c r="F52" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.306</v>
+        <v>7.916</v>
       </c>
     </row>
   </sheetData>
@@ -2280,29 +2280,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>47.54</v>
+        <v>37.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>6.359</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2311,75 +2311,75 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29.99</v>
+        <v>29.61</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="G3" t="n">
-        <v>13.541</v>
+        <v>6.229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29.89</v>
+        <v>27.71</v>
       </c>
       <c r="F4" t="n">
-        <v>0.47</v>
+        <v>0.82</v>
       </c>
       <c r="G4" t="n">
-        <v>5.697</v>
+        <v>26.172</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22.94</v>
+        <v>24.27</v>
       </c>
       <c r="F5" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="G5" t="n">
-        <v>24.092</v>
+        <v>14.244</v>
       </c>
     </row>
     <row r="6">
@@ -2404,75 +2404,75 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19.47</v>
+        <v>22.62</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="G6" t="n">
-        <v>3.88</v>
+        <v>3.962</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.07</v>
+        <v>21.62</v>
       </c>
       <c r="F7" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="G7" t="n">
-        <v>3.135</v>
+        <v>31.369</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17.82</v>
+        <v>18.36</v>
       </c>
       <c r="F8" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="G8" t="n">
-        <v>32.755</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="9">
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16.53</v>
+        <v>15.45</v>
       </c>
       <c r="F9" t="n">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>11.512</v>
+        <v>12.045</v>
       </c>
     </row>
     <row r="10">
@@ -2528,13 +2528,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>16.49</v>
+        <v>14.91</v>
       </c>
       <c r="F10" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="G10" t="n">
-        <v>0.858</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="11">
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.45</v>
+        <v>14.64</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="G11" t="n">
-        <v>2.57</v>
+        <v>2.573</v>
       </c>
     </row>
     <row r="12">
@@ -2590,29 +2590,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>11.28</v>
+        <v>12.77</v>
       </c>
       <c r="F12" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="G12" t="n">
-        <v>5.143</v>
+        <v>5.254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2621,91 +2621,91 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.06</v>
+        <v>12.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.522</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.859999999999999</v>
+        <v>11.85</v>
       </c>
       <c r="F14" t="n">
-        <v>0.58</v>
+        <v>0.92</v>
       </c>
       <c r="G14" t="n">
-        <v>2.044</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.09</v>
+        <v>11.76</v>
       </c>
       <c r="F15" t="n">
-        <v>1.08</v>
+        <v>0.58</v>
       </c>
       <c r="G15" t="n">
-        <v>2.348</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2714,106 +2714,106 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.18</v>
+        <v>11.09</v>
       </c>
       <c r="F16" t="n">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="G16" t="n">
-        <v>1.429</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.98</v>
+        <v>7.82</v>
       </c>
       <c r="F17" t="n">
-        <v>0.58</v>
+        <v>1.05</v>
       </c>
       <c r="G17" t="n">
-        <v>4.387</v>
+        <v>1.961</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.77</v>
+        <v>6.85</v>
       </c>
       <c r="F18" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="G18" t="n">
-        <v>1.188</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.68</v>
+        <v>6.17</v>
       </c>
       <c r="F19" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="G19" t="n">
-        <v>0.135</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="20">
@@ -2838,106 +2838,106 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.3</v>
+        <v>6.14</v>
       </c>
       <c r="F20" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="G20" t="n">
-        <v>9.497</v>
+        <v>9.503</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.57</v>
+        <v>5.32</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="G21" t="n">
-        <v>3.252</v>
+        <v>1.638</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.29</v>
+        <v>5.2</v>
       </c>
       <c r="F22" t="n">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="G22" t="n">
-        <v>1.699</v>
+        <v>4.606</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.97</v>
+        <v>4.12</v>
       </c>
       <c r="F23" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="G23" t="n">
-        <v>2.451</v>
+        <v>7.916</v>
       </c>
     </row>
     <row r="24">
@@ -2962,726 +2962,726 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.89</v>
+        <v>4.07</v>
       </c>
       <c r="F24" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="G24" t="n">
-        <v>9.627000000000001</v>
+        <v>9.483000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.87</v>
+        <v>4.07</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="G25" t="n">
-        <v>4.49</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.62</v>
+        <v>3.86</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9</v>
+        <v>1.52</v>
       </c>
       <c r="G26" t="n">
-        <v>1.808</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.39</v>
+        <v>3.61</v>
       </c>
       <c r="F27" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="G27" t="n">
-        <v>32.913</v>
+        <v>9.601000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.03</v>
+        <v>3.42</v>
       </c>
       <c r="F28" t="n">
-        <v>0.53</v>
+        <v>0.91</v>
       </c>
       <c r="G28" t="n">
-        <v>4.879</v>
+        <v>1.745</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.57</v>
+        <v>2.82</v>
       </c>
       <c r="F29" t="n">
-        <v>1.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>40.961</v>
+        <v>4.676</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.28</v>
+        <v>2.44</v>
       </c>
       <c r="F30" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="G30" t="n">
-        <v>8.103999999999999</v>
+        <v>0.356</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.22</v>
+        <v>2.41</v>
       </c>
       <c r="F31" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="G31" t="n">
-        <v>7.193</v>
+        <v>41.669</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.14</v>
+        <v>2.23</v>
       </c>
       <c r="F32" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="G32" t="n">
-        <v>3.437</v>
+        <v>3.332</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="F33" t="n">
-        <v>0.98</v>
+        <v>0.58</v>
       </c>
       <c r="G33" t="n">
-        <v>1.714</v>
+        <v>1.138</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="F34" t="n">
-        <v>1.35</v>
+        <v>0.72</v>
       </c>
       <c r="G34" t="n">
-        <v>0.643</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>1.62</v>
       </c>
       <c r="F35" t="n">
         <v>0.73</v>
       </c>
       <c r="G35" t="n">
-        <v>7.587</v>
+        <v>7.269</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6</v>
+        <v>-0.47</v>
       </c>
       <c r="F36" t="n">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="G36" t="n">
-        <v>21.302</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.58</v>
+        <v>-1.25</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4</v>
+        <v>7.417</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.55</v>
+        <v>-1.37</v>
       </c>
       <c r="F38" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="G38" t="n">
-        <v>9.369</v>
+        <v>1.675</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.53</v>
+        <v>-1.42</v>
       </c>
       <c r="F39" t="n">
-        <v>0.43</v>
+        <v>0.72</v>
       </c>
       <c r="G39" t="n">
-        <v>1.264</v>
+        <v>3.274</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.25</v>
+        <v>-1.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="G40" t="n">
-        <v>0.385</v>
+        <v>3.343</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>-2.41</v>
       </c>
       <c r="F41" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
-        <v>3.77</v>
+        <v>2.444</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-0.23</v>
+        <v>-2.64</v>
       </c>
       <c r="F42" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="G42" t="n">
-        <v>1.702</v>
+        <v>1.225</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-0.62</v>
+        <v>-3.36</v>
       </c>
       <c r="F43" t="n">
-        <v>0.65</v>
+        <v>1.03</v>
       </c>
       <c r="G43" t="n">
-        <v>3.492</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-0.72</v>
+        <v>-3.44</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G44" t="n">
-        <v>0.735</v>
+        <v>15.892</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-1.58</v>
+        <v>-3.68</v>
       </c>
       <c r="F45" t="n">
-        <v>0.98</v>
+        <v>0.74</v>
       </c>
       <c r="G45" t="n">
-        <v>0.493</v>
+        <v>21.175</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3.12</v>
+        <v>-4.31</v>
       </c>
       <c r="F46" t="n">
-        <v>1.36</v>
+        <v>0.58</v>
       </c>
       <c r="G46" t="n">
-        <v>16.019</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-4.68</v>
+        <v>-4.51</v>
       </c>
       <c r="F47" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="G47" t="n">
-        <v>7.575</v>
+        <v>3.578</v>
       </c>
     </row>
     <row r="48">
@@ -3706,106 +3706,106 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-5.37</v>
+        <v>-4.65</v>
       </c>
       <c r="F48" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="G48" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-5.58</v>
+        <v>-5.61</v>
       </c>
       <c r="F49" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4</v>
+        <v>31.578</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-7.13</v>
+        <v>-8.16</v>
       </c>
       <c r="F50" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="G50" t="n">
-        <v>6.748</v>
+        <v>7.428</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-7.85</v>
+        <v>-11.45</v>
       </c>
       <c r="F51" t="n">
-        <v>0.62</v>
+        <v>1.34</v>
       </c>
       <c r="G51" t="n">
-        <v>0.306</v>
+        <v>6.835</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-16.44</v>
+        <v>-17.93</v>
       </c>
       <c r="F52" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="G52" t="n">
-        <v>0.29</v>
+        <v>0.289</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.54</v>
+        <v>37.33</v>
       </c>
       <c r="C2" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="D2" t="n">
-        <v>6.359</v>
+        <v>5.92</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.47</v>
+        <v>22.62</v>
       </c>
       <c r="C3" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="D3" t="n">
-        <v>3.88</v>
+        <v>3.962</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,77 +3921,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.1</v>
+        <v>21.62</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6</v>
+        <v>0.88</v>
       </c>
       <c r="D4" t="n">
-        <v>19.638</v>
+        <v>31.369</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.82</v>
+        <v>16.52333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.85</v>
+        <v>0.8033333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>32.755</v>
+        <v>20.87</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.49</v>
+        <v>15.06</v>
       </c>
       <c r="C6" t="n">
-        <v>0.48</v>
+        <v>0.905</v>
       </c>
       <c r="D6" t="n">
-        <v>0.858</v>
+        <v>67.84099999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.255</v>
+        <v>14.91</v>
       </c>
       <c r="C7" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="D7" t="n">
-        <v>65.053</v>
+        <v>0.914</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.17</v>
+        <v>13.648</v>
       </c>
       <c r="C8" t="n">
-        <v>0.924</v>
+        <v>0.9880000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>10.004</v>
+        <v>9.881</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -4020,13 +4020,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.28</v>
+        <v>12.77</v>
       </c>
       <c r="C9" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="D9" t="n">
-        <v>5.143</v>
+        <v>5.254</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.859999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="C10" t="n">
         <v>0.58</v>
       </c>
       <c r="D10" t="n">
-        <v>2.044</v>
+        <v>2.15</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.68</v>
+        <v>7.82</v>
       </c>
       <c r="C11" t="n">
-        <v>0.52</v>
+        <v>1.05</v>
       </c>
       <c r="D11" t="n">
-        <v>0.135</v>
+        <v>1.961</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,17 +4073,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.3</v>
+        <v>6.85</v>
       </c>
       <c r="C12" t="n">
-        <v>0.91</v>
+        <v>0.53</v>
       </c>
       <c r="D12" t="n">
-        <v>9.497</v>
+        <v>0.137</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,36 +4092,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.700000000000001</v>
+        <v>6.14</v>
       </c>
       <c r="C13" t="n">
-        <v>1.135</v>
+        <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>18.26</v>
+        <v>9.503</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.29</v>
+        <v>5.32</v>
       </c>
       <c r="C14" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="D14" t="n">
-        <v>1.699</v>
+        <v>1.638</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,36 +4130,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.13</v>
+        <v>4.07</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.82</v>
       </c>
       <c r="D15" t="n">
-        <v>12.758</v>
+        <v>9.483000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.89</v>
+        <v>3.86</v>
       </c>
       <c r="C16" t="n">
-        <v>0.86</v>
+        <v>1.52</v>
       </c>
       <c r="D16" t="n">
-        <v>9.627000000000001</v>
+        <v>0.664</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.62</v>
+        <v>3.42</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="D17" t="n">
-        <v>1.808</v>
+        <v>1.745</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,17 +4187,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.48</v>
+        <v>2.523333333333333</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5233333333333333</v>
+        <v>0.6033333333333334</v>
       </c>
       <c r="D18" t="n">
-        <v>5.888999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
@@ -4206,17 +4206,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="C19" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="D19" t="n">
-        <v>32.913</v>
+        <v>0.356</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4225,17 +4225,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7250000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="D20" t="n">
-        <v>4.954</v>
+        <v>18.88</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -4244,207 +4244,207 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.03</v>
+        <v>1.445</v>
       </c>
       <c r="C21" t="n">
-        <v>0.98</v>
+        <v>0.6975</v>
       </c>
       <c r="D21" t="n">
-        <v>1.714</v>
+        <v>22.426</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.03</v>
+        <v>0.64</v>
       </c>
       <c r="C22" t="n">
-        <v>1.35</v>
+        <v>0.7849999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.643</v>
+        <v>1.116</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.02</v>
+        <v>0.4299999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.73</v>
+        <v>0.735</v>
       </c>
       <c r="D23" t="n">
-        <v>7.587</v>
+        <v>5.007</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6</v>
+        <v>0.3400000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.65</v>
+        <v>0.86</v>
       </c>
       <c r="D24" t="n">
-        <v>21.302</v>
+        <v>23.808</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0.7533333333333334</v>
       </c>
       <c r="C25" t="n">
-        <v>0.67</v>
+        <v>0.5133333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>3.77</v>
+        <v>5.706</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1825000000000001</v>
+        <v>-1.25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D26" t="n">
-        <v>22.022</v>
+        <v>7.417</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.235</v>
+        <v>-3.36</v>
       </c>
       <c r="C27" t="n">
-        <v>0.765</v>
+        <v>1.03</v>
       </c>
       <c r="D27" t="n">
-        <v>1.12</v>
+        <v>0.452</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3549999999999998</v>
+        <v>-3.68</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="D28" t="n">
-        <v>10.026</v>
+        <v>21.175</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.92</v>
+        <v>-4.51</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9650000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="D29" t="n">
-        <v>24.123</v>
+        <v>3.578</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.58</v>
+        <v>-5.285</v>
       </c>
       <c r="C30" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="D30" t="n">
-        <v>0.493</v>
+        <v>9.872</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-7.85</v>
+        <v>-5.61</v>
       </c>
       <c r="C31" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.306</v>
+        <v>31.578</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-7.930000000000001</v>
+        <v>-6.93</v>
       </c>
       <c r="C32" t="n">
-        <v>1.275</v>
+        <v>1.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.711</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1985</v>
+        <v>1970</v>
       </c>
       <c r="E2" t="n">
-        <v>3.39</v>
+        <v>-0.76</v>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>-1.25</v>
       </c>
       <c r="G2" t="n">
-        <v>33.65</v>
+        <v>33.02</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6562</v>
+        <v>-2.2723</v>
       </c>
       <c r="I2" t="n">
-        <v>23.4</v>
+        <v>19.3</v>
       </c>
       <c r="J2" t="n">
-        <v>26.5</v>
+        <v>20.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.26</v>
+        <v>4.33</v>
       </c>
       <c r="L2" t="n">
-        <v>-20.4</v>
+        <v>-25.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4530</v>
+        <v>4500</v>
       </c>
       <c r="E3" t="n">
-        <v>2.26</v>
+        <v>-0.66</v>
       </c>
       <c r="F3" t="n">
-        <v>17.82</v>
+        <v>21.62</v>
       </c>
       <c r="G3" t="n">
-        <v>69.39</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>205.7796</v>
+        <v>193.9451</v>
       </c>
       <c r="I3" t="n">
+        <v>65</v>
+      </c>
+      <c r="J3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="J3" t="n">
-        <v>72.5</v>
-      </c>
       <c r="K3" t="n">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="L3" t="n">
-        <v>-11.8</v>
+        <v>-7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>89.8</v>
+        <v>88.2</v>
       </c>
       <c r="E4" t="n">
-        <v>4.42</v>
+        <v>-1.78</v>
       </c>
       <c r="F4" t="n">
-        <v>-16.44</v>
+        <v>-17.93</v>
       </c>
       <c r="G4" t="n">
-        <v>21.28</v>
+        <v>20.62</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.6482</v>
+        <v>-7.7049</v>
       </c>
       <c r="I4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J4" t="n">
-        <v>15.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>6.13</v>
+        <v>6.11</v>
       </c>
       <c r="L4" t="n">
-        <v>8.699999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="M4" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>315</v>
+        <v>303.5</v>
       </c>
       <c r="E5" t="n">
-        <v>6.96</v>
+        <v>-3.65</v>
       </c>
       <c r="F5" t="n">
-        <v>47.54</v>
+        <v>37.33</v>
       </c>
       <c r="G5" t="n">
-        <v>76.42</v>
+        <v>68.48</v>
       </c>
       <c r="H5" t="n">
-        <v>28.147</v>
+        <v>28.0912</v>
       </c>
       <c r="I5" t="n">
-        <v>92.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>100</v>
+        <v>84.5</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>8.08</v>
       </c>
       <c r="L5" t="n">
-        <v>39.4</v>
+        <v>35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.96</v>
+        <v>3.69</v>
       </c>
       <c r="F6" t="n">
-        <v>29.89</v>
+        <v>29.61</v>
       </c>
       <c r="G6" t="n">
-        <v>66.53</v>
+        <v>68.8</v>
       </c>
       <c r="H6" t="n">
-        <v>40.0057</v>
+        <v>39.075</v>
       </c>
       <c r="I6" t="n">
-        <v>64.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="J6" t="n">
-        <v>75</v>
+        <v>87.7</v>
       </c>
       <c r="K6" t="n">
-        <v>6.97</v>
+        <v>7.26</v>
       </c>
       <c r="L6" t="n">
-        <v>77.90000000000001</v>
+        <v>144.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.47</v>
+        <v>0.91</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>248</v>
+        <v>250.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.61</v>
+        <v>1.01</v>
       </c>
       <c r="F7" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>46.99</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2696</v>
+        <v>-0.1947</v>
       </c>
       <c r="I7" t="n">
-        <v>39.8</v>
+        <v>54.5</v>
       </c>
       <c r="J7" t="n">
-        <v>15.8</v>
+        <v>42.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="L7" t="n">
-        <v>-32.2</v>
+        <v>-8.9</v>
       </c>
       <c r="M7" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>165.5</v>
+        <v>190.5</v>
       </c>
       <c r="E2" t="n">
-        <v>4.75</v>
+        <v>6.42</v>
       </c>
       <c r="F2" t="n">
-        <v>262</v>
+        <v>334</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.961</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>534</v>
+        <v>270.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3.69</v>
+        <v>7.55</v>
       </c>
       <c r="F3" t="n">
-        <v>245</v>
+        <v>284</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.229</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1480</v>
+        <v>291.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.34</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>198</v>
+        <v>273</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,135 +572,135 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.664</v>
+        <v>6.513</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>471</v>
+        <v>29.6</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.32</v>
+        <v>-3.27</v>
       </c>
       <c r="F5" t="n">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14.244</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3295</v>
+        <v>172</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.49</v>
+        <v>3.93</v>
       </c>
       <c r="F6" t="n">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6.835</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>251.5</v>
+        <v>3540</v>
       </c>
       <c r="E7" t="n">
-        <v>9.83</v>
+        <v>7.44</v>
       </c>
       <c r="F7" t="n">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.356</v>
+        <v>7.966</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>147.5</v>
+        <v>69.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3.87</v>
+        <v>-2.39</v>
       </c>
       <c r="F8" t="n">
-        <v>145</v>
+        <v>226</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26.172</v>
+        <v>2.303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>2460</v>
       </c>
       <c r="E9" t="n">
-        <v>3.17</v>
+        <v>1.44</v>
       </c>
       <c r="F9" t="n">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.422</v>
+        <v>44.714</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.82</v>
+        <v>8.42</v>
       </c>
       <c r="F10" t="n">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,169 +776,169 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.444</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>303.5</v>
+        <v>41.75</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.65</v>
+        <v>-0.71</v>
       </c>
       <c r="F11" t="n">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.92</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>715</v>
+        <v>944</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.51</v>
       </c>
       <c r="F12" t="n">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.638</v>
+        <v>8.061</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>912</v>
+        <v>110.5</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.67</v>
+        <v>-1.34</v>
       </c>
       <c r="F13" t="n">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.428</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6500</v>
+        <v>121</v>
       </c>
       <c r="E14" t="n">
-        <v>5.35</v>
+        <v>3.86</v>
       </c>
       <c r="F14" t="n">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>12.045</v>
+        <v>3.872</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>344</v>
+        <v>2140</v>
       </c>
       <c r="E15" t="n">
-        <v>1.03</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.606</v>
+        <v>8.407999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>65.5</v>
+        <v>556</v>
       </c>
       <c r="E16" t="n">
-        <v>1.87</v>
+        <v>4.12</v>
       </c>
       <c r="F16" t="n">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,67 +980,67 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.914</v>
+        <v>6.643</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1685</v>
+        <v>51.1</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.46</v>
+        <v>-1.54</v>
       </c>
       <c r="F17" t="n">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15.892</v>
+        <v>1.459</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71.2</v>
+        <v>638</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.91</v>
       </c>
       <c r="F18" t="n">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,101 +1048,101 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.277</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>274.5</v>
+        <v>156</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="F19" t="n">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.332</v>
+        <v>29.579</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>88.2</v>
+        <v>284</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.78</v>
+        <v>3.46</v>
       </c>
       <c r="F20" t="n">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.289</v>
+        <v>3.658</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27.55</v>
+        <v>1495</v>
       </c>
       <c r="E21" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="F21" t="n">
-        <v>106</v>
+        <v>155</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.534</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2425</v>
+        <v>343</v>
       </c>
       <c r="E22" t="n">
-        <v>1.89</v>
+        <v>-0.29</v>
       </c>
       <c r="F22" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,271 +1184,271 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>41.669</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>170</v>
+        <v>27.3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.59</v>
+        <v>-0.91</v>
       </c>
       <c r="F23" t="n">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>21.175</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>116.5</v>
+        <v>187.5</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1</v>
+        <v>3.02</v>
       </c>
       <c r="F24" t="n">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.578</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4500</v>
+        <v>250.5</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>31.369</v>
+        <v>7.516</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>250.5</v>
+        <v>7150</v>
       </c>
       <c r="E26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="F26" t="n">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7.269</v>
+        <v>13.064</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>71.2</v>
+        <v>150.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1.86</v>
+        <v>-0.66</v>
       </c>
       <c r="F27" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.503</v>
+        <v>2.975</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>42.05</v>
+        <v>500</v>
       </c>
       <c r="E28" t="n">
-        <v>1.82</v>
+        <v>6.16</v>
       </c>
       <c r="F28" t="n">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.727</v>
+        <v>15.665</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>112</v>
+        <v>558</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.44</v>
+        <v>2.39</v>
       </c>
       <c r="F29" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.573</v>
+        <v>1.878</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>108</v>
+        <v>61.7</v>
       </c>
       <c r="E30" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="F30" t="n">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,67 +1456,67 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.397</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>51.9</v>
+        <v>4710</v>
       </c>
       <c r="E31" t="n">
-        <v>1.96</v>
+        <v>4.67</v>
       </c>
       <c r="F31" t="n">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.432</v>
+        <v>33.713</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>86.7</v>
+        <v>1735</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.46</v>
+        <v>2.97</v>
       </c>
       <c r="F32" t="n">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,67 +1524,67 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.675</v>
+        <v>17.051</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>265</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>1.34</v>
+        <v>2.9</v>
       </c>
       <c r="F33" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.254</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1970</v>
+        <v>20.15</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.76</v>
+        <v>-0.98</v>
       </c>
       <c r="F34" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,143 +1592,143 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7.417</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>64.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="E35" t="n">
-        <v>3.53</v>
+        <v>3.93</v>
       </c>
       <c r="F35" t="n">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.15</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2710</v>
+        <v>525</v>
       </c>
       <c r="E36" t="n">
-        <v>0.37</v>
+        <v>7.58</v>
       </c>
       <c r="F36" t="n">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3.962</v>
+        <v>34.345</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>614</v>
+        <v>179.5</v>
       </c>
       <c r="E37" t="n">
-        <v>1.49</v>
+        <v>5.59</v>
       </c>
       <c r="F37" t="n">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>9.483000000000001</v>
+        <v>22.565</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>545</v>
+        <v>727</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.55</v>
+        <v>1.68</v>
       </c>
       <c r="F38" t="n">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.745</v>
+        <v>1.688</v>
       </c>
     </row>
     <row r="39">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18.7</v>
+        <v>18.75</v>
       </c>
       <c r="E39" t="n">
         <v>0.27</v>
       </c>
       <c r="F39" t="n">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,67 +1762,67 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.452</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>488</v>
+        <v>277</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.91</v>
+        <v>2.21</v>
       </c>
       <c r="F40" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>31.578</v>
+        <v>1.116</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>151.5</v>
+        <v>2845</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.98</v>
+        <v>4.98</v>
       </c>
       <c r="F41" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,67 +1830,67 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.065</v>
+        <v>4.251</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20.35</v>
+        <v>314</v>
       </c>
       <c r="E42" t="n">
-        <v>2.01</v>
+        <v>3.46</v>
       </c>
       <c r="F42" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.389</v>
+        <v>6.091</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>242.5</v>
+        <v>120.5</v>
       </c>
       <c r="E43" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,67 +1898,67 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.274</v>
+        <v>3.913</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>186.5</v>
+        <v>396.5</v>
       </c>
       <c r="E44" t="n">
-        <v>1.91</v>
+        <v>0.38</v>
       </c>
       <c r="F44" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>9.601000000000001</v>
+        <v>3.079</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30.6</v>
+        <v>65</v>
       </c>
       <c r="E45" t="n">
-        <v>2.51</v>
+        <v>0.62</v>
       </c>
       <c r="F45" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.137</v>
+        <v>2.192</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>120.5</v>
+        <v>240.5</v>
       </c>
       <c r="E46" t="n">
-        <v>4.78</v>
+        <v>-0.82</v>
       </c>
       <c r="F46" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,135 +2000,135 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4.25</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>62</v>
+        <v>282</v>
       </c>
       <c r="E47" t="n">
-        <v>2.99</v>
+        <v>1.44</v>
       </c>
       <c r="F47" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.676</v>
+        <v>8.007</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>61.5</v>
+        <v>186.5</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.95</v>
+        <v>9.715</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>395</v>
+        <v>61</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.13</v>
+        <v>-1.61</v>
       </c>
       <c r="F49" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.343</v>
+        <v>4.141</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>277</v>
+        <v>111</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.95</v>
+        <v>2.78</v>
       </c>
       <c r="F50" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.225</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>271</v>
+        <v>88.2</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,33 +2170,33 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.138</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E52" t="n">
-        <v>0.36</v>
+        <v>2.17</v>
       </c>
       <c r="F52" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>7.916</v>
+        <v>1.019</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>37.33</v>
+        <v>48.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>5.92</v>
+        <v>6.091</v>
       </c>
     </row>
     <row r="3">
@@ -2311,75 +2311,75 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29.61</v>
+        <v>36.95</v>
       </c>
       <c r="F3" t="n">
-        <v>0.91</v>
+        <v>1.18</v>
       </c>
       <c r="G3" t="n">
-        <v>6.229</v>
+        <v>6.643</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27.71</v>
+        <v>34.05</v>
       </c>
       <c r="F4" t="n">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="G4" t="n">
-        <v>26.172</v>
+        <v>15.665</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24.27</v>
+        <v>33.91</v>
       </c>
       <c r="F5" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="G5" t="n">
-        <v>14.244</v>
+        <v>29.579</v>
       </c>
     </row>
     <row r="6">
@@ -2404,106 +2404,106 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22.62</v>
+        <v>32.02</v>
       </c>
       <c r="F6" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>3.962</v>
+        <v>4.251</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21.62</v>
+        <v>27.68</v>
       </c>
       <c r="F7" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G7" t="n">
-        <v>31.369</v>
+        <v>13.064</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>18.36</v>
+        <v>25.65</v>
       </c>
       <c r="F8" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="G8" t="n">
-        <v>3.065</v>
+        <v>6.513</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15.45</v>
+        <v>24.27</v>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="G9" t="n">
-        <v>12.045</v>
+        <v>33.713</v>
       </c>
     </row>
     <row r="10">
@@ -2528,91 +2528,91 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>14.91</v>
+        <v>17.63</v>
       </c>
       <c r="F10" t="n">
-        <v>0.61</v>
+        <v>0.75</v>
       </c>
       <c r="G10" t="n">
-        <v>0.914</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.64</v>
+        <v>13.53</v>
       </c>
       <c r="F11" t="n">
-        <v>0.85</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>2.573</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.77</v>
+        <v>12.39</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58</v>
+        <v>1.29</v>
       </c>
       <c r="G12" t="n">
-        <v>5.254</v>
+        <v>0.522</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2621,29 +2621,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.3</v>
+        <v>12.31</v>
       </c>
       <c r="F13" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="G13" t="n">
-        <v>2.277</v>
+        <v>2.975</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2652,13 +2652,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11.85</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.432</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="15">
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>11.76</v>
+        <v>9.43</v>
       </c>
       <c r="F15" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="G15" t="n">
-        <v>2.15</v>
+        <v>2.192</v>
       </c>
     </row>
     <row r="16">
@@ -2714,1098 +2714,1098 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.09</v>
+        <v>8.98</v>
       </c>
       <c r="F16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.534</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.82</v>
+        <v>8.84</v>
       </c>
       <c r="F17" t="n">
-        <v>1.05</v>
+        <v>0.96</v>
       </c>
       <c r="G17" t="n">
-        <v>1.961</v>
+        <v>1.459</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.85</v>
+        <v>8.69</v>
       </c>
       <c r="F18" t="n">
-        <v>0.53</v>
+        <v>0.84</v>
       </c>
       <c r="G18" t="n">
-        <v>0.137</v>
+        <v>10.276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.17</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.53</v>
+        <v>0.93</v>
       </c>
       <c r="G19" t="n">
-        <v>4.25</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.14</v>
+        <v>8.42</v>
       </c>
       <c r="F20" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="G20" t="n">
-        <v>9.503</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="G21" t="n">
-        <v>1.638</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.2</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.89</v>
+        <v>0.54</v>
       </c>
       <c r="G22" t="n">
-        <v>4.606</v>
+        <v>8.007</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.12</v>
+        <v>6.92</v>
       </c>
       <c r="F23" t="n">
-        <v>0.52</v>
+        <v>1.49</v>
       </c>
       <c r="G23" t="n">
-        <v>7.916</v>
+        <v>2.303</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.07</v>
+        <v>6.69</v>
       </c>
       <c r="F24" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>9.483000000000001</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.07</v>
+        <v>6.53</v>
       </c>
       <c r="F25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.422</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3.86</v>
+        <v>6.27</v>
       </c>
       <c r="F26" t="n">
-        <v>1.52</v>
+        <v>0.6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.664</v>
+        <v>9.715</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3.61</v>
+        <v>6.17</v>
       </c>
       <c r="F27" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="G27" t="n">
-        <v>9.601000000000001</v>
+        <v>3.658</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="F28" t="n">
-        <v>0.91</v>
+        <v>1.53</v>
       </c>
       <c r="G28" t="n">
-        <v>1.745</v>
+        <v>0.702</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.82</v>
+        <v>5.44</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="G29" t="n">
-        <v>4.676</v>
+        <v>1.688</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.44</v>
+        <v>5.28</v>
       </c>
       <c r="F30" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.356</v>
+        <v>1.878</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.41</v>
+        <v>3.13</v>
       </c>
       <c r="F31" t="n">
-        <v>0.99</v>
+        <v>0.82</v>
       </c>
       <c r="G31" t="n">
-        <v>41.669</v>
+        <v>8.407999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.23</v>
+        <v>3.01</v>
       </c>
       <c r="F32" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>3.332</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="F33" t="n">
-        <v>0.58</v>
+        <v>1.13</v>
       </c>
       <c r="G33" t="n">
-        <v>1.138</v>
+        <v>44.714</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="F34" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="G34" t="n">
-        <v>0.389</v>
+        <v>7.516</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="F35" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="G35" t="n">
-        <v>7.269</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.47</v>
+        <v>0.36</v>
       </c>
       <c r="F36" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="G36" t="n">
-        <v>0.727</v>
+        <v>1.116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
       <c r="F37" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="G37" t="n">
-        <v>7.417</v>
+        <v>8.061</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.37</v>
+        <v>-0.57</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G38" t="n">
-        <v>1.675</v>
+        <v>34.345</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.42</v>
+        <v>-0.83</v>
       </c>
       <c r="F39" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="G39" t="n">
-        <v>3.274</v>
+        <v>22.565</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.5</v>
+        <v>-0.86</v>
       </c>
       <c r="F40" t="n">
-        <v>0.53</v>
+        <v>1.12</v>
       </c>
       <c r="G40" t="n">
-        <v>3.343</v>
+        <v>17.051</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.41</v>
+        <v>-1.22</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G41" t="n">
-        <v>2.444</v>
+        <v>3.872</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.64</v>
+        <v>-1.23</v>
       </c>
       <c r="F42" t="n">
-        <v>0.43</v>
+        <v>0.84</v>
       </c>
       <c r="G42" t="n">
-        <v>1.225</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-3.36</v>
+        <v>-2</v>
       </c>
       <c r="F43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="G43" t="n">
-        <v>0.452</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.44</v>
+        <v>-3.21</v>
       </c>
       <c r="F44" t="n">
-        <v>1.2</v>
+        <v>0.59</v>
       </c>
       <c r="G44" t="n">
-        <v>15.892</v>
+        <v>3.913</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.68</v>
+        <v>-3.58</v>
       </c>
       <c r="F45" t="n">
-        <v>0.74</v>
+        <v>1.23</v>
       </c>
       <c r="G45" t="n">
-        <v>21.175</v>
+        <v>7.966</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-4.31</v>
+        <v>-3.6</v>
       </c>
       <c r="F46" t="n">
-        <v>0.58</v>
+        <v>1.03</v>
       </c>
       <c r="G46" t="n">
-        <v>0.397</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-4.51</v>
+        <v>-4.37</v>
       </c>
       <c r="F47" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="G47" t="n">
-        <v>3.578</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-4.65</v>
+        <v>-4.69</v>
       </c>
       <c r="F48" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="G48" t="n">
-        <v>0.95</v>
+        <v>4.141</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-5.61</v>
+        <v>-6.09</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>31.578</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-8.16</v>
+        <v>-6.15</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="G50" t="n">
-        <v>7.428</v>
+        <v>3.079</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-11.45</v>
+        <v>-9.44</v>
       </c>
       <c r="F51" t="n">
-        <v>1.34</v>
+        <v>0.49</v>
       </c>
       <c r="G51" t="n">
-        <v>6.835</v>
+        <v>1.019</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-17.93</v>
+        <v>-15.98</v>
       </c>
       <c r="F52" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="G52" t="n">
-        <v>0.289</v>
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.33</v>
+        <v>48.11</v>
       </c>
       <c r="C2" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="D2" t="n">
-        <v>5.92</v>
+        <v>6.091</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.62</v>
+        <v>32.02</v>
       </c>
       <c r="C3" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>3.962</v>
+        <v>4.251</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,17 +3921,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.62</v>
+        <v>25.65</v>
       </c>
       <c r="C4" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="D4" t="n">
-        <v>31.369</v>
+        <v>6.513</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.52333333333333</v>
+        <v>24.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8033333333333333</v>
+        <v>0.9533333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>20.87</v>
+        <v>22.708</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -3959,74 +3959,74 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.06</v>
+        <v>24.27</v>
       </c>
       <c r="C6" t="n">
-        <v>0.905</v>
+        <v>0.92</v>
       </c>
       <c r="D6" t="n">
-        <v>67.84099999999999</v>
+        <v>33.713</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14.91</v>
+        <v>18.145</v>
       </c>
       <c r="C7" t="n">
-        <v>0.61</v>
+        <v>1.045</v>
       </c>
       <c r="D7" t="n">
-        <v>0.914</v>
+        <v>74.29300000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.648</v>
+        <v>17.63</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9880000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>9.881</v>
+        <v>0.98</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.77</v>
+        <v>13.53</v>
       </c>
       <c r="C9" t="n">
-        <v>0.58</v>
+        <v>1.29</v>
       </c>
       <c r="D9" t="n">
-        <v>5.254</v>
+        <v>2.277</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -4035,36 +4035,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.76</v>
+        <v>12.05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.58</v>
+        <v>1.205</v>
       </c>
       <c r="D10" t="n">
-        <v>2.15</v>
+        <v>21.03</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7.82</v>
+        <v>9.43</v>
       </c>
       <c r="C11" t="n">
-        <v>1.05</v>
+        <v>0.67</v>
       </c>
       <c r="D11" t="n">
-        <v>1.961</v>
+        <v>2.192</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,36 +4073,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.85</v>
+        <v>9.4</v>
       </c>
       <c r="C12" t="n">
-        <v>0.53</v>
+        <v>1.12</v>
       </c>
       <c r="D12" t="n">
-        <v>0.137</v>
+        <v>9.946999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.14</v>
+        <v>8.69</v>
       </c>
       <c r="C13" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="D13" t="n">
-        <v>9.503</v>
+        <v>10.276</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,17 +4111,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.32</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>1.05</v>
+        <v>0.93</v>
       </c>
       <c r="D14" t="n">
-        <v>1.638</v>
+        <v>10.09</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,17 +4130,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.07</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="D15" t="n">
-        <v>9.483000000000001</v>
+        <v>0.438</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,36 +4149,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.86</v>
+        <v>7.295</v>
       </c>
       <c r="C16" t="n">
-        <v>1.52</v>
+        <v>0.84</v>
       </c>
       <c r="D16" t="n">
-        <v>0.664</v>
+        <v>5.62</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="C17" t="n">
-        <v>0.91</v>
+        <v>1.53</v>
       </c>
       <c r="D17" t="n">
-        <v>1.745</v>
+        <v>0.702</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,36 +4187,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.523333333333333</v>
+        <v>5.44</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6033333333333334</v>
+        <v>1.08</v>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>1.688</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.44</v>
+        <v>5.28</v>
       </c>
       <c r="C19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.356</v>
+        <v>1.878</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4225,17 +4225,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3.595</v>
       </c>
       <c r="C20" t="n">
-        <v>1.19</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>18.88</v>
+        <v>25.058</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -4244,112 +4244,112 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.445</v>
+        <v>3.425</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6975</v>
+        <v>1.01</v>
       </c>
       <c r="D21" t="n">
-        <v>22.426</v>
+        <v>10.516</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.64</v>
+        <v>3.13</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="D22" t="n">
-        <v>1.116</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4299999999999999</v>
+        <v>3.01</v>
       </c>
       <c r="C23" t="n">
-        <v>0.735</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>5.007</v>
+        <v>0.144</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3400000000000001</v>
+        <v>2.2275</v>
       </c>
       <c r="C24" t="n">
-        <v>0.86</v>
+        <v>0.7825</v>
       </c>
       <c r="D24" t="n">
-        <v>23.808</v>
+        <v>23.023</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.7533333333333334</v>
+        <v>-0.57</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5133333333333333</v>
+        <v>0.73</v>
       </c>
       <c r="D25" t="n">
-        <v>5.706</v>
+        <v>34.345</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.25</v>
+        <v>-0.83</v>
       </c>
       <c r="C26" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="D26" t="n">
-        <v>7.417</v>
+        <v>22.565</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-3.36</v>
+        <v>-1.22</v>
       </c>
       <c r="C27" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="D27" t="n">
-        <v>0.452</v>
+        <v>3.872</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,96 +4377,96 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-3.68</v>
+        <v>-1.615</v>
       </c>
       <c r="C28" t="n">
-        <v>0.74</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>21.175</v>
+        <v>1.119</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.51</v>
+        <v>-1.795</v>
       </c>
       <c r="C29" t="n">
-        <v>0.72</v>
+        <v>1.29</v>
       </c>
       <c r="D29" t="n">
-        <v>3.578</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-5.285</v>
+        <v>-3.6</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8</v>
+        <v>1.03</v>
       </c>
       <c r="D30" t="n">
-        <v>9.872</v>
+        <v>0.448</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-5.61</v>
+        <v>-4.09</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6</v>
+        <v>0.6466666666666666</v>
       </c>
       <c r="D31" t="n">
-        <v>31.578</v>
+        <v>11.034</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-6.93</v>
+        <v>-5.076666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>1.2</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>0.711</v>
+        <v>5.214</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4572,38 +4572,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1970</v>
+        <v>2140</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.76</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.25</v>
+        <v>3.13</v>
       </c>
       <c r="G2" t="n">
-        <v>33.02</v>
+        <v>48.18</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.2723</v>
+        <v>8.237</v>
       </c>
       <c r="I2" t="n">
-        <v>19.3</v>
+        <v>74.7</v>
       </c>
       <c r="J2" t="n">
-        <v>20.4</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="L2" t="n">
-        <v>-25.4</v>
+        <v>69.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4500</v>
+        <v>4710</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.66</v>
+        <v>4.67</v>
       </c>
       <c r="F3" t="n">
-        <v>21.62</v>
+        <v>24.27</v>
       </c>
       <c r="G3" t="n">
-        <v>65.84999999999999</v>
+        <v>72.11</v>
       </c>
       <c r="H3" t="n">
-        <v>193.9451</v>
+        <v>199.215</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>77.3</v>
       </c>
       <c r="J3" t="n">
-        <v>68.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.88</v>
+        <v>4.77</v>
       </c>
       <c r="L3" t="n">
-        <v>-7.4</v>
+        <v>38.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4679,31 +4679,31 @@
         <v>88.2</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-17.93</v>
+        <v>-15.98</v>
       </c>
       <c r="G4" t="n">
-        <v>20.62</v>
+        <v>20.91</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.7049</v>
+        <v>-7.6615</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>17.4</v>
       </c>
       <c r="J4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>6.11</v>
+        <v>6.01</v>
       </c>
       <c r="L4" t="n">
-        <v>6.8</v>
+        <v>-33</v>
       </c>
       <c r="M4" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>303.5</v>
+        <v>314</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.65</v>
+        <v>3.46</v>
       </c>
       <c r="F5" t="n">
-        <v>37.33</v>
+        <v>48.11</v>
       </c>
       <c r="G5" t="n">
-        <v>68.48</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>28.0912</v>
+        <v>28.565</v>
       </c>
       <c r="I5" t="n">
-        <v>80.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8.08</v>
+        <v>7.59</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>-5.2</v>
       </c>
       <c r="M5" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>534</v>
+        <v>556</v>
       </c>
       <c r="E6" t="n">
-        <v>3.69</v>
+        <v>4.12</v>
       </c>
       <c r="F6" t="n">
-        <v>29.61</v>
+        <v>36.95</v>
       </c>
       <c r="G6" t="n">
-        <v>68.8</v>
+        <v>66.12</v>
       </c>
       <c r="H6" t="n">
-        <v>39.075</v>
+        <v>39.6555</v>
       </c>
       <c r="I6" t="n">
-        <v>71.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>87.7</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>7.26</v>
+        <v>6.9</v>
       </c>
       <c r="L6" t="n">
-        <v>144.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.91</v>
+        <v>1.18</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4835,31 +4835,31 @@
         <v>250.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>46.99</v>
+        <v>50.65</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1947</v>
+        <v>-0.1339</v>
       </c>
       <c r="I7" t="n">
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="J7" t="n">
         <v>42.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="L7" t="n">
-        <v>-8.9</v>
+        <v>48.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>190.5</v>
+        <v>103</v>
       </c>
       <c r="E2" t="n">
-        <v>6.42</v>
+        <v>9.57</v>
       </c>
       <c r="F2" t="n">
-        <v>334</v>
+        <v>271</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.522</v>
+        <v>2.398</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>270.5</v>
+        <v>301.5</v>
       </c>
       <c r="E3" t="n">
-        <v>7.55</v>
+        <v>3.43</v>
       </c>
       <c r="F3" t="n">
-        <v>284</v>
+        <v>230</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.438</v>
+        <v>7.334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>291.5</v>
+        <v>292.5</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>2.99</v>
       </c>
       <c r="F4" t="n">
-        <v>273</v>
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,67 +572,67 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.513</v>
+        <v>4.045</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.6</v>
+        <v>1875</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.27</v>
+        <v>8.07</v>
       </c>
       <c r="F5" t="n">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.144</v>
+        <v>19.757</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>172</v>
+        <v>68.8</v>
       </c>
       <c r="E6" t="n">
-        <v>3.93</v>
+        <v>2.08</v>
       </c>
       <c r="F6" t="n">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,67 +640,67 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.277</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3540</v>
+        <v>7615</v>
       </c>
       <c r="E7" t="n">
-        <v>7.44</v>
+        <v>6.5</v>
       </c>
       <c r="F7" t="n">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7.966</v>
+        <v>14.462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69.5</v>
+        <v>191</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.39</v>
+        <v>0.26</v>
       </c>
       <c r="F8" t="n">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.303</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2460</v>
+        <v>5010</v>
       </c>
       <c r="E9" t="n">
-        <v>1.44</v>
+        <v>6.37</v>
       </c>
       <c r="F9" t="n">
-        <v>204</v>
+        <v>149</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>44.714</v>
+        <v>37.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>94</v>
+        <v>572</v>
       </c>
       <c r="E10" t="n">
-        <v>8.42</v>
+        <v>2.88</v>
       </c>
       <c r="F10" t="n">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,101 +776,101 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.962</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>41.75</v>
+        <v>740</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.71</v>
+        <v>1.79</v>
       </c>
       <c r="F11" t="n">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.737</v>
+        <v>1.793</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>944</v>
+        <v>172</v>
       </c>
       <c r="E12" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8.061</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>110.5</v>
+        <v>2150</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.34</v>
+        <v>0.47</v>
       </c>
       <c r="F13" t="n">
-        <v>180</v>
+        <v>119</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.658</v>
+        <v>8.257</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>18.65</v>
       </c>
       <c r="E14" t="n">
-        <v>3.86</v>
+        <v>-0.53</v>
       </c>
       <c r="F14" t="n">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3.872</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2140</v>
+        <v>263.5</v>
       </c>
       <c r="E15" t="n">
-        <v>8.630000000000001</v>
+        <v>-2.59</v>
       </c>
       <c r="F15" t="n">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8.407999999999999</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>556</v>
+        <v>663</v>
       </c>
       <c r="E16" t="n">
-        <v>4.12</v>
+        <v>3.92</v>
       </c>
       <c r="F16" t="n">
-        <v>167</v>
+        <v>103</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,543 +980,543 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6.643</v>
+        <v>10.951</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51.1</v>
+        <v>186.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.54</v>
+        <v>-0.53</v>
       </c>
       <c r="F17" t="n">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.459</v>
+        <v>2.239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>638</v>
+        <v>548</v>
       </c>
       <c r="E18" t="n">
-        <v>3.91</v>
+        <v>-1.79</v>
       </c>
       <c r="F18" t="n">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10.276</v>
+        <v>1.815</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>156</v>
+        <v>2480</v>
       </c>
       <c r="E19" t="n">
-        <v>5.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>29.579</v>
+        <v>45.524</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="E20" t="n">
-        <v>3.46</v>
+        <v>0.64</v>
       </c>
       <c r="F20" t="n">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.658</v>
+        <v>29.466</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1495</v>
+        <v>931</v>
       </c>
       <c r="E21" t="n">
-        <v>1.01</v>
+        <v>-1.38</v>
       </c>
       <c r="F21" t="n">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.702</v>
+        <v>7.717</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>343</v>
+        <v>29.25</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.29</v>
+        <v>-1.18</v>
       </c>
       <c r="F22" t="n">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4.81</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27.3</v>
+        <v>120</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.91</v>
+        <v>-0.83</v>
       </c>
       <c r="F23" t="n">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.552</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>187.5</v>
+        <v>1475</v>
       </c>
       <c r="E24" t="n">
-        <v>3.02</v>
+        <v>-1.34</v>
       </c>
       <c r="F24" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.455</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>250.5</v>
+        <v>154.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="F25" t="n">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7.516</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7150</v>
+        <v>86.5</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>-1.93</v>
       </c>
       <c r="F26" t="n">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13.064</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>150.5</v>
+        <v>3665</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.66</v>
+        <v>3.53</v>
       </c>
       <c r="F27" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.975</v>
+        <v>8.337</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>500</v>
+        <v>389</v>
       </c>
       <c r="E28" t="n">
-        <v>6.16</v>
+        <v>2.78</v>
       </c>
       <c r="F28" t="n">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>15.665</v>
+        <v>2.502</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>558</v>
+        <v>490.5</v>
       </c>
       <c r="E29" t="n">
-        <v>2.39</v>
+        <v>-1.9</v>
       </c>
       <c r="F29" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.878</v>
+        <v>15.634</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>61.7</v>
+        <v>72.7</v>
       </c>
       <c r="E30" t="n">
-        <v>0.33</v>
+        <v>-1.76</v>
       </c>
       <c r="F30" t="n">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.982</v>
+        <v>9.664</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4710</v>
+        <v>308</v>
       </c>
       <c r="E31" t="n">
-        <v>4.67</v>
+        <v>-1.91</v>
       </c>
       <c r="F31" t="n">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>33.713</v>
+        <v>6.051</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1735</v>
+        <v>286</v>
       </c>
       <c r="E32" t="n">
-        <v>2.97</v>
+        <v>1.06</v>
       </c>
       <c r="F32" t="n">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,237 +1524,237 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>17.051</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>67.40000000000001</v>
+        <v>113</v>
       </c>
       <c r="E33" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="F33" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.98</v>
+        <v>2.749</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>20.15</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.98</v>
+        <v>1.29</v>
       </c>
       <c r="F34" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.382</v>
+        <v>2.346</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="E35" t="n">
-        <v>3.93</v>
+        <v>-3.06</v>
       </c>
       <c r="F35" t="n">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10.09</v>
+        <v>21.672</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>525</v>
+        <v>2830</v>
       </c>
       <c r="E36" t="n">
-        <v>7.58</v>
+        <v>-0.53</v>
       </c>
       <c r="F36" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>34.345</v>
+        <v>4.276</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>179.5</v>
+        <v>288.5</v>
       </c>
       <c r="E37" t="n">
-        <v>5.59</v>
+        <v>2.3</v>
       </c>
       <c r="F37" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>22.565</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>727</v>
+        <v>344.5</v>
       </c>
       <c r="E38" t="n">
-        <v>1.68</v>
+        <v>0.44</v>
       </c>
       <c r="F38" t="n">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.688</v>
+        <v>4.872</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18.75</v>
+        <v>250</v>
       </c>
       <c r="E39" t="n">
-        <v>0.27</v>
+        <v>-0.2</v>
       </c>
       <c r="F39" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,67 +1762,67 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.448</v>
+        <v>7.423</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>277</v>
+        <v>516</v>
       </c>
       <c r="E40" t="n">
-        <v>2.21</v>
+        <v>-1.71</v>
       </c>
       <c r="F40" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.116</v>
+        <v>32.766</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2845</v>
+        <v>242</v>
       </c>
       <c r="E41" t="n">
-        <v>4.98</v>
+        <v>0.62</v>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4.251</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>314</v>
+        <v>117</v>
       </c>
       <c r="E42" t="n">
-        <v>3.46</v>
+        <v>-2.9</v>
       </c>
       <c r="F42" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6.091</v>
+        <v>3.361</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>120.5</v>
+        <v>27.2</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="F43" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.913</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>396.5</v>
+        <v>109.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.38</v>
+        <v>-1.35</v>
       </c>
       <c r="F44" t="n">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.079</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>65</v>
+        <v>276.5</v>
       </c>
       <c r="E45" t="n">
-        <v>0.62</v>
+        <v>-0.18</v>
       </c>
       <c r="F45" t="n">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,67 +1966,67 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.192</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>240.5</v>
+        <v>41.95</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.82</v>
+        <v>0.48</v>
       </c>
       <c r="F46" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2.98</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>282</v>
+        <v>61.8</v>
       </c>
       <c r="E47" t="n">
-        <v>1.44</v>
+        <v>0.16</v>
       </c>
       <c r="F47" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,33 +2034,33 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.007</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>186.5</v>
+        <v>51.1</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,33 +2068,33 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.715</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>61</v>
+        <v>186.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.61</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>4.141</v>
+        <v>9.723000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>111</v>
+        <v>20.25</v>
       </c>
       <c r="E50" t="n">
-        <v>2.78</v>
+        <v>0.5</v>
       </c>
       <c r="F50" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,75 +2136,75 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.4</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>88.2</v>
+        <v>65.2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="F51" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.29</v>
+        <v>2.104</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>283</v>
+        <v>61.1</v>
       </c>
       <c r="E52" t="n">
-        <v>2.17</v>
+        <v>0.16</v>
       </c>
       <c r="F52" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1.019</v>
+        <v>3.698</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48.11</v>
+        <v>51.72</v>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>6.091</v>
+        <v>6.051</v>
       </c>
     </row>
     <row r="3">
@@ -2311,199 +2311,199 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36.95</v>
+        <v>49.93</v>
       </c>
       <c r="F3" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="G3" t="n">
-        <v>6.643</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34.05</v>
+        <v>41.94</v>
       </c>
       <c r="F4" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="G4" t="n">
-        <v>15.665</v>
+        <v>14.462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33.91</v>
+        <v>38.17</v>
       </c>
       <c r="F5" t="n">
-        <v>0.96</v>
+        <v>1.12</v>
       </c>
       <c r="G5" t="n">
-        <v>29.579</v>
+        <v>15.634</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32.02</v>
+        <v>33.07</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>4.251</v>
+        <v>37.69</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27.68</v>
+        <v>28.64</v>
       </c>
       <c r="F7" t="n">
-        <v>1.18</v>
+        <v>0.63</v>
       </c>
       <c r="G7" t="n">
-        <v>13.064</v>
+        <v>4.276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25.65</v>
+        <v>27.13</v>
       </c>
       <c r="F8" t="n">
-        <v>0.91</v>
+        <v>0.99</v>
       </c>
       <c r="G8" t="n">
-        <v>6.513</v>
+        <v>29.466</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24.27</v>
+        <v>26.15</v>
       </c>
       <c r="F9" t="n">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="G9" t="n">
-        <v>33.713</v>
+        <v>7.334</v>
       </c>
     </row>
     <row r="10">
@@ -2528,106 +2528,106 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.63</v>
+        <v>20.28</v>
       </c>
       <c r="F10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.53</v>
+        <v>17.45</v>
       </c>
       <c r="F11" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="G11" t="n">
-        <v>2.277</v>
+        <v>2.398</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.39</v>
+        <v>17.05</v>
       </c>
       <c r="F12" t="n">
-        <v>1.29</v>
+        <v>0.93</v>
       </c>
       <c r="G12" t="n">
-        <v>0.522</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.31</v>
+        <v>14.39</v>
       </c>
       <c r="F13" t="n">
-        <v>0.97</v>
+        <v>0.63</v>
       </c>
       <c r="G13" t="n">
-        <v>2.975</v>
+        <v>2.104</v>
       </c>
     </row>
     <row r="14">
@@ -2652,246 +2652,246 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.949999999999999</v>
+        <v>14.26</v>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>2.658</v>
+        <v>2.749</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.43</v>
+        <v>13.91</v>
       </c>
       <c r="F15" t="n">
-        <v>0.67</v>
+        <v>1.41</v>
       </c>
       <c r="G15" t="n">
-        <v>2.192</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.98</v>
+        <v>12.35</v>
       </c>
       <c r="F16" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="G16" t="n">
-        <v>0.552</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8.84</v>
+        <v>11.99</v>
       </c>
       <c r="F17" t="n">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="G17" t="n">
-        <v>1.459</v>
+        <v>10.951</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.69</v>
+        <v>10.69</v>
       </c>
       <c r="F18" t="n">
-        <v>0.84</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>10.276</v>
+        <v>2.346</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.539999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="F19" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="G19" t="n">
-        <v>10.09</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="G20" t="n">
-        <v>1.962</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G21" t="n">
-        <v>0.438</v>
+        <v>4.045</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2900,122 +2900,122 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8.050000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="F22" t="n">
-        <v>0.54</v>
+        <v>1.24</v>
       </c>
       <c r="G22" t="n">
-        <v>8.007</v>
+        <v>19.757</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.92</v>
+        <v>7.02</v>
       </c>
       <c r="F23" t="n">
-        <v>1.49</v>
+        <v>1.06</v>
       </c>
       <c r="G23" t="n">
-        <v>2.303</v>
+        <v>1.793</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.69</v>
+        <v>6.9</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="G24" t="n">
-        <v>4.81</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6.53</v>
+        <v>6.27</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="G25" t="n">
-        <v>2.455</v>
+        <v>9.723000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3024,649 +3024,649 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="G26" t="n">
-        <v>9.715</v>
+        <v>4.872</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6.17</v>
+        <v>5.36</v>
       </c>
       <c r="F27" t="n">
-        <v>0.85</v>
+        <v>1.49</v>
       </c>
       <c r="G27" t="n">
-        <v>3.658</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5.65</v>
+        <v>4.73</v>
       </c>
       <c r="F28" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="G28" t="n">
-        <v>0.702</v>
+        <v>45.524</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.44</v>
+        <v>3.02</v>
       </c>
       <c r="F29" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="G29" t="n">
-        <v>1.688</v>
+        <v>9.664</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.28</v>
+        <v>2.99</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1.878</v>
+        <v>32.766</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="F31" t="n">
-        <v>0.82</v>
+        <v>1.16</v>
       </c>
       <c r="G31" t="n">
-        <v>8.407999999999999</v>
+        <v>2.239</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.01</v>
+        <v>2.67</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="G32" t="n">
-        <v>0.144</v>
+        <v>7.423</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="F33" t="n">
-        <v>1.13</v>
+        <v>0.98</v>
       </c>
       <c r="G33" t="n">
-        <v>44.714</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="F34" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="G34" t="n">
-        <v>7.516</v>
+        <v>1.815</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4</v>
+        <v>8.257</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="F36" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="G36" t="n">
-        <v>1.116</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.32</v>
+        <v>-0.54</v>
       </c>
       <c r="F37" t="n">
-        <v>1.02</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>8.061</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.57</v>
+        <v>-0.82</v>
       </c>
       <c r="F38" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="G38" t="n">
-        <v>34.345</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.83</v>
+        <v>-1.11</v>
       </c>
       <c r="F39" t="n">
-        <v>0.83</v>
+        <v>1.19</v>
       </c>
       <c r="G39" t="n">
-        <v>22.565</v>
+        <v>8.337</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-0.86</v>
+        <v>-1.22</v>
       </c>
       <c r="F40" t="n">
-        <v>1.12</v>
+        <v>0.88</v>
       </c>
       <c r="G40" t="n">
-        <v>17.051</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.22</v>
+        <v>-1.64</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="G41" t="n">
-        <v>3.872</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-1.23</v>
+        <v>-1.69</v>
       </c>
       <c r="F42" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="G42" t="n">
-        <v>0.382</v>
+        <v>21.672</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2</v>
+        <v>-2.86</v>
       </c>
       <c r="F43" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="G43" t="n">
-        <v>0.737</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.21</v>
+        <v>-3.23</v>
       </c>
       <c r="F44" t="n">
-        <v>0.59</v>
+        <v>0.95</v>
       </c>
       <c r="G44" t="n">
-        <v>3.913</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.58</v>
+        <v>-3.39</v>
       </c>
       <c r="F45" t="n">
-        <v>1.23</v>
+        <v>0.76</v>
       </c>
       <c r="G45" t="n">
-        <v>7.966</v>
+        <v>2.808</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3.6</v>
+        <v>-5.27</v>
       </c>
       <c r="F46" t="n">
-        <v>1.03</v>
+        <v>0.57</v>
       </c>
       <c r="G46" t="n">
-        <v>0.448</v>
+        <v>3.698</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3675,106 +3675,106 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-4.37</v>
+        <v>-6.02</v>
       </c>
       <c r="F47" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="G47" t="n">
-        <v>2.98</v>
+        <v>3.361</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-4.69</v>
+        <v>-6.51</v>
       </c>
       <c r="F48" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>4.141</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-6.09</v>
+        <v>-7.07</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="G49" t="n">
-        <v>0.982</v>
+        <v>2.502</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-6.15</v>
+        <v>-7.82</v>
       </c>
       <c r="F50" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="G50" t="n">
-        <v>3.079</v>
+        <v>7.717</v>
       </c>
     </row>
     <row r="51">
@@ -3799,13 +3799,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-9.44</v>
+        <v>-9.49</v>
       </c>
       <c r="F51" t="n">
-        <v>0.49</v>
+        <v>0.64</v>
       </c>
       <c r="G51" t="n">
-        <v>1.019</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-15.98</v>
+        <v>-17.99</v>
       </c>
       <c r="F52" t="n">
-        <v>1.29</v>
+        <v>0.97</v>
       </c>
       <c r="G52" t="n">
-        <v>0.29</v>
+        <v>0.288</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.11</v>
+        <v>51.72</v>
       </c>
       <c r="C2" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="D2" t="n">
-        <v>6.091</v>
+        <v>6.051</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.02</v>
+        <v>33.07</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.251</v>
+        <v>37.69</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,55 +3921,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.65</v>
+        <v>29.09333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.91</v>
+        <v>1.026666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>6.513</v>
+        <v>23.209</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.3</v>
+        <v>28.64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9533333333333333</v>
+        <v>0.63</v>
       </c>
       <c r="D5" t="n">
-        <v>22.708</v>
+        <v>4.276</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.27</v>
+        <v>26.15</v>
       </c>
       <c r="C6" t="n">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="D6" t="n">
-        <v>33.713</v>
+        <v>7.334</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3978,17 +3978,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.145</v>
+        <v>20.415</v>
       </c>
       <c r="C7" t="n">
-        <v>1.045</v>
+        <v>1.19</v>
       </c>
       <c r="D7" t="n">
-        <v>74.29300000000001</v>
+        <v>22.799</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.63</v>
+        <v>20.28</v>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4016,55 +4016,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.53</v>
+        <v>15.93</v>
       </c>
       <c r="C9" t="n">
-        <v>1.29</v>
+        <v>1.035</v>
       </c>
       <c r="D9" t="n">
-        <v>2.277</v>
+        <v>74.99000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.05</v>
+        <v>14.39</v>
       </c>
       <c r="C10" t="n">
-        <v>1.205</v>
+        <v>0.63</v>
       </c>
       <c r="D10" t="n">
-        <v>21.03</v>
+        <v>2.104</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.43</v>
+        <v>13.91</v>
       </c>
       <c r="C11" t="n">
-        <v>0.67</v>
+        <v>1.41</v>
       </c>
       <c r="D11" t="n">
-        <v>2.192</v>
+        <v>2.31</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,20 +4073,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.4</v>
+        <v>12.99</v>
       </c>
       <c r="C12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="D12" t="n">
-        <v>9.946999999999999</v>
+        <v>6.443</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.69</v>
+        <v>11.99</v>
       </c>
       <c r="C13" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="D13" t="n">
-        <v>10.276</v>
+        <v>10.951</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,36 +4111,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.539999999999999</v>
+        <v>11.974</v>
       </c>
       <c r="C14" t="n">
-        <v>0.93</v>
+        <v>1.058</v>
       </c>
       <c r="D14" t="n">
-        <v>10.09</v>
+        <v>10.15</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.02</v>
       </c>
       <c r="C15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="D15" t="n">
-        <v>0.438</v>
+        <v>1.793</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,20 +4149,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.295</v>
+        <v>6.9</v>
       </c>
       <c r="C16" t="n">
-        <v>0.84</v>
+        <v>1.13</v>
       </c>
       <c r="D16" t="n">
-        <v>5.62</v>
+        <v>0.446</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.65</v>
+        <v>5.36</v>
       </c>
       <c r="C17" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="D17" t="n">
-        <v>0.702</v>
+        <v>0.704</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,36 +4187,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.44</v>
+        <v>4.295</v>
       </c>
       <c r="C18" t="n">
-        <v>1.08</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>1.688</v>
+        <v>27.557</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.28</v>
+        <v>3.02</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="D19" t="n">
-        <v>1.878</v>
+        <v>9.664</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4225,74 +4225,74 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.595</v>
+        <v>2.99</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="D20" t="n">
-        <v>25.058</v>
+        <v>32.766</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.425</v>
+        <v>2.49</v>
       </c>
       <c r="C21" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="D21" t="n">
-        <v>10.516</v>
+        <v>0.144</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.13</v>
+        <v>2.1075</v>
       </c>
       <c r="C22" t="n">
-        <v>0.82</v>
+        <v>0.7625</v>
       </c>
       <c r="D22" t="n">
-        <v>8.407999999999999</v>
+        <v>22.984</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.01</v>
+        <v>1.11</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="D23" t="n">
-        <v>0.144</v>
+        <v>1.815</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4301,39 +4301,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.2275</v>
+        <v>0.7</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7825</v>
+        <v>0.95</v>
       </c>
       <c r="D24" t="n">
-        <v>23.023</v>
+        <v>8.257</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.57</v>
+        <v>-1.43</v>
       </c>
       <c r="C25" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="D25" t="n">
-        <v>34.345</v>
+        <v>1.075</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.83</v>
+        <v>-1.69</v>
       </c>
       <c r="C26" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="D26" t="n">
-        <v>22.565</v>
+        <v>21.672</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,36 +4358,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.22</v>
+        <v>-2.535</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9</v>
+        <v>1.135</v>
       </c>
       <c r="D27" t="n">
-        <v>3.872</v>
+        <v>9.956</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.615</v>
+        <v>-2.819999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9299999999999999</v>
+        <v>1.145</v>
       </c>
       <c r="D28" t="n">
-        <v>1.119</v>
+        <v>0.8360000000000001</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -4396,36 +4396,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.795</v>
+        <v>-2.86</v>
       </c>
       <c r="C29" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-3.6</v>
+        <v>-3.23</v>
       </c>
       <c r="C30" t="n">
-        <v>1.03</v>
+        <v>0.95</v>
       </c>
       <c r="D30" t="n">
-        <v>0.448</v>
+        <v>3.758</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-4.09</v>
+        <v>-4.893333333333334</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D31" t="n">
-        <v>11.034</v>
+        <v>9.867000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-5.076666666666667</v>
+        <v>-5.7</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="D32" t="n">
-        <v>5.214</v>
+        <v>4.289</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
@@ -4572,38 +4572,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2140</v>
+        <v>2150</v>
       </c>
       <c r="E2" t="n">
-        <v>8.630000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="F2" t="n">
-        <v>3.13</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="n">
-        <v>48.18</v>
+        <v>51.91</v>
       </c>
       <c r="H2" t="n">
-        <v>8.237</v>
+        <v>11.31</v>
       </c>
       <c r="I2" t="n">
-        <v>74.7</v>
+        <v>77.5</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>4.31</v>
+        <v>4.19</v>
       </c>
       <c r="L2" t="n">
-        <v>69.2</v>
+        <v>19.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4710</v>
+        <v>5010</v>
       </c>
       <c r="E3" t="n">
-        <v>4.67</v>
+        <v>6.37</v>
       </c>
       <c r="F3" t="n">
-        <v>24.27</v>
+        <v>33.07</v>
       </c>
       <c r="G3" t="n">
-        <v>72.11</v>
+        <v>70.62</v>
       </c>
       <c r="H3" t="n">
-        <v>199.215</v>
+        <v>207.9773</v>
       </c>
       <c r="I3" t="n">
-        <v>77.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>89.7</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>4.77</v>
+        <v>4.39</v>
       </c>
       <c r="L3" t="n">
-        <v>38.3</v>
+        <v>48.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88.2</v>
+        <v>86.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-1.93</v>
       </c>
       <c r="F4" t="n">
-        <v>-15.98</v>
+        <v>-17.99</v>
       </c>
       <c r="G4" t="n">
-        <v>20.91</v>
+        <v>14.09</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.6615</v>
+        <v>-8.059799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="J4" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6.01</v>
+        <v>5.97</v>
       </c>
       <c r="L4" t="n">
-        <v>-33</v>
+        <v>-23.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.29</v>
+        <v>0.97</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E5" t="n">
-        <v>3.46</v>
+        <v>-1.91</v>
       </c>
       <c r="F5" t="n">
-        <v>48.11</v>
+        <v>51.72</v>
       </c>
       <c r="G5" t="n">
-        <v>69.09999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="H5" t="n">
-        <v>28.565</v>
+        <v>27.8535</v>
       </c>
       <c r="I5" t="n">
-        <v>84.2</v>
+        <v>77.8</v>
       </c>
       <c r="J5" t="n">
-        <v>98.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="K5" t="n">
-        <v>7.59</v>
+        <v>7.41</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.2</v>
+        <v>-31.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="E6" t="n">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
       <c r="F6" t="n">
-        <v>36.95</v>
+        <v>49.93</v>
       </c>
       <c r="G6" t="n">
-        <v>66.12</v>
+        <v>61.21</v>
       </c>
       <c r="H6" t="n">
-        <v>39.6555</v>
+        <v>38.668</v>
       </c>
       <c r="I6" t="n">
-        <v>79.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>6.9</v>
+        <v>6.64</v>
       </c>
       <c r="L6" t="n">
-        <v>67.40000000000001</v>
+        <v>24.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>250.5</v>
+        <v>250</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>2.67</v>
       </c>
       <c r="G7" t="n">
-        <v>50.65</v>
+        <v>40.91</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1339</v>
+        <v>-0.8758</v>
       </c>
       <c r="I7" t="n">
-        <v>53</v>
+        <v>47.2</v>
       </c>
       <c r="J7" t="n">
-        <v>42.1</v>
+        <v>36.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>48.1</v>
+        <v>-43.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>103</v>
+        <v>105.5</v>
       </c>
       <c r="E2" t="n">
-        <v>9.57</v>
+        <v>2.43</v>
       </c>
       <c r="F2" t="n">
-        <v>271</v>
+        <v>452</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.398</v>
+        <v>3.033</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>301.5</v>
+        <v>203</v>
       </c>
       <c r="E3" t="n">
-        <v>3.43</v>
+        <v>6.28</v>
       </c>
       <c r="F3" t="n">
-        <v>230</v>
+        <v>425</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7.334</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>292.5</v>
+        <v>317</v>
       </c>
       <c r="E4" t="n">
-        <v>2.99</v>
+        <v>5.14</v>
       </c>
       <c r="F4" t="n">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.045</v>
+        <v>8.664999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1875</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>8.07</v>
+        <v>0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>19.757</v>
+        <v>1.185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>68.8</v>
+        <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>2.08</v>
+        <v>4.56</v>
       </c>
       <c r="F6" t="n">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.05</v>
+        <v>2.525</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7615</v>
+        <v>254.5</v>
       </c>
       <c r="E7" t="n">
-        <v>6.5</v>
+        <v>-3.42</v>
       </c>
       <c r="F7" t="n">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14.462</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="E8" t="n">
-        <v>0.26</v>
+        <v>0.58</v>
       </c>
       <c r="F8" t="n">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.548</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5010</v>
+        <v>971</v>
       </c>
       <c r="E9" t="n">
-        <v>6.37</v>
+        <v>4.3</v>
       </c>
       <c r="F9" t="n">
-        <v>149</v>
+        <v>214</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>37.69</v>
+        <v>8.499000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>572</v>
+        <v>1900</v>
       </c>
       <c r="E10" t="n">
-        <v>2.88</v>
+        <v>1.33</v>
       </c>
       <c r="F10" t="n">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.19</v>
+        <v>20.502</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>740</v>
+        <v>5180</v>
       </c>
       <c r="E11" t="n">
-        <v>1.79</v>
+        <v>3.39</v>
       </c>
       <c r="F11" t="n">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,67 +810,67 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.793</v>
+        <v>40.456</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>172</v>
+        <v>3715</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="F12" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.31</v>
+        <v>8.872</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2150</v>
+        <v>755</v>
       </c>
       <c r="E13" t="n">
-        <v>0.47</v>
+        <v>2.03</v>
       </c>
       <c r="F13" t="n">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,67 +878,67 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8.257</v>
+        <v>1.899</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.65</v>
+        <v>160</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.53</v>
+        <v>1.91</v>
       </c>
       <c r="F14" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.45</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>263.5</v>
+        <v>693</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.59</v>
+        <v>4.52</v>
       </c>
       <c r="F15" t="n">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.446</v>
+        <v>11.853</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>663</v>
+        <v>547</v>
       </c>
       <c r="E16" t="n">
-        <v>3.92</v>
+        <v>-4.37</v>
       </c>
       <c r="F16" t="n">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,169 +980,169 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10.951</v>
+        <v>7.269</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>186.5</v>
+        <v>2185</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.53</v>
+        <v>1.63</v>
       </c>
       <c r="F17" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.239</v>
+        <v>8.497999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>548</v>
+        <v>292</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.79</v>
+        <v>-0.17</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.815</v>
+        <v>4.209</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2480</v>
+        <v>180.5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8100000000000001</v>
+        <v>-3.22</v>
       </c>
       <c r="F19" t="n">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>45.524</v>
+        <v>9.521000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>157</v>
+        <v>253</v>
       </c>
       <c r="E20" t="n">
-        <v>0.64</v>
+        <v>1.2</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>29.466</v>
+        <v>7.546</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>931</v>
+        <v>84.2</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.38</v>
+        <v>-2.66</v>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,67 +1150,67 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7.717</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29.25</v>
+        <v>557</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.18</v>
+        <v>1.64</v>
       </c>
       <c r="F22" t="n">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.144</v>
+        <v>1.787</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>120</v>
+        <v>18.65</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,237 +1218,237 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.758</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1475</v>
+        <v>20.5</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.34</v>
+        <v>1.23</v>
       </c>
       <c r="F24" t="n">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.704</v>
+        <v>0.358</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>154.5</v>
+        <v>2460</v>
       </c>
       <c r="E25" t="n">
-        <v>2.66</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3.065</v>
+        <v>45.961</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>86.5</v>
+        <v>3110</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.93</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.288</v>
+        <v>4.793</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3665</v>
+        <v>42.5</v>
       </c>
       <c r="E27" t="n">
-        <v>3.53</v>
+        <v>1.31</v>
       </c>
       <c r="F27" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8.337</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>389</v>
+        <v>501</v>
       </c>
       <c r="E28" t="n">
-        <v>2.78</v>
+        <v>2.14</v>
       </c>
       <c r="F28" t="n">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.502</v>
+        <v>16.401</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>490.5</v>
+        <v>497</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.9</v>
+        <v>-3.68</v>
       </c>
       <c r="F29" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>15.634</v>
+        <v>31.484</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72.7</v>
+        <v>1475</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>9.664</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>308</v>
+        <v>154.5</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.91</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6.051</v>
+        <v>2.843</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>286</v>
+        <v>284.5</v>
       </c>
       <c r="E32" t="n">
-        <v>1.06</v>
+        <v>-1.39</v>
       </c>
       <c r="F32" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,203 +1524,203 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.82</v>
+        <v>6.933</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>113</v>
+        <v>384</v>
       </c>
       <c r="E33" t="n">
-        <v>2.26</v>
+        <v>-1.29</v>
       </c>
       <c r="F33" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.749</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>70.40000000000001</v>
+        <v>171</v>
       </c>
       <c r="E34" t="n">
-        <v>1.29</v>
+        <v>-1.72</v>
       </c>
       <c r="F34" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.346</v>
+        <v>21.334</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.06</v>
+        <v>-1.62</v>
       </c>
       <c r="F35" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>21.672</v>
+        <v>6.093</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2830</v>
+        <v>118</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.53</v>
+        <v>-1.67</v>
       </c>
       <c r="F36" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4.276</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>288.5</v>
+        <v>342</v>
       </c>
       <c r="E37" t="n">
-        <v>2.3</v>
+        <v>-0.73</v>
       </c>
       <c r="F37" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7.8</v>
+        <v>4.891</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>344.5</v>
+        <v>50.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.44</v>
+        <v>-1.17</v>
       </c>
       <c r="F38" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,101 +1728,101 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4.872</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>250</v>
+        <v>71.8</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.2</v>
+        <v>-1.24</v>
       </c>
       <c r="F39" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7.423</v>
+        <v>9.324</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>516</v>
+        <v>285</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.71</v>
+        <v>-0.35</v>
       </c>
       <c r="F40" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>32.766</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>242</v>
+        <v>112</v>
       </c>
       <c r="E41" t="n">
-        <v>0.62</v>
+        <v>-0.88</v>
       </c>
       <c r="F41" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.808</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>117</v>
+        <v>242.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.9</v>
+        <v>0.21</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,41 +1864,41 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.361</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>27.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.37</v>
+        <v>-0.92</v>
       </c>
       <c r="F43" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.552</v>
+        <v>2.083</v>
       </c>
     </row>
     <row r="44">
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>109.5</v>
+        <v>110</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.35</v>
+        <v>0.46</v>
       </c>
       <c r="F44" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,67 +1932,67 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.385</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>276.5</v>
+        <v>61.2</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.18</v>
+        <v>-0.97</v>
       </c>
       <c r="F45" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.967</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>41.95</v>
+        <v>272</v>
       </c>
       <c r="E46" t="n">
-        <v>0.48</v>
+        <v>-1.63</v>
       </c>
       <c r="F46" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,67 +2000,67 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.714</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>61.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>0.16</v>
+        <v>-1.14</v>
       </c>
       <c r="F47" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.966</v>
+        <v>2.306</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>51.1</v>
+        <v>27.05</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0.55</v>
       </c>
       <c r="F48" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,101 +2068,101 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.438</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>186.5</v>
+        <v>29.25</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9.723000000000001</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>20.25</v>
+        <v>8375</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5</v>
+        <v>9.98</v>
       </c>
       <c r="F50" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.361</v>
+        <v>15.494</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>65.2</v>
+        <v>116.5</v>
       </c>
       <c r="E51" t="n">
-        <v>0.31</v>
+        <v>-0.43</v>
       </c>
       <c r="F51" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.104</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="52">
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>61.1</v>
+        <v>60.8</v>
       </c>
       <c r="E52" t="n">
-        <v>0.16</v>
+        <v>-0.49</v>
       </c>
       <c r="F52" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.698</v>
+        <v>3.146</v>
       </c>
     </row>
   </sheetData>
@@ -2261,513 +2261,513 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>51.72</v>
+        <v>50.36</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="G2" t="n">
-        <v>6.051</v>
+        <v>15.494</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>49.93</v>
+        <v>48.89</v>
       </c>
       <c r="F3" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>7.19</v>
+        <v>6.093</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41.94</v>
+        <v>41.69</v>
       </c>
       <c r="F4" t="n">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="G4" t="n">
-        <v>14.462</v>
+        <v>4.793</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38.17</v>
+        <v>38.69</v>
       </c>
       <c r="F5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
-        <v>15.634</v>
+        <v>40.456</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33.07</v>
+        <v>32.36</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>1.51</v>
       </c>
       <c r="G6" t="n">
-        <v>37.69</v>
+        <v>8.664999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28.64</v>
+        <v>32.19</v>
       </c>
       <c r="F7" t="n">
-        <v>0.63</v>
+        <v>1.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.276</v>
+        <v>16.401</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>27.13</v>
+        <v>30.39</v>
       </c>
       <c r="F8" t="n">
-        <v>0.99</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>29.466</v>
+        <v>7.269</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26.15</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G9" t="n">
-        <v>7.334</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.28</v>
+        <v>20.57</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.78</v>
       </c>
       <c r="G10" t="n">
-        <v>1.05</v>
+        <v>3.033</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.45</v>
+        <v>18.02</v>
       </c>
       <c r="F11" t="n">
-        <v>1.19</v>
+        <v>1.84</v>
       </c>
       <c r="G11" t="n">
-        <v>2.398</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.05</v>
+        <v>17.26</v>
       </c>
       <c r="F12" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="G12" t="n">
-        <v>3.065</v>
+        <v>11.853</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14.39</v>
+        <v>15.6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.63</v>
+        <v>1.37</v>
       </c>
       <c r="G13" t="n">
-        <v>2.104</v>
+        <v>1.185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.26</v>
+        <v>14.95</v>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
-        <v>2.749</v>
+        <v>2.517</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13.91</v>
+        <v>11.76</v>
       </c>
       <c r="F15" t="n">
-        <v>1.41</v>
+        <v>0.64</v>
       </c>
       <c r="G15" t="n">
-        <v>2.31</v>
+        <v>2.083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.35</v>
+        <v>11.11</v>
       </c>
       <c r="F16" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="G16" t="n">
-        <v>0.548</v>
+        <v>20.502</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.99</v>
+        <v>9.19</v>
       </c>
       <c r="F17" t="n">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
-        <v>10.951</v>
+        <v>2.843</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2776,29 +2776,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10.69</v>
+        <v>8.74</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.346</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.07</v>
+        <v>7.98</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="G19" t="n">
-        <v>1.438</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2838,199 +2838,199 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.800000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="G20" t="n">
-        <v>0.552</v>
+        <v>2.306</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8.529999999999999</v>
+        <v>7.45</v>
       </c>
       <c r="F21" t="n">
-        <v>1.09</v>
+        <v>0.91</v>
       </c>
       <c r="G21" t="n">
-        <v>4.045</v>
+        <v>1.416</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8.07</v>
+        <v>7.1</v>
       </c>
       <c r="F22" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="G22" t="n">
-        <v>19.757</v>
+        <v>1.899</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7.02</v>
+        <v>6.76</v>
       </c>
       <c r="F23" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="G23" t="n">
-        <v>1.793</v>
+        <v>4.209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.9</v>
+        <v>6.56</v>
       </c>
       <c r="F24" t="n">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="G24" t="n">
-        <v>0.446</v>
+        <v>2.525</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6.27</v>
+        <v>4.8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="G25" t="n">
-        <v>9.723000000000001</v>
+        <v>8.497999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="F26" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="G26" t="n">
-        <v>4.872</v>
+        <v>9.324</v>
       </c>
     </row>
     <row r="27">
@@ -3055,292 +3055,292 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5.36</v>
+        <v>4.24</v>
       </c>
       <c r="F27" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="G27" t="n">
-        <v>0.704</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.73</v>
+        <v>4.12</v>
       </c>
       <c r="F28" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="G28" t="n">
-        <v>45.524</v>
+        <v>7.546</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.02</v>
+        <v>4.11</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="G29" t="n">
-        <v>9.664</v>
+        <v>4.891</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7</v>
+        <v>1.12</v>
       </c>
       <c r="G30" t="n">
-        <v>32.766</v>
+        <v>45.961</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="F31" t="n">
-        <v>1.16</v>
+        <v>0.95</v>
       </c>
       <c r="G31" t="n">
-        <v>2.239</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.67</v>
+        <v>1.19</v>
       </c>
       <c r="F32" t="n">
-        <v>0.82</v>
+        <v>1.42</v>
       </c>
       <c r="G32" t="n">
-        <v>7.423</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.49</v>
+        <v>1.12</v>
       </c>
       <c r="F33" t="n">
-        <v>0.98</v>
+        <v>0.73</v>
       </c>
       <c r="G33" t="n">
-        <v>0.144</v>
+        <v>9.521000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="F34" t="n">
         <v>0.98</v>
       </c>
       <c r="G34" t="n">
-        <v>1.815</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.7</v>
+        <v>0.49</v>
       </c>
       <c r="F35" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="G35" t="n">
-        <v>8.257</v>
+        <v>0.358</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="G36" t="n">
-        <v>7.8</v>
+        <v>1.787</v>
       </c>
     </row>
     <row r="37">
@@ -3365,308 +3365,308 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.54</v>
+        <v>-0.18</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="G37" t="n">
-        <v>0.967</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.82</v>
+        <v>-0.92</v>
       </c>
       <c r="F38" t="n">
-        <v>0.62</v>
+        <v>1.3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.385</v>
+        <v>8.499000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.11</v>
+        <v>-1.42</v>
       </c>
       <c r="F39" t="n">
-        <v>1.19</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>8.337</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.22</v>
+        <v>-2.1</v>
       </c>
       <c r="F40" t="n">
-        <v>0.88</v>
+        <v>1.03</v>
       </c>
       <c r="G40" t="n">
-        <v>0.361</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.64</v>
+        <v>-2.55</v>
       </c>
       <c r="F41" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
-        <v>0.714</v>
+        <v>31.484</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-1.69</v>
+        <v>-3.13</v>
       </c>
       <c r="F42" t="n">
-        <v>0.77</v>
+        <v>1.23</v>
       </c>
       <c r="G42" t="n">
-        <v>21.672</v>
+        <v>8.872</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.86</v>
+        <v>-3.28</v>
       </c>
       <c r="F43" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="G43" t="n">
-        <v>0.45</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.23</v>
+        <v>-3.39</v>
       </c>
       <c r="F44" t="n">
-        <v>0.95</v>
+        <v>0.64</v>
       </c>
       <c r="G44" t="n">
-        <v>3.758</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.39</v>
+        <v>-3.88</v>
       </c>
       <c r="F45" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="G45" t="n">
-        <v>2.808</v>
+        <v>2.238</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-5.27</v>
+        <v>-3.89</v>
       </c>
       <c r="F46" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="G46" t="n">
-        <v>3.698</v>
+        <v>6.933</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3675,60 +3675,60 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-6.02</v>
+        <v>-4.4</v>
       </c>
       <c r="F47" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="G47" t="n">
-        <v>3.361</v>
+        <v>3.146</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-6.51</v>
+        <v>-4.47</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.966</v>
+        <v>21.334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3737,75 +3737,75 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-7.07</v>
+        <v>-4.68</v>
       </c>
       <c r="F49" t="n">
         <v>0.75</v>
       </c>
       <c r="G49" t="n">
-        <v>2.502</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-7.82</v>
+        <v>-6.42</v>
       </c>
       <c r="F50" t="n">
-        <v>1.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>7.717</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-9.49</v>
+        <v>-7.91</v>
       </c>
       <c r="F51" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="G51" t="n">
-        <v>0.82</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-17.99</v>
+        <v>-21.28</v>
       </c>
       <c r="F52" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="G52" t="n">
-        <v>0.288</v>
+        <v>0.286</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.72</v>
+        <v>48.89</v>
       </c>
       <c r="C2" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="D2" t="n">
-        <v>6.051</v>
+        <v>6.093</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33.07</v>
+        <v>41.69</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="D3" t="n">
-        <v>37.69</v>
+        <v>4.793</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,36 +3921,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.09333333333333</v>
+        <v>38.69</v>
       </c>
       <c r="C4" t="n">
-        <v>1.026666666666667</v>
+        <v>1.09</v>
       </c>
       <c r="D4" t="n">
-        <v>23.209</v>
+        <v>40.456</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.64</v>
+        <v>32.36</v>
       </c>
       <c r="C5" t="n">
-        <v>0.63</v>
+        <v>1.51</v>
       </c>
       <c r="D5" t="n">
-        <v>4.276</v>
+        <v>8.664999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,55 +3959,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.15</v>
+        <v>23.615</v>
       </c>
       <c r="C6" t="n">
-        <v>1.17</v>
+        <v>1.145</v>
       </c>
       <c r="D6" t="n">
-        <v>7.334</v>
+        <v>24.366</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.415</v>
+        <v>19.73</v>
       </c>
       <c r="C7" t="n">
-        <v>1.19</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>22.799</v>
+        <v>24.05</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20.28</v>
+        <v>17.26</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="D8" t="n">
-        <v>1.05</v>
+        <v>11.853</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4016,39 +4016,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.93</v>
+        <v>15.6</v>
       </c>
       <c r="C9" t="n">
-        <v>1.035</v>
+        <v>1.37</v>
       </c>
       <c r="D9" t="n">
-        <v>74.99000000000001</v>
+        <v>1.185</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.39</v>
+        <v>15.4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="D10" t="n">
-        <v>2.104</v>
+        <v>77.271</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.91</v>
+        <v>14.95</v>
       </c>
       <c r="C11" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="D11" t="n">
-        <v>2.31</v>
+        <v>2.517</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12.99</v>
+        <v>13.665</v>
       </c>
       <c r="C12" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="D12" t="n">
-        <v>6.443</v>
+        <v>7.241999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -4092,17 +4092,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11.99</v>
+        <v>11.76</v>
       </c>
       <c r="C13" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="D13" t="n">
-        <v>10.951</v>
+        <v>2.083</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.974</v>
+        <v>8.254000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>1.058</v>
+        <v>1.006</v>
       </c>
       <c r="D14" t="n">
-        <v>10.15</v>
+        <v>9.768000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
@@ -4134,13 +4134,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.02</v>
+        <v>7.1</v>
       </c>
       <c r="C15" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="D15" t="n">
-        <v>1.793</v>
+        <v>1.899</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,17 +4149,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="C16" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="D16" t="n">
-        <v>0.446</v>
+        <v>8.497999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,17 +4168,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.36</v>
+        <v>4.4</v>
       </c>
       <c r="C17" t="n">
-        <v>1.49</v>
+        <v>0.88</v>
       </c>
       <c r="D17" t="n">
-        <v>0.704</v>
+        <v>9.324</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,58 +4187,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.295</v>
+        <v>4.24</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9199999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="D18" t="n">
-        <v>27.557</v>
+        <v>0.714</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.02</v>
+        <v>3.609999999999999</v>
       </c>
       <c r="C19" t="n">
         <v>0.95</v>
       </c>
       <c r="D19" t="n">
-        <v>9.664</v>
+        <v>27.435</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7</v>
+        <v>1.355</v>
       </c>
       <c r="D20" t="n">
-        <v>32.766</v>
+        <v>11.024</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.49</v>
+        <v>1.92</v>
       </c>
       <c r="C21" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="D21" t="n">
         <v>0.144</v>
@@ -4263,153 +4263,153 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1075</v>
+        <v>1.19</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7625</v>
+        <v>1.42</v>
       </c>
       <c r="D22" t="n">
-        <v>22.984</v>
+        <v>0.478</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.11</v>
+        <v>0.7325000000000002</v>
       </c>
       <c r="C23" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="D23" t="n">
-        <v>1.815</v>
+        <v>22.905</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C24" t="n">
-        <v>0.95</v>
+        <v>0.925</v>
       </c>
       <c r="D24" t="n">
-        <v>8.257</v>
+        <v>1.096</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.43</v>
+        <v>0.36</v>
       </c>
       <c r="C25" t="n">
-        <v>0.95</v>
+        <v>1.02</v>
       </c>
       <c r="D25" t="n">
-        <v>1.075</v>
+        <v>1.787</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.69</v>
+        <v>-1.630000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.77</v>
+        <v>1.385</v>
       </c>
       <c r="D26" t="n">
-        <v>21.672</v>
+        <v>1.01</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.535</v>
+        <v>-2.1</v>
       </c>
       <c r="C27" t="n">
-        <v>1.135</v>
+        <v>1.03</v>
       </c>
       <c r="D27" t="n">
-        <v>9.956</v>
+        <v>0.455</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.819999999999999</v>
+        <v>-2.55</v>
       </c>
       <c r="C28" t="n">
-        <v>1.145</v>
+        <v>0.8</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8360000000000001</v>
+        <v>31.484</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.86</v>
+        <v>-2.913333333333334</v>
       </c>
       <c r="C29" t="n">
-        <v>1.05</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="D29" t="n">
-        <v>0.45</v>
+        <v>3.889</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-3.23</v>
+        <v>-3.28</v>
       </c>
       <c r="C30" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="D30" t="n">
-        <v>3.758</v>
+        <v>3.641</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4434,36 +4434,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-4.893333333333334</v>
+        <v>-4.47</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>9.867000000000001</v>
+        <v>21.334</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-5.7</v>
+        <v>-4.576666666666667</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>4.289</v>
+        <v>8.619</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2150</v>
+        <v>2185</v>
       </c>
       <c r="E2" t="n">
-        <v>0.47</v>
+        <v>1.63</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="G2" t="n">
-        <v>51.91</v>
+        <v>59.52</v>
       </c>
       <c r="H2" t="n">
-        <v>11.31</v>
+        <v>24.7338</v>
       </c>
       <c r="I2" t="n">
-        <v>77.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>19.3</v>
+        <v>38.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,38 +4624,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5010</v>
+        <v>5180</v>
       </c>
       <c r="E3" t="n">
-        <v>6.37</v>
+        <v>3.39</v>
       </c>
       <c r="F3" t="n">
-        <v>33.07</v>
+        <v>38.69</v>
       </c>
       <c r="G3" t="n">
-        <v>70.62</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>207.9773</v>
+        <v>244.8894</v>
       </c>
       <c r="I3" t="n">
-        <v>94.09999999999999</v>
+        <v>100.4</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>86.5</v>
+        <v>84.2</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.93</v>
+        <v>-2.66</v>
       </c>
       <c r="F4" t="n">
-        <v>-17.99</v>
+        <v>-21.28</v>
       </c>
       <c r="G4" t="n">
-        <v>14.09</v>
+        <v>13.96</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.059799999999999</v>
+        <v>-8.139099999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5.97</v>
+        <v>6.11</v>
       </c>
       <c r="L4" t="n">
-        <v>-23.4</v>
+        <v>25.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.91</v>
+        <v>-1.62</v>
       </c>
       <c r="F5" t="n">
-        <v>51.72</v>
+        <v>48.89</v>
       </c>
       <c r="G5" t="n">
-        <v>63.8</v>
+        <v>62.32</v>
       </c>
       <c r="H5" t="n">
-        <v>27.8535</v>
+        <v>27.4591</v>
       </c>
       <c r="I5" t="n">
-        <v>77.8</v>
+        <v>72.5</v>
       </c>
       <c r="J5" t="n">
-        <v>90.5</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>7.41</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>-31.5</v>
+        <v>-21.8</v>
       </c>
       <c r="M5" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>572</v>
+        <v>547</v>
       </c>
       <c r="E6" t="n">
-        <v>2.88</v>
+        <v>-4.37</v>
       </c>
       <c r="F6" t="n">
-        <v>49.93</v>
+        <v>30.39</v>
       </c>
       <c r="G6" t="n">
-        <v>61.21</v>
+        <v>51.13</v>
       </c>
       <c r="H6" t="n">
-        <v>38.668</v>
+        <v>37.8032</v>
       </c>
       <c r="I6" t="n">
-        <v>86.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>65.3</v>
       </c>
       <c r="K6" t="n">
-        <v>6.64</v>
+        <v>6.84</v>
       </c>
       <c r="L6" t="n">
-        <v>24.4</v>
+        <v>40.9</v>
       </c>
       <c r="M6" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.67</v>
+        <v>4.12</v>
       </c>
       <c r="G7" t="n">
-        <v>40.91</v>
+        <v>53.23</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8758</v>
+        <v>-0.3943</v>
       </c>
       <c r="I7" t="n">
-        <v>47.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>36.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="L7" t="n">
-        <v>-43.7</v>
+        <v>29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>105.5</v>
+        <v>107</v>
       </c>
       <c r="E2" t="n">
-        <v>2.43</v>
+        <v>1.42</v>
       </c>
       <c r="F2" t="n">
-        <v>452</v>
+        <v>353</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.033</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>203</v>
+        <v>950</v>
       </c>
       <c r="E3" t="n">
-        <v>6.28</v>
+        <v>-2.16</v>
       </c>
       <c r="F3" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.724</v>
+        <v>9.196</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>317</v>
+        <v>42.85</v>
       </c>
       <c r="E4" t="n">
-        <v>5.14</v>
+        <v>0.82</v>
       </c>
       <c r="F4" t="n">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.664999999999999</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68.90000000000001</v>
+        <v>3305</v>
       </c>
       <c r="E5" t="n">
-        <v>0.15</v>
+        <v>6.27</v>
       </c>
       <c r="F5" t="n">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.185</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E6" t="n">
-        <v>4.56</v>
+        <v>0.49</v>
       </c>
       <c r="F6" t="n">
-        <v>258</v>
+        <v>199</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.525</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>254.5</v>
+        <v>20.45</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.42</v>
+        <v>-0.24</v>
       </c>
       <c r="F7" t="n">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.478</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>173</v>
+        <v>761</v>
       </c>
       <c r="E8" t="n">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="F8" t="n">
-        <v>223</v>
+        <v>181</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.517</v>
+        <v>2.055</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>971</v>
+        <v>2215</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3</v>
+        <v>1.37</v>
       </c>
       <c r="F9" t="n">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8.499000000000001</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1900</v>
+        <v>304</v>
       </c>
       <c r="E10" t="n">
-        <v>1.33</v>
+        <v>-4.1</v>
       </c>
       <c r="F10" t="n">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>20.502</v>
+        <v>8.651</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5180</v>
+        <v>256</v>
       </c>
       <c r="E11" t="n">
-        <v>3.39</v>
+        <v>1.19</v>
       </c>
       <c r="F11" t="n">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,67 +810,67 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>40.456</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3715</v>
+        <v>2500</v>
       </c>
       <c r="E12" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="F12" t="n">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8.872</v>
+        <v>47.002</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>755</v>
+        <v>8385</v>
       </c>
       <c r="E13" t="n">
-        <v>2.03</v>
+        <v>0.12</v>
       </c>
       <c r="F13" t="n">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,339 +878,339 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.899</v>
+        <v>15.497</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>160</v>
+        <v>18.65</v>
       </c>
       <c r="E14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>31.31</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>693</v>
+        <v>251</v>
       </c>
       <c r="E15" t="n">
-        <v>4.52</v>
+        <v>-1.38</v>
       </c>
       <c r="F15" t="n">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11.853</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.37</v>
+        <v>3.62</v>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7.269</v>
+        <v>32.675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2185</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.63</v>
+        <v>-0.36</v>
       </c>
       <c r="F17" t="n">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8.497999999999999</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>292</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.17</v>
+        <v>1.81</v>
       </c>
       <c r="F18" t="n">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.209</v>
+        <v>9.526</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>180.5</v>
+        <v>545</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.22</v>
+        <v>-2.15</v>
       </c>
       <c r="F19" t="n">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.521000000000001</v>
+        <v>1.693</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>253</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2</v>
+        <v>-0.33</v>
       </c>
       <c r="F20" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7.546</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>84.2</v>
+        <v>1900</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.66</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.286</v>
+        <v>20.391</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>557</v>
+        <v>693</v>
       </c>
       <c r="E22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.787</v>
+        <v>11.902</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.65</v>
+        <v>119</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="F23" t="n">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,203 +1218,203 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.455</v>
+        <v>3.692</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20.5</v>
+        <v>173</v>
       </c>
       <c r="E24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.358</v>
+        <v>2.526</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2460</v>
+        <v>26.75</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.11</v>
       </c>
       <c r="F25" t="n">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>45.961</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3110</v>
+        <v>497</v>
       </c>
       <c r="E26" t="n">
-        <v>9.890000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="F26" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.793</v>
+        <v>16.137</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>42.5</v>
+        <v>153</v>
       </c>
       <c r="E27" t="n">
-        <v>1.31</v>
+        <v>-0.97</v>
       </c>
       <c r="F27" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.738</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>501</v>
+        <v>5185</v>
       </c>
       <c r="E28" t="n">
-        <v>2.14</v>
+        <v>0.1</v>
       </c>
       <c r="F28" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>16.401</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>497</v>
+        <v>3760</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.68</v>
+        <v>1.21</v>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,67 +1422,67 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>31.484</v>
+        <v>8.843</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1475</v>
+        <v>50</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="F30" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.714</v>
+        <v>1.395</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>154.5</v>
+        <v>67.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="F31" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,67 +1490,67 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.843</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>284.5</v>
+        <v>111.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.39</v>
+        <v>-0.45</v>
       </c>
       <c r="F32" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.933</v>
+        <v>2.604</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>384</v>
+        <v>284.5</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.29</v>
+        <v>-0.18</v>
       </c>
       <c r="F33" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,67 +1558,67 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.238</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>171</v>
+        <v>341.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.72</v>
+        <v>-0.15</v>
       </c>
       <c r="F34" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.334</v>
+        <v>4.905</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>303</v>
+        <v>286.5</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.62</v>
+        <v>-1.88</v>
       </c>
       <c r="F35" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,67 +1626,67 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6.093</v>
+        <v>4.035</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.67</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3.641</v>
+        <v>31.611</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>342</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.73</v>
+        <v>-1.01</v>
       </c>
       <c r="F37" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.891</v>
+        <v>2.256</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>50.5</v>
+        <v>1480</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.17</v>
+        <v>0.34</v>
       </c>
       <c r="F38" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,67 +1728,67 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1.416</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>71.8</v>
+        <v>383</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.24</v>
+        <v>-0.26</v>
       </c>
       <c r="F39" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>9.324</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>285</v>
+        <v>63.1</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.35</v>
+        <v>-2.32</v>
       </c>
       <c r="F40" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.739</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>112</v>
+        <v>59.9</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.88</v>
+        <v>-1.48</v>
       </c>
       <c r="F41" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.658</v>
+        <v>2.714</v>
       </c>
     </row>
     <row r="42">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>242.5</v>
+        <v>243</v>
       </c>
       <c r="E42" t="n">
         <v>0.21</v>
       </c>
       <c r="F42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,30 +1864,30 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>64.59999999999999</v>
+        <v>172.5</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.92</v>
+        <v>0.88</v>
       </c>
       <c r="F43" t="n">
         <v>57</v>
@@ -1898,67 +1898,67 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.083</v>
+        <v>21.383</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>110</v>
+        <v>302.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.46</v>
+        <v>-0.17</v>
       </c>
       <c r="F44" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.38</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>61.2</v>
+        <v>113.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.97</v>
+        <v>-2.58</v>
       </c>
       <c r="F45" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,33 +1966,33 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.947</v>
+        <v>2.398</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>272</v>
+        <v>283.5</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.63</v>
+        <v>-0.35</v>
       </c>
       <c r="F46" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,101 +2000,101 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.912</v>
+        <v>6.335</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>69.59999999999999</v>
+        <v>180</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.14</v>
+        <v>-0.28</v>
       </c>
       <c r="F47" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.306</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>27.05</v>
+        <v>29.25</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.55</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.545</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>29.25</v>
+        <v>109</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,67 +2102,67 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.144</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8375</v>
+        <v>272</v>
       </c>
       <c r="E50" t="n">
-        <v>9.98</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>15.494</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>116.5</v>
+        <v>552</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.43</v>
+        <v>0.91</v>
       </c>
       <c r="F51" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,41 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.873</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2609</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>陽明</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Yang Ming</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="F52" t="n">
-        <v>32</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Accumulation (Up)</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>3.146</v>
+        <v>7.324</v>
       </c>
     </row>
   </sheetData>
@@ -2218,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2261,94 +2227,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50.36</v>
+        <v>52.78</v>
       </c>
       <c r="F2" t="n">
-        <v>1.06</v>
+        <v>0.82</v>
       </c>
       <c r="G2" t="n">
-        <v>15.494</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48.89</v>
+        <v>37.14</v>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="G3" t="n">
-        <v>6.093</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41.69</v>
+        <v>36.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.71</v>
+        <v>1.14</v>
       </c>
       <c r="G4" t="n">
-        <v>4.793</v>
+        <v>15.497</v>
       </c>
     </row>
     <row r="5">
@@ -2373,60 +2339,60 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38.69</v>
+        <v>31.43</v>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G5" t="n">
-        <v>40.456</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32.36</v>
+        <v>29.55</v>
       </c>
       <c r="F6" t="n">
-        <v>1.51</v>
+        <v>1.13</v>
       </c>
       <c r="G6" t="n">
-        <v>8.664999999999999</v>
+        <v>31.611</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2435,75 +2401,75 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32.19</v>
+        <v>28.97</v>
       </c>
       <c r="F7" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="G7" t="n">
-        <v>16.401</v>
+        <v>7.324</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30.39</v>
+        <v>24.59</v>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>7.269</v>
+        <v>8.651</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>22.72</v>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="G9" t="n">
-        <v>31.31</v>
+        <v>16.137</v>
       </c>
     </row>
     <row r="10">
@@ -2528,168 +2494,168 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.57</v>
+        <v>17.45</v>
       </c>
       <c r="F10" t="n">
-        <v>1.78</v>
+        <v>2.21</v>
       </c>
       <c r="G10" t="n">
-        <v>3.033</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18.02</v>
+        <v>17.06</v>
       </c>
       <c r="F11" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>0.724</v>
+        <v>11.902</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.26</v>
+        <v>13.82</v>
       </c>
       <c r="F12" t="n">
-        <v>0.99</v>
+        <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>11.853</v>
+        <v>2.526</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15.6</v>
+        <v>13.02</v>
       </c>
       <c r="F13" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="G13" t="n">
-        <v>1.185</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.95</v>
+        <v>10.47</v>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>0.99</v>
       </c>
       <c r="G14" t="n">
-        <v>2.517</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>11.76</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="G15" t="n">
-        <v>2.083</v>
+        <v>2.604</v>
       </c>
     </row>
     <row r="16">
@@ -2714,91 +2680,91 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11.11</v>
+        <v>8.57</v>
       </c>
       <c r="F16" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="G16" t="n">
-        <v>20.502</v>
+        <v>20.391</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.19</v>
+        <v>7.66</v>
       </c>
       <c r="F17" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>2.843</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.74</v>
+        <v>7.36</v>
       </c>
       <c r="F18" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="G18" t="n">
-        <v>2.658</v>
+        <v>2.055</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2807,29 +2773,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.98</v>
+        <v>7.3</v>
       </c>
       <c r="F19" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="G19" t="n">
-        <v>0.545</v>
+        <v>1.395</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2838,29 +2804,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7.91</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>1.19</v>
+        <v>0.84</v>
       </c>
       <c r="G20" t="n">
-        <v>2.306</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2869,106 +2835,106 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7.45</v>
+        <v>6.66</v>
       </c>
       <c r="F21" t="n">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="G21" t="n">
-        <v>1.416</v>
+        <v>2.256</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.1</v>
+        <v>5.19</v>
       </c>
       <c r="F22" t="n">
-        <v>1.16</v>
+        <v>0.77</v>
       </c>
       <c r="G22" t="n">
-        <v>1.899</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.76</v>
+        <v>4.99</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2</v>
+        <v>0.65</v>
       </c>
       <c r="G23" t="n">
-        <v>4.209</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6.56</v>
+        <v>4.47</v>
       </c>
       <c r="F24" t="n">
-        <v>1.41</v>
+        <v>0.92</v>
       </c>
       <c r="G24" t="n">
-        <v>2.525</v>
+        <v>9.526</v>
       </c>
     </row>
     <row r="25">
@@ -2993,106 +2959,106 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.8</v>
+        <v>4.24</v>
       </c>
       <c r="F25" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="G25" t="n">
-        <v>8.497999999999999</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="F26" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="G26" t="n">
-        <v>9.324</v>
+        <v>2.714</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.24</v>
+        <v>3.85</v>
       </c>
       <c r="F27" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="G27" t="n">
-        <v>0.714</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
       <c r="G28" t="n">
-        <v>7.546</v>
+        <v>47.002</v>
       </c>
     </row>
     <row r="29">
@@ -3117,44 +3083,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4.11</v>
+        <v>2.71</v>
       </c>
       <c r="F29" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="G29" t="n">
-        <v>4.891</v>
+        <v>4.905</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="F30" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="G30" t="n">
-        <v>45.961</v>
+        <v>0.694</v>
       </c>
     </row>
     <row r="31">
@@ -3179,122 +3145,122 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="F31" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.19</v>
+        <v>0.17</v>
       </c>
       <c r="F32" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="G32" t="n">
-        <v>0.478</v>
+        <v>4.035</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.12</v>
+        <v>0.11</v>
       </c>
       <c r="F33" t="n">
-        <v>0.73</v>
+        <v>1.62</v>
       </c>
       <c r="G33" t="n">
-        <v>9.521000000000001</v>
+        <v>9.196</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.71</v>
+        <v>-0.18</v>
       </c>
       <c r="F34" t="n">
-        <v>0.98</v>
+        <v>0.63</v>
       </c>
       <c r="G34" t="n">
-        <v>0.738</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3303,447 +3269,447 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.49</v>
+        <v>-0.35</v>
       </c>
       <c r="F35" t="n">
-        <v>0.87</v>
+        <v>1.26</v>
       </c>
       <c r="G35" t="n">
-        <v>0.358</v>
+        <v>0.764</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="F36" t="n">
-        <v>1.02</v>
+        <v>0.87</v>
       </c>
       <c r="G36" t="n">
-        <v>1.787</v>
+        <v>32.675</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.18</v>
+        <v>-1.1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.912</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.92</v>
+        <v>-1.3</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3</v>
+        <v>0.77</v>
       </c>
       <c r="G38" t="n">
-        <v>8.499000000000001</v>
+        <v>2.398</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.42</v>
+        <v>-1.68</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="G39" t="n">
-        <v>2.6</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-2.1</v>
+        <v>-2.15</v>
       </c>
       <c r="F40" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="G40" t="n">
-        <v>0.455</v>
+        <v>1.693</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.55</v>
+        <v>-3.55</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G41" t="n">
-        <v>31.484</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-3.13</v>
+        <v>-3.62</v>
       </c>
       <c r="F42" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="G42" t="n">
-        <v>8.872</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-3.28</v>
+        <v>-4.31</v>
       </c>
       <c r="F43" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="G43" t="n">
-        <v>3.641</v>
+        <v>8.843</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.39</v>
+        <v>-4.96</v>
       </c>
       <c r="F44" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="G44" t="n">
-        <v>0.38</v>
+        <v>21.383</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.88</v>
+        <v>-5.18</v>
       </c>
       <c r="F45" t="n">
-        <v>0.79</v>
+        <v>1.04</v>
       </c>
       <c r="G45" t="n">
-        <v>2.238</v>
+        <v>3.692</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3.89</v>
+        <v>-5.48</v>
       </c>
       <c r="F46" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="G46" t="n">
-        <v>6.933</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-4.4</v>
+        <v>-5.49</v>
       </c>
       <c r="F47" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G47" t="n">
-        <v>3.146</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-4.47</v>
+        <v>-6.69</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="G48" t="n">
-        <v>21.334</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-4.68</v>
+        <v>-7.65</v>
       </c>
       <c r="F49" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G49" t="n">
-        <v>0.739</v>
+        <v>6.335</v>
       </c>
     </row>
     <row r="50">
@@ -3768,75 +3734,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-6.42</v>
+        <v>-8.68</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="G50" t="n">
-        <v>0.947</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-7.91</v>
+        <v>-21.93</v>
       </c>
       <c r="F51" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="G51" t="n">
-        <v>2.873</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>8096</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CoAsia</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Design Service</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>-21.28</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.286</v>
+        <v>0.284</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3822,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.89</v>
+        <v>52.78</v>
       </c>
       <c r="C2" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="D2" t="n">
-        <v>6.093</v>
+        <v>6.14</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3841,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.69</v>
+        <v>37.14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.71</v>
+        <v>0.98</v>
       </c>
       <c r="D3" t="n">
-        <v>4.793</v>
+        <v>5.508</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3925,13 +3860,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.69</v>
+        <v>31.43</v>
       </c>
       <c r="C4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="D4" t="n">
-        <v>40.456</v>
+        <v>39.83</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3944,13 +3879,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.36</v>
+        <v>24.59</v>
       </c>
       <c r="C5" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="D5" t="n">
-        <v>8.664999999999999</v>
+        <v>8.651</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,150 +3894,150 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.615</v>
+        <v>17.06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.145</v>
+        <v>1.04</v>
       </c>
       <c r="D6" t="n">
-        <v>24.366</v>
+        <v>11.902</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.73</v>
+        <v>16.685</v>
       </c>
       <c r="C7" t="n">
-        <v>1.083333333333333</v>
+        <v>1.135</v>
       </c>
       <c r="D7" t="n">
-        <v>24.05</v>
+        <v>78.613</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.26</v>
+        <v>16.295</v>
       </c>
       <c r="C8" t="n">
-        <v>0.99</v>
+        <v>1.185</v>
       </c>
       <c r="D8" t="n">
-        <v>11.853</v>
+        <v>24.34</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="C9" t="n">
-        <v>1.37</v>
+        <v>1.003333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>1.185</v>
+        <v>23.809</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.4</v>
+        <v>13.82</v>
       </c>
       <c r="C10" t="n">
-        <v>1.13</v>
+        <v>1.69</v>
       </c>
       <c r="D10" t="n">
-        <v>77.271</v>
+        <v>2.526</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.95</v>
+        <v>8.81</v>
       </c>
       <c r="C11" t="n">
-        <v>1.62</v>
+        <v>1.735</v>
       </c>
       <c r="D11" t="n">
-        <v>2.517</v>
+        <v>7.555</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.665</v>
+        <v>8.042</v>
       </c>
       <c r="C12" t="n">
-        <v>1.49</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>7.241999999999999</v>
+        <v>9.516</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11.76</v>
+        <v>7.66</v>
       </c>
       <c r="C13" t="n">
-        <v>0.64</v>
+        <v>1.44</v>
       </c>
       <c r="D13" t="n">
-        <v>2.083</v>
+        <v>1.111</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,36 +4046,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.254000000000001</v>
+        <v>7.36</v>
       </c>
       <c r="C14" t="n">
-        <v>1.006</v>
+        <v>1.25</v>
       </c>
       <c r="D14" t="n">
-        <v>9.768000000000001</v>
+        <v>2.055</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.1</v>
+        <v>4.99</v>
       </c>
       <c r="C15" t="n">
-        <v>1.16</v>
+        <v>0.65</v>
       </c>
       <c r="D15" t="n">
-        <v>1.899</v>
+        <v>1.983</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,17 +4084,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.8</v>
+        <v>4.47</v>
       </c>
       <c r="C16" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="D16" t="n">
-        <v>8.497999999999999</v>
+        <v>9.526</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,17 +4103,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.4</v>
+        <v>4.24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.88</v>
+        <v>1.23</v>
       </c>
       <c r="D17" t="n">
-        <v>9.324</v>
+        <v>9.08</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4187,93 +4122,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.24</v>
+        <v>2.626666666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>1.52</v>
+        <v>0.7366666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.714</v>
+        <v>7.452</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.609999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="C19" t="n">
-        <v>0.95</v>
+        <v>1.07</v>
       </c>
       <c r="D19" t="n">
-        <v>27.435</v>
+        <v>0.694</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.82</v>
+        <v>1.56</v>
       </c>
       <c r="C20" t="n">
-        <v>1.355</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>11.024</v>
+        <v>0.146</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.92</v>
+        <v>0.46</v>
       </c>
       <c r="C21" t="n">
-        <v>0.95</v>
+        <v>0.955</v>
       </c>
       <c r="D21" t="n">
-        <v>0.144</v>
+        <v>26.726</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.19</v>
+        <v>0.11</v>
       </c>
       <c r="C22" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="D22" t="n">
-        <v>0.478</v>
+        <v>9.196</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,112 +4217,112 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7325000000000002</v>
+        <v>-0.39</v>
       </c>
       <c r="C23" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="D23" t="n">
-        <v>22.905</v>
+        <v>32.675</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6</v>
+        <v>-0.8049999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.925</v>
+        <v>0.8525</v>
       </c>
       <c r="D24" t="n">
-        <v>1.096</v>
+        <v>23.143</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.36</v>
+        <v>-1.015</v>
       </c>
       <c r="C25" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="D25" t="n">
-        <v>1.787</v>
+        <v>1.116</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.630000000000001</v>
+        <v>-2.15</v>
       </c>
       <c r="C26" t="n">
-        <v>1.385</v>
+        <v>1.04</v>
       </c>
       <c r="D26" t="n">
-        <v>1.01</v>
+        <v>1.693</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.1</v>
+        <v>-3.07</v>
       </c>
       <c r="C27" t="n">
-        <v>1.03</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>0.455</v>
+        <v>3.741</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.55</v>
+        <v>-3.62</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="D28" t="n">
-        <v>31.484</v>
+        <v>0.456</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4396,36 +4331,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.913333333333334</v>
+        <v>-4.455</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7333333333333334</v>
+        <v>1.49</v>
       </c>
       <c r="D29" t="n">
-        <v>3.889</v>
+        <v>1.049</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-3.28</v>
+        <v>-4.96</v>
       </c>
       <c r="C30" t="n">
-        <v>1.01</v>
+        <v>0.8</v>
       </c>
       <c r="D30" t="n">
-        <v>3.641</v>
+        <v>21.383</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4434,17 +4369,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-4.47</v>
+        <v>-5.18</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="D31" t="n">
-        <v>21.334</v>
+        <v>3.692</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4453,20 +4388,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-4.576666666666667</v>
+        <v>-6.69</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7466666666666667</v>
+        <v>1.62</v>
       </c>
       <c r="D32" t="n">
-        <v>8.619</v>
+        <v>0.455</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4572,34 +4507,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2185</v>
+        <v>2215</v>
       </c>
       <c r="E2" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>4.24</v>
       </c>
       <c r="G2" t="n">
-        <v>59.52</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>24.7338</v>
+        <v>34.6707</v>
       </c>
       <c r="I2" t="n">
-        <v>85.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="L2" t="n">
-        <v>38.4</v>
+        <v>81</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,38 +4559,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5180</v>
+        <v>5185</v>
       </c>
       <c r="E3" t="n">
-        <v>3.39</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>38.69</v>
+        <v>31.43</v>
       </c>
       <c r="G3" t="n">
-        <v>74.93000000000001</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8894</v>
+        <v>270.1449</v>
       </c>
       <c r="I3" t="n">
-        <v>100.4</v>
+        <v>94.8</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
-        <v>54</v>
+        <v>-16.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4676,34 +4611,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.66</v>
+        <v>-0.36</v>
       </c>
       <c r="F4" t="n">
-        <v>-21.28</v>
+        <v>-21.93</v>
       </c>
       <c r="G4" t="n">
-        <v>13.96</v>
+        <v>16.44</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.139099999999999</v>
+        <v>-8.114599999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>6.11</v>
+        <v>5.41</v>
       </c>
       <c r="L4" t="n">
-        <v>25.4</v>
+        <v>-7.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4663,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>303</v>
+        <v>302.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.62</v>
+        <v>-0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>48.89</v>
+        <v>52.78</v>
       </c>
       <c r="G5" t="n">
-        <v>62.32</v>
+        <v>70.03</v>
       </c>
       <c r="H5" t="n">
-        <v>27.4591</v>
+        <v>25.6809</v>
       </c>
       <c r="I5" t="n">
-        <v>72.5</v>
+        <v>71.2</v>
       </c>
       <c r="J5" t="n">
-        <v>83.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8.029999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="L5" t="n">
-        <v>-21.8</v>
+        <v>-50</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4715,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.37</v>
+        <v>0.91</v>
       </c>
       <c r="F6" t="n">
-        <v>30.39</v>
+        <v>28.97</v>
       </c>
       <c r="G6" t="n">
-        <v>51.13</v>
+        <v>56.46</v>
       </c>
       <c r="H6" t="n">
-        <v>37.8032</v>
+        <v>36.9637</v>
       </c>
       <c r="I6" t="n">
-        <v>70.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="J6" t="n">
-        <v>65.3</v>
+        <v>72.2</v>
       </c>
       <c r="K6" t="n">
-        <v>6.84</v>
+        <v>6.55</v>
       </c>
       <c r="L6" t="n">
-        <v>40.9</v>
+        <v>-75.09999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4767,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F7" t="n">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="G7" t="n">
-        <v>53.23</v>
+        <v>63.93</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3943</v>
+        <v>0.0577</v>
       </c>
       <c r="I7" t="n">
-        <v>68.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="J7" t="n">
-        <v>68.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="L7" t="n">
-        <v>29</v>
+        <v>17.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.96</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>107</v>
+        <v>276</v>
       </c>
       <c r="E2" t="n">
-        <v>1.42</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.52</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>950</v>
+        <v>112</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.16</v>
+        <v>4.67</v>
       </c>
       <c r="F3" t="n">
-        <v>296</v>
+        <v>231</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,67 +538,67 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9.196</v>
+        <v>4.059</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42.85</v>
+        <v>20.3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.82</v>
+        <v>-0.73</v>
       </c>
       <c r="F4" t="n">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.764</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3305</v>
+        <v>188.5</v>
       </c>
       <c r="E5" t="n">
-        <v>6.27</v>
+        <v>2.17</v>
       </c>
       <c r="F5" t="n">
-        <v>203</v>
+        <v>127</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5.508</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="6">
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>204</v>
+        <v>206.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.49</v>
+        <v>1.23</v>
       </c>
       <c r="F6" t="n">
-        <v>199</v>
+        <v>124</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,135 +640,135 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.765</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.45</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.24</v>
+        <v>-1.98</v>
       </c>
       <c r="F7" t="n">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.352</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>761</v>
+        <v>543</v>
       </c>
       <c r="E8" t="n">
-        <v>0.79</v>
+        <v>-0.37</v>
       </c>
       <c r="F8" t="n">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.055</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2215</v>
+        <v>250.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1.37</v>
+        <v>-2.15</v>
       </c>
       <c r="F9" t="n">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9.08</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>304</v>
+        <v>2125</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1</v>
+        <v>-4.06</v>
       </c>
       <c r="F10" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8.651</v>
+        <v>8.741</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>256</v>
+        <v>749</v>
       </c>
       <c r="E11" t="n">
-        <v>1.19</v>
+        <v>-1.58</v>
       </c>
       <c r="F11" t="n">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,237 +810,237 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7.78</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2500</v>
+        <v>948</v>
       </c>
       <c r="E12" t="n">
-        <v>1.63</v>
+        <v>-0.21</v>
       </c>
       <c r="F12" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>47.002</v>
+        <v>9.242000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8385</v>
+        <v>5285</v>
       </c>
       <c r="E13" t="n">
-        <v>0.12</v>
+        <v>1.93</v>
       </c>
       <c r="F13" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>15.497</v>
+        <v>41.175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.65</v>
+        <v>3230</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="F14" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.456</v>
+        <v>5.538</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.38</v>
+        <v>2.3</v>
       </c>
       <c r="F15" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.455</v>
+        <v>9.051</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>515</v>
+        <v>18.65</v>
       </c>
       <c r="E16" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>32.675</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>83.90000000000001</v>
+        <v>1910</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.36</v>
+        <v>0.53</v>
       </c>
       <c r="F17" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.284</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73.09999999999999</v>
+        <v>8525</v>
       </c>
       <c r="E18" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="F18" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9.526</v>
+        <v>15.082</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>545</v>
+        <v>154</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.15</v>
+        <v>-3.75</v>
       </c>
       <c r="F19" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.693</v>
+        <v>30.231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>378</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.33</v>
+        <v>-1.31</v>
       </c>
       <c r="F20" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,67 +1116,67 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.948</v>
+        <v>2.087</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1900</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>20.391</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>693</v>
+        <v>2475</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,67 +1184,67 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>11.902</v>
+        <v>46.103</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>119</v>
+        <v>170.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.85</v>
+        <v>-1.45</v>
       </c>
       <c r="F23" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.692</v>
+        <v>2.489</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="F24" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.526</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1272,21 +1272,21 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.75</v>
+        <v>26.45</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="F25" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.551</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="26">
@@ -1306,13 +1306,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8</v>
+        <v>1.01</v>
       </c>
       <c r="F26" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,101 +1320,101 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>16.137</v>
+        <v>15.927</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>153</v>
+        <v>59.9</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.97</v>
+        <v>-1.8</v>
       </c>
       <c r="F27" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.71</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5185</v>
+        <v>338.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1</v>
+        <v>-0.88</v>
       </c>
       <c r="F28" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>39.83</v>
+        <v>4.833</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3760</v>
+        <v>503</v>
       </c>
       <c r="E29" t="n">
-        <v>1.21</v>
+        <v>-2.33</v>
       </c>
       <c r="F29" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,101 +1422,101 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>8.843</v>
+        <v>30.774</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>699</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.99</v>
+        <v>0.87</v>
       </c>
       <c r="F30" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.395</v>
+        <v>11.973</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>67.5</v>
+        <v>117</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.03</v>
+        <v>-1.68</v>
       </c>
       <c r="F31" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.111</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>111.5</v>
+        <v>1480</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,67 +1524,67 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2.604</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>284.5</v>
+        <v>306.5</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.18</v>
+        <v>1.32</v>
       </c>
       <c r="F33" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.71</v>
+        <v>6.231</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>341.5</v>
+        <v>243</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,101 +1592,101 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4.905</v>
+        <v>2.148</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>286.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.88</v>
+        <v>1.58</v>
       </c>
       <c r="F35" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.035</v>
+        <v>1.906</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>160</v>
+        <v>284.5</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>31.611</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>68.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.01</v>
+        <v>0.15</v>
       </c>
       <c r="F37" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.256</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1480</v>
+        <v>68.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.34</v>
+        <v>-0.58</v>
       </c>
       <c r="F38" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.694</v>
+        <v>2.216</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>383</v>
+        <v>184.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.26</v>
+        <v>2.5</v>
       </c>
       <c r="F39" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.14</v>
+        <v>9.536</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>63.1</v>
+        <v>110.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.32</v>
+        <v>-0.9</v>
       </c>
       <c r="F40" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,33 +1796,33 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.983</v>
+        <v>2.548</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>59.9</v>
+        <v>150</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.48</v>
+        <v>-1.96</v>
       </c>
       <c r="F41" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,67 +1830,67 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.714</v>
+        <v>2.559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>243</v>
+        <v>110.5</v>
       </c>
       <c r="E42" t="n">
-        <v>0.21</v>
+        <v>1.38</v>
       </c>
       <c r="F42" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.34</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>172.5</v>
+        <v>3770</v>
       </c>
       <c r="E43" t="n">
-        <v>0.88</v>
+        <v>0.27</v>
       </c>
       <c r="F43" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,67 +1898,67 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>21.383</v>
+        <v>8.787000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>302.5</v>
+        <v>287</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.17</v>
+        <v>1.23</v>
       </c>
       <c r="F44" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6.14</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>113.5</v>
+        <v>171.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.58</v>
+        <v>-0.58</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,67 +1966,67 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.398</v>
+        <v>20.512</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>283.5</v>
+        <v>287</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.35</v>
+        <v>0.17</v>
       </c>
       <c r="F46" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.335</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>180</v>
+        <v>272.5</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.28</v>
+        <v>0.18</v>
       </c>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.51</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="48">
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,67 +2068,67 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.146</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>109</v>
+        <v>115.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.91</v>
+        <v>1.76</v>
       </c>
       <c r="F49" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.348</v>
+        <v>2.214</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>272</v>
+        <v>49.6</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F50" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,41 +2136,75 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.891</v>
+        <v>1.349</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2609</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>陽明</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Yang Ming</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>28</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Accumulation (Up)</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>2.557</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>2455</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>全新</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Visual Photonics</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>552</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F51" t="n">
-        <v>25</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="D52" t="n">
+        <v>554</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F52" t="n">
+        <v>12</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>Accumulation (Up)</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>7.324</v>
+      <c r="H52" t="n">
+        <v>7.267</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,280 +2261,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52.78</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>6.14</v>
+        <v>15.082</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>37.14</v>
+        <v>40.92</v>
       </c>
       <c r="F3" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="G3" t="n">
-        <v>5.508</v>
+        <v>6.231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36.9</v>
+        <v>36.74</v>
       </c>
       <c r="F4" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
-        <v>15.497</v>
+        <v>41.175</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>31.43</v>
+        <v>29.96</v>
       </c>
       <c r="F5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>39.83</v>
+        <v>30.231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>29.55</v>
+        <v>27.94</v>
       </c>
       <c r="F6" t="n">
-        <v>1.13</v>
+        <v>0.89</v>
       </c>
       <c r="G6" t="n">
-        <v>31.611</v>
+        <v>7.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28.97</v>
+        <v>25.66</v>
       </c>
       <c r="F7" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>7.324</v>
+        <v>9.051</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>24.59</v>
+        <v>24.03</v>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>2.38</v>
       </c>
       <c r="G8" t="n">
-        <v>8.651</v>
+        <v>4.059</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22.72</v>
+        <v>21.89</v>
       </c>
       <c r="F9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>16.137</v>
+        <v>5.538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.45</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="G10" t="n">
-        <v>3.52</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="11">
@@ -2525,13 +2559,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.06</v>
+        <v>15.54</v>
       </c>
       <c r="F11" t="n">
         <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>11.902</v>
+        <v>11.973</v>
       </c>
     </row>
     <row r="12">
@@ -2556,75 +2590,75 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.82</v>
+        <v>12.91</v>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="G12" t="n">
-        <v>2.526</v>
+        <v>2.489</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13.02</v>
+        <v>12.68</v>
       </c>
       <c r="F13" t="n">
-        <v>2.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.765</v>
+        <v>15.927</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10.47</v>
+        <v>7.91</v>
       </c>
       <c r="F14" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="G14" t="n">
-        <v>2.71</v>
+        <v>20.484</v>
       </c>
     </row>
     <row r="15">
@@ -2649,153 +2683,153 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.779999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>2.604</v>
+        <v>2.548</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.57</v>
+        <v>7.48</v>
       </c>
       <c r="F16" t="n">
-        <v>1.19</v>
+        <v>0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>20.391</v>
+        <v>1.349</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.66</v>
+        <v>7.37</v>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>0.93</v>
       </c>
       <c r="G17" t="n">
-        <v>1.111</v>
+        <v>2.216</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.36</v>
+        <v>6.46</v>
       </c>
       <c r="F18" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="G18" t="n">
-        <v>2.055</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.3</v>
+        <v>6.25</v>
       </c>
       <c r="F19" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>1.395</v>
+        <v>2.054</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2804,29 +2838,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>6.01</v>
       </c>
       <c r="F20" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="G20" t="n">
-        <v>0.551</v>
+        <v>2.559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2835,13 +2869,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.66</v>
+        <v>5.59</v>
       </c>
       <c r="F21" t="n">
-        <v>1.03</v>
+        <v>0.78</v>
       </c>
       <c r="G21" t="n">
-        <v>2.256</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="22">
@@ -2866,742 +2900,742 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5.19</v>
+        <v>4.52</v>
       </c>
       <c r="F22" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>2.148</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.99</v>
+        <v>3.61</v>
       </c>
       <c r="F23" t="n">
-        <v>0.65</v>
+        <v>1.25</v>
       </c>
       <c r="G23" t="n">
-        <v>1.983</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.47</v>
+        <v>3.57</v>
       </c>
       <c r="F24" t="n">
-        <v>0.92</v>
+        <v>1.68</v>
       </c>
       <c r="G24" t="n">
-        <v>9.526</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4.24</v>
+        <v>3.45</v>
       </c>
       <c r="F25" t="n">
-        <v>1.23</v>
+        <v>0.89</v>
       </c>
       <c r="G25" t="n">
-        <v>9.08</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3.99</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>0.67</v>
+        <v>1.11</v>
       </c>
       <c r="G26" t="n">
-        <v>2.714</v>
+        <v>46.103</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="F27" t="n">
-        <v>1.05</v>
+        <v>0.58</v>
       </c>
       <c r="G27" t="n">
-        <v>7.78</v>
+        <v>2.557</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.82</v>
+        <v>2.79</v>
       </c>
       <c r="F28" t="n">
-        <v>1.14</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>47.002</v>
+        <v>9.536</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="F29" t="n">
-        <v>0.92</v>
+        <v>1.86</v>
       </c>
       <c r="G29" t="n">
-        <v>4.905</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="F30" t="n">
-        <v>1.07</v>
+        <v>0.91</v>
       </c>
       <c r="G30" t="n">
-        <v>0.694</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="G31" t="n">
-        <v>0.146</v>
+        <v>2.214</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.17</v>
+        <v>1.58</v>
       </c>
       <c r="F32" t="n">
-        <v>1.26</v>
+        <v>0.64</v>
       </c>
       <c r="G32" t="n">
-        <v>4.035</v>
+        <v>1.906</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.11</v>
+        <v>1.5</v>
       </c>
       <c r="F33" t="n">
-        <v>1.62</v>
+        <v>0.83</v>
       </c>
       <c r="G33" t="n">
-        <v>9.196</v>
+        <v>4.833</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.18</v>
+        <v>1.02</v>
       </c>
       <c r="F34" t="n">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="G34" t="n">
-        <v>0.891</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.35</v>
+        <v>-0.6</v>
       </c>
       <c r="F35" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="G35" t="n">
-        <v>0.764</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.39</v>
+        <v>-0.91</v>
       </c>
       <c r="F36" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="G36" t="n">
-        <v>32.675</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-1.1</v>
+        <v>-1.04</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="G37" t="n">
-        <v>9.51</v>
+        <v>9.242000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.3</v>
+        <v>-1.09</v>
       </c>
       <c r="F38" t="n">
-        <v>0.77</v>
+        <v>0.63</v>
       </c>
       <c r="G38" t="n">
-        <v>2.398</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.68</v>
+        <v>-1.39</v>
       </c>
       <c r="F39" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="G39" t="n">
-        <v>0.352</v>
+        <v>8.741</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-2.15</v>
+        <v>-1.75</v>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="G40" t="n">
-        <v>1.693</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-3.55</v>
+        <v>-1.82</v>
       </c>
       <c r="F41" t="n">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="G41" t="n">
-        <v>2.14</v>
+        <v>8.787000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-3.62</v>
+        <v>-2.4</v>
       </c>
       <c r="F42" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="G42" t="n">
-        <v>0.456</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-4.31</v>
+        <v>-2.61</v>
       </c>
       <c r="F43" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="G43" t="n">
-        <v>8.843</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-4.96</v>
+        <v>-4.53</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="G44" t="n">
-        <v>21.383</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-5.18</v>
+        <v>-4.65</v>
       </c>
       <c r="F45" t="n">
-        <v>1.04</v>
+        <v>0.74</v>
       </c>
       <c r="G45" t="n">
-        <v>3.692</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3610,13 +3644,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-5.48</v>
+        <v>-4.7</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="G46" t="n">
-        <v>0.71</v>
+        <v>2.087</v>
       </c>
     </row>
     <row r="47">
@@ -3641,137 +3675,168 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.49</v>
+        <v>-5</v>
       </c>
       <c r="F47" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="G47" t="n">
-        <v>0.348</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-6.69</v>
+        <v>-7.02</v>
       </c>
       <c r="F48" t="n">
-        <v>1.62</v>
+        <v>0.89</v>
       </c>
       <c r="G48" t="n">
-        <v>0.455</v>
+        <v>30.774</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-7.65</v>
+        <v>-7.8</v>
       </c>
       <c r="F49" t="n">
         <v>0.72</v>
       </c>
       <c r="G49" t="n">
-        <v>6.335</v>
+        <v>20.512</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-8.68</v>
+        <v>-8.24</v>
       </c>
       <c r="F50" t="n">
-        <v>0.75</v>
+        <v>1.01</v>
       </c>
       <c r="G50" t="n">
-        <v>0.948</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Inventec</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AI Server/OEM</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>-8.69</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>8096</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>擎亞</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>CoAsia</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Design Service</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>-21.93</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.284</v>
+      <c r="E52" t="n">
+        <v>-22.71</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.282</v>
       </c>
     </row>
   </sheetData>
@@ -3822,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.78</v>
+        <v>40.92</v>
       </c>
       <c r="C2" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="D2" t="n">
-        <v>6.14</v>
+        <v>6.231</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3837,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.14</v>
+        <v>36.74</v>
       </c>
       <c r="C3" t="n">
-        <v>0.98</v>
+        <v>1.1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.508</v>
+        <v>41.175</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3856,17 +3921,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.43</v>
+        <v>25.66</v>
       </c>
       <c r="C4" t="n">
-        <v>1.08</v>
+        <v>1.68</v>
       </c>
       <c r="D4" t="n">
-        <v>39.83</v>
+        <v>9.051</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3875,17 +3940,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.59</v>
+        <v>21.89</v>
       </c>
       <c r="C5" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="D5" t="n">
-        <v>8.651</v>
+        <v>5.538</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3894,20 +3959,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.06</v>
+        <v>21.09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.04</v>
+        <v>1.085</v>
       </c>
       <c r="D6" t="n">
-        <v>11.902</v>
+        <v>23.869</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3917,13 +3982,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.685</v>
+        <v>16.48</v>
       </c>
       <c r="C7" t="n">
-        <v>1.135</v>
+        <v>1.075</v>
       </c>
       <c r="D7" t="n">
-        <v>78.613</v>
+        <v>76.334</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -3932,39 +3997,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.295</v>
+        <v>15.54</v>
       </c>
       <c r="C8" t="n">
-        <v>1.185</v>
+        <v>1.04</v>
       </c>
       <c r="D8" t="n">
-        <v>24.34</v>
+        <v>11.973</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.4</v>
+        <v>13.82</v>
       </c>
       <c r="C9" t="n">
-        <v>1.003333333333333</v>
+        <v>1.815</v>
       </c>
       <c r="D9" t="n">
-        <v>23.809</v>
+        <v>7.739000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3974,13 +4039,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.82</v>
+        <v>12.91</v>
       </c>
       <c r="C10" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="D10" t="n">
-        <v>2.526</v>
+        <v>2.489</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -3989,20 +4054,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.81</v>
+        <v>11.87333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>1.735</v>
+        <v>0.8099999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>7.555</v>
+        <v>23.524</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -4012,13 +4077,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.042</v>
+        <v>6.85</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.874</v>
       </c>
       <c r="D12" t="n">
-        <v>9.516</v>
+        <v>9.222000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
@@ -4031,13 +4096,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7.66</v>
+        <v>6.46</v>
       </c>
       <c r="C13" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="D13" t="n">
-        <v>1.111</v>
+        <v>1.09</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4050,13 +4115,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.36</v>
+        <v>6.25</v>
       </c>
       <c r="C14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="D14" t="n">
-        <v>2.055</v>
+        <v>2.054</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4065,17 +4130,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.99</v>
+        <v>3.45</v>
       </c>
       <c r="C15" t="n">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>1.983</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4084,36 +4149,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.47</v>
+        <v>3.073333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>0.92</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="D16" t="n">
-        <v>9.526</v>
+        <v>6.919</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.24</v>
+        <v>2.79</v>
       </c>
       <c r="C17" t="n">
-        <v>1.23</v>
+        <v>1.86</v>
       </c>
       <c r="D17" t="n">
-        <v>9.08</v>
+        <v>0.57</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4122,55 +4187,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.626666666666667</v>
+        <v>2.09</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7366666666666667</v>
+        <v>0.91</v>
       </c>
       <c r="D18" t="n">
-        <v>7.452</v>
+        <v>0.145</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="C19" t="n">
-        <v>1.07</v>
+        <v>0.95</v>
       </c>
       <c r="D19" t="n">
-        <v>0.694</v>
+        <v>26.664</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="D20" t="n">
-        <v>0.146</v>
+        <v>1.906</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4179,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.46</v>
+        <v>1.265</v>
       </c>
       <c r="C21" t="n">
-        <v>0.955</v>
+        <v>1.635</v>
       </c>
       <c r="D21" t="n">
-        <v>26.726</v>
+        <v>12.002</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -4198,17 +4263,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.11</v>
+        <v>1.02</v>
       </c>
       <c r="C22" t="n">
-        <v>1.62</v>
+        <v>0.84</v>
       </c>
       <c r="D22" t="n">
-        <v>9.196</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4217,17 +4282,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.39</v>
+        <v>-0.91</v>
       </c>
       <c r="C23" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="D23" t="n">
-        <v>32.675</v>
+        <v>1.692</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4240,13 +4305,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.8049999999999999</v>
+        <v>-1.25</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8525</v>
+        <v>0.8575</v>
       </c>
       <c r="D24" t="n">
-        <v>23.143</v>
+        <v>22.809</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -4255,112 +4320,112 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.015</v>
+        <v>-1.39</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D25" t="n">
-        <v>1.116</v>
+        <v>8.741</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.15</v>
+        <v>-2.075</v>
       </c>
       <c r="C26" t="n">
-        <v>1.04</v>
+        <v>1.325</v>
       </c>
       <c r="D26" t="n">
-        <v>1.693</v>
+        <v>1.084</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-3.07</v>
+        <v>-2.61</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7166666666666667</v>
+        <v>1.04</v>
       </c>
       <c r="D27" t="n">
-        <v>3.741</v>
+        <v>0.459</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-3.62</v>
+        <v>-2.855</v>
       </c>
       <c r="C28" t="n">
-        <v>1.02</v>
+        <v>1.475</v>
       </c>
       <c r="D28" t="n">
-        <v>0.456</v>
+        <v>1.086</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.455</v>
+        <v>-3.44</v>
       </c>
       <c r="C29" t="n">
-        <v>1.49</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>1.049</v>
+        <v>3.616</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-4.96</v>
+        <v>-7.02</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="D30" t="n">
-        <v>21.383</v>
+        <v>30.774</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4369,17 +4434,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-5.18</v>
+        <v>-7.8</v>
       </c>
       <c r="C31" t="n">
-        <v>1.04</v>
+        <v>0.72</v>
       </c>
       <c r="D31" t="n">
-        <v>3.692</v>
+        <v>20.512</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4388,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-6.69</v>
+        <v>-8.24</v>
       </c>
       <c r="C32" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="D32" t="n">
-        <v>0.455</v>
+        <v>3.49</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4507,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2215</v>
+        <v>2125</v>
       </c>
       <c r="E2" t="n">
-        <v>1.37</v>
+        <v>-4.06</v>
       </c>
       <c r="F2" t="n">
-        <v>4.24</v>
+        <v>-1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>68.06999999999999</v>
+        <v>58.21</v>
       </c>
       <c r="H2" t="n">
-        <v>34.6707</v>
+        <v>34.7304</v>
       </c>
       <c r="I2" t="n">
-        <v>90.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>69.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.26</v>
+        <v>4.57</v>
       </c>
       <c r="L2" t="n">
-        <v>81</v>
+        <v>4.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4559,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5185</v>
+        <v>5285</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>1.93</v>
       </c>
       <c r="F3" t="n">
-        <v>31.43</v>
+        <v>36.74</v>
       </c>
       <c r="G3" t="n">
-        <v>74.06999999999999</v>
+        <v>74.44</v>
       </c>
       <c r="H3" t="n">
-        <v>270.1449</v>
+        <v>292.7155</v>
       </c>
       <c r="I3" t="n">
-        <v>94.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="L3" t="n">
-        <v>-16.6</v>
+        <v>-0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4611,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.36</v>
+        <v>0.83</v>
       </c>
       <c r="F4" t="n">
-        <v>-21.93</v>
+        <v>-22.71</v>
       </c>
       <c r="G4" t="n">
-        <v>16.44</v>
+        <v>17.01</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.114599999999999</v>
+        <v>-7.9622</v>
       </c>
       <c r="I4" t="n">
-        <v>17.9</v>
+        <v>22.4</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="L4" t="n">
-        <v>-7.2</v>
+        <v>-19.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4663,34 +4728,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>302.5</v>
+        <v>306.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.17</v>
+        <v>1.32</v>
       </c>
       <c r="F5" t="n">
-        <v>52.78</v>
+        <v>40.92</v>
       </c>
       <c r="G5" t="n">
-        <v>70.03</v>
+        <v>66.67</v>
       </c>
       <c r="H5" t="n">
-        <v>25.6809</v>
+        <v>24.7975</v>
       </c>
       <c r="I5" t="n">
-        <v>71.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>77.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K5" t="n">
-        <v>7.78</v>
+        <v>7.43</v>
       </c>
       <c r="L5" t="n">
-        <v>-50</v>
+        <v>-43.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4715,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E6" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="F6" t="n">
-        <v>28.97</v>
+        <v>27.94</v>
       </c>
       <c r="G6" t="n">
-        <v>56.46</v>
+        <v>56.25</v>
       </c>
       <c r="H6" t="n">
-        <v>36.9637</v>
+        <v>35.8479</v>
       </c>
       <c r="I6" t="n">
-        <v>72.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>72.2</v>
+        <v>75</v>
       </c>
       <c r="K6" t="n">
-        <v>6.55</v>
+        <v>5.98</v>
       </c>
       <c r="L6" t="n">
-        <v>-75.09999999999999</v>
+        <v>-87.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.28</v>
+        <v>0.89</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4767,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>256</v>
+        <v>250.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1.19</v>
+        <v>-2.15</v>
       </c>
       <c r="F7" t="n">
-        <v>3.85</v>
+        <v>-0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>63.93</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0577</v>
+        <v>-0.0124</v>
       </c>
       <c r="I7" t="n">
-        <v>89.2</v>
+        <v>43.5</v>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
+        <v>42.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="L7" t="n">
-        <v>17.3</v>
+        <v>14.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -496,7 +496,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.57</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         <v>4.67</v>
       </c>
       <c r="F3" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.059</v>
+        <v>4.056</v>
       </c>
     </row>
     <row r="4">
@@ -598,7 +598,7 @@
         <v>2.17</v>
       </c>
       <c r="F5" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>2.759</v>
       </c>
     </row>
     <row r="6">
@@ -632,7 +632,7 @@
         <v>1.23</v>
       </c>
       <c r="F6" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.804</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="7">
@@ -666,7 +666,7 @@
         <v>-1.98</v>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="8">
@@ -700,7 +700,7 @@
         <v>-0.37</v>
       </c>
       <c r="F8" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.692</v>
+        <v>1.689</v>
       </c>
     </row>
     <row r="9">
@@ -734,7 +734,7 @@
         <v>-2.15</v>
       </c>
       <c r="F9" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7.52</v>
+        <v>7.504</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2125</v>
+        <v>749</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.06</v>
+        <v>-1.58</v>
       </c>
       <c r="F10" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,41 +776,41 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8.741</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>749</v>
+        <v>2125</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.58</v>
+        <v>-4.06</v>
       </c>
       <c r="F11" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.054</v>
+        <v>8.701000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -836,7 +836,7 @@
         <v>-0.21</v>
       </c>
       <c r="F12" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>9.242000000000001</v>
+        <v>9.223000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -870,7 +870,7 @@
         <v>1.93</v>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>41.175</v>
+        <v>41.018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3230</v>
+        <v>311</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.27</v>
+        <v>2.3</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5.538</v>
+        <v>9.042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>311</v>
+        <v>3230</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3</v>
+        <v>-2.27</v>
       </c>
       <c r="F15" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9.051</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="16">
@@ -986,61 +986,61 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1910</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.53</v>
+        <v>0.83</v>
       </c>
       <c r="F17" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>20.484</v>
+        <v>0.281</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8525</v>
+        <v>154</v>
       </c>
       <c r="E18" t="n">
-        <v>1.67</v>
+        <v>-3.75</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>15.082</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>154</v>
+        <v>8525</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.75</v>
+        <v>1.67</v>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,67 +1082,67 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>30.231</v>
+        <v>15.059</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>378</v>
+        <v>1910</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.31</v>
+        <v>0.53</v>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.087</v>
+        <v>20.422</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>84.59999999999999</v>
+        <v>378</v>
       </c>
       <c r="E21" t="n">
-        <v>0.83</v>
+        <v>-1.31</v>
       </c>
       <c r="F21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.282</v>
+        <v>2.082</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2475</v>
+        <v>170.5</v>
       </c>
       <c r="E22" t="n">
-        <v>-1</v>
+        <v>-1.45</v>
       </c>
       <c r="F22" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,33 +1184,33 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>46.103</v>
+        <v>2.488</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>170.5</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.45</v>
+        <v>-1.5</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,33 +1218,33 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.489</v>
+        <v>9.297000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72</v>
+        <v>2475</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="F24" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9.300000000000001</v>
+        <v>45.951</v>
       </c>
     </row>
     <row r="25">
@@ -1278,7 +1278,7 @@
         <v>-1.12</v>
       </c>
       <c r="F25" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="26">
@@ -1312,7 +1312,7 @@
         <v>1.01</v>
       </c>
       <c r="F26" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>15.927</v>
+        <v>15.918</v>
       </c>
     </row>
     <row r="27">
@@ -1346,7 +1346,7 @@
         <v>-1.8</v>
       </c>
       <c r="F27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>-0.88</v>
       </c>
       <c r="F28" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.833</v>
+        <v>4.827</v>
       </c>
     </row>
     <row r="29">
@@ -1414,7 +1414,7 @@
         <v>-2.33</v>
       </c>
       <c r="F29" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>30.774</v>
+        <v>30.727</v>
       </c>
     </row>
     <row r="30">
@@ -1448,7 +1448,7 @@
         <v>0.87</v>
       </c>
       <c r="F30" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>11.973</v>
+        <v>11.959</v>
       </c>
     </row>
     <row r="31">
@@ -1482,7 +1482,7 @@
         <v>-1.68</v>
       </c>
       <c r="F31" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3.49</v>
+        <v>3.487</v>
       </c>
     </row>
     <row r="32">
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1550,7 +1550,7 @@
         <v>1.32</v>
       </c>
       <c r="F33" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6.231</v>
+        <v>6.229</v>
       </c>
     </row>
     <row r="34">
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.148</v>
+        <v>2.146</v>
       </c>
     </row>
     <row r="35">
@@ -1632,35 +1632,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>284.5</v>
+        <v>68.5</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="F36" t="n">
         <v>54</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.6850000000000001</v>
+        <v>2.216</v>
       </c>
     </row>
     <row r="37">
@@ -1700,58 +1700,58 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>68.5</v>
+        <v>184.5</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.58</v>
+        <v>2.5</v>
       </c>
       <c r="F38" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.216</v>
+        <v>9.532999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>184.5</v>
+        <v>284.5</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>53</v>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>9.536</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1802,69 +1802,69 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>150</v>
+        <v>110.5</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.96</v>
+        <v>1.38</v>
       </c>
       <c r="F41" t="n">
         <v>49</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.559</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>110.5</v>
+        <v>150</v>
       </c>
       <c r="E42" t="n">
-        <v>1.38</v>
+        <v>-1.96</v>
       </c>
       <c r="F42" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.33</v>
+        <v>2.558</v>
       </c>
     </row>
     <row r="43">
@@ -1890,7 +1890,7 @@
         <v>0.27</v>
       </c>
       <c r="F43" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8.787000000000001</v>
+        <v>8.763999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -1924,7 +1924,7 @@
         <v>1.23</v>
       </c>
       <c r="F44" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6.18</v>
+        <v>6.177</v>
       </c>
     </row>
     <row r="45">
@@ -1958,7 +1958,7 @@
         <v>-0.58</v>
       </c>
       <c r="F45" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>20.512</v>
+        <v>20.501</v>
       </c>
     </row>
     <row r="46">
@@ -1992,7 +1992,7 @@
         <v>0.17</v>
       </c>
       <c r="F46" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.68</v>
+        <v>3.678</v>
       </c>
     </row>
     <row r="47">
@@ -2026,7 +2026,7 @@
         <v>0.18</v>
       </c>
       <c r="F47" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.844</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="48">
@@ -2128,7 +2128,7 @@
         <v>-0.8</v>
       </c>
       <c r="F50" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>7.267</v>
+        <v>7.266</v>
       </c>
     </row>
   </sheetData>
@@ -2286,7 +2286,7 @@
         <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>15.082</v>
+        <v>15.059</v>
       </c>
     </row>
     <row r="3">
@@ -2314,10 +2314,10 @@
         <v>40.92</v>
       </c>
       <c r="F3" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G3" t="n">
-        <v>6.231</v>
+        <v>6.229</v>
       </c>
     </row>
     <row r="4">
@@ -2345,10 +2345,10 @@
         <v>36.74</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
-        <v>41.175</v>
+        <v>41.018</v>
       </c>
     </row>
     <row r="5">
@@ -2379,7 +2379,7 @@
         <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>30.231</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="6">
@@ -2410,7 +2410,7 @@
         <v>0.89</v>
       </c>
       <c r="G6" t="n">
-        <v>7.267</v>
+        <v>7.266</v>
       </c>
     </row>
     <row r="7">
@@ -2441,7 +2441,7 @@
         <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>9.051</v>
+        <v>9.042</v>
       </c>
     </row>
     <row r="8">
@@ -2472,7 +2472,7 @@
         <v>2.38</v>
       </c>
       <c r="G8" t="n">
-        <v>4.059</v>
+        <v>4.056</v>
       </c>
     </row>
     <row r="9">
@@ -2500,10 +2500,10 @@
         <v>21.89</v>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>5.538</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="10">
@@ -2531,10 +2531,10 @@
         <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>0.804</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="11">
@@ -2562,10 +2562,10 @@
         <v>15.54</v>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="G11" t="n">
-        <v>11.973</v>
+        <v>11.959</v>
       </c>
     </row>
     <row r="12">
@@ -2596,7 +2596,7 @@
         <v>1.42</v>
       </c>
       <c r="G12" t="n">
-        <v>2.489</v>
+        <v>2.488</v>
       </c>
     </row>
     <row r="13">
@@ -2624,10 +2624,10 @@
         <v>12.68</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="G13" t="n">
-        <v>15.927</v>
+        <v>15.918</v>
       </c>
     </row>
     <row r="14">
@@ -2655,10 +2655,10 @@
         <v>7.91</v>
       </c>
       <c r="F14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="G14" t="n">
-        <v>20.484</v>
+        <v>20.422</v>
       </c>
     </row>
     <row r="15">
@@ -2813,7 +2813,7 @@
         <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.054</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="20">
@@ -2844,7 +2844,7 @@
         <v>0.96</v>
       </c>
       <c r="G20" t="n">
-        <v>2.559</v>
+        <v>2.558</v>
       </c>
     </row>
     <row r="21">
@@ -2875,7 +2875,7 @@
         <v>0.78</v>
       </c>
       <c r="G21" t="n">
-        <v>0.55</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="22">
@@ -2906,7 +2906,7 @@
         <v>0.76</v>
       </c>
       <c r="G22" t="n">
-        <v>2.148</v>
+        <v>2.146</v>
       </c>
     </row>
     <row r="23">
@@ -2937,7 +2937,7 @@
         <v>1.25</v>
       </c>
       <c r="G23" t="n">
-        <v>3.68</v>
+        <v>3.678</v>
       </c>
     </row>
     <row r="24">
@@ -2968,7 +2968,7 @@
         <v>1.68</v>
       </c>
       <c r="G24" t="n">
-        <v>2.76</v>
+        <v>2.759</v>
       </c>
     </row>
     <row r="25">
@@ -2999,7 +2999,7 @@
         <v>0.89</v>
       </c>
       <c r="G25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.297000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3027,10 +3027,10 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G26" t="n">
-        <v>46.103</v>
+        <v>45.951</v>
       </c>
     </row>
     <row r="27">
@@ -3092,7 +3092,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>9.536</v>
+        <v>9.532999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3120,10 +3120,10 @@
         <v>2.79</v>
       </c>
       <c r="F29" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G29" t="n">
-        <v>0.57</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3151,7 +3151,7 @@
         <v>2.09</v>
       </c>
       <c r="F30" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G30" t="n">
         <v>0.145</v>
@@ -3244,10 +3244,10 @@
         <v>1.5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G33" t="n">
-        <v>4.833</v>
+        <v>4.827</v>
       </c>
     </row>
     <row r="34">
@@ -3278,7 +3278,7 @@
         <v>0.84</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3309,7 +3309,7 @@
         <v>1.11</v>
       </c>
       <c r="G35" t="n">
-        <v>7.52</v>
+        <v>7.504</v>
       </c>
     </row>
     <row r="36">
@@ -3340,7 +3340,7 @@
         <v>1.12</v>
       </c>
       <c r="G36" t="n">
-        <v>1.692</v>
+        <v>1.689</v>
       </c>
     </row>
     <row r="37">
@@ -3368,10 +3368,10 @@
         <v>-1.04</v>
       </c>
       <c r="F37" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G37" t="n">
-        <v>9.242000000000001</v>
+        <v>9.223000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3402,7 +3402,7 @@
         <v>0.63</v>
       </c>
       <c r="G38" t="n">
-        <v>0.844</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="39">
@@ -3430,10 +3430,10 @@
         <v>-1.39</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G39" t="n">
-        <v>8.741</v>
+        <v>8.701000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3461,10 +3461,10 @@
         <v>-1.75</v>
       </c>
       <c r="F40" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G40" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="41">
@@ -3492,10 +3492,10 @@
         <v>-1.82</v>
       </c>
       <c r="F41" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="G41" t="n">
-        <v>8.787000000000001</v>
+        <v>8.763999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3588,7 +3588,7 @@
         <v>0.67</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -3616,10 +3616,10 @@
         <v>-4.65</v>
       </c>
       <c r="F45" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="G45" t="n">
-        <v>6.18</v>
+        <v>6.177</v>
       </c>
     </row>
     <row r="46">
@@ -3647,10 +3647,10 @@
         <v>-4.7</v>
       </c>
       <c r="F46" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="G46" t="n">
-        <v>2.087</v>
+        <v>2.082</v>
       </c>
     </row>
     <row r="47">
@@ -3709,10 +3709,10 @@
         <v>-7.02</v>
       </c>
       <c r="F48" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="G48" t="n">
-        <v>30.774</v>
+        <v>30.727</v>
       </c>
     </row>
     <row r="49">
@@ -3740,10 +3740,10 @@
         <v>-7.8</v>
       </c>
       <c r="F49" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G49" t="n">
-        <v>20.512</v>
+        <v>20.501</v>
       </c>
     </row>
     <row r="50">
@@ -3774,7 +3774,7 @@
         <v>1.01</v>
       </c>
       <c r="G50" t="n">
-        <v>3.49</v>
+        <v>3.487</v>
       </c>
     </row>
     <row r="51">
@@ -3833,10 +3833,10 @@
         <v>-22.71</v>
       </c>
       <c r="F52" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="G52" t="n">
-        <v>0.282</v>
+        <v>0.281</v>
       </c>
     </row>
   </sheetData>
@@ -3890,10 +3890,10 @@
         <v>40.92</v>
       </c>
       <c r="C2" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="D2" t="n">
-        <v>6.231</v>
+        <v>6.229</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3909,10 +3909,10 @@
         <v>36.74</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="D3" t="n">
-        <v>41.175</v>
+        <v>41.018</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3931,7 +3931,7 @@
         <v>1.68</v>
       </c>
       <c r="D4" t="n">
-        <v>9.051</v>
+        <v>9.042</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3947,10 +3947,10 @@
         <v>21.89</v>
       </c>
       <c r="C5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.538</v>
+        <v>5.526</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3966,10 +3966,10 @@
         <v>21.09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.085</v>
+        <v>1.08</v>
       </c>
       <c r="D6" t="n">
-        <v>23.869</v>
+        <v>23.823</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -3985,10 +3985,10 @@
         <v>16.48</v>
       </c>
       <c r="C7" t="n">
-        <v>1.075</v>
+        <v>1.07</v>
       </c>
       <c r="D7" t="n">
-        <v>76.334</v>
+        <v>76.161</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -4004,10 +4004,10 @@
         <v>15.54</v>
       </c>
       <c r="C8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="D8" t="n">
-        <v>11.973</v>
+        <v>11.959</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4026,7 +4026,7 @@
         <v>1.815</v>
       </c>
       <c r="D9" t="n">
-        <v>7.739000000000001</v>
+        <v>7.734</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -4045,7 +4045,7 @@
         <v>1.42</v>
       </c>
       <c r="D10" t="n">
-        <v>2.489</v>
+        <v>2.488</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4061,10 +4061,10 @@
         <v>11.87333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8099999999999999</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="D11" t="n">
-        <v>23.524</v>
+        <v>23.514</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -4083,7 +4083,7 @@
         <v>0.874</v>
       </c>
       <c r="D12" t="n">
-        <v>9.222000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
@@ -4121,7 +4121,7 @@
         <v>1.2</v>
       </c>
       <c r="D14" t="n">
-        <v>2.054</v>
+        <v>2.05</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4140,7 +4140,7 @@
         <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4159,7 +4159,7 @@
         <v>0.6866666666666666</v>
       </c>
       <c r="D16" t="n">
-        <v>6.919</v>
+        <v>6.917</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -4175,10 +4175,10 @@
         <v>2.79</v>
       </c>
       <c r="C17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="D17" t="n">
-        <v>0.57</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4194,7 +4194,7 @@
         <v>2.09</v>
       </c>
       <c r="C18" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="D18" t="n">
         <v>0.145</v>
@@ -4213,10 +4213,10 @@
         <v>1.63</v>
       </c>
       <c r="C19" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>26.664</v>
+        <v>26.599</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -4251,10 +4251,10 @@
         <v>1.265</v>
       </c>
       <c r="C21" t="n">
-        <v>1.635</v>
+        <v>1.63</v>
       </c>
       <c r="D21" t="n">
-        <v>12.002</v>
+        <v>11.982</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -4273,7 +4273,7 @@
         <v>0.84</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4292,7 +4292,7 @@
         <v>1.12</v>
       </c>
       <c r="D23" t="n">
-        <v>1.692</v>
+        <v>1.689</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4308,10 +4308,10 @@
         <v>-1.25</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8575</v>
+        <v>0.855</v>
       </c>
       <c r="D24" t="n">
-        <v>22.809</v>
+        <v>22.784</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -4327,10 +4327,10 @@
         <v>-1.39</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="D25" t="n">
-        <v>8.741</v>
+        <v>8.701000000000001</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4346,10 +4346,10 @@
         <v>-2.075</v>
       </c>
       <c r="C26" t="n">
-        <v>1.325</v>
+        <v>1.32</v>
       </c>
       <c r="D26" t="n">
-        <v>1.084</v>
+        <v>1.083</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -4384,10 +4384,10 @@
         <v>-2.855</v>
       </c>
       <c r="C28" t="n">
-        <v>1.475</v>
+        <v>1.465</v>
       </c>
       <c r="D28" t="n">
-        <v>1.086</v>
+        <v>1.083</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -4403,10 +4403,10 @@
         <v>-3.44</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="D29" t="n">
-        <v>3.616</v>
+        <v>3.609</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -4422,10 +4422,10 @@
         <v>-7.02</v>
       </c>
       <c r="C30" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="D30" t="n">
-        <v>30.774</v>
+        <v>30.727</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4441,10 +4441,10 @@
         <v>-7.8</v>
       </c>
       <c r="C31" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="D31" t="n">
-        <v>20.512</v>
+        <v>20.501</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
         <v>1.01</v>
       </c>
       <c r="D32" t="n">
-        <v>3.49</v>
+        <v>3.487</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4596,10 +4596,10 @@
         <v>4.57</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4</v>
+        <v>-4.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4648,10 +4648,10 @@
         <v>4.46</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5</v>
+        <v>-7.8</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
         <v>5.26</v>
       </c>
       <c r="L4" t="n">
-        <v>-19.7</v>
+        <v>-21.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>7.43</v>
       </c>
       <c r="L5" t="n">
-        <v>-43.2</v>
+        <v>-43.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>5.98</v>
       </c>
       <c r="L6" t="n">
-        <v>-87.5</v>
+        <v>-88</v>
       </c>
       <c r="M6" t="n">
         <v>0.89</v>
@@ -4856,7 +4856,7 @@
         <v>1.81</v>
       </c>
       <c r="L7" t="n">
-        <v>14.1</v>
+        <v>10.2</v>
       </c>
       <c r="M7" t="n">
         <v>1.11</v>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -4584,7 +4584,7 @@
         <v>58.21</v>
       </c>
       <c r="H2" t="n">
-        <v>34.7304</v>
+        <v>46.851</v>
       </c>
       <c r="I2" t="n">
         <v>65.09999999999999</v>
@@ -4636,7 +4636,7 @@
         <v>74.44</v>
       </c>
       <c r="H3" t="n">
-        <v>292.7155</v>
+        <v>308.6067</v>
       </c>
       <c r="I3" t="n">
         <v>96.59999999999999</v>
@@ -4688,7 +4688,7 @@
         <v>17.01</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.9622</v>
+        <v>-6.5291</v>
       </c>
       <c r="I4" t="n">
         <v>22.4</v>
@@ -4740,7 +4740,7 @@
         <v>66.67</v>
       </c>
       <c r="H5" t="n">
-        <v>24.7975</v>
+        <v>26.6613</v>
       </c>
       <c r="I5" t="n">
         <v>73.59999999999999</v>
@@ -4792,7 +4792,7 @@
         <v>56.25</v>
       </c>
       <c r="H6" t="n">
-        <v>35.8479</v>
+        <v>38.1546</v>
       </c>
       <c r="I6" t="n">
         <v>73.59999999999999</v>
@@ -4844,7 +4844,7 @@
         <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0124</v>
+        <v>0.8746</v>
       </c>
       <c r="I7" t="n">
         <v>43.5</v>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>276</v>
+        <v>303.5</v>
       </c>
       <c r="E2" t="n">
         <v>9.960000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>316</v>
+        <v>430</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>112</v>
+        <v>178.5</v>
       </c>
       <c r="E3" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="F3" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,67 +538,67 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.056</v>
+        <v>2.717</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.3</v>
+        <v>210</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.73</v>
+        <v>1.69</v>
       </c>
       <c r="F4" t="n">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.344</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>188.5</v>
+        <v>4910</v>
       </c>
       <c r="E5" t="n">
-        <v>2.17</v>
+        <v>-7.1</v>
       </c>
       <c r="F5" t="n">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,101 +606,101 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.759</v>
+        <v>40.317</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>206.5</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="n">
-        <v>1.23</v>
+        <v>0.8</v>
       </c>
       <c r="F6" t="n">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.802</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>104.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.98</v>
+        <v>-6.7</v>
       </c>
       <c r="F7" t="n">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.739</v>
+        <v>3.947</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>543</v>
+        <v>88.7</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.37</v>
+        <v>4.85</v>
       </c>
       <c r="F8" t="n">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,67 +708,67 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.689</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>250.5</v>
+        <v>2475</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.15</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7.504</v>
+        <v>47.428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>749</v>
+        <v>1835</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.58</v>
+        <v>-3.93</v>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,109 +776,109 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.05</v>
+        <v>19.738</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2125</v>
+        <v>3305</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.06</v>
+        <v>2.32</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8.701000000000001</v>
+        <v>5.755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>948</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.21</v>
+        <v>0.78</v>
       </c>
       <c r="F12" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>9.223000000000001</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5285</v>
+        <v>760</v>
       </c>
       <c r="E13" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="F13" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>41.018</v>
+        <v>2.154</v>
       </c>
     </row>
     <row r="14">
@@ -898,183 +898,183 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>311</v>
+        <v>294.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3</v>
+        <v>-5.31</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.042</v>
+        <v>8.204000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3230</v>
+        <v>250.5</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.526</v>
+        <v>7.502</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.65</v>
+        <v>945</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.459</v>
+        <v>9.101000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>84.59999999999999</v>
+        <v>189</v>
       </c>
       <c r="E17" t="n">
-        <v>0.83</v>
+        <v>0.27</v>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.281</v>
+        <v>2.723</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>154</v>
+        <v>540</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.75</v>
+        <v>-0.55</v>
       </c>
       <c r="F18" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>30.21</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8525</v>
+        <v>151.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15.059</v>
+        <v>2.567</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1910</v>
+        <v>687</v>
       </c>
       <c r="E20" t="n">
-        <v>0.53</v>
+        <v>-1.72</v>
       </c>
       <c r="F20" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,143 +1116,143 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>20.422</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>378</v>
+        <v>68.7</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.31</v>
+        <v>0.29</v>
       </c>
       <c r="F21" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.082</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>170.5</v>
+        <v>49.1</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.45</v>
+        <v>-1.01</v>
       </c>
       <c r="F22" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.488</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>41.5</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5</v>
+        <v>-1.19</v>
       </c>
       <c r="F23" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9.297000000000001</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2475</v>
+        <v>111.5</v>
       </c>
       <c r="E24" t="n">
-        <v>-1</v>
+        <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>45.951</v>
+        <v>2.572</v>
       </c>
     </row>
     <row r="25">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.45</v>
+        <v>26.05</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.12</v>
+        <v>-1.51</v>
       </c>
       <c r="F25" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.549</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>502</v>
+        <v>238</v>
       </c>
       <c r="E26" t="n">
-        <v>1.01</v>
+        <v>-2.06</v>
       </c>
       <c r="F26" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,33 +1320,33 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>15.918</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>59.9</v>
+        <v>281</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8</v>
+        <v>-2.09</v>
       </c>
       <c r="F27" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.92</v>
+        <v>5.554</v>
       </c>
     </row>
     <row r="28">
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>338.5</v>
+        <v>336.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.88</v>
+        <v>-0.59</v>
       </c>
       <c r="F28" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,101 +1388,101 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.827</v>
+        <v>4.789</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>503</v>
+        <v>286</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.33</v>
+        <v>0.53</v>
       </c>
       <c r="F29" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>30.727</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>699</v>
+        <v>59.2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.87</v>
+        <v>-1.17</v>
       </c>
       <c r="F30" t="n">
         <v>62</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>11.959</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>117</v>
+        <v>185.5</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.68</v>
+        <v>0.54</v>
       </c>
       <c r="F31" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3.487</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1480</v>
+        <v>7925</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-7.04</v>
       </c>
       <c r="F32" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.6820000000000001</v>
+        <v>13.701</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>306.5</v>
+        <v>153.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1.32</v>
+        <v>-0.32</v>
       </c>
       <c r="F33" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6.229</v>
+        <v>28.511</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-2.09</v>
       </c>
       <c r="F34" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.146</v>
+        <v>3.341</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>64.09999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="E35" t="n">
-        <v>1.58</v>
+        <v>-2.01</v>
       </c>
       <c r="F35" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.906</v>
+        <v>2.449</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>68.5</v>
+        <v>1475</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="F36" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.216</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>67.59999999999999</v>
+        <v>2115</v>
       </c>
       <c r="E37" t="n">
-        <v>0.15</v>
+        <v>-0.47</v>
       </c>
       <c r="F37" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.09</v>
+        <v>8.599</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>184.5</v>
+        <v>111</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>-3.9</v>
       </c>
       <c r="F38" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,30 +1728,30 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>9.532999999999999</v>
+        <v>2.063</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>284.5</v>
+        <v>377</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="F39" t="n">
         <v>53</v>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.6840000000000001</v>
+        <v>2.003</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>110.5</v>
+        <v>118.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9</v>
+        <v>1.28</v>
       </c>
       <c r="F40" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,135 +1796,135 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2.548</v>
+        <v>3.445</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>110.5</v>
+        <v>493</v>
       </c>
       <c r="E41" t="n">
-        <v>1.38</v>
+        <v>-1.79</v>
       </c>
       <c r="F41" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.33</v>
+        <v>14.816</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>150</v>
+        <v>3685</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.96</v>
+        <v>-2.25</v>
       </c>
       <c r="F42" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.558</v>
+        <v>8.439</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3770</v>
+        <v>72.3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8.763999999999999</v>
+        <v>9.105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>287</v>
+        <v>20.1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.23</v>
+        <v>-0.99</v>
       </c>
       <c r="F44" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,67 +1932,67 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6.177</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>171.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.58</v>
+        <v>0.74</v>
       </c>
       <c r="F45" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>20.501</v>
+        <v>1.098</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>287</v>
+        <v>506</v>
       </c>
       <c r="E46" t="n">
-        <v>0.17</v>
+        <v>0.6</v>
       </c>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.678</v>
+        <v>29.625</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>272.5</v>
+        <v>174</v>
       </c>
       <c r="E47" t="n">
-        <v>0.18</v>
+        <v>1.46</v>
       </c>
       <c r="F47" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.843</v>
+        <v>19.878</v>
       </c>
     </row>
     <row r="48">
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29.25</v>
+        <v>29.2</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="F48" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2074,27 +2074,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>115.5</v>
+        <v>297.5</v>
       </c>
       <c r="E49" t="n">
-        <v>1.76</v>
+        <v>-2.94</v>
       </c>
       <c r="F49" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.214</v>
+        <v>5.893</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>49.6</v>
+        <v>110</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.8</v>
+        <v>-0.45</v>
       </c>
       <c r="F50" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,41 +2136,41 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.349</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>59.6</v>
+        <v>272</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.5</v>
+        <v>-0.18</v>
       </c>
       <c r="F51" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.557</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="E52" t="n">
-        <v>0.36</v>
+        <v>-1.99</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>7.266</v>
+        <v>7.095</v>
       </c>
     </row>
   </sheetData>
@@ -2280,447 +2280,447 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>31.75</v>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
-        <v>15.059</v>
+        <v>13.701</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40.92</v>
+        <v>30.12</v>
       </c>
       <c r="F3" t="n">
-        <v>0.67</v>
+        <v>1.08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.229</v>
+        <v>5.755</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36.74</v>
+        <v>25.12</v>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>0.61</v>
       </c>
       <c r="G4" t="n">
-        <v>41.018</v>
+        <v>7.095</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29.96</v>
+        <v>24.48</v>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>0.58</v>
       </c>
       <c r="G5" t="n">
-        <v>30.21</v>
+        <v>5.893</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27.94</v>
+        <v>23.21</v>
       </c>
       <c r="F6" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="G6" t="n">
-        <v>7.266</v>
+        <v>40.317</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25.66</v>
+        <v>18.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>0.89</v>
       </c>
       <c r="G7" t="n">
-        <v>9.042</v>
+        <v>28.511</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>24.03</v>
+        <v>16.67</v>
       </c>
       <c r="F8" t="n">
-        <v>2.38</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
-        <v>4.056</v>
+        <v>2.717</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21.89</v>
+        <v>16.34</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
-        <v>5.526</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>15.47</v>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="G10" t="n">
-        <v>0.802</v>
+        <v>3.947</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15.54</v>
+        <v>14.31</v>
       </c>
       <c r="F11" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="G11" t="n">
-        <v>11.959</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.91</v>
+        <v>12.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1.42</v>
+        <v>0.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.488</v>
+        <v>14.816</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12.68</v>
+        <v>10.63</v>
       </c>
       <c r="F13" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="G13" t="n">
-        <v>15.918</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.91</v>
+        <v>9.07</v>
       </c>
       <c r="F14" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="G14" t="n">
-        <v>20.422</v>
+        <v>8.204000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>1.19</v>
       </c>
       <c r="G15" t="n">
-        <v>2.548</v>
+        <v>2.154</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.48</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8</v>
+        <v>1.23</v>
       </c>
       <c r="G16" t="n">
-        <v>1.349</v>
+        <v>1.098</v>
       </c>
     </row>
     <row r="17">
@@ -2745,308 +2745,308 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.37</v>
+        <v>6.68</v>
       </c>
       <c r="F17" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="G17" t="n">
-        <v>2.216</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.46</v>
+        <v>5.69</v>
       </c>
       <c r="F18" t="n">
-        <v>1.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>1.09</v>
+        <v>2.572</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.25</v>
+        <v>5.21</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>2.05</v>
+        <v>2.567</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.01</v>
+        <v>4.21</v>
       </c>
       <c r="F20" t="n">
-        <v>0.96</v>
+        <v>0.66</v>
       </c>
       <c r="G20" t="n">
-        <v>2.558</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.59</v>
+        <v>3.91</v>
       </c>
       <c r="F21" t="n">
-        <v>0.78</v>
+        <v>0.48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.549</v>
+        <v>2.449</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.52</v>
+        <v>3.29</v>
       </c>
       <c r="F22" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="G22" t="n">
-        <v>2.146</v>
+        <v>9.105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.61</v>
+        <v>3.17</v>
       </c>
       <c r="F23" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="G23" t="n">
-        <v>3.678</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.57</v>
+        <v>3.03</v>
       </c>
       <c r="F24" t="n">
-        <v>1.68</v>
+        <v>0.68</v>
       </c>
       <c r="G24" t="n">
-        <v>2.759</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>0.89</v>
+        <v>1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>9.297000000000001</v>
+        <v>2.723</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1</v>
+        <v>0.48</v>
       </c>
       <c r="G26" t="n">
-        <v>45.951</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3055,261 +3055,261 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="F27" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="G27" t="n">
-        <v>2.557</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="G28" t="n">
-        <v>9.532999999999999</v>
+        <v>47.428</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.79</v>
+        <v>1.87</v>
       </c>
       <c r="F29" t="n">
-        <v>1.85</v>
+        <v>0.66</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5669999999999999</v>
+        <v>1.234</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="G30" t="n">
-        <v>0.145</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="F31" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="G31" t="n">
-        <v>2.214</v>
+        <v>4.789</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.58</v>
+        <v>0.27</v>
       </c>
       <c r="F32" t="n">
-        <v>0.64</v>
+        <v>1.17</v>
       </c>
       <c r="G32" t="n">
-        <v>1.906</v>
+        <v>19.738</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>-0.45</v>
       </c>
       <c r="F33" t="n">
-        <v>0.82</v>
+        <v>0.53</v>
       </c>
       <c r="G33" t="n">
-        <v>4.827</v>
+        <v>2.063</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.02</v>
+        <v>-0.55</v>
       </c>
       <c r="F34" t="n">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.6</v>
+        <v>-0.72</v>
       </c>
       <c r="F35" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="G35" t="n">
-        <v>7.504</v>
+        <v>0.718</v>
       </c>
     </row>
     <row r="36">
@@ -3334,478 +3334,478 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="F36" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1.689</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-1.04</v>
+        <v>-0.99</v>
       </c>
       <c r="F37" t="n">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="G37" t="n">
-        <v>9.223000000000001</v>
+        <v>7.502</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.09</v>
+        <v>-1.23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.63</v>
+        <v>1.18</v>
       </c>
       <c r="G38" t="n">
-        <v>0.843</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.39</v>
+        <v>-1.31</v>
       </c>
       <c r="F39" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="G39" t="n">
-        <v>8.701000000000001</v>
+        <v>0.476</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.75</v>
+        <v>-1.63</v>
       </c>
       <c r="F40" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.739</v>
+        <v>8.599</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.82</v>
+        <v>-2.09</v>
       </c>
       <c r="F41" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="G41" t="n">
-        <v>8.763999999999999</v>
+        <v>3.341</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.4</v>
+        <v>-2.72</v>
       </c>
       <c r="F42" t="n">
-        <v>1.31</v>
+        <v>0.72</v>
       </c>
       <c r="G42" t="n">
-        <v>0.344</v>
+        <v>0.651</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.61</v>
+        <v>-2.78</v>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="G43" t="n">
-        <v>0.459</v>
+        <v>9.101000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-4.53</v>
+        <v>-4.13</v>
       </c>
       <c r="F44" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6840000000000001</v>
+        <v>19.878</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-4.65</v>
+        <v>-4.14</v>
       </c>
       <c r="F45" t="n">
         <v>0.73</v>
       </c>
       <c r="G45" t="n">
-        <v>6.177</v>
+        <v>2.003</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-4.7</v>
+        <v>-5.03</v>
       </c>
       <c r="F46" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="G46" t="n">
-        <v>2.082</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5</v>
+        <v>-6.3</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="G47" t="n">
-        <v>0.33</v>
+        <v>29.625</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-7.02</v>
+        <v>-6.32</v>
       </c>
       <c r="F48" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="G48" t="n">
-        <v>30.727</v>
+        <v>3.445</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-7.8</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="G49" t="n">
-        <v>20.501</v>
+        <v>8.439</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-8.24</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>1.01</v>
+        <v>0.64</v>
       </c>
       <c r="G50" t="n">
-        <v>3.487</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-8.69</v>
+        <v>-11.5</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>0.92</v>
+        <v>5.554</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-22.71</v>
+        <v>-18.59</v>
       </c>
       <c r="F52" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="G52" t="n">
-        <v>0.281</v>
+        <v>0.306</v>
       </c>
     </row>
   </sheetData>
@@ -3883,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.92</v>
+        <v>30.12</v>
       </c>
       <c r="C2" t="n">
-        <v>0.67</v>
+        <v>1.08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.229</v>
+        <v>5.755</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.74</v>
+        <v>24.48</v>
       </c>
       <c r="C3" t="n">
-        <v>1.09</v>
+        <v>0.58</v>
       </c>
       <c r="D3" t="n">
-        <v>41.018</v>
+        <v>5.893</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,17 +3921,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.66</v>
+        <v>23.21</v>
       </c>
       <c r="C4" t="n">
-        <v>1.68</v>
+        <v>1.13</v>
       </c>
       <c r="D4" t="n">
-        <v>9.042</v>
+        <v>40.317</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3940,17 +3940,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.89</v>
+        <v>16.67</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="D5" t="n">
-        <v>5.526</v>
+        <v>2.717</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,36 +3959,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.09</v>
+        <v>14.31</v>
       </c>
       <c r="C6" t="n">
-        <v>1.08</v>
+        <v>1.99</v>
       </c>
       <c r="D6" t="n">
-        <v>23.823</v>
+        <v>0.78</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.48</v>
+        <v>11.555</v>
       </c>
       <c r="C7" t="n">
-        <v>1.07</v>
+        <v>0.855</v>
       </c>
       <c r="D7" t="n">
-        <v>76.161</v>
+        <v>22.14</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -3997,96 +3997,96 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.54</v>
+        <v>10.79666666666667</v>
       </c>
       <c r="C8" t="n">
-        <v>1.03</v>
+        <v>0.6366666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>11.959</v>
+        <v>22.226</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.82</v>
+        <v>10.63</v>
       </c>
       <c r="C9" t="n">
-        <v>1.815</v>
+        <v>0.92</v>
       </c>
       <c r="D9" t="n">
-        <v>7.734</v>
+        <v>11.64</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.91</v>
+        <v>10.325</v>
       </c>
       <c r="C10" t="n">
-        <v>1.42</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>2.488</v>
+        <v>75.93899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.87333333333333</v>
+        <v>9.07</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8066666666666666</v>
+        <v>1.55</v>
       </c>
       <c r="D11" t="n">
-        <v>23.514</v>
+        <v>8.204000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.85</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>0.874</v>
+        <v>1.19</v>
       </c>
       <c r="D12" t="n">
-        <v>9.220000000000001</v>
+        <v>2.154</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.46</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="D13" t="n">
-        <v>1.09</v>
+        <v>1.098</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,74 +4111,74 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.25</v>
+        <v>6.69</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2</v>
+        <v>1.74</v>
       </c>
       <c r="D14" t="n">
-        <v>2.05</v>
+        <v>7.288</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.45</v>
+        <v>4.524</v>
       </c>
       <c r="C15" t="n">
-        <v>0.89</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>9.297000000000001</v>
+        <v>9.173999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.073333333333333</v>
+        <v>3.29</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.74</v>
       </c>
       <c r="D16" t="n">
-        <v>6.917</v>
+        <v>9.105</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="C17" t="n">
-        <v>1.85</v>
+        <v>0.68</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5669999999999999</v>
+        <v>1.925</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.09</v>
+        <v>2.82</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9</v>
+        <v>0.48</v>
       </c>
       <c r="D18" t="n">
         <v>0.145</v>
@@ -4206,36 +4206,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>26.599</v>
+        <v>6.592000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="C20" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="D20" t="n">
-        <v>1.906</v>
+        <v>0.672</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4248,13 +4248,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.265</v>
+        <v>0.1100000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>1.63</v>
+        <v>1.545</v>
       </c>
       <c r="D21" t="n">
-        <v>11.982</v>
+        <v>11.824</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -4263,17 +4263,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.02</v>
+        <v>-0.92</v>
       </c>
       <c r="C22" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6820000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,20 +4282,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.91</v>
+        <v>-0.975</v>
       </c>
       <c r="C23" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="D23" t="n">
-        <v>1.689</v>
+        <v>1.04</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -4305,13 +4305,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.25</v>
+        <v>-1.09</v>
       </c>
       <c r="C24" t="n">
-        <v>0.855</v>
+        <v>0.745</v>
       </c>
       <c r="D24" t="n">
-        <v>22.784</v>
+        <v>22.833</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -4320,55 +4320,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.39</v>
+        <v>-1.125</v>
       </c>
       <c r="C25" t="n">
-        <v>1.28</v>
+        <v>1.425</v>
       </c>
       <c r="D25" t="n">
-        <v>8.701000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.075</v>
+        <v>-1.31</v>
       </c>
       <c r="C26" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.083</v>
+        <v>0.476</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.61</v>
+        <v>-1.63</v>
       </c>
       <c r="C27" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.459</v>
+        <v>8.599</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,74 +4377,74 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.855</v>
+        <v>-2.47</v>
       </c>
       <c r="C28" t="n">
-        <v>1.465</v>
+        <v>0.62</v>
       </c>
       <c r="D28" t="n">
-        <v>1.083</v>
+        <v>3.468</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-3.44</v>
+        <v>-4.13</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.59</v>
       </c>
       <c r="D29" t="n">
-        <v>3.609</v>
+        <v>19.878</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-7.02</v>
+        <v>-5.615</v>
       </c>
       <c r="C30" t="n">
-        <v>0.88</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>30.727</v>
+        <v>25.292</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-7.8</v>
+        <v>-6.3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="D31" t="n">
-        <v>20.501</v>
+        <v>29.625</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-8.24</v>
+        <v>-6.32</v>
       </c>
       <c r="C32" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="D32" t="n">
-        <v>3.487</v>
+        <v>3.445</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2125</v>
+        <v>2115</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.06</v>
+        <v>-0.47</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.39</v>
+        <v>-1.63</v>
       </c>
       <c r="G2" t="n">
-        <v>58.21</v>
+        <v>51.67</v>
       </c>
       <c r="H2" t="n">
-        <v>46.851</v>
+        <v>38.8017</v>
       </c>
       <c r="I2" t="n">
-        <v>65.09999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="J2" t="n">
-        <v>69.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>4.57</v>
+        <v>4.44</v>
       </c>
       <c r="L2" t="n">
-        <v>-4.3</v>
+        <v>-45.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,38 +4624,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5285</v>
+        <v>4910</v>
       </c>
       <c r="E3" t="n">
-        <v>1.93</v>
+        <v>-7.1</v>
       </c>
       <c r="F3" t="n">
-        <v>36.74</v>
+        <v>23.21</v>
       </c>
       <c r="G3" t="n">
-        <v>74.44</v>
+        <v>54.14</v>
       </c>
       <c r="H3" t="n">
-        <v>308.6067</v>
+        <v>278.59</v>
       </c>
       <c r="I3" t="n">
-        <v>96.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>56.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.46</v>
+        <v>4.74</v>
       </c>
       <c r="L3" t="n">
-        <v>-7.8</v>
+        <v>60.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.83</v>
+        <v>4.85</v>
       </c>
       <c r="F4" t="n">
-        <v>-22.71</v>
+        <v>-18.59</v>
       </c>
       <c r="G4" t="n">
-        <v>17.01</v>
+        <v>26.08</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.5291</v>
+        <v>-6.5089</v>
       </c>
       <c r="I4" t="n">
-        <v>22.4</v>
+        <v>34.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>28.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.26</v>
+        <v>5.12</v>
       </c>
       <c r="L4" t="n">
-        <v>-21.2</v>
+        <v>33.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>306.5</v>
+        <v>297.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1.32</v>
+        <v>-2.94</v>
       </c>
       <c r="F5" t="n">
-        <v>40.92</v>
+        <v>24.48</v>
       </c>
       <c r="G5" t="n">
-        <v>66.67</v>
+        <v>54.55</v>
       </c>
       <c r="H5" t="n">
-        <v>26.6613</v>
+        <v>24.2938</v>
       </c>
       <c r="I5" t="n">
-        <v>73.59999999999999</v>
+        <v>62.6</v>
       </c>
       <c r="J5" t="n">
-        <v>81.7</v>
+        <v>62.4</v>
       </c>
       <c r="K5" t="n">
-        <v>7.43</v>
+        <v>7.45</v>
       </c>
       <c r="L5" t="n">
-        <v>-43.8</v>
+        <v>-64.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="E6" t="n">
-        <v>0.36</v>
+        <v>-1.99</v>
       </c>
       <c r="F6" t="n">
-        <v>27.94</v>
+        <v>25.12</v>
       </c>
       <c r="G6" t="n">
-        <v>56.25</v>
+        <v>61.26</v>
       </c>
       <c r="H6" t="n">
-        <v>38.1546</v>
+        <v>34.7263</v>
       </c>
       <c r="I6" t="n">
-        <v>73.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>75</v>
+        <v>49.1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.98</v>
+        <v>5.79</v>
       </c>
       <c r="L6" t="n">
-        <v>-88</v>
+        <v>-92.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4835,31 +4835,31 @@
         <v>250.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.15</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6</v>
+        <v>-0.99</v>
       </c>
       <c r="G7" t="n">
         <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8746</v>
+        <v>-0.1171</v>
       </c>
       <c r="I7" t="n">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="J7" t="n">
         <v>42.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="L7" t="n">
-        <v>10.2</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>303.5</v>
+        <v>333.5</v>
       </c>
       <c r="E2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>430</v>
+        <v>326</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.78</v>
+        <v>1.004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>178.5</v>
+        <v>19.2</v>
       </c>
       <c r="E3" t="n">
-        <v>4.69</v>
+        <v>2.13</v>
       </c>
       <c r="F3" t="n">
-        <v>225</v>
+        <v>321</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.717</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>210</v>
+        <v>207.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1.69</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.864</v>
+        <v>3.216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4910</v>
+        <v>114.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.1</v>
+        <v>9.57</v>
       </c>
       <c r="F5" t="n">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,67 +606,67 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>40.317</v>
+        <v>4.685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>1035</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8</v>
+        <v>9.52</v>
       </c>
       <c r="F6" t="n">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.476</v>
+        <v>10.357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>104.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.7</v>
+        <v>5.42</v>
       </c>
       <c r="F7" t="n">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,67 +674,67 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.947</v>
+        <v>1.995</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>88.7</v>
+        <v>3305</v>
       </c>
       <c r="E8" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.306</v>
+        <v>5.009</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2475</v>
+        <v>114.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="F9" t="n">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,33 +742,33 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>47.428</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1835</v>
+        <v>2480</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.93</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19.738</v>
+        <v>48.066</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3305</v>
+        <v>42.85</v>
       </c>
       <c r="E11" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,67 +810,67 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.755</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64.59999999999999</v>
+        <v>181</v>
       </c>
       <c r="E12" t="n">
-        <v>0.78</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="n">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.925</v>
+        <v>2.846</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>760</v>
+        <v>546</v>
       </c>
       <c r="E13" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="F13" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.154</v>
+        <v>1.671</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>294.5</v>
+        <v>542</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.31</v>
+        <v>9.94</v>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,441 +912,441 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.204000000000001</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>250.5</v>
+        <v>210.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="F15" t="n">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7.502</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>945</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.32</v>
+        <v>2.64</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9.101000000000001</v>
+        <v>1.181</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>189</v>
+        <v>289.5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.27</v>
+        <v>3.02</v>
       </c>
       <c r="F17" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.723</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>540</v>
+        <v>289</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.55</v>
+        <v>1.05</v>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.68</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>151.5</v>
+        <v>75.3</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4.15</v>
       </c>
       <c r="F19" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.567</v>
+        <v>9.218999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>687</v>
+        <v>20.45</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.72</v>
+        <v>1.74</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>11.64</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68.7</v>
+        <v>111</v>
       </c>
       <c r="E21" t="n">
-        <v>0.29</v>
+        <v>-0.45</v>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.25</v>
+        <v>2.347</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49.1</v>
+        <v>1890</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.01</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.234</v>
+        <v>20.494</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41.5</v>
+        <v>4920</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.19</v>
+        <v>0.2</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.718</v>
+        <v>40.239</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>111.5</v>
+        <v>122.5</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9</v>
+        <v>3.38</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.572</v>
+        <v>3.507</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.05</v>
+        <v>251.5</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.51</v>
+        <v>0.4</v>
       </c>
       <c r="F25" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.551</v>
+        <v>7.431</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>238</v>
+        <v>26.1</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.06</v>
+        <v>0.19</v>
       </c>
       <c r="F26" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.08</v>
+        <v>0.517</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>281</v>
+        <v>88.3</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.09</v>
+        <v>-0.45</v>
       </c>
       <c r="F27" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,67 +1354,67 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.554</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>336.5</v>
+        <v>703</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.59</v>
+        <v>2.33</v>
       </c>
       <c r="F28" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.789</v>
+        <v>11.327</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>286</v>
+        <v>2150</v>
       </c>
       <c r="E29" t="n">
-        <v>0.53</v>
+        <v>1.65</v>
       </c>
       <c r="F29" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,67 +1422,67 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.651</v>
+        <v>7.235</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>59.2</v>
+        <v>294.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.17</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.902</v>
+        <v>8.000999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>185.5</v>
+        <v>333.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0.54</v>
+        <v>-0.89</v>
       </c>
       <c r="F31" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9.640000000000001</v>
+        <v>4.677</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7925</v>
+        <v>179.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.04</v>
+        <v>3.16</v>
       </c>
       <c r="F32" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,135 +1524,135 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>13.701</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>153.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.32</v>
+        <v>-0.44</v>
       </c>
       <c r="F33" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>28.511</v>
+        <v>2.195</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>281</v>
+        <v>59.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.09</v>
+        <v>0.51</v>
       </c>
       <c r="F34" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3.341</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>58.4</v>
+        <v>519</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.01</v>
+        <v>2.57</v>
       </c>
       <c r="F35" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.449</v>
+        <v>27.325</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1475</v>
+        <v>760</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.672</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2115</v>
+        <v>151</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.47</v>
+        <v>-0.33</v>
       </c>
       <c r="F37" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,41 +1694,41 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>8.599</v>
+        <v>2.392</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>111</v>
+        <v>1460</v>
       </c>
       <c r="E38" t="n">
-        <v>-3.9</v>
+        <v>-1.02</v>
       </c>
       <c r="F38" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2.063</v>
+        <v>0.662</v>
       </c>
     </row>
     <row r="39">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>377</v>
+        <v>377.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.26</v>
+        <v>0.13</v>
       </c>
       <c r="F39" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.003</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>118.5</v>
+        <v>49.15</v>
       </c>
       <c r="E40" t="n">
-        <v>1.28</v>
+        <v>0.1</v>
       </c>
       <c r="F40" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,101 +1796,101 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.445</v>
+        <v>1.191</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>493</v>
+        <v>279.5</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.79</v>
+        <v>-0.53</v>
       </c>
       <c r="F41" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>14.816</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3685</v>
+        <v>288.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.25</v>
+        <v>-3.03</v>
       </c>
       <c r="F42" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8.439</v>
+        <v>5.464</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>72.3</v>
+        <v>154.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="F43" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,101 +1898,101 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>9.105</v>
+        <v>27.811</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>20.1</v>
+        <v>239.5</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.99</v>
+        <v>0.63</v>
       </c>
       <c r="F44" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.322</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>68.09999999999999</v>
+        <v>3740</v>
       </c>
       <c r="E45" t="n">
-        <v>0.74</v>
+        <v>1.49</v>
       </c>
       <c r="F45" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.098</v>
+        <v>8.398999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>506</v>
+        <v>59.4</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6</v>
+        <v>1.71</v>
       </c>
       <c r="F46" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>29.625</v>
+        <v>1.887</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="E47" t="n">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="F47" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>19.878</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="48">
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29.2</v>
+        <v>29.25</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.17</v>
+        <v>0.17</v>
       </c>
       <c r="F48" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,33 +2068,33 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.145</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>297.5</v>
+        <v>8040</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.94</v>
+        <v>1.45</v>
       </c>
       <c r="F49" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5.893</v>
+        <v>13.352</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>110</v>
+        <v>184.5</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.45</v>
+        <v>-0.54</v>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.315</v>
+        <v>9.417999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>272</v>
+        <v>114</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.18</v>
+        <v>2.7</v>
       </c>
       <c r="F51" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="52">
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.99</v>
+        <v>1.66</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>7.095</v>
+        <v>6.377</v>
       </c>
     </row>
   </sheetData>
@@ -2261,125 +2261,125 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>31.75</v>
+        <v>37.71</v>
       </c>
       <c r="F2" t="n">
-        <v>0.95</v>
+        <v>1.46</v>
       </c>
       <c r="G2" t="n">
-        <v>13.701</v>
+        <v>5.009</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30.12</v>
+        <v>31.8</v>
       </c>
       <c r="F3" t="n">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="G3" t="n">
-        <v>5.755</v>
+        <v>13.352</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25.12</v>
+        <v>31.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.61</v>
+        <v>2.22</v>
       </c>
       <c r="G4" t="n">
-        <v>7.095</v>
+        <v>1.004</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24.48</v>
+        <v>28.51</v>
       </c>
       <c r="F5" t="n">
-        <v>0.58</v>
+        <v>2.25</v>
       </c>
       <c r="G5" t="n">
-        <v>5.893</v>
+        <v>4.685</v>
       </c>
     </row>
     <row r="6">
@@ -2404,75 +2404,75 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23.21</v>
+        <v>25.35</v>
       </c>
       <c r="F6" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="G6" t="n">
-        <v>40.317</v>
+        <v>40.239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.08</v>
+        <v>21.12</v>
       </c>
       <c r="F7" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>28.511</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.67</v>
+        <v>20.38</v>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2.717</v>
+        <v>11.327</v>
       </c>
     </row>
     <row r="9">
@@ -2497,308 +2497,308 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16.34</v>
+        <v>20.29</v>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>0.864</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>15.47</v>
+        <v>19.77</v>
       </c>
       <c r="F10" t="n">
-        <v>2.35</v>
+        <v>0.86</v>
       </c>
       <c r="G10" t="n">
-        <v>3.947</v>
+        <v>27.811</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.31</v>
+        <v>19.47</v>
       </c>
       <c r="F11" t="n">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>0.78</v>
+        <v>2.846</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.3</v>
+        <v>17.28</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="G12" t="n">
-        <v>14.816</v>
+        <v>5.464</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.63</v>
+        <v>16.57</v>
       </c>
       <c r="F13" t="n">
-        <v>0.92</v>
+        <v>1.84</v>
       </c>
       <c r="G13" t="n">
-        <v>11.64</v>
+        <v>3.216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.07</v>
+        <v>15.72</v>
       </c>
       <c r="F14" t="n">
-        <v>1.55</v>
+        <v>0.44</v>
       </c>
       <c r="G14" t="n">
-        <v>8.204000000000001</v>
+        <v>6.377</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>14.59</v>
       </c>
       <c r="F15" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="G15" t="n">
-        <v>2.154</v>
+        <v>8.000999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.789999999999999</v>
+        <v>13.49</v>
       </c>
       <c r="F16" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="G16" t="n">
-        <v>1.098</v>
+        <v>10.357</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.68</v>
+        <v>13.47</v>
       </c>
       <c r="F17" t="n">
-        <v>0.63</v>
+        <v>1.11</v>
       </c>
       <c r="G17" t="n">
-        <v>2.25</v>
+        <v>1.181</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.69</v>
+        <v>9.15</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="G18" t="n">
-        <v>2.572</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2807,230 +2807,230 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.21</v>
+        <v>5.72</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="G19" t="n">
-        <v>2.567</v>
+        <v>2.195</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.21</v>
+        <v>4.86</v>
       </c>
       <c r="F20" t="n">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="G20" t="n">
-        <v>9.640000000000001</v>
+        <v>2.392</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.91</v>
+        <v>4.51</v>
       </c>
       <c r="F21" t="n">
-        <v>0.48</v>
+        <v>0.91</v>
       </c>
       <c r="G21" t="n">
-        <v>2.449</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="F22" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="G22" t="n">
-        <v>9.105</v>
+        <v>9.417999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.17</v>
+        <v>3.42</v>
       </c>
       <c r="F23" t="n">
-        <v>0.64</v>
+        <v>1.13</v>
       </c>
       <c r="G23" t="n">
-        <v>0.551</v>
+        <v>48.066</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="F24" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="G24" t="n">
-        <v>1.925</v>
+        <v>9.218999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="F25" t="n">
-        <v>1.62</v>
+        <v>0.96</v>
       </c>
       <c r="G25" t="n">
-        <v>2.723</v>
+        <v>1.995</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="F26" t="n">
-        <v>0.48</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>0.145</v>
+        <v>20.494</v>
       </c>
     </row>
     <row r="27">
@@ -3055,60 +3055,60 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.81</v>
+        <v>2.57</v>
       </c>
       <c r="F27" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="F28" t="n">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
       <c r="G28" t="n">
-        <v>47.428</v>
+        <v>0.662</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3117,323 +3117,323 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="F29" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="G29" t="n">
-        <v>1.234</v>
+        <v>0.517</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="F30" t="n">
-        <v>0.67</v>
+        <v>1.34</v>
       </c>
       <c r="G30" t="n">
-        <v>0.672</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="F31" t="n">
-        <v>0.66</v>
+        <v>1.43</v>
       </c>
       <c r="G31" t="n">
-        <v>4.789</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.27</v>
+        <v>1.24</v>
       </c>
       <c r="F32" t="n">
-        <v>1.17</v>
+        <v>0.71</v>
       </c>
       <c r="G32" t="n">
-        <v>19.738</v>
+        <v>1.191</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.45</v>
+        <v>1.11</v>
       </c>
       <c r="F33" t="n">
-        <v>0.53</v>
+        <v>1.12</v>
       </c>
       <c r="G33" t="n">
-        <v>2.063</v>
+        <v>1.671</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.55</v>
+        <v>0.99</v>
       </c>
       <c r="F34" t="n">
-        <v>0.41</v>
+        <v>1.33</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.322</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.72</v>
+        <v>0.6</v>
       </c>
       <c r="F35" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.718</v>
+        <v>7.431</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.92</v>
+        <v>0.45</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G36" t="n">
-        <v>1.68</v>
+        <v>2.347</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.99</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.02</v>
+        <v>0.47</v>
       </c>
       <c r="G37" t="n">
-        <v>7.502</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.23</v>
+        <v>-0.17</v>
       </c>
       <c r="F38" t="n">
-        <v>1.18</v>
+        <v>0.6</v>
       </c>
       <c r="G38" t="n">
-        <v>0.322</v>
+        <v>1.887</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.31</v>
+        <v>-0.36</v>
       </c>
       <c r="F39" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="G39" t="n">
-        <v>0.476</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="40">
@@ -3458,153 +3458,153 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.63</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="G40" t="n">
-        <v>8.599</v>
+        <v>7.235</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.09</v>
+        <v>-1.48</v>
       </c>
       <c r="F41" t="n">
-        <v>1.13</v>
+        <v>0.73</v>
       </c>
       <c r="G41" t="n">
-        <v>3.341</v>
+        <v>4.677</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.72</v>
+        <v>-1.56</v>
       </c>
       <c r="F42" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="G42" t="n">
-        <v>0.651</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.78</v>
+        <v>-1.64</v>
       </c>
       <c r="F43" t="n">
-        <v>1.47</v>
+        <v>0.68</v>
       </c>
       <c r="G43" t="n">
-        <v>9.101000000000001</v>
+        <v>18.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-4.13</v>
+        <v>-1.68</v>
       </c>
       <c r="F44" t="n">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
       <c r="G44" t="n">
-        <v>19.878</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3613,106 +3613,106 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-4.14</v>
+        <v>-1.87</v>
       </c>
       <c r="F45" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>2.003</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-5.03</v>
+        <v>-2.78</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="G46" t="n">
-        <v>0.315</v>
+        <v>3.507</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-6.3</v>
+        <v>-4.36</v>
       </c>
       <c r="F47" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="G47" t="n">
-        <v>29.625</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-6.32</v>
+        <v>-4.42</v>
       </c>
       <c r="F48" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="G48" t="n">
-        <v>3.445</v>
+        <v>27.325</v>
       </c>
     </row>
     <row r="49">
@@ -3737,75 +3737,75 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-8.640000000000001</v>
+        <v>-7.5</v>
       </c>
       <c r="F49" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G49" t="n">
-        <v>8.439</v>
+        <v>8.398999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="G50" t="n">
-        <v>0.902</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-11.5</v>
+        <v>-10.79</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="G51" t="n">
-        <v>5.554</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="52">
@@ -3833,10 +3833,10 @@
         <v>-18.59</v>
       </c>
       <c r="F52" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.306</v>
+        <v>0.312</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.12</v>
+        <v>37.71</v>
       </c>
       <c r="C2" t="n">
-        <v>1.08</v>
+        <v>1.46</v>
       </c>
       <c r="D2" t="n">
-        <v>5.755</v>
+        <v>5.009</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.48</v>
+        <v>31.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.58</v>
+        <v>2.22</v>
       </c>
       <c r="D3" t="n">
-        <v>5.893</v>
+        <v>1.004</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3925,13 +3925,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.21</v>
+        <v>25.35</v>
       </c>
       <c r="C4" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="D4" t="n">
-        <v>40.317</v>
+        <v>40.239</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3940,17 +3940,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.67</v>
+        <v>20.38</v>
       </c>
       <c r="C5" t="n">
-        <v>1.38</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>2.717</v>
+        <v>11.327</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,17 +3959,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.31</v>
+        <v>19.47</v>
       </c>
       <c r="C6" t="n">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="D6" t="n">
-        <v>0.78</v>
+        <v>2.846</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3978,93 +3978,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.555</v>
+        <v>17.28</v>
       </c>
       <c r="C7" t="n">
-        <v>0.855</v>
+        <v>0.58</v>
       </c>
       <c r="D7" t="n">
-        <v>22.14</v>
+        <v>5.464</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10.79666666666667</v>
+        <v>16.51</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6366666666666667</v>
+        <v>1.58</v>
       </c>
       <c r="D8" t="n">
-        <v>22.226</v>
+        <v>8.112</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.63</v>
+        <v>15.03</v>
       </c>
       <c r="C9" t="n">
-        <v>0.92</v>
+        <v>1.745</v>
       </c>
       <c r="D9" t="n">
-        <v>11.64</v>
+        <v>13.573</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.325</v>
+        <v>14.59</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9299999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="D10" t="n">
-        <v>75.93899999999999</v>
+        <v>8.000999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.07</v>
+        <v>13.47</v>
       </c>
       <c r="C11" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="D11" t="n">
-        <v>8.204000000000001</v>
+        <v>1.181</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,55 +4073,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>12.15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.19</v>
+        <v>0.7</v>
       </c>
       <c r="D12" t="n">
-        <v>2.154</v>
+        <v>21.751</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8.789999999999999</v>
+        <v>11.76</v>
       </c>
       <c r="C13" t="n">
-        <v>1.23</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>1.098</v>
+        <v>22.767</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.69</v>
+        <v>11.595</v>
       </c>
       <c r="C14" t="n">
-        <v>1.74</v>
+        <v>0.9949999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>7.288</v>
+        <v>75.87700000000001</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -4130,20 +4130,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.524</v>
+        <v>9.15</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6860000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="D15" t="n">
-        <v>9.173999999999999</v>
+        <v>2.12</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4153,13 +4153,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="D16" t="n">
-        <v>9.105</v>
+        <v>9.218999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,36 +4168,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.03</v>
+        <v>2.884</v>
       </c>
       <c r="C17" t="n">
-        <v>0.68</v>
+        <v>0.754</v>
       </c>
       <c r="D17" t="n">
-        <v>1.925</v>
+        <v>8.641999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="C18" t="n">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="D18" t="n">
-        <v>0.145</v>
+        <v>1.995</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4206,58 +4206,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.09</v>
+        <v>2.46</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="D19" t="n">
-        <v>6.592000000000001</v>
+        <v>0.662</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.72</v>
+        <v>1.505</v>
       </c>
       <c r="C20" t="n">
-        <v>0.67</v>
+        <v>1.335</v>
       </c>
       <c r="D20" t="n">
-        <v>0.672</v>
+        <v>1.077</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1100000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="C21" t="n">
-        <v>1.545</v>
+        <v>1.43</v>
       </c>
       <c r="D21" t="n">
-        <v>11.824</v>
+        <v>0.541</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.92</v>
+        <v>1.11</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="D22" t="n">
-        <v>1.68</v>
+        <v>1.671</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,17 +4282,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.975</v>
+        <v>0.8499999999999996</v>
       </c>
       <c r="C23" t="n">
-        <v>1.16</v>
+        <v>1.425</v>
       </c>
       <c r="D23" t="n">
-        <v>1.04</v>
+        <v>1.215</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -4301,55 +4301,55 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.09</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.745</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="D24" t="n">
-        <v>22.833</v>
+        <v>5.825</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.125</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>1.425</v>
+        <v>1.24</v>
       </c>
       <c r="D25" t="n">
-        <v>1.17</v>
+        <v>7.235</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.31</v>
+        <v>-1.64</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="D26" t="n">
-        <v>0.476</v>
+        <v>18.21</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.63</v>
+        <v>-1.68</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1</v>
+        <v>0.42</v>
       </c>
       <c r="D27" t="n">
-        <v>8.599</v>
+        <v>0.137</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,93 +4377,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.47</v>
+        <v>-2.005</v>
       </c>
       <c r="C28" t="n">
-        <v>0.62</v>
+        <v>0.8075</v>
       </c>
       <c r="D28" t="n">
-        <v>3.468</v>
+        <v>22.403</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.13</v>
+        <v>-2.196666666666667</v>
       </c>
       <c r="C29" t="n">
-        <v>0.59</v>
+        <v>0.6366666666666667</v>
       </c>
       <c r="D29" t="n">
-        <v>19.878</v>
+        <v>3.442</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-5.615</v>
+        <v>-2.78</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9299999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="D30" t="n">
-        <v>25.292</v>
+        <v>3.507</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-6.3</v>
+        <v>-2.819999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>0.74</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>29.625</v>
+        <v>25.831</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-6.32</v>
+        <v>-4.42</v>
       </c>
       <c r="C32" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="D32" t="n">
-        <v>3.445</v>
+        <v>27.325</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2115</v>
+        <v>2150</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.47</v>
+        <v>1.65</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.63</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>51.67</v>
+        <v>55.2</v>
       </c>
       <c r="H2" t="n">
-        <v>38.8017</v>
+        <v>34.9447</v>
       </c>
       <c r="I2" t="n">
-        <v>62.9</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>66.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="K2" t="n">
         <v>4.44</v>
       </c>
       <c r="L2" t="n">
-        <v>-45.2</v>
+        <v>-11.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,38 +4624,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4910</v>
+        <v>4920</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.1</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>23.21</v>
+        <v>25.35</v>
       </c>
       <c r="G3" t="n">
-        <v>54.14</v>
+        <v>55.93</v>
       </c>
       <c r="H3" t="n">
-        <v>278.59</v>
+        <v>249.1677</v>
       </c>
       <c r="I3" t="n">
-        <v>69.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>56.1</v>
+        <v>57.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.74</v>
+        <v>4.79</v>
       </c>
       <c r="L3" t="n">
-        <v>60.7</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88.7</v>
+        <v>88.3</v>
       </c>
       <c r="E4" t="n">
-        <v>4.85</v>
+        <v>-0.45</v>
       </c>
       <c r="F4" t="n">
         <v>-18.59</v>
       </c>
       <c r="G4" t="n">
-        <v>26.08</v>
+        <v>29.25</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.5089</v>
+        <v>-6.2051</v>
       </c>
       <c r="I4" t="n">
-        <v>34.7</v>
+        <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>28.9</v>
+        <v>27.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.12</v>
+        <v>4.85</v>
       </c>
       <c r="L4" t="n">
-        <v>33.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>297.5</v>
+        <v>288.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.94</v>
+        <v>-3.03</v>
       </c>
       <c r="F5" t="n">
-        <v>24.48</v>
+        <v>17.28</v>
       </c>
       <c r="G5" t="n">
-        <v>54.55</v>
+        <v>56.41</v>
       </c>
       <c r="H5" t="n">
-        <v>24.2938</v>
+        <v>21.2976</v>
       </c>
       <c r="I5" t="n">
-        <v>62.6</v>
+        <v>50.4</v>
       </c>
       <c r="J5" t="n">
-        <v>62.4</v>
+        <v>43</v>
       </c>
       <c r="K5" t="n">
-        <v>7.45</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
-        <v>-64.7</v>
+        <v>-41.8</v>
       </c>
       <c r="M5" t="n">
         <v>0.58</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.99</v>
+        <v>1.66</v>
       </c>
       <c r="F6" t="n">
-        <v>25.12</v>
+        <v>15.72</v>
       </c>
       <c r="G6" t="n">
-        <v>61.26</v>
+        <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>34.7263</v>
+        <v>32.087</v>
       </c>
       <c r="I6" t="n">
-        <v>64.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="J6" t="n">
-        <v>49.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>5.79</v>
+        <v>5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>-92.2</v>
+        <v>-88</v>
       </c>
       <c r="M6" t="n">
-        <v>0.61</v>
+        <v>0.44</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>250.5</v>
+        <v>251.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.99</v>
+        <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1171</v>
+        <v>-0.1801</v>
       </c>
       <c r="I7" t="n">
-        <v>44.5</v>
+        <v>52.3</v>
       </c>
       <c r="J7" t="n">
-        <v>42.1</v>
+        <v>52.6</v>
       </c>
       <c r="K7" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>-9.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>333.5</v>
+        <v>366.5</v>
       </c>
       <c r="E2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="F2" t="n">
-        <v>326</v>
+        <v>477</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.004</v>
+        <v>1.281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.2</v>
+        <v>211.5</v>
       </c>
       <c r="E3" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="F3" t="n">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.541</v>
+        <v>3.708</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>207.5</v>
+        <v>1085</v>
       </c>
       <c r="E4" t="n">
-        <v>9.789999999999999</v>
+        <v>4.83</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.216</v>
+        <v>11.468</v>
       </c>
     </row>
     <row r="5">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>114.5</v>
+        <v>115.5</v>
       </c>
       <c r="E5" t="n">
-        <v>9.57</v>
+        <v>0.87</v>
       </c>
       <c r="F5" t="n">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4.685</v>
+        <v>4.854</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1035</v>
+        <v>302.5</v>
       </c>
       <c r="E6" t="n">
-        <v>9.52</v>
+        <v>4.85</v>
       </c>
       <c r="F6" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10.357</v>
+        <v>5.871</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68.09999999999999</v>
+        <v>115</v>
       </c>
       <c r="E7" t="n">
-        <v>5.42</v>
+        <v>0.44</v>
       </c>
       <c r="F7" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.995</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3305</v>
+        <v>184.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="F8" t="n">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,33 +708,33 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.009</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>114.5</v>
+        <v>18.95</v>
       </c>
       <c r="E9" t="n">
-        <v>4.09</v>
+        <v>-1.3</v>
       </c>
       <c r="F9" t="n">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,67 +742,67 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.32</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2480</v>
+        <v>48.85</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>-0.61</v>
       </c>
       <c r="F10" t="n">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>48.066</v>
+        <v>1.183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>42.85</v>
+        <v>150.5</v>
       </c>
       <c r="E11" t="n">
-        <v>3.25</v>
+        <v>-0.33</v>
       </c>
       <c r="F11" t="n">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.755</v>
+        <v>2.376</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>181</v>
+        <v>762</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>0.26</v>
       </c>
       <c r="F12" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,33 +844,33 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.846</v>
+        <v>2.147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>546</v>
+        <v>190.5</v>
       </c>
       <c r="E13" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="F13" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,41 +878,41 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.671</v>
+        <v>10.021</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>542</v>
+        <v>334</v>
       </c>
       <c r="E14" t="n">
-        <v>9.94</v>
+        <v>0.15</v>
       </c>
       <c r="F14" t="n">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>16.07</v>
+        <v>4.694</v>
       </c>
     </row>
     <row r="15">
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>210.5</v>
+        <v>213</v>
       </c>
       <c r="E15" t="n">
-        <v>0.24</v>
+        <v>1.19</v>
       </c>
       <c r="F15" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.903</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>69.90000000000001</v>
+        <v>2510</v>
       </c>
       <c r="E16" t="n">
-        <v>2.64</v>
+        <v>1.21</v>
       </c>
       <c r="F16" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.181</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>289.5</v>
+        <v>42.2</v>
       </c>
       <c r="E17" t="n">
-        <v>3.02</v>
+        <v>-1.52</v>
       </c>
       <c r="F17" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,237 +1014,237 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3.427</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>289</v>
+        <v>110.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.05</v>
+        <v>-0.45</v>
       </c>
       <c r="F18" t="n">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.653</v>
+        <v>2.316</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>75.3</v>
+        <v>538</v>
       </c>
       <c r="E19" t="n">
-        <v>4.15</v>
+        <v>-0.74</v>
       </c>
       <c r="F19" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.218999999999999</v>
+        <v>15.139</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20.45</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.74</v>
+        <v>-0.73</v>
       </c>
       <c r="F20" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.322</v>
+        <v>2.141</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.45</v>
+        <v>0.99</v>
       </c>
       <c r="F21" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.347</v>
+        <v>7.469</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1890</v>
+        <v>26</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>-0.38</v>
       </c>
       <c r="F22" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20.494</v>
+        <v>0.517</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4920</v>
+        <v>87.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2</v>
+        <v>-0.91</v>
       </c>
       <c r="F23" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>40.239</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>122.5</v>
+        <v>547</v>
       </c>
       <c r="E24" t="n">
-        <v>3.38</v>
+        <v>0.18</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.507</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>251.5</v>
+        <v>74.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4</v>
+        <v>-1.06</v>
       </c>
       <c r="F25" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>7.431</v>
+        <v>8.903</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.1</v>
+        <v>20.3</v>
       </c>
       <c r="E26" t="n">
-        <v>0.19</v>
+        <v>-0.73</v>
       </c>
       <c r="F26" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,67 +1320,67 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.517</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>88.3</v>
+        <v>3245</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.45</v>
+        <v>-1.82</v>
       </c>
       <c r="F27" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.312</v>
+        <v>4.982</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>703</v>
+        <v>238</v>
       </c>
       <c r="E28" t="n">
-        <v>2.33</v>
+        <v>-0.63</v>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>11.327</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2150</v>
+        <v>66.8</v>
       </c>
       <c r="E29" t="n">
-        <v>1.65</v>
+        <v>-1.91</v>
       </c>
       <c r="F29" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>7.235</v>
+        <v>1.789</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>294.5</v>
+        <v>180</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="F30" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,67 +1456,67 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>8.000999999999999</v>
+        <v>17.632</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>333.5</v>
+        <v>161.5</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.89</v>
+        <v>4.53</v>
       </c>
       <c r="F31" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.677</v>
+        <v>28.217</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>179.5</v>
+        <v>292.5</v>
       </c>
       <c r="E32" t="n">
-        <v>3.16</v>
+        <v>1.04</v>
       </c>
       <c r="F32" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,101 +1524,101 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>18.21</v>
+        <v>3.345</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>68.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.44</v>
+        <v>-1.57</v>
       </c>
       <c r="F33" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.195</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>59.5</v>
+        <v>289.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="F34" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.877</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>519</v>
+        <v>2110</v>
       </c>
       <c r="E35" t="n">
-        <v>2.57</v>
+        <v>-1.86</v>
       </c>
       <c r="F35" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>27.325</v>
+        <v>6.878</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>760</v>
+        <v>121</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>-1.22</v>
       </c>
       <c r="F36" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.12</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>151</v>
+        <v>296</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.33</v>
+        <v>0.51</v>
       </c>
       <c r="F37" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,203 +1694,203 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.392</v>
+        <v>7.487</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1460</v>
+        <v>59.7</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.02</v>
+        <v>0.34</v>
       </c>
       <c r="F38" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.662</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>377.5</v>
+        <v>710</v>
       </c>
       <c r="E39" t="n">
-        <v>0.13</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.983</v>
+        <v>10.889</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>49.15</v>
+        <v>1905</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1</v>
+        <v>0.79</v>
       </c>
       <c r="F40" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.191</v>
+        <v>20.523</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>279.5</v>
+        <v>519</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.337</v>
+        <v>25.948</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>288.5</v>
+        <v>29.2</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.03</v>
+        <v>-0.17</v>
       </c>
       <c r="F42" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5.464</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>154.5</v>
+        <v>4980</v>
       </c>
       <c r="E43" t="n">
-        <v>0.65</v>
+        <v>1.22</v>
       </c>
       <c r="F43" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,64 +1898,64 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>27.811</v>
+        <v>41.019</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>239.5</v>
+        <v>380</v>
       </c>
       <c r="E44" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="F44" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.02</v>
+        <v>1.969</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3740</v>
+        <v>284.5</v>
       </c>
       <c r="E45" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="F45" t="n">
         <v>50</v>
@@ -1966,30 +1966,30 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8.398999999999999</v>
+        <v>5.311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>59.4</v>
+        <v>1475</v>
       </c>
       <c r="E46" t="n">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="F46" t="n">
         <v>48</v>
@@ -2000,64 +2000,64 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.887</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>275</v>
+        <v>7900</v>
       </c>
       <c r="E47" t="n">
-        <v>1.1</v>
+        <v>-1.74</v>
       </c>
       <c r="F47" t="n">
         <v>45</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.806</v>
+        <v>12.588</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29.25</v>
+        <v>3765</v>
       </c>
       <c r="E48" t="n">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="F48" t="n">
         <v>44</v>
@@ -2068,64 +2068,64 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.137</v>
+        <v>8.196</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8040</v>
+        <v>58.8</v>
       </c>
       <c r="E49" t="n">
-        <v>1.45</v>
+        <v>-1.01</v>
       </c>
       <c r="F49" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>13.352</v>
+        <v>1.759</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>184.5</v>
+        <v>272</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.54</v>
+        <v>-1.09</v>
       </c>
       <c r="F50" t="n">
         <v>40</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9.417999999999999</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="51">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>114</v>
+        <v>112.5</v>
       </c>
       <c r="E51" t="n">
-        <v>2.7</v>
+        <v>-1.32</v>
       </c>
       <c r="F51" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.918</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="52">
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E52" t="n">
-        <v>1.66</v>
+        <v>-1.09</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>6.377</v>
+        <v>5.607</v>
       </c>
     </row>
   </sheetData>
@@ -2261,32 +2261,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>37.71</v>
+        <v>43.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.46</v>
+        <v>2.61</v>
       </c>
       <c r="G2" t="n">
-        <v>5.009</v>
+        <v>1.281</v>
       </c>
     </row>
     <row r="3">
@@ -2311,137 +2311,137 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="F3" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="G3" t="n">
-        <v>13.352</v>
+        <v>12.588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31.1</v>
+        <v>23.93</v>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="G4" t="n">
-        <v>1.004</v>
+        <v>4.854</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28.51</v>
+        <v>22.92</v>
       </c>
       <c r="F5" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="G5" t="n">
-        <v>4.685</v>
+        <v>4.982</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25.35</v>
+        <v>21.89</v>
       </c>
       <c r="F6" t="n">
-        <v>1.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>40.239</v>
+        <v>28.217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21.12</v>
+        <v>20.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="G7" t="n">
-        <v>16.07</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="8">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20.38</v>
+        <v>16.39</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>11.327</v>
+        <v>10.889</v>
       </c>
     </row>
     <row r="9">
@@ -2497,153 +2497,153 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20.29</v>
+        <v>16.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="G9" t="n">
-        <v>0.903</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19.77</v>
+        <v>15.68</v>
       </c>
       <c r="F10" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="G10" t="n">
-        <v>27.811</v>
+        <v>5.871</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19.47</v>
+        <v>15.41</v>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G11" t="n">
-        <v>2.846</v>
+        <v>41.019</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17.28</v>
+        <v>15.26</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>5.464</v>
+        <v>3.708</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>16.57</v>
+        <v>10.08</v>
       </c>
       <c r="F13" t="n">
-        <v>1.84</v>
+        <v>0.71</v>
       </c>
       <c r="G13" t="n">
-        <v>3.216</v>
+        <v>1.168</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2652,401 +2652,401 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15.72</v>
+        <v>9.35</v>
       </c>
       <c r="F14" t="n">
-        <v>0.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6.377</v>
+        <v>15.139</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14.59</v>
+        <v>9.15</v>
       </c>
       <c r="F15" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="G15" t="n">
-        <v>8.000999999999999</v>
+        <v>11.468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.49</v>
+        <v>6.09</v>
       </c>
       <c r="F16" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="G16" t="n">
-        <v>10.357</v>
+        <v>7.487</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13.47</v>
+        <v>6.06</v>
       </c>
       <c r="F17" t="n">
         <v>1.11</v>
       </c>
       <c r="G17" t="n">
-        <v>1.181</v>
+        <v>2.147</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.15</v>
+        <v>5.23</v>
       </c>
       <c r="F18" t="n">
-        <v>1.15</v>
+        <v>0.84</v>
       </c>
       <c r="G18" t="n">
-        <v>2.12</v>
+        <v>8.903</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.72</v>
+        <v>4.67</v>
       </c>
       <c r="F19" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="G19" t="n">
-        <v>2.195</v>
+        <v>10.021</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.86</v>
+        <v>4.2</v>
       </c>
       <c r="F20" t="n">
-        <v>0.82</v>
+        <v>0.18</v>
       </c>
       <c r="G20" t="n">
-        <v>2.392</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.51</v>
+        <v>3.79</v>
       </c>
       <c r="F21" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="G21" t="n">
-        <v>3.427</v>
+        <v>2.376</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.65</v>
+        <v>3.17</v>
       </c>
       <c r="F22" t="n">
-        <v>0.67</v>
+        <v>1.12</v>
       </c>
       <c r="G22" t="n">
-        <v>9.417999999999999</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="F23" t="n">
-        <v>1.13</v>
+        <v>0.73</v>
       </c>
       <c r="G23" t="n">
-        <v>48.066</v>
+        <v>3.345</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="F24" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="G24" t="n">
-        <v>9.218999999999999</v>
+        <v>17.632</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.87</v>
+        <v>2.14</v>
       </c>
       <c r="F25" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="G25" t="n">
-        <v>1.995</v>
+        <v>20.523</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.72</v>
+        <v>2.11</v>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>0.76</v>
       </c>
       <c r="G26" t="n">
-        <v>20.494</v>
+        <v>2.141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3055,60 +3055,60 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.57</v>
+        <v>2.08</v>
       </c>
       <c r="F27" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="G27" t="n">
-        <v>2.02</v>
+        <v>1.759</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="F28" t="n">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="G28" t="n">
-        <v>0.662</v>
+        <v>0.517</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3117,695 +3117,695 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.15</v>
+        <v>0.72</v>
       </c>
       <c r="F29" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="G29" t="n">
-        <v>0.517</v>
+        <v>1.183</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.02</v>
+        <v>0.34</v>
       </c>
       <c r="F30" t="n">
-        <v>1.34</v>
+        <v>0.59</v>
       </c>
       <c r="G30" t="n">
-        <v>0.755</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.32</v>
+        <v>0.19</v>
       </c>
       <c r="F31" t="n">
-        <v>1.43</v>
+        <v>0.76</v>
       </c>
       <c r="G31" t="n">
-        <v>0.541</v>
+        <v>25.948</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G32" t="n">
-        <v>1.191</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.11</v>
+        <v>-0.25</v>
       </c>
       <c r="F33" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="G33" t="n">
-        <v>1.671</v>
+        <v>0.319</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.99</v>
+        <v>-0.45</v>
       </c>
       <c r="F34" t="n">
-        <v>1.33</v>
+        <v>0.85</v>
       </c>
       <c r="G34" t="n">
-        <v>0.322</v>
+        <v>2.316</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.6</v>
+        <v>-0.47</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="G35" t="n">
-        <v>7.431</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.45</v>
+        <v>-0.52</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8</v>
+        <v>1.46</v>
       </c>
       <c r="G36" t="n">
-        <v>2.347</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="F37" t="n">
-        <v>0.47</v>
+        <v>1.09</v>
       </c>
       <c r="G37" t="n">
-        <v>1.918</v>
+        <v>6.878</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.17</v>
+        <v>-0.78</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6</v>
+        <v>1.03</v>
       </c>
       <c r="G38" t="n">
-        <v>1.887</v>
+        <v>7.469</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.36</v>
+        <v>-0.91</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4</v>
+        <v>1.06</v>
       </c>
       <c r="G39" t="n">
-        <v>0.806</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.22</v>
       </c>
       <c r="F40" t="n">
-        <v>1.24</v>
+        <v>0.74</v>
       </c>
       <c r="G40" t="n">
-        <v>7.235</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.48</v>
+        <v>-1.45</v>
       </c>
       <c r="F41" t="n">
-        <v>0.73</v>
+        <v>0.38</v>
       </c>
       <c r="G41" t="n">
-        <v>4.677</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-1.56</v>
+        <v>-1.47</v>
       </c>
       <c r="F42" t="n">
-        <v>0.74</v>
+        <v>1.06</v>
       </c>
       <c r="G42" t="n">
-        <v>0.32</v>
+        <v>1.789</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-1.64</v>
+        <v>-1.75</v>
       </c>
       <c r="F43" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="G43" t="n">
-        <v>18.21</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-1.68</v>
+        <v>-1.86</v>
       </c>
       <c r="F44" t="n">
-        <v>0.42</v>
+        <v>0.78</v>
       </c>
       <c r="G44" t="n">
-        <v>0.137</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-1.87</v>
+        <v>-2.34</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="G45" t="n">
-        <v>0.653</v>
+        <v>4.694</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-2.78</v>
+        <v>-3.38</v>
       </c>
       <c r="F46" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="G46" t="n">
-        <v>3.507</v>
+        <v>1.969</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-4.36</v>
+        <v>-5.32</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7</v>
+        <v>0.58</v>
       </c>
       <c r="G47" t="n">
-        <v>1.983</v>
+        <v>5.311</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-4.42</v>
+        <v>-6.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.85</v>
+        <v>0.97</v>
       </c>
       <c r="G48" t="n">
-        <v>27.325</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-7.5</v>
+        <v>-7.3</v>
       </c>
       <c r="F49" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="G49" t="n">
-        <v>8.398999999999999</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-8.359999999999999</v>
+        <v>-10.36</v>
       </c>
       <c r="F50" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="G50" t="n">
-        <v>5.337</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-10.79</v>
+        <v>-11.24</v>
       </c>
       <c r="F51" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="G51" t="n">
-        <v>0.877</v>
+        <v>8.196</v>
       </c>
     </row>
     <row r="52">
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-18.59</v>
+        <v>-21.13</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G52" t="n">
         <v>0.312</v>
@@ -3883,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.71</v>
+        <v>43.25</v>
       </c>
       <c r="C2" t="n">
-        <v>1.46</v>
+        <v>2.61</v>
       </c>
       <c r="D2" t="n">
-        <v>5.009</v>
+        <v>1.281</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.1</v>
+        <v>22.92</v>
       </c>
       <c r="C3" t="n">
-        <v>2.22</v>
+        <v>1.37</v>
       </c>
       <c r="D3" t="n">
-        <v>1.004</v>
+        <v>4.982</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,17 +3921,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.35</v>
+        <v>20.2</v>
       </c>
       <c r="C4" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="D4" t="n">
-        <v>40.239</v>
+        <v>3.029</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.38</v>
+        <v>16.39</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="D5" t="n">
-        <v>11.327</v>
+        <v>10.889</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,17 +3959,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.47</v>
+        <v>15.68</v>
       </c>
       <c r="C6" t="n">
-        <v>1.44</v>
+        <v>0.73</v>
       </c>
       <c r="D6" t="n">
-        <v>2.846</v>
+        <v>5.871</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3978,17 +3978,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.28</v>
+        <v>15.41</v>
       </c>
       <c r="C7" t="n">
-        <v>0.58</v>
+        <v>0.88</v>
       </c>
       <c r="D7" t="n">
-        <v>5.464</v>
+        <v>41.019</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.51</v>
+        <v>13.46</v>
       </c>
       <c r="C8" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="D8" t="n">
-        <v>8.112</v>
+        <v>8.199</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -4016,17 +4016,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.03</v>
+        <v>12.53</v>
       </c>
       <c r="C9" t="n">
-        <v>1.745</v>
+        <v>0.905</v>
       </c>
       <c r="D9" t="n">
-        <v>13.573</v>
+        <v>76.937</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -4035,112 +4035,112 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.59</v>
+        <v>12.205</v>
       </c>
       <c r="C10" t="n">
-        <v>1.35</v>
+        <v>1.785</v>
       </c>
       <c r="D10" t="n">
-        <v>8.000999999999999</v>
+        <v>15.176</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.47</v>
+        <v>10.27</v>
       </c>
       <c r="C11" t="n">
-        <v>1.11</v>
+        <v>0.62</v>
       </c>
       <c r="D11" t="n">
-        <v>1.181</v>
+        <v>20.784</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12.15</v>
+        <v>10.08</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="D12" t="n">
-        <v>21.751</v>
+        <v>1.168</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11.76</v>
+        <v>6.09</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7066666666666667</v>
+        <v>1.01</v>
       </c>
       <c r="D13" t="n">
-        <v>22.767</v>
+        <v>7.487</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.595</v>
+        <v>6.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9949999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="D14" t="n">
-        <v>75.87700000000001</v>
+        <v>2.147</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.15</v>
+        <v>5.23</v>
       </c>
       <c r="C15" t="n">
-        <v>1.15</v>
+        <v>0.84</v>
       </c>
       <c r="D15" t="n">
-        <v>2.12</v>
+        <v>8.903</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,58 +4149,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="C16" t="n">
-        <v>0.83</v>
+        <v>0.6966666666666667</v>
       </c>
       <c r="D16" t="n">
-        <v>9.218999999999999</v>
+        <v>21.034</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.884</v>
+        <v>2.27</v>
       </c>
       <c r="C17" t="n">
-        <v>0.754</v>
+        <v>0.64</v>
       </c>
       <c r="D17" t="n">
-        <v>8.641999999999999</v>
+        <v>17.632</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.87</v>
+        <v>1.546</v>
       </c>
       <c r="C18" t="n">
-        <v>0.96</v>
+        <v>0.8160000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>1.995</v>
+        <v>8.532999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.46</v>
+        <v>0.34</v>
       </c>
       <c r="C19" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="D19" t="n">
-        <v>0.662</v>
+        <v>0.64</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4225,112 +4225,112 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.505</v>
+        <v>0.19</v>
       </c>
       <c r="C20" t="n">
-        <v>1.335</v>
+        <v>0.76</v>
       </c>
       <c r="D20" t="n">
-        <v>1.077</v>
+        <v>25.948</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.32</v>
+        <v>0.11</v>
       </c>
       <c r="C21" t="n">
-        <v>1.43</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="D21" t="n">
-        <v>0.541</v>
+        <v>5.499</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.11</v>
+        <v>-0.36</v>
       </c>
       <c r="C22" t="n">
-        <v>1.12</v>
+        <v>1.285</v>
       </c>
       <c r="D22" t="n">
-        <v>1.671</v>
+        <v>1.06</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8499999999999996</v>
+        <v>-0.52</v>
       </c>
       <c r="C23" t="n">
-        <v>1.425</v>
+        <v>1.46</v>
       </c>
       <c r="D23" t="n">
-        <v>1.215</v>
+        <v>0.545</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7999999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5733333333333334</v>
+        <v>1.09</v>
       </c>
       <c r="D24" t="n">
-        <v>5.825</v>
+        <v>6.878</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.91</v>
       </c>
       <c r="C25" t="n">
-        <v>1.24</v>
+        <v>1.06</v>
       </c>
       <c r="D25" t="n">
-        <v>7.235</v>
+        <v>1.624</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,17 +4339,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.64</v>
+        <v>-1.22</v>
       </c>
       <c r="C26" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="D26" t="n">
-        <v>18.21</v>
+        <v>3.37</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,17 +4358,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.68</v>
+        <v>-1.47</v>
       </c>
       <c r="C27" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
       <c r="D27" t="n">
-        <v>0.137</v>
+        <v>1.789</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,74 +4377,74 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.005</v>
+        <v>-1.59</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8075</v>
+        <v>0.72</v>
       </c>
       <c r="D28" t="n">
-        <v>22.403</v>
+        <v>25.834</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.196666666666667</v>
+        <v>-2.2025</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6366666666666667</v>
+        <v>0.79</v>
       </c>
       <c r="D29" t="n">
-        <v>3.442</v>
+        <v>23.049</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.78</v>
+        <v>-2.23</v>
       </c>
       <c r="C30" t="n">
-        <v>0.77</v>
+        <v>0.5933333333333334</v>
       </c>
       <c r="D30" t="n">
-        <v>3.507</v>
+        <v>3.35</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.819999999999999</v>
+        <v>-2.525</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8600000000000001</v>
+        <v>1.155</v>
       </c>
       <c r="D31" t="n">
-        <v>25.831</v>
+        <v>1.207</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -4453,17 +4453,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-4.42</v>
+        <v>-7.3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="D32" t="n">
-        <v>27.325</v>
+        <v>0.115</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2150</v>
+        <v>2110</v>
       </c>
       <c r="E2" t="n">
-        <v>1.65</v>
+        <v>-1.86</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="G2" t="n">
-        <v>55.2</v>
+        <v>51.88</v>
       </c>
       <c r="H2" t="n">
-        <v>34.9447</v>
+        <v>32.5437</v>
       </c>
       <c r="I2" t="n">
-        <v>73.59999999999999</v>
+        <v>62</v>
       </c>
       <c r="J2" t="n">
-        <v>78</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
       <c r="L2" t="n">
-        <v>-11.5</v>
+        <v>-40.1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4920</v>
+        <v>4980</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>1.22</v>
       </c>
       <c r="F3" t="n">
-        <v>25.35</v>
+        <v>15.41</v>
       </c>
       <c r="G3" t="n">
-        <v>55.93</v>
+        <v>60.17</v>
       </c>
       <c r="H3" t="n">
-        <v>249.1677</v>
+        <v>240.5171</v>
       </c>
       <c r="I3" t="n">
-        <v>68.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="J3" t="n">
-        <v>57.3</v>
+        <v>64.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
+        <v>-47.3</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88.3</v>
+        <v>87.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.45</v>
+        <v>-0.91</v>
       </c>
       <c r="F4" t="n">
-        <v>-18.59</v>
+        <v>-21.13</v>
       </c>
       <c r="G4" t="n">
-        <v>29.25</v>
+        <v>29.05</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.2051</v>
+        <v>-5.8729</v>
       </c>
       <c r="I4" t="n">
-        <v>35.6</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>27.5</v>
+        <v>45.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-8.800000000000001</v>
+        <v>-16.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>288.5</v>
+        <v>302.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.03</v>
+        <v>4.85</v>
       </c>
       <c r="F5" t="n">
-        <v>17.28</v>
+        <v>15.68</v>
       </c>
       <c r="G5" t="n">
-        <v>56.41</v>
+        <v>63.49</v>
       </c>
       <c r="H5" t="n">
-        <v>21.2976</v>
+        <v>20.3329</v>
       </c>
       <c r="I5" t="n">
-        <v>50.4</v>
+        <v>65.5</v>
       </c>
       <c r="J5" t="n">
-        <v>43</v>
+        <v>52.8</v>
       </c>
       <c r="K5" t="n">
-        <v>7.6</v>
+        <v>7.74</v>
       </c>
       <c r="L5" t="n">
-        <v>-41.8</v>
+        <v>61.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>🚀 BUY STRONG</t>
         </is>
       </c>
     </row>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="E6" t="n">
-        <v>1.66</v>
+        <v>-1.09</v>
       </c>
       <c r="F6" t="n">
-        <v>15.72</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>53.76</v>
       </c>
       <c r="H6" t="n">
-        <v>32.087</v>
+        <v>30.1922</v>
       </c>
       <c r="I6" t="n">
-        <v>74.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>64.90000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="K6" t="n">
-        <v>5.4</v>
+        <v>5.27</v>
       </c>
       <c r="L6" t="n">
-        <v>-88</v>
+        <v>-80.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>251.5</v>
+        <v>254</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4</v>
+        <v>0.99</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>-0.78</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1801</v>
+        <v>0.0597</v>
       </c>
       <c r="I7" t="n">
-        <v>52.3</v>
+        <v>75.8</v>
       </c>
       <c r="J7" t="n">
-        <v>52.6</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="L7" t="n">
-        <v>-9.1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>366.5</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>9.9</v>
+        <v>4.35</v>
       </c>
       <c r="F2" t="n">
-        <v>477</v>
+        <v>321</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.281</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="3">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>211.5</v>
+        <v>221.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.93</v>
+        <v>4.73</v>
       </c>
       <c r="F3" t="n">
-        <v>327</v>
+        <v>246</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3.708</v>
+        <v>4.313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1085</v>
+        <v>308</v>
       </c>
       <c r="E4" t="n">
-        <v>4.83</v>
+        <v>5.3</v>
       </c>
       <c r="F4" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11.468</v>
+        <v>3.872</v>
       </c>
     </row>
     <row r="5">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>115.5</v>
+        <v>127</v>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4.854</v>
+        <v>5.846</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>302.5</v>
+        <v>352</v>
       </c>
       <c r="E6" t="n">
-        <v>4.85</v>
+        <v>-3.96</v>
       </c>
       <c r="F6" t="n">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5.871</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>115</v>
+        <v>1190</v>
       </c>
       <c r="E7" t="n">
-        <v>0.44</v>
+        <v>9.68</v>
       </c>
       <c r="F7" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.288</v>
+        <v>13.091</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>184.5</v>
+        <v>76.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1.93</v>
+        <v>2.68</v>
       </c>
       <c r="F8" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,101 +708,101 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3.029</v>
+        <v>9.561999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.95</v>
+        <v>28.65</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3</v>
+        <v>-1.88</v>
       </c>
       <c r="F9" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.545</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.85</v>
+        <v>70.8</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.61</v>
+        <v>2.91</v>
       </c>
       <c r="F10" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.183</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>150.5</v>
+        <v>68.3</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.33</v>
+        <v>2.25</v>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.376</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>762</v>
+        <v>303</v>
       </c>
       <c r="E12" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="F12" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,98 +844,98 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2.147</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>190.5</v>
+        <v>48.85</v>
       </c>
       <c r="E13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>10.021</v>
+        <v>1.169</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>334</v>
+        <v>215.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.15</v>
+        <v>1.17</v>
       </c>
       <c r="F14" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.694</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>213</v>
+        <v>591</v>
       </c>
       <c r="E15" t="n">
-        <v>1.19</v>
+        <v>9.85</v>
       </c>
       <c r="F15" t="n">
         <v>104</v>
@@ -946,101 +946,101 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.895</v>
+        <v>16.246</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2510</v>
+        <v>251</v>
       </c>
       <c r="E16" t="n">
-        <v>1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="F16" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>48.72</v>
+        <v>7.396</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42.2</v>
+        <v>537</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.52</v>
+        <v>-1.83</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.741</v>
+        <v>1.585</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>110.5</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.45</v>
+        <v>-1.17</v>
       </c>
       <c r="F18" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.316</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>538</v>
+        <v>187</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.74</v>
+        <v>1.36</v>
       </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,67 +1082,67 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15.139</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>67.90000000000001</v>
+        <v>2500</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.73</v>
+        <v>-0.4</v>
       </c>
       <c r="F20" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.141</v>
+        <v>47.793</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>254</v>
+        <v>713</v>
       </c>
       <c r="E21" t="n">
-        <v>0.99</v>
+        <v>0.42</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,67 +1150,67 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7.469</v>
+        <v>10.749</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.38</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.517</v>
+        <v>17.451</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>87.5</v>
+        <v>382</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.91</v>
+        <v>0.53</v>
       </c>
       <c r="F23" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,33 +1218,33 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.312</v>
+        <v>1.985</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="E24" t="n">
-        <v>0.18</v>
+        <v>1.35</v>
       </c>
       <c r="F24" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.624</v>
+        <v>25.876</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>74.5</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.06</v>
+        <v>0.26</v>
       </c>
       <c r="F25" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,33 +1286,33 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>8.903</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>20.3</v>
+        <v>332</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.73</v>
+        <v>-0.6</v>
       </c>
       <c r="F26" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,30 +1320,30 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.319</v>
+        <v>4.677</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3245</v>
+        <v>186.5</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.82</v>
+        <v>-2.1</v>
       </c>
       <c r="F27" t="n">
         <v>73</v>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.982</v>
+        <v>9.365</v>
       </c>
     </row>
     <row r="28">
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.63</v>
+        <v>0.84</v>
       </c>
       <c r="F28" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.93</v>
+        <v>1.889</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>66.8</v>
+        <v>2095</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.91</v>
+        <v>-0.71</v>
       </c>
       <c r="F29" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,101 +1422,101 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.789</v>
+        <v>6.735</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>180</v>
+        <v>150.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17.632</v>
+        <v>2.354</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>161.5</v>
+        <v>111.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4.53</v>
+        <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>28.217</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>292.5</v>
+        <v>3170</v>
       </c>
       <c r="E32" t="n">
-        <v>1.04</v>
+        <v>-2.31</v>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,30 +1524,30 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.345</v>
+        <v>4.732</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>68.8</v>
+        <v>4950</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.57</v>
+        <v>-0.6</v>
       </c>
       <c r="F33" t="n">
         <v>61</v>
@@ -1558,30 +1558,30 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.168</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>289.5</v>
+        <v>1460</v>
       </c>
       <c r="E34" t="n">
-        <v>0.17</v>
+        <v>-1.02</v>
       </c>
       <c r="F34" t="n">
         <v>61</v>
@@ -1592,67 +1592,67 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.633</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2110</v>
+        <v>67.3</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.86</v>
+        <v>-0.88</v>
       </c>
       <c r="F35" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6.878</v>
+        <v>2.073</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>121</v>
+        <v>3810</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.22</v>
+        <v>1.2</v>
       </c>
       <c r="F36" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,30 +1660,30 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3.37</v>
+        <v>8.234</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>296</v>
+        <v>754</v>
       </c>
       <c r="E37" t="n">
-        <v>0.51</v>
+        <v>-1.05</v>
       </c>
       <c r="F37" t="n">
         <v>59</v>
@@ -1694,101 +1694,101 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7.487</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>59.7</v>
+        <v>1885</v>
       </c>
       <c r="E38" t="n">
-        <v>0.34</v>
+        <v>-1.05</v>
       </c>
       <c r="F38" t="n">
         <v>58</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.865</v>
+        <v>19.577</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>710</v>
+        <v>26.15</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="F39" t="n">
         <v>58</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10.889</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1905</v>
+        <v>161.5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,101 +1796,101 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>20.523</v>
+        <v>27.935</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>519</v>
+        <v>89</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="F41" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>25.948</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>29.2</v>
+        <v>295.5</v>
       </c>
       <c r="E42" t="n">
         <v>-0.17</v>
       </c>
       <c r="F42" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.115</v>
+        <v>7.186</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4980</v>
+        <v>290</v>
       </c>
       <c r="E43" t="n">
-        <v>1.22</v>
+        <v>0.17</v>
       </c>
       <c r="F43" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>41.019</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="E44" t="n">
-        <v>0.66</v>
+        <v>0.37</v>
       </c>
       <c r="F44" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,67 +1932,67 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.969</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>284.5</v>
+        <v>42.35</v>
       </c>
       <c r="E45" t="n">
-        <v>1.79</v>
+        <v>0.36</v>
       </c>
       <c r="F45" t="n">
         <v>50</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5.311</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1475</v>
+        <v>20.35</v>
       </c>
       <c r="E46" t="n">
-        <v>1.03</v>
+        <v>0.25</v>
       </c>
       <c r="F46" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.64</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7900</v>
+        <v>580</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.74</v>
+        <v>6.23</v>
       </c>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,64 +2034,64 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>12.588</v>
+        <v>5.101</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3765</v>
+        <v>122</v>
       </c>
       <c r="E48" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="F48" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>8.196</v>
+        <v>3.363</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>58.8</v>
+        <v>281.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.01</v>
+        <v>-1.05</v>
       </c>
       <c r="F49" t="n">
         <v>42</v>
@@ -2102,41 +2102,41 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.759</v>
+        <v>4.705</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>272</v>
+        <v>59.7</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.09</v>
+        <v>1.53</v>
       </c>
       <c r="F50" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.748</v>
+        <v>1.697</v>
       </c>
     </row>
     <row r="51">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>112.5</v>
+        <v>113</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.32</v>
+        <v>0.44</v>
       </c>
       <c r="F51" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,33 +2170,33 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.81</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>546</v>
+        <v>7900</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.09</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5.607</v>
+        <v>12.282</v>
       </c>
     </row>
   </sheetData>
@@ -2261,94 +2261,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43.25</v>
+        <v>40.8</v>
       </c>
       <c r="F2" t="n">
-        <v>2.61</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>1.281</v>
+        <v>5.846</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31.78</v>
+        <v>37.06</v>
       </c>
       <c r="F3" t="n">
-        <v>0.72</v>
+        <v>2.69</v>
       </c>
       <c r="G3" t="n">
-        <v>12.588</v>
+        <v>1.335</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23.93</v>
+        <v>34.01</v>
       </c>
       <c r="F4" t="n">
-        <v>1.91</v>
+        <v>0.52</v>
       </c>
       <c r="G4" t="n">
-        <v>4.854</v>
+        <v>12.282</v>
       </c>
     </row>
     <row r="5">
@@ -2373,13 +2373,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22.92</v>
+        <v>32.36</v>
       </c>
       <c r="F5" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.982</v>
+        <v>4.732</v>
       </c>
     </row>
     <row r="6">
@@ -2404,416 +2404,416 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21.89</v>
+        <v>28.17</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
-        <v>28.217</v>
+        <v>27.935</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.2</v>
+        <v>25.88</v>
       </c>
       <c r="F7" t="n">
-        <v>1.27</v>
+        <v>0.97</v>
       </c>
       <c r="G7" t="n">
-        <v>3.029</v>
+        <v>16.246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.39</v>
+        <v>25.08</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>1.26</v>
       </c>
       <c r="G8" t="n">
-        <v>10.889</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>16.08</v>
+        <v>23.74</v>
       </c>
       <c r="F9" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="G9" t="n">
-        <v>0.895</v>
+        <v>4.313</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>15.68</v>
+        <v>23.06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.73</v>
+        <v>1.38</v>
       </c>
       <c r="G10" t="n">
-        <v>5.871</v>
+        <v>13.091</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15.41</v>
+        <v>21.05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="G11" t="n">
-        <v>41.019</v>
+        <v>10.749</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15.26</v>
+        <v>16.8</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="G12" t="n">
-        <v>3.708</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10.08</v>
+        <v>16.31</v>
       </c>
       <c r="F13" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="G13" t="n">
-        <v>1.168</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9.35</v>
+        <v>15.79</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="G14" t="n">
-        <v>15.139</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.15</v>
+        <v>14.19</v>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>0.79</v>
       </c>
       <c r="G15" t="n">
-        <v>11.468</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.09</v>
+        <v>10.79</v>
       </c>
       <c r="F16" t="n">
         <v>1.01</v>
       </c>
       <c r="G16" t="n">
-        <v>7.487</v>
+        <v>3.872</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.06</v>
+        <v>9.24</v>
       </c>
       <c r="F17" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="G17" t="n">
-        <v>2.147</v>
+        <v>7.186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.23</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G18" t="n">
-        <v>8.903</v>
+        <v>19.577</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.67</v>
+        <v>8.66</v>
       </c>
       <c r="F19" t="n">
-        <v>0.61</v>
+        <v>0.9</v>
       </c>
       <c r="G19" t="n">
-        <v>10.021</v>
+        <v>9.561999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2838,370 +2838,370 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.2</v>
+        <v>7.01</v>
       </c>
       <c r="F20" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="G20" t="n">
-        <v>5.607</v>
+        <v>5.101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.79</v>
+        <v>5.13</v>
       </c>
       <c r="F21" t="n">
-        <v>0.84</v>
+        <v>1.07</v>
       </c>
       <c r="G21" t="n">
-        <v>2.376</v>
+        <v>47.793</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.17</v>
+        <v>4.94</v>
       </c>
       <c r="F22" t="n">
-        <v>1.12</v>
+        <v>0.9</v>
       </c>
       <c r="G22" t="n">
-        <v>48.72</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.99</v>
+        <v>4.88</v>
       </c>
       <c r="F23" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="G23" t="n">
-        <v>3.345</v>
+        <v>2.354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.27</v>
+        <v>3.83</v>
       </c>
       <c r="F24" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="G24" t="n">
-        <v>17.632</v>
+        <v>1.697</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>1.45</v>
       </c>
       <c r="G25" t="n">
-        <v>20.523</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="F26" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>2.141</v>
+        <v>1.889</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="F27" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="G27" t="n">
-        <v>1.759</v>
+        <v>2.277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="F28" t="n">
-        <v>0.84</v>
+        <v>1.21</v>
       </c>
       <c r="G28" t="n">
-        <v>0.517</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.72</v>
+        <v>1.54</v>
       </c>
       <c r="F29" t="n">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="G29" t="n">
-        <v>1.183</v>
+        <v>25.876</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.34</v>
+        <v>1.45</v>
       </c>
       <c r="F30" t="n">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="G30" t="n">
-        <v>0.64</v>
+        <v>6.735</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.19</v>
+        <v>1.05</v>
       </c>
       <c r="F31" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="G31" t="n">
-        <v>25.948</v>
+        <v>2.073</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3210,432 +3210,432 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="F32" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.25</v>
+        <v>0.54</v>
       </c>
       <c r="F33" t="n">
-        <v>1.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.319</v>
+        <v>9.365</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.45</v>
+        <v>0.47</v>
       </c>
       <c r="F34" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="G34" t="n">
-        <v>2.316</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.47</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1.34</v>
+        <v>0.65</v>
       </c>
       <c r="G35" t="n">
-        <v>0.741</v>
+        <v>17.451</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1.46</v>
+        <v>0.6</v>
       </c>
       <c r="G36" t="n">
-        <v>0.545</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="G37" t="n">
-        <v>6.878</v>
+        <v>7.396</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.78</v>
+        <v>-0.26</v>
       </c>
       <c r="F38" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="G38" t="n">
-        <v>7.469</v>
+        <v>0.544</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.91</v>
+        <v>-0.31</v>
       </c>
       <c r="F39" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="G39" t="n">
-        <v>1.624</v>
+        <v>1.169</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.22</v>
+        <v>-0.49</v>
       </c>
       <c r="F40" t="n">
-        <v>0.74</v>
+        <v>0.91</v>
       </c>
       <c r="G40" t="n">
-        <v>3.37</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.45</v>
+        <v>-0.57</v>
       </c>
       <c r="F41" t="n">
-        <v>0.38</v>
+        <v>0.83</v>
       </c>
       <c r="G41" t="n">
-        <v>0.748</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-1.47</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>1.06</v>
+        <v>0.64</v>
       </c>
       <c r="G42" t="n">
-        <v>1.789</v>
+        <v>3.363</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-1.75</v>
+        <v>-1.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.44</v>
+        <v>1.07</v>
       </c>
       <c r="G43" t="n">
-        <v>1.81</v>
+        <v>1.585</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-1.86</v>
+        <v>-1.48</v>
       </c>
       <c r="F44" t="n">
         <v>0.78</v>
       </c>
       <c r="G44" t="n">
-        <v>0.633</v>
+        <v>4.677</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-2.34</v>
+        <v>-1.8</v>
       </c>
       <c r="F45" t="n">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
       <c r="G45" t="n">
-        <v>4.694</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3644,75 +3644,75 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3.38</v>
+        <v>-2.19</v>
       </c>
       <c r="F46" t="n">
-        <v>0.62</v>
+        <v>0.75</v>
       </c>
       <c r="G46" t="n">
-        <v>1.969</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.32</v>
+        <v>-2.99</v>
       </c>
       <c r="F47" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="G47" t="n">
-        <v>5.311</v>
+        <v>1.985</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-6.5</v>
+        <v>-8.58</v>
       </c>
       <c r="F48" t="n">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="G48" t="n">
-        <v>0.288</v>
+        <v>8.234</v>
       </c>
     </row>
     <row r="49">
@@ -3737,75 +3737,75 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-7.3</v>
+        <v>-10.33</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>0.115</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-10.36</v>
+        <v>-10.63</v>
       </c>
       <c r="F50" t="n">
-        <v>0.74</v>
+        <v>0.61</v>
       </c>
       <c r="G50" t="n">
-        <v>0.865</v>
+        <v>4.705</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-11.24</v>
+        <v>-11.41</v>
       </c>
       <c r="F51" t="n">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="G51" t="n">
-        <v>8.196</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-21.13</v>
+        <v>-18.32</v>
       </c>
       <c r="F52" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="G52" t="n">
-        <v>0.312</v>
+        <v>0.318</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.25</v>
+        <v>37.06</v>
       </c>
       <c r="C2" t="n">
-        <v>2.61</v>
+        <v>2.69</v>
       </c>
       <c r="D2" t="n">
-        <v>1.281</v>
+        <v>1.335</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.92</v>
+        <v>32.36</v>
       </c>
       <c r="C3" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.982</v>
+        <v>4.732</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,36 +3921,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.2</v>
+        <v>25.795</v>
       </c>
       <c r="C4" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="D4" t="n">
-        <v>3.029</v>
+        <v>9.718</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.39</v>
+        <v>25.08</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8</v>
+        <v>1.26</v>
       </c>
       <c r="D5" t="n">
-        <v>10.889</v>
+        <v>3.129</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3959,36 +3959,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.68</v>
+        <v>23.4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.73</v>
+        <v>1.575</v>
       </c>
       <c r="D6" t="n">
-        <v>5.871</v>
+        <v>17.404</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.41</v>
+        <v>21.05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="D7" t="n">
-        <v>41.019</v>
+        <v>10.749</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3997,17 +3997,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.46</v>
+        <v>16.65</v>
       </c>
       <c r="C8" t="n">
-        <v>1.32</v>
+        <v>0.8700000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>8.199</v>
+        <v>75.72799999999999</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -4016,112 +4016,112 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.53</v>
+        <v>16.31</v>
       </c>
       <c r="C9" t="n">
-        <v>0.905</v>
+        <v>0.84</v>
       </c>
       <c r="D9" t="n">
-        <v>76.937</v>
+        <v>6.1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.205</v>
+        <v>15.79</v>
       </c>
       <c r="C10" t="n">
-        <v>1.785</v>
+        <v>0.93</v>
       </c>
       <c r="D10" t="n">
-        <v>15.176</v>
+        <v>36.41</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.27</v>
+        <v>14.19</v>
       </c>
       <c r="C11" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="D11" t="n">
-        <v>20.784</v>
+        <v>1.27</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.08</v>
+        <v>12.715</v>
       </c>
       <c r="C12" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.168</v>
+        <v>20.516</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.09</v>
+        <v>11.81666666666666</v>
       </c>
       <c r="C13" t="n">
-        <v>1.01</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>7.487</v>
+        <v>21.665</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.06</v>
+        <v>9.24</v>
       </c>
       <c r="C14" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="D14" t="n">
-        <v>2.147</v>
+        <v>7.186</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4134,13 +4134,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.23</v>
+        <v>8.66</v>
       </c>
       <c r="C15" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="D15" t="n">
-        <v>8.903</v>
+        <v>9.561999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,74 +4149,74 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.35</v>
+        <v>4.94</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6966666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D16" t="n">
-        <v>21.034</v>
+        <v>2.08</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.27</v>
+        <v>2.356666666666667</v>
       </c>
       <c r="C17" t="n">
-        <v>0.64</v>
+        <v>0.5366666666666666</v>
       </c>
       <c r="D17" t="n">
-        <v>17.632</v>
+        <v>5.314</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.546</v>
+        <v>2.25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8160000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="D18" t="n">
-        <v>8.532999999999999</v>
+        <v>1.76</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.34</v>
+        <v>1.54</v>
       </c>
       <c r="C19" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="D19" t="n">
-        <v>0.64</v>
+        <v>25.876</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4225,74 +4225,74 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.19</v>
+        <v>1.468</v>
       </c>
       <c r="C20" t="n">
-        <v>0.76</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>25.948</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.11</v>
+        <v>1.45</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5733333333333334</v>
+        <v>0.79</v>
       </c>
       <c r="D21" t="n">
-        <v>5.499</v>
+        <v>6.735</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.36</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1.285</v>
+        <v>0.6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.06</v>
+        <v>0.607</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.46</v>
+        <v>0.65</v>
       </c>
       <c r="D23" t="n">
-        <v>0.545</v>
+        <v>17.451</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4301,36 +4301,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.71</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>1.09</v>
+        <v>0.97</v>
       </c>
       <c r="D24" t="n">
-        <v>6.878</v>
+        <v>1.034</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.91</v>
+        <v>-0.26</v>
       </c>
       <c r="C25" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="D25" t="n">
-        <v>1.624</v>
+        <v>0.544</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,36 +4339,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.22</v>
+        <v>-0.7599999999999998</v>
       </c>
       <c r="C26" t="n">
-        <v>0.74</v>
+        <v>1.05</v>
       </c>
       <c r="D26" t="n">
-        <v>3.37</v>
+        <v>1.245</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.47</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>1.06</v>
+        <v>0.64</v>
       </c>
       <c r="D27" t="n">
-        <v>1.789</v>
+        <v>3.363</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4381,13 +4381,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.59</v>
+        <v>-0.835</v>
       </c>
       <c r="C28" t="n">
         <v>0.72</v>
       </c>
       <c r="D28" t="n">
-        <v>25.834</v>
+        <v>24.282</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -4396,20 +4396,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.2025</v>
+        <v>-1.1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.79</v>
+        <v>1.07</v>
       </c>
       <c r="D29" t="n">
-        <v>23.049</v>
+        <v>1.585</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4419,13 +4419,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.23</v>
+        <v>-2.326666666666667</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5933333333333334</v>
+        <v>0.6033333333333334</v>
       </c>
       <c r="D30" t="n">
-        <v>3.35</v>
+        <v>3.288</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
@@ -4434,20 +4434,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.525</v>
+        <v>-3.0875</v>
       </c>
       <c r="C31" t="n">
-        <v>1.155</v>
+        <v>0.7975</v>
       </c>
       <c r="D31" t="n">
-        <v>1.207</v>
+        <v>22.261</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-7.3</v>
+        <v>-10.33</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.115</v>
+        <v>0.106</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2110</v>
+        <v>2095</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.86</v>
+        <v>-0.71</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.71</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="n">
-        <v>51.88</v>
+        <v>52.27</v>
       </c>
       <c r="H2" t="n">
-        <v>32.5437</v>
+        <v>29.095</v>
       </c>
       <c r="I2" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J2" t="n">
-        <v>64.40000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.54</v>
+        <v>4.57</v>
       </c>
       <c r="L2" t="n">
-        <v>-40.1</v>
+        <v>-32.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>0.79</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="E3" t="n">
-        <v>1.22</v>
+        <v>-0.6</v>
       </c>
       <c r="F3" t="n">
-        <v>15.41</v>
+        <v>15.79</v>
       </c>
       <c r="G3" t="n">
-        <v>60.17</v>
+        <v>56.85</v>
       </c>
       <c r="H3" t="n">
-        <v>240.5171</v>
+        <v>228.6055</v>
       </c>
       <c r="I3" t="n">
-        <v>71.2</v>
+        <v>66.7</v>
       </c>
       <c r="J3" t="n">
-        <v>64.3</v>
+        <v>60.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.66</v>
+        <v>4.53</v>
       </c>
       <c r="L3" t="n">
-        <v>-47.3</v>
+        <v>-39.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.91</v>
+        <v>1.71</v>
       </c>
       <c r="F4" t="n">
-        <v>-21.13</v>
+        <v>-18.32</v>
       </c>
       <c r="G4" t="n">
-        <v>29.05</v>
+        <v>43.91</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.8729</v>
+        <v>-5.426</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>41.8</v>
       </c>
       <c r="J4" t="n">
-        <v>45.6</v>
+        <v>75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.18</v>
       </c>
       <c r="L4" t="n">
-        <v>-16.5</v>
+        <v>-42.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>302.5</v>
+        <v>303</v>
       </c>
       <c r="E5" t="n">
-        <v>4.85</v>
+        <v>0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>15.68</v>
+        <v>16.31</v>
       </c>
       <c r="G5" t="n">
-        <v>63.49</v>
+        <v>54</v>
       </c>
       <c r="H5" t="n">
-        <v>20.3329</v>
+        <v>19.3853</v>
       </c>
       <c r="I5" t="n">
-        <v>65.5</v>
+        <v>64.2</v>
       </c>
       <c r="J5" t="n">
-        <v>52.8</v>
+        <v>54.7</v>
       </c>
       <c r="K5" t="n">
-        <v>7.74</v>
+        <v>7.59</v>
       </c>
       <c r="L5" t="n">
-        <v>61.9</v>
+        <v>20.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>🚀 BUY STRONG</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.09</v>
+        <v>6.23</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>7.01</v>
       </c>
       <c r="G6" t="n">
-        <v>53.76</v>
+        <v>61.65</v>
       </c>
       <c r="H6" t="n">
-        <v>30.1922</v>
+        <v>31.0759</v>
       </c>
       <c r="I6" t="n">
-        <v>64.40000000000001</v>
+        <v>102.3</v>
       </c>
       <c r="J6" t="n">
-        <v>54.4</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>5.27</v>
+        <v>5.15</v>
       </c>
       <c r="L6" t="n">
-        <v>-80.5</v>
+        <v>-51.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E7" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I7" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M7" t="n">
         <v>0.99</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="G7" t="n">
-        <v>53.85</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0597</v>
-      </c>
-      <c r="I7" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.03</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -490,13 +490,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E2" t="n">
-        <v>4.35</v>
+        <v>7.5</v>
       </c>
       <c r="F2" t="n">
-        <v>321</v>
+        <v>558</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.318</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.5</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
-        <v>4.73</v>
+        <v>-2.36</v>
       </c>
       <c r="F3" t="n">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.313</v>
+        <v>6.167</v>
       </c>
     </row>
     <row r="4">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>308</v>
+        <v>297.5</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3</v>
+        <v>-3.41</v>
       </c>
       <c r="F4" t="n">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.872</v>
+        <v>3.953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>127</v>
+        <v>298</v>
       </c>
       <c r="E5" t="n">
-        <v>9.960000000000001</v>
+        <v>5.86</v>
       </c>
       <c r="F5" t="n">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,33 +606,33 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5.846</v>
+        <v>4.865</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>352</v>
+        <v>152.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.96</v>
+        <v>-5.57</v>
       </c>
       <c r="F6" t="n">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.335</v>
+        <v>27.813</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1190</v>
+        <v>615</v>
       </c>
       <c r="E7" t="n">
-        <v>9.68</v>
+        <v>4.06</v>
       </c>
       <c r="F7" t="n">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>13.091</v>
+        <v>17.103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76.5</v>
+        <v>2005</v>
       </c>
       <c r="E8" t="n">
-        <v>2.68</v>
+        <v>6.37</v>
       </c>
       <c r="F8" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,67 +708,67 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9.561999999999999</v>
+        <v>21.579</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.65</v>
+        <v>1180</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.88</v>
+        <v>-0.84</v>
       </c>
       <c r="F9" t="n">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.106</v>
+        <v>13.625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70.8</v>
+        <v>214.5</v>
       </c>
       <c r="E10" t="n">
-        <v>2.91</v>
+        <v>-3.16</v>
       </c>
       <c r="F10" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.27</v>
+        <v>4.338</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68.3</v>
+        <v>254</v>
       </c>
       <c r="E11" t="n">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.76</v>
+        <v>7.693</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="E12" t="n">
-        <v>0.17</v>
+        <v>-4.55</v>
       </c>
       <c r="F12" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,67 +844,67 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6.1</v>
+        <v>1.342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48.85</v>
+        <v>216</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="F13" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.169</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>215.5</v>
+        <v>3950</v>
       </c>
       <c r="E14" t="n">
-        <v>1.17</v>
+        <v>3.67</v>
       </c>
       <c r="F14" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.927</v>
+        <v>8.768000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>591</v>
+        <v>2575</v>
       </c>
       <c r="E15" t="n">
-        <v>9.85</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,101 +946,101 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.246</v>
+        <v>50.843</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>251</v>
+        <v>68.2</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.18</v>
+        <v>-3.67</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7.396</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>537</v>
+        <v>742</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.83</v>
+        <v>4.07</v>
       </c>
       <c r="F17" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.585</v>
+        <v>11.405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>234.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.17</v>
+        <v>-2.29</v>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,203 +1048,203 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.823</v>
+        <v>1.844</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>187</v>
+        <v>58.3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.36</v>
+        <v>-1.19</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.129</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2500</v>
+        <v>269.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4</v>
+        <v>-1.28</v>
       </c>
       <c r="F20" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>47.793</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>713</v>
+        <v>5165</v>
       </c>
       <c r="E21" t="n">
-        <v>0.42</v>
+        <v>4.34</v>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.749</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>179</v>
+        <v>68.5</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="F22" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>17.451</v>
+        <v>1.672</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>382</v>
+        <v>189.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.53</v>
+        <v>1.61</v>
       </c>
       <c r="F23" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.985</v>
+        <v>9.057</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>526</v>
+        <v>75.8</v>
       </c>
       <c r="E24" t="n">
-        <v>1.35</v>
+        <v>-0.92</v>
       </c>
       <c r="F24" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,101 +1252,101 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>25.876</v>
+        <v>9.513</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>331</v>
       </c>
       <c r="E25" t="n">
-        <v>0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="F25" t="n">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.544</v>
+        <v>4.694</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>332</v>
+        <v>181</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6</v>
+        <v>1.12</v>
       </c>
       <c r="F26" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.677</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>186.5</v>
+        <v>18.9</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.1</v>
+        <v>-0.53</v>
       </c>
       <c r="F27" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.365</v>
+        <v>0.539</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>240</v>
+        <v>530</v>
       </c>
       <c r="E28" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="F28" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,33 +1388,33 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.889</v>
+        <v>24.042</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2095</v>
+        <v>289.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.71</v>
+        <v>-0.17</v>
       </c>
       <c r="F29" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,67 +1422,67 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6.735</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>150.5</v>
+        <v>121.5</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-0.41</v>
       </c>
       <c r="F30" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.354</v>
+        <v>3.217</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>111.5</v>
+        <v>378</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9</v>
+        <v>-1.05</v>
       </c>
       <c r="F31" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.277</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3170</v>
+        <v>184</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.31</v>
+        <v>-1.6</v>
       </c>
       <c r="F32" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,101 +1524,101 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.732</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4950</v>
+        <v>20.1</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6</v>
+        <v>-1.23</v>
       </c>
       <c r="F33" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>36.41</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1460</v>
+        <v>28.35</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.02</v>
+        <v>-1.05</v>
       </c>
       <c r="F34" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.607</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>67.3</v>
+        <v>90</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.88</v>
+        <v>1.12</v>
       </c>
       <c r="F35" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,67 +1626,67 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.073</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3810</v>
+        <v>543</v>
       </c>
       <c r="E36" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="F36" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>8.234</v>
+        <v>1.597</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>754</v>
+        <v>2100</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.05</v>
+        <v>0.24</v>
       </c>
       <c r="F37" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.08</v>
+        <v>6.661</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1885</v>
+        <v>294</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.05</v>
+        <v>-0.51</v>
       </c>
       <c r="F38" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>19.577</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="39">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>26.15</v>
+        <v>25.9</v>
       </c>
       <c r="E39" t="n">
-        <v>0.58</v>
+        <v>-0.96</v>
       </c>
       <c r="F39" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.487</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>161.5</v>
+        <v>755</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="F40" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,67 +1796,67 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>27.935</v>
+        <v>2.055</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>89</v>
+        <v>1475</v>
       </c>
       <c r="E41" t="n">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="F41" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.318</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>295.5</v>
+        <v>152</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.17</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,237 +1864,237 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>7.186</v>
+        <v>2.321</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>290</v>
+        <v>111.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.612</v>
+        <v>2.156</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>273</v>
+        <v>3155</v>
       </c>
       <c r="E44" t="n">
-        <v>0.37</v>
+        <v>-0.47</v>
       </c>
       <c r="F44" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.6909999999999999</v>
+        <v>4.684</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>42.35</v>
+        <v>48.55</v>
       </c>
       <c r="E45" t="n">
-        <v>0.36</v>
+        <v>-0.61</v>
       </c>
       <c r="F45" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.723</v>
+        <v>1.104</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>20.35</v>
+        <v>41.9</v>
       </c>
       <c r="E46" t="n">
-        <v>0.25</v>
+        <v>-1.06</v>
       </c>
       <c r="F46" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.311</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>580</v>
+        <v>292</v>
       </c>
       <c r="E47" t="n">
-        <v>6.23</v>
+        <v>-3.63</v>
       </c>
       <c r="F47" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5.101</v>
+        <v>5.867</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>122</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>0.83</v>
+        <v>0.15</v>
       </c>
       <c r="F48" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>3.363</v>
+        <v>2.006</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>281.5</v>
+        <v>110.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.05</v>
+        <v>-2.21</v>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>4.705</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>59.7</v>
+        <v>8600</v>
       </c>
       <c r="E50" t="n">
-        <v>1.53</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.697</v>
+        <v>13.014</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>113</v>
+        <v>58.7</v>
       </c>
       <c r="E51" t="n">
-        <v>0.44</v>
+        <v>-1.68</v>
       </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,33 +2170,33 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.728</v>
+        <v>1.606</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7900</v>
+        <v>606</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>12.282</v>
+        <v>4.756</v>
       </c>
     </row>
   </sheetData>
@@ -2261,94 +2261,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>40.8</v>
+        <v>48.28</v>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>0.44</v>
       </c>
       <c r="G2" t="n">
-        <v>5.846</v>
+        <v>13.014</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>37.06</v>
+        <v>39.17</v>
       </c>
       <c r="F3" t="n">
-        <v>2.69</v>
+        <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.335</v>
+        <v>6.167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34.01</v>
+        <v>37.74</v>
       </c>
       <c r="F4" t="n">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="G4" t="n">
-        <v>12.282</v>
+        <v>17.103</v>
       </c>
     </row>
     <row r="5">
@@ -2373,261 +2373,261 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32.36</v>
+        <v>35.41</v>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>4.732</v>
+        <v>4.684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28.17</v>
+        <v>30.58</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>2.53</v>
       </c>
       <c r="G6" t="n">
-        <v>27.935</v>
+        <v>1.342</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25.88</v>
+        <v>27.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.97</v>
+        <v>1.47</v>
       </c>
       <c r="G7" t="n">
-        <v>16.246</v>
+        <v>13.625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25.08</v>
+        <v>25.98</v>
       </c>
       <c r="F8" t="n">
-        <v>1.26</v>
+        <v>0.85</v>
       </c>
       <c r="G8" t="n">
-        <v>3.129</v>
+        <v>11.405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>23.74</v>
+        <v>25.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="G9" t="n">
-        <v>4.313</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>23.06</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>1.38</v>
+        <v>0.82</v>
       </c>
       <c r="G10" t="n">
-        <v>13.091</v>
+        <v>27.813</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.05</v>
+        <v>21.88</v>
       </c>
       <c r="F11" t="n">
-        <v>0.77</v>
+        <v>1.85</v>
       </c>
       <c r="G11" t="n">
-        <v>10.749</v>
+        <v>4.338</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>16.8</v>
+        <v>21.16</v>
       </c>
       <c r="F12" t="n">
-        <v>1.24</v>
+        <v>0.84</v>
       </c>
       <c r="G12" t="n">
-        <v>0.927</v>
+        <v>5.867</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>16.31</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>0.84</v>
+        <v>1.26</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="14">
@@ -2652,137 +2652,137 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15.79</v>
+        <v>19.01</v>
       </c>
       <c r="F14" t="n">
         <v>0.93</v>
       </c>
       <c r="G14" t="n">
-        <v>36.41</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14.19</v>
+        <v>15.43</v>
       </c>
       <c r="F15" t="n">
-        <v>0.79</v>
+        <v>0.27</v>
       </c>
       <c r="G15" t="n">
-        <v>1.27</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10.79</v>
+        <v>15.18</v>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>2.17</v>
       </c>
       <c r="G16" t="n">
-        <v>3.872</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.24</v>
+        <v>13.92</v>
       </c>
       <c r="F17" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="G17" t="n">
-        <v>7.186</v>
+        <v>21.579</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.960000000000001</v>
+        <v>12.64</v>
       </c>
       <c r="F18" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>19.577</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="19">
@@ -2807,75 +2807,75 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.66</v>
+        <v>11.8</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G19" t="n">
-        <v>9.561999999999999</v>
+        <v>9.513</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7.01</v>
+        <v>10.99</v>
       </c>
       <c r="F20" t="n">
-        <v>0.23</v>
+        <v>0.74</v>
       </c>
       <c r="G20" t="n">
-        <v>5.101</v>
+        <v>24.042</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.13</v>
+        <v>10.89</v>
       </c>
       <c r="F21" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="G21" t="n">
-        <v>47.793</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="22">
@@ -2900,881 +2900,881 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.94</v>
+        <v>10.58</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="G22" t="n">
-        <v>2.08</v>
+        <v>2.055</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.88</v>
+        <v>8.18</v>
       </c>
       <c r="F23" t="n">
-        <v>0.79</v>
+        <v>1.23</v>
       </c>
       <c r="G23" t="n">
-        <v>2.354</v>
+        <v>3.953</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.83</v>
+        <v>8.06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.53</v>
+        <v>1.15</v>
       </c>
       <c r="G24" t="n">
-        <v>1.697</v>
+        <v>50.843</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.56</v>
+        <v>7.1</v>
       </c>
       <c r="F25" t="n">
-        <v>1.45</v>
+        <v>0.76</v>
       </c>
       <c r="G25" t="n">
-        <v>0.318</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.889</v>
+        <v>6.661</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.29</v>
+        <v>4.26</v>
       </c>
       <c r="F27" t="n">
-        <v>0.84</v>
+        <v>1.34</v>
       </c>
       <c r="G27" t="n">
-        <v>2.277</v>
+        <v>1.672</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.25</v>
+        <v>3.85</v>
       </c>
       <c r="F28" t="n">
-        <v>1.21</v>
+        <v>0.72</v>
       </c>
       <c r="G28" t="n">
-        <v>1.76</v>
+        <v>3.217</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.54</v>
+        <v>3.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="G29" t="n">
-        <v>25.876</v>
+        <v>2.321</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.45</v>
+        <v>3.04</v>
       </c>
       <c r="F30" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>6.735</v>
+        <v>1.597</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="F31" t="n">
-        <v>0.77</v>
+        <v>1.04</v>
       </c>
       <c r="G31" t="n">
-        <v>2.073</v>
+        <v>7.693</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.89</v>
+        <v>2.43</v>
       </c>
       <c r="F32" t="n">
-        <v>0.39</v>
+        <v>0.62</v>
       </c>
       <c r="G32" t="n">
-        <v>1.728</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.54</v>
+        <v>1.56</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>9.365</v>
+        <v>1.606</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.47</v>
+        <v>1.22</v>
       </c>
       <c r="F34" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="G34" t="n">
-        <v>0.723</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="F35" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>17.451</v>
+        <v>9.057</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.607</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F37" t="n">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="G37" t="n">
-        <v>7.396</v>
+        <v>2.006</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.26</v>
+        <v>-0.33</v>
       </c>
       <c r="F38" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G38" t="n">
-        <v>0.544</v>
+        <v>4.865</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.31</v>
+        <v>-0.53</v>
       </c>
       <c r="F39" t="n">
-        <v>0.86</v>
+        <v>1.49</v>
       </c>
       <c r="G39" t="n">
-        <v>1.169</v>
+        <v>0.539</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-0.49</v>
+        <v>-0.89</v>
       </c>
       <c r="F40" t="n">
         <v>0.91</v>
       </c>
       <c r="G40" t="n">
-        <v>0.311</v>
+        <v>2.156</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-0.57</v>
+        <v>-1.1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>0.487</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.19</v>
       </c>
       <c r="F42" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="G42" t="n">
-        <v>3.363</v>
+        <v>4.694</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-1.1</v>
+        <v>-1.88</v>
       </c>
       <c r="F43" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="G43" t="n">
-        <v>1.585</v>
+        <v>1.844</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-1.48</v>
+        <v>-2.1</v>
       </c>
       <c r="F44" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="G44" t="n">
-        <v>4.677</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-1.8</v>
+        <v>-2.19</v>
       </c>
       <c r="F45" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-2.19</v>
+        <v>-2.47</v>
       </c>
       <c r="F46" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="G46" t="n">
-        <v>0.612</v>
+        <v>8.768000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-2.99</v>
+        <v>-3</v>
       </c>
       <c r="F47" t="n">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="G47" t="n">
-        <v>1.985</v>
+        <v>0.458</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-8.58</v>
+        <v>-3.67</v>
       </c>
       <c r="F48" t="n">
-        <v>0.48</v>
+        <v>0.95</v>
       </c>
       <c r="G48" t="n">
-        <v>8.234</v>
+        <v>1.104</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-10.33</v>
+        <v>-4.33</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="G49" t="n">
-        <v>0.106</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-10.63</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="G50" t="n">
-        <v>4.705</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="51">
@@ -3799,13 +3799,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-11.41</v>
+        <v>-10.31</v>
       </c>
       <c r="F51" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="G51" t="n">
-        <v>0.823</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-18.32</v>
+        <v>-13.03</v>
       </c>
       <c r="F52" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="G52" t="n">
-        <v>0.318</v>
+        <v>0.314</v>
       </c>
     </row>
   </sheetData>
@@ -3883,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.06</v>
+        <v>35.41</v>
       </c>
       <c r="C2" t="n">
-        <v>2.69</v>
+        <v>1.01</v>
       </c>
       <c r="D2" t="n">
-        <v>1.335</v>
+        <v>4.684</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32.36</v>
+        <v>30.58</v>
       </c>
       <c r="C3" t="n">
-        <v>1.09</v>
+        <v>2.53</v>
       </c>
       <c r="D3" t="n">
-        <v>4.732</v>
+        <v>1.342</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,20 +3921,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.795</v>
+        <v>25.98</v>
       </c>
       <c r="C4" t="n">
-        <v>1.34</v>
+        <v>0.85</v>
       </c>
       <c r="D4" t="n">
-        <v>9.718</v>
+        <v>11.405</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.08</v>
+        <v>25.17</v>
       </c>
       <c r="C5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="D5" t="n">
         <v>3.129</v>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.4</v>
+        <v>24.585</v>
       </c>
       <c r="C6" t="n">
-        <v>1.575</v>
+        <v>1.66</v>
       </c>
       <c r="D6" t="n">
-        <v>17.404</v>
+        <v>17.963</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -3978,36 +3978,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.05</v>
+        <v>23.675</v>
       </c>
       <c r="C7" t="n">
-        <v>0.77</v>
+        <v>1.415</v>
       </c>
       <c r="D7" t="n">
-        <v>10.749</v>
+        <v>10.12</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.65</v>
+        <v>22.905</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8700000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="D8" t="n">
-        <v>75.72799999999999</v>
+        <v>21.782</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -4016,36 +4016,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.31</v>
+        <v>22.78333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>0.84</v>
+        <v>1.193333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>6.1</v>
+        <v>22.294</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.79</v>
+        <v>21.16</v>
       </c>
       <c r="C10" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="D10" t="n">
-        <v>36.41</v>
+        <v>5.867</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.19</v>
+        <v>19.01</v>
       </c>
       <c r="C11" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="D11" t="n">
-        <v>1.27</v>
+        <v>37.62</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,17 +4073,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12.715</v>
+        <v>15.03</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5</v>
+        <v>0.9849999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>20.516</v>
+        <v>78.65600000000001</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -4092,36 +4092,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11.81666666666666</v>
+        <v>12.64</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8833333333333333</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>21.665</v>
+        <v>7.06</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.24</v>
+        <v>11.8</v>
       </c>
       <c r="C14" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>7.186</v>
+        <v>9.513</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,17 +4130,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.66</v>
+        <v>10.99</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
       <c r="D15" t="n">
-        <v>9.561999999999999</v>
+        <v>24.042</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,17 +4149,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.94</v>
+        <v>10.89</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="D16" t="n">
-        <v>2.08</v>
+        <v>1.125</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,36 +4168,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.356666666666667</v>
+        <v>10.58</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5366666666666666</v>
+        <v>0.86</v>
       </c>
       <c r="D17" t="n">
-        <v>5.314</v>
+        <v>2.055</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.25</v>
+        <v>7.1</v>
       </c>
       <c r="C18" t="n">
-        <v>1.21</v>
+        <v>0.76</v>
       </c>
       <c r="D18" t="n">
-        <v>1.76</v>
+        <v>17.03</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4206,55 +4206,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.54</v>
+        <v>6.795</v>
       </c>
       <c r="C19" t="n">
-        <v>0.67</v>
+        <v>0.925</v>
       </c>
       <c r="D19" t="n">
-        <v>25.876</v>
+        <v>26.444</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.468</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="D20" t="n">
-        <v>8.359999999999999</v>
+        <v>6.661</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.45</v>
+        <v>4.26</v>
       </c>
       <c r="C21" t="n">
-        <v>0.79</v>
+        <v>1.34</v>
       </c>
       <c r="D21" t="n">
-        <v>6.735</v>
+        <v>1.672</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4263,17 +4263,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="D22" t="n">
-        <v>0.607</v>
+        <v>3.217</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,55 +4282,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3.485</v>
       </c>
       <c r="C23" t="n">
-        <v>0.65</v>
+        <v>1.08</v>
       </c>
       <c r="D23" t="n">
-        <v>17.451</v>
+        <v>1.286</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.01000000000000001</v>
+        <v>3.04</v>
       </c>
       <c r="C24" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.034</v>
+        <v>1.597</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.26</v>
+        <v>2.43</v>
       </c>
       <c r="C25" t="n">
-        <v>1.44</v>
+        <v>0.62</v>
       </c>
       <c r="D25" t="n">
-        <v>0.544</v>
+        <v>0.597</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -4339,36 +4339,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7599999999999998</v>
+        <v>0.1233333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>1.05</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>1.245</v>
+        <v>3.083</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="C27" t="n">
-        <v>0.64</v>
+        <v>1.49</v>
       </c>
       <c r="D27" t="n">
-        <v>3.363</v>
+        <v>0.539</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,77 +4377,77 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.835</v>
+        <v>-0.8620000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>0.72</v>
+        <v>0.8699999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>24.282</v>
+        <v>8.045</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.1</v>
+        <v>-1.55</v>
       </c>
       <c r="C29" t="n">
-        <v>1.07</v>
+        <v>0.5933333333333334</v>
       </c>
       <c r="D29" t="n">
-        <v>1.585</v>
+        <v>5.075</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.326666666666667</v>
+        <v>-2.085</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6033333333333334</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>3.288</v>
+        <v>22.254</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.0875</v>
+        <v>-2.145</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7975</v>
+        <v>0.86</v>
       </c>
       <c r="D31" t="n">
-        <v>22.261</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-10.33</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="D32" t="n">
-        <v>0.106</v>
+        <v>0.098</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.71</v>
+        <v>0.24</v>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>52.27</v>
+        <v>59.32</v>
       </c>
       <c r="H2" t="n">
-        <v>29.095</v>
+        <v>15.8684</v>
       </c>
       <c r="I2" t="n">
-        <v>57</v>
+        <v>57.2</v>
       </c>
       <c r="J2" t="n">
-        <v>59.3</v>
+        <v>61</v>
       </c>
       <c r="K2" t="n">
-        <v>4.57</v>
+        <v>4.34</v>
       </c>
       <c r="L2" t="n">
-        <v>-32.5</v>
+        <v>-20.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,31 +4624,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4950</v>
+        <v>5165</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6</v>
+        <v>4.34</v>
       </c>
       <c r="F3" t="n">
-        <v>15.79</v>
+        <v>19.01</v>
       </c>
       <c r="G3" t="n">
-        <v>56.85</v>
+        <v>66.48</v>
       </c>
       <c r="H3" t="n">
-        <v>228.6055</v>
+        <v>233.5474</v>
       </c>
       <c r="I3" t="n">
-        <v>66.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>60.8</v>
+        <v>86</v>
       </c>
       <c r="K3" t="n">
-        <v>4.53</v>
+        <v>4.38</v>
       </c>
       <c r="L3" t="n">
-        <v>-39.3</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
         <v>0.93</v>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>1.71</v>
+        <v>1.12</v>
       </c>
       <c r="F4" t="n">
-        <v>-18.32</v>
+        <v>-13.03</v>
       </c>
       <c r="G4" t="n">
-        <v>43.91</v>
+        <v>48.47</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.426</v>
+        <v>-5.707</v>
       </c>
       <c r="I4" t="n">
-        <v>41.8</v>
+        <v>47.6</v>
       </c>
       <c r="J4" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>4.18</v>
+        <v>4.02</v>
       </c>
       <c r="L4" t="n">
-        <v>-42.4</v>
+        <v>-17.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>-3.63</v>
       </c>
       <c r="F5" t="n">
-        <v>16.31</v>
+        <v>21.16</v>
       </c>
       <c r="G5" t="n">
-        <v>54</v>
+        <v>50.94</v>
       </c>
       <c r="H5" t="n">
-        <v>19.3853</v>
+        <v>17.1148</v>
       </c>
       <c r="I5" t="n">
-        <v>64.2</v>
+        <v>44.9</v>
       </c>
       <c r="J5" t="n">
-        <v>54.7</v>
+        <v>13.2</v>
       </c>
       <c r="K5" t="n">
-        <v>7.59</v>
+        <v>7.45</v>
       </c>
       <c r="L5" t="n">
-        <v>20.6</v>
+        <v>-40.7</v>
       </c>
       <c r="M5" t="n">
         <v>0.84</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>⚠️ TAKE PROFIT</t>
         </is>
       </c>
     </row>
@@ -4780,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="E6" t="n">
-        <v>6.23</v>
+        <v>4.48</v>
       </c>
       <c r="F6" t="n">
-        <v>7.01</v>
+        <v>15.43</v>
       </c>
       <c r="G6" t="n">
-        <v>61.65</v>
+        <v>71.16</v>
       </c>
       <c r="H6" t="n">
-        <v>31.0759</v>
+        <v>31.6583</v>
       </c>
       <c r="I6" t="n">
-        <v>102.3</v>
+        <v>114.1</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="L6" t="n">
-        <v>-51.3</v>
+        <v>-69.90000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.18</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>60.71</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0076</v>
+        <v>-0.2638</v>
       </c>
       <c r="I7" t="n">
-        <v>48.9</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>47.4</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1</v>
+        <v>52.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5</v>
+        <v>0.79</v>
       </c>
       <c r="F2" t="n">
-        <v>558</v>
+        <v>294</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.435</v>
+        <v>8.364000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>127.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.36</v>
+        <v>-1.16</v>
       </c>
       <c r="F3" t="n">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.167</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>297.5</v>
+        <v>567</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.41</v>
+        <v>-6.44</v>
       </c>
       <c r="F4" t="n">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,67 +572,67 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.953</v>
+        <v>4.228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="E5" t="n">
-        <v>5.86</v>
+        <v>-3.63</v>
       </c>
       <c r="F5" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4.865</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>152.5</v>
+        <v>310.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.57</v>
+        <v>4.37</v>
       </c>
       <c r="F6" t="n">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>27.813</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>191</v>
       </c>
       <c r="E7" t="n">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="F7" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>17.103</v>
+        <v>3.523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2005</v>
+        <v>4180</v>
       </c>
       <c r="E8" t="n">
-        <v>6.37</v>
+        <v>5.82</v>
       </c>
       <c r="F8" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,67 +708,67 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.579</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1180</v>
+        <v>147.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.84</v>
+        <v>-3.28</v>
       </c>
       <c r="F9" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>13.625</v>
+        <v>28.103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>214.5</v>
+        <v>127.5</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.16</v>
+        <v>2.82</v>
       </c>
       <c r="F10" t="n">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,33 +776,33 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4.338</v>
+        <v>6.722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>254</v>
+        <v>4920</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2</v>
+        <v>-4.74</v>
       </c>
       <c r="F11" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7.693</v>
+        <v>36.046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>336</v>
+        <v>2050</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.55</v>
+        <v>2.24</v>
       </c>
       <c r="F12" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,33 +844,33 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.342</v>
+        <v>22.433</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>216</v>
+        <v>8375</v>
       </c>
       <c r="E13" t="n">
-        <v>0.23</v>
+        <v>-2.62</v>
       </c>
       <c r="F13" t="n">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,67 +878,67 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.972</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3950</v>
+        <v>370</v>
       </c>
       <c r="E14" t="n">
-        <v>3.67</v>
+        <v>-2.12</v>
       </c>
       <c r="F14" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.768000000000001</v>
+        <v>1.843</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2575</v>
+        <v>1205</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="F15" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50.843</v>
+        <v>14.221</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>68.2</v>
+        <v>299</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.67</v>
+        <v>0.34</v>
       </c>
       <c r="F16" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.125</v>
+        <v>4.718</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>742</v>
+        <v>154.5</v>
       </c>
       <c r="E17" t="n">
-        <v>4.07</v>
+        <v>1.64</v>
       </c>
       <c r="F17" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11.405</v>
+        <v>2.341</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>234.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.29</v>
+        <v>1.48</v>
       </c>
       <c r="F18" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,33 +1048,33 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.844</v>
+        <v>2.038</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58.3</v>
+        <v>49.3</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.19</v>
+        <v>1.54</v>
       </c>
       <c r="F19" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,237 +1082,237 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>269.5</v>
+        <v>2585</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.28</v>
+        <v>0.39</v>
       </c>
       <c r="F20" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.65</v>
+        <v>51.598</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5165</v>
+        <v>28.2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.34</v>
+        <v>-0.53</v>
       </c>
       <c r="F21" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>37.62</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>68.5</v>
+        <v>298</v>
       </c>
       <c r="E22" t="n">
-        <v>0.29</v>
+        <v>1.36</v>
       </c>
       <c r="F22" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.672</v>
+        <v>7.265</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>189.5</v>
+        <v>41.55</v>
       </c>
       <c r="E23" t="n">
-        <v>1.61</v>
+        <v>-0.84</v>
       </c>
       <c r="F23" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9.057</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>75.8</v>
+        <v>58.6</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.92</v>
+        <v>0.51</v>
       </c>
       <c r="F24" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9.513</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>331</v>
+        <v>112</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3</v>
+        <v>0.45</v>
       </c>
       <c r="F25" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.694</v>
+        <v>2.168</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>181</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>1.12</v>
+        <v>0.15</v>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,33 +1320,33 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>17.03</v>
+        <v>1.656</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18.9</v>
+        <v>215</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.53</v>
+        <v>0.23</v>
       </c>
       <c r="F27" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,33 +1354,33 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.539</v>
+        <v>4.413</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>530</v>
+        <v>210.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.76</v>
+        <v>-2.55</v>
       </c>
       <c r="F28" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1388,67 +1388,67 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>24.042</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>289.5</v>
+        <v>267</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.17</v>
+        <v>-0.93</v>
       </c>
       <c r="F29" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.575</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>121.5</v>
+        <v>1470</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.41</v>
+        <v>-0.34</v>
       </c>
       <c r="F30" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,33 +1456,33 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3.217</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>378</v>
+        <v>333.5</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.05</v>
+        <v>0.76</v>
       </c>
       <c r="F31" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1490,33 +1490,33 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.858</v>
+        <v>4.554</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>184</v>
+        <v>592</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.6</v>
+        <v>-3.74</v>
       </c>
       <c r="F32" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1524,67 +1524,67 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.129</v>
+        <v>16.319</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>20.1</v>
+        <v>525</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.23</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.304</v>
+        <v>22.661</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>28.35</v>
+        <v>25.95</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.05</v>
+        <v>0.19</v>
       </c>
       <c r="F34" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,101 +1592,101 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.098</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>90</v>
+        <v>3115</v>
       </c>
       <c r="E35" t="n">
-        <v>1.12</v>
+        <v>-1.27</v>
       </c>
       <c r="F35" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.314</v>
+        <v>4.592</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>543</v>
+        <v>189.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.597</v>
+        <v>8.551</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2100</v>
+        <v>744</v>
       </c>
       <c r="E37" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="F37" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,33 +1694,33 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6.661</v>
+        <v>11.199</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>294</v>
+        <v>18.95</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.51</v>
+        <v>0.26</v>
       </c>
       <c r="F38" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7.06</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>25.9</v>
+        <v>88.8</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.96</v>
+        <v>-1.33</v>
       </c>
       <c r="F39" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,33 +1762,33 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.458</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>755</v>
+        <v>177.5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.13</v>
+        <v>-1.93</v>
       </c>
       <c r="F40" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1796,67 +1796,67 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2.055</v>
+        <v>16.325</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1475</v>
+        <v>236.5</v>
       </c>
       <c r="E41" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="F41" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.597</v>
+        <v>1.703</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>152</v>
+        <v>755</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.321</v>
+        <v>2.059</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>111.5</v>
+        <v>20.1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,101 +1898,101 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.156</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3155</v>
+        <v>537</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.47</v>
+        <v>-1.1</v>
       </c>
       <c r="F44" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4.684</v>
+        <v>1.569</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>48.55</v>
+        <v>74.3</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.61</v>
+        <v>-1.98</v>
       </c>
       <c r="F45" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.104</v>
+        <v>9.257999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>41.9</v>
+        <v>59.2</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.06</v>
+        <v>0.85</v>
       </c>
       <c r="F46" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,33 +2000,33 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.681</v>
+        <v>1.574</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>292</v>
+        <v>119.5</v>
       </c>
       <c r="E47" t="n">
-        <v>-3.63</v>
+        <v>-1.65</v>
       </c>
       <c r="F47" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,101 +2034,101 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5.867</v>
+        <v>3.064</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>67.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="E48" t="n">
-        <v>0.15</v>
+        <v>-1.76</v>
       </c>
       <c r="F48" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.006</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>110.5</v>
+        <v>2090</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.21</v>
+        <v>-0.48</v>
       </c>
       <c r="F49" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.625</v>
+        <v>6.471</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8600</v>
+        <v>345</v>
       </c>
       <c r="E50" t="n">
-        <v>8.859999999999999</v>
+        <v>2.68</v>
       </c>
       <c r="F50" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>13.014</v>
+        <v>1.394</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>58.7</v>
+        <v>111.5</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.68</v>
+        <v>0.9</v>
       </c>
       <c r="F51" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,41 +2170,41 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.606</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>606</v>
+        <v>284</v>
       </c>
       <c r="E52" t="n">
-        <v>4.48</v>
+        <v>-2.74</v>
       </c>
       <c r="F52" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4.756</v>
+        <v>5.523</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48.28</v>
+        <v>44.15</v>
       </c>
       <c r="F2" t="n">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="G2" t="n">
-        <v>13.014</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="3">
@@ -2311,137 +2311,137 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39.17</v>
+        <v>41.51</v>
       </c>
       <c r="F3" t="n">
         <v>1.6</v>
       </c>
       <c r="G3" t="n">
-        <v>6.167</v>
+        <v>6.722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>37.74</v>
+        <v>34.08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.14</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>17.103</v>
+        <v>1.394</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>35.41</v>
+        <v>31.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>4.684</v>
+        <v>16.319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30.58</v>
+        <v>30.61</v>
       </c>
       <c r="F6" t="n">
-        <v>2.53</v>
+        <v>0.85</v>
       </c>
       <c r="G6" t="n">
-        <v>1.342</v>
+        <v>4.592</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27.29</v>
+        <v>27.33</v>
       </c>
       <c r="F7" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="G7" t="n">
-        <v>13.625</v>
+        <v>3.523</v>
       </c>
     </row>
     <row r="8">
@@ -2466,75 +2466,75 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25.98</v>
+        <v>26.53</v>
       </c>
       <c r="F8" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>11.405</v>
+        <v>11.199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25.17</v>
+        <v>22.83</v>
       </c>
       <c r="F9" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="G9" t="n">
-        <v>3.129</v>
+        <v>14.221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>17.27</v>
       </c>
       <c r="F10" t="n">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="G10" t="n">
-        <v>27.813</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="11">
@@ -2559,1191 +2559,1191 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.88</v>
+        <v>17.17</v>
       </c>
       <c r="F11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G11" t="n">
-        <v>4.338</v>
+        <v>4.413</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>21.16</v>
+        <v>13.74</v>
       </c>
       <c r="F12" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="G12" t="n">
-        <v>5.867</v>
+        <v>7.265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>13.46</v>
       </c>
       <c r="F13" t="n">
-        <v>1.26</v>
+        <v>0.99</v>
       </c>
       <c r="G13" t="n">
-        <v>0.972</v>
+        <v>28.103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19.01</v>
+        <v>13.33</v>
       </c>
       <c r="F14" t="n">
-        <v>0.93</v>
+        <v>2.42</v>
       </c>
       <c r="G14" t="n">
-        <v>37.62</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>15.43</v>
+        <v>12.33</v>
       </c>
       <c r="F15" t="n">
-        <v>0.27</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>4.756</v>
+        <v>22.433</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>15.18</v>
+        <v>12.3</v>
       </c>
       <c r="F16" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G16" t="n">
-        <v>0.435</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13.92</v>
+        <v>11.44</v>
       </c>
       <c r="F17" t="n">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="G17" t="n">
-        <v>21.579</v>
+        <v>36.046</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.64</v>
+        <v>9.65</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>7.06</v>
+        <v>2.059</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>11.8</v>
+        <v>9.02</v>
       </c>
       <c r="F19" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="G19" t="n">
-        <v>9.513</v>
+        <v>5.523</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.99</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="G20" t="n">
-        <v>24.042</v>
+        <v>9.257999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>10.89</v>
+        <v>7.58</v>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="G21" t="n">
-        <v>1.125</v>
+        <v>51.598</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10.58</v>
+        <v>7.39</v>
       </c>
       <c r="F22" t="n">
-        <v>0.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>2.055</v>
+        <v>4.228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8.18</v>
+        <v>5.85</v>
       </c>
       <c r="F23" t="n">
-        <v>1.23</v>
+        <v>0.8</v>
       </c>
       <c r="G23" t="n">
-        <v>3.953</v>
+        <v>22.661</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8.06</v>
+        <v>3.94</v>
       </c>
       <c r="F24" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="G24" t="n">
-        <v>50.843</v>
+        <v>1.656</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7.1</v>
+        <v>3.72</v>
       </c>
       <c r="F25" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="G25" t="n">
-        <v>17.03</v>
+        <v>6.471</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G26" t="n">
-        <v>6.661</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.26</v>
+        <v>2.66</v>
       </c>
       <c r="F27" t="n">
-        <v>1.34</v>
+        <v>0.88</v>
       </c>
       <c r="G27" t="n">
-        <v>1.672</v>
+        <v>2.341</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3.85</v>
+        <v>2.48</v>
       </c>
       <c r="F28" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="G28" t="n">
-        <v>3.217</v>
+        <v>1.569</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3.4</v>
+        <v>2.01</v>
       </c>
       <c r="F29" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="G29" t="n">
-        <v>2.321</v>
+        <v>16.325</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3.04</v>
+        <v>1.72</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1.597</v>
+        <v>1.574</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.63</v>
+        <v>1.5</v>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>7.693</v>
+        <v>1.703</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2.43</v>
+        <v>0.3</v>
       </c>
       <c r="F32" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="G32" t="n">
-        <v>0.597</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="G33" t="n">
-        <v>1.606</v>
+        <v>8.364000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="G34" t="n">
-        <v>0.575</v>
+        <v>2.038</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.53</v>
+        <v>-0.5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="G35" t="n">
-        <v>9.057</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.25</v>
+        <v>-0.79</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.35</v>
       </c>
       <c r="G36" t="n">
-        <v>1.858</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.15</v>
+        <v>-0.95</v>
       </c>
       <c r="F37" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="G37" t="n">
-        <v>2.006</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.33</v>
+        <v>-1.65</v>
       </c>
       <c r="F38" t="n">
-        <v>0.88</v>
+        <v>0.72</v>
       </c>
       <c r="G38" t="n">
-        <v>4.865</v>
+        <v>3.064</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.53</v>
+        <v>-1.71</v>
       </c>
       <c r="F39" t="n">
-        <v>1.49</v>
+        <v>0.79</v>
       </c>
       <c r="G39" t="n">
-        <v>0.539</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-0.89</v>
+        <v>-1.93</v>
       </c>
       <c r="F40" t="n">
-        <v>0.91</v>
+        <v>1.1</v>
       </c>
       <c r="G40" t="n">
-        <v>2.156</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.1</v>
+        <v>-2.24</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="G41" t="n">
-        <v>0.65</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-1.19</v>
+        <v>-2.61</v>
       </c>
       <c r="F42" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="G42" t="n">
-        <v>4.694</v>
+        <v>2.168</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-1.88</v>
+        <v>-2.63</v>
       </c>
       <c r="F43" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="G43" t="n">
-        <v>1.844</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-2.1</v>
+        <v>-2.92</v>
       </c>
       <c r="F44" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>0.681</v>
+        <v>4.718</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-2.19</v>
+        <v>-3.04</v>
       </c>
       <c r="F45" t="n">
-        <v>0.77</v>
+        <v>0.39</v>
       </c>
       <c r="G45" t="n">
-        <v>0.304</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-2.47</v>
+        <v>-3.22</v>
       </c>
       <c r="F46" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>8.768000000000001</v>
+        <v>1.843</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-3</v>
+        <v>-3.26</v>
       </c>
       <c r="F47" t="n">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="G47" t="n">
-        <v>0.458</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-3.67</v>
+        <v>-3.33</v>
       </c>
       <c r="F48" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="G48" t="n">
-        <v>1.104</v>
+        <v>4.554</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-4.33</v>
+        <v>-4.29</v>
       </c>
       <c r="F49" t="n">
-        <v>0.43</v>
+        <v>0.84</v>
       </c>
       <c r="G49" t="n">
-        <v>1.625</v>
+        <v>8.551</v>
       </c>
     </row>
     <row r="50">
@@ -3768,13 +3768,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.32</v>
       </c>
       <c r="F50" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="G50" t="n">
-        <v>0.098</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="51">
@@ -3799,13 +3799,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-10.31</v>
+        <v>-13.19</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-13.03</v>
+        <v>-14.6</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G52" t="n">
-        <v>0.314</v>
+        <v>0.312</v>
       </c>
     </row>
   </sheetData>
@@ -3883,17 +3883,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.41</v>
+        <v>34.08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="D2" t="n">
-        <v>4.684</v>
+        <v>1.394</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3902,17 +3902,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.58</v>
+        <v>30.61</v>
       </c>
       <c r="C3" t="n">
-        <v>2.53</v>
+        <v>0.85</v>
       </c>
       <c r="D3" t="n">
-        <v>1.342</v>
+        <v>4.592</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3921,17 +3921,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.98</v>
+        <v>27.33</v>
       </c>
       <c r="C4" t="n">
-        <v>0.85</v>
+        <v>1.19</v>
       </c>
       <c r="D4" t="n">
-        <v>11.405</v>
+        <v>3.523</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -3940,55 +3940,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.17</v>
+        <v>26.905</v>
       </c>
       <c r="C5" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="D5" t="n">
-        <v>3.129</v>
+        <v>11.112</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.585</v>
+        <v>26.53</v>
       </c>
       <c r="C6" t="n">
-        <v>1.66</v>
+        <v>0.8</v>
       </c>
       <c r="D6" t="n">
-        <v>17.963</v>
+        <v>11.199</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.675</v>
+        <v>21.6</v>
       </c>
       <c r="C7" t="n">
-        <v>1.415</v>
+        <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>10.12</v>
+        <v>22.53</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -3997,17 +3997,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.905</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>0.54</v>
+        <v>1.685</v>
       </c>
       <c r="D8" t="n">
-        <v>21.782</v>
+        <v>18.634</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -4020,13 +4020,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.78333333333333</v>
+        <v>17.47333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>1.193333333333333</v>
+        <v>1.43</v>
       </c>
       <c r="D9" t="n">
-        <v>22.294</v>
+        <v>21.017</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -4035,17 +4035,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21.16</v>
+        <v>13.74</v>
       </c>
       <c r="C10" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="D10" t="n">
-        <v>5.867</v>
+        <v>7.265</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19.01</v>
+        <v>11.44</v>
       </c>
       <c r="C11" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="D11" t="n">
-        <v>37.62</v>
+        <v>36.046</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4077,13 +4077,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.03</v>
+        <v>10.52</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9849999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="D12" t="n">
-        <v>78.65600000000001</v>
+        <v>79.70099999999999</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -4092,17 +4092,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12.64</v>
+        <v>9.65</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="D13" t="n">
-        <v>7.06</v>
+        <v>2.059</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,17 +4111,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.8</v>
+        <v>9.02</v>
       </c>
       <c r="C14" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="D14" t="n">
-        <v>9.513</v>
+        <v>5.523</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -4130,17 +4130,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.99</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="D15" t="n">
-        <v>24.042</v>
+        <v>9.257999999999999</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,17 +4149,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10.89</v>
+        <v>5.85</v>
       </c>
       <c r="C16" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1.125</v>
+        <v>22.661</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,36 +4168,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10.58</v>
+        <v>4.705</v>
       </c>
       <c r="C17" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>2.055</v>
+        <v>27.151</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.1</v>
+        <v>3.94</v>
       </c>
       <c r="C18" t="n">
-        <v>0.76</v>
+        <v>1.25</v>
       </c>
       <c r="D18" t="n">
-        <v>17.03</v>
+        <v>1.656</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4206,36 +4206,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.795</v>
+        <v>3.72</v>
       </c>
       <c r="C19" t="n">
-        <v>0.925</v>
+        <v>0.66</v>
       </c>
       <c r="D19" t="n">
-        <v>26.444</v>
+        <v>6.471</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="D20" t="n">
-        <v>6.661</v>
+        <v>0.595</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.26</v>
+        <v>2.48</v>
       </c>
       <c r="C21" t="n">
-        <v>1.34</v>
+        <v>0.93</v>
       </c>
       <c r="D21" t="n">
-        <v>1.672</v>
+        <v>1.569</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4263,17 +4263,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.85</v>
+        <v>2.01</v>
       </c>
       <c r="C22" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="D22" t="n">
-        <v>3.217</v>
+        <v>16.325</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.485</v>
+        <v>1.335</v>
       </c>
       <c r="C23" t="n">
-        <v>1.08</v>
+        <v>0.915</v>
       </c>
       <c r="D23" t="n">
-        <v>1.286</v>
+        <v>1.283</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -4301,17 +4301,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.04</v>
+        <v>0.3</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="D24" t="n">
-        <v>1.597</v>
+        <v>1.012</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -4320,39 +4320,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.43</v>
+        <v>0.05999999999999991</v>
       </c>
       <c r="C25" t="n">
-        <v>0.62</v>
+        <v>0.5666666666666668</v>
       </c>
       <c r="D25" t="n">
-        <v>0.597</v>
+        <v>4.837</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1233333333333333</v>
+        <v>-0.6159999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.876</v>
       </c>
       <c r="D26" t="n">
-        <v>3.083</v>
+        <v>8.09</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.53</v>
+        <v>-0.79</v>
       </c>
       <c r="C27" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="D27" t="n">
-        <v>0.539</v>
+        <v>0.545</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,77 +4377,77 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.8620000000000001</v>
+        <v>-1.65</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8699999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="D28" t="n">
-        <v>8.045</v>
+        <v>3.064</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.55</v>
+        <v>-1.975</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5933333333333334</v>
+        <v>0.87</v>
       </c>
       <c r="D29" t="n">
-        <v>5.075</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.085</v>
+        <v>-2.803333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="D30" t="n">
-        <v>22.254</v>
+        <v>3.021</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.145</v>
+        <v>-5.2025</v>
       </c>
       <c r="C31" t="n">
-        <v>0.86</v>
+        <v>0.9875</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9850000000000001</v>
+        <v>22.24</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-9.710000000000001</v>
+        <v>-9.32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="D32" t="n">
-        <v>0.098</v>
+        <v>0.094</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2100</v>
+        <v>2090</v>
       </c>
       <c r="E2" t="n">
-        <v>0.24</v>
+        <v>-0.48</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>3.72</v>
       </c>
       <c r="G2" t="n">
-        <v>59.32</v>
+        <v>64.22</v>
       </c>
       <c r="H2" t="n">
-        <v>15.8684</v>
+        <v>13.6767</v>
       </c>
       <c r="I2" t="n">
-        <v>57.2</v>
+        <v>53</v>
       </c>
       <c r="J2" t="n">
-        <v>61</v>
+        <v>57.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>-20.4</v>
+        <v>-53</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,38 +4624,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5165</v>
+        <v>4920</v>
       </c>
       <c r="E3" t="n">
-        <v>4.34</v>
+        <v>-4.74</v>
       </c>
       <c r="F3" t="n">
-        <v>19.01</v>
+        <v>11.44</v>
       </c>
       <c r="G3" t="n">
-        <v>66.48</v>
+        <v>59.09</v>
       </c>
       <c r="H3" t="n">
-        <v>233.5474</v>
+        <v>216.2743</v>
       </c>
       <c r="I3" t="n">
-        <v>83.09999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="J3" t="n">
-        <v>86</v>
+        <v>57.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9</v>
+        <v>35.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>❌ EXIT</t>
         </is>
       </c>
     </row>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>88.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1.12</v>
+        <v>-1.33</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.03</v>
+        <v>-14.6</v>
       </c>
       <c r="G4" t="n">
-        <v>48.47</v>
+        <v>57.22</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.707</v>
+        <v>-5.14</v>
       </c>
       <c r="I4" t="n">
-        <v>47.6</v>
+        <v>45.3</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>80.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.02</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>-17.9</v>
+        <v>-36.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,38 +4728,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.63</v>
+        <v>-2.74</v>
       </c>
       <c r="F5" t="n">
-        <v>21.16</v>
+        <v>9.02</v>
       </c>
       <c r="G5" t="n">
-        <v>50.94</v>
+        <v>45.7</v>
       </c>
       <c r="H5" t="n">
-        <v>17.1148</v>
+        <v>15.4057</v>
       </c>
       <c r="I5" t="n">
-        <v>44.9</v>
+        <v>25.1</v>
       </c>
       <c r="J5" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7.45</v>
+        <v>7.22</v>
       </c>
       <c r="L5" t="n">
-        <v>-40.7</v>
+        <v>-70.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⚠️ TAKE PROFIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>606</v>
+        <v>567</v>
       </c>
       <c r="E6" t="n">
-        <v>4.48</v>
+        <v>-6.44</v>
       </c>
       <c r="F6" t="n">
-        <v>15.43</v>
+        <v>7.39</v>
       </c>
       <c r="G6" t="n">
-        <v>71.16</v>
+        <v>56.84</v>
       </c>
       <c r="H6" t="n">
-        <v>31.6583</v>
+        <v>30.5205</v>
       </c>
       <c r="I6" t="n">
-        <v>114.1</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>100</v>
+        <v>57.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.93</v>
+        <v>5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>-69.90000000000001</v>
+        <v>115.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>❌ EXIT</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>0.79</v>
       </c>
       <c r="F7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>60.71</v>
+        <v>62.71</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2638</v>
+        <v>0.2697</v>
       </c>
       <c r="I7" t="n">
-        <v>73.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="J7" t="n">
-        <v>78.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
-        <v>52.3</v>
+        <v>194.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>256</v>
+        <v>140</v>
       </c>
       <c r="E2" t="n">
-        <v>0.79</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>294</v>
+        <v>428</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8.364000000000001</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>127.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.16</v>
+        <v>9.91</v>
       </c>
       <c r="F3" t="n">
-        <v>244</v>
+        <v>410</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.47</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="4">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.44</v>
+        <v>-1.41</v>
       </c>
       <c r="F4" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,101 +572,101 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.228</v>
+        <v>4.488</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>279</v>
+        <v>4190</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.63</v>
+        <v>0.24</v>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.541</v>
+        <v>9.763</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>310.5</v>
+        <v>365</v>
       </c>
       <c r="E6" t="n">
-        <v>4.37</v>
+        <v>-1.35</v>
       </c>
       <c r="F6" t="n">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.39</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8</v>
+        <v>4.19</v>
       </c>
       <c r="F7" t="n">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,33 +674,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.523</v>
+        <v>4.808</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4180</v>
+        <v>287</v>
       </c>
       <c r="E8" t="n">
-        <v>5.82</v>
+        <v>2.87</v>
       </c>
       <c r="F8" t="n">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,67 +708,67 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9.720000000000001</v>
+        <v>0.553</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>147.5</v>
+        <v>1215</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.28</v>
+        <v>0.83</v>
       </c>
       <c r="F9" t="n">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>28.103</v>
+        <v>14.631</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>127.5</v>
+        <v>113</v>
       </c>
       <c r="E10" t="n">
-        <v>2.82</v>
+        <v>0.89</v>
       </c>
       <c r="F10" t="n">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,101 +776,101 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.722</v>
+        <v>2.169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4920</v>
+        <v>232.5</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.74</v>
+        <v>-1.69</v>
       </c>
       <c r="F11" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>36.046</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2050</v>
+        <v>4835</v>
       </c>
       <c r="E12" t="n">
-        <v>2.24</v>
+        <v>-1.73</v>
       </c>
       <c r="F12" t="n">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>22.433</v>
+        <v>33.331</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8375</v>
+        <v>252</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.62</v>
+        <v>-1.56</v>
       </c>
       <c r="F13" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,67 +878,67 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12.81</v>
+        <v>8.252000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.12</v>
+        <v>0.33</v>
       </c>
       <c r="F14" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.843</v>
+        <v>4.609</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1205</v>
+        <v>8460</v>
       </c>
       <c r="E15" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="F15" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>14.221</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>299</v>
+        <v>307.5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.34</v>
+        <v>-0.97</v>
       </c>
       <c r="F16" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,271 +980,271 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.718</v>
+        <v>4.457</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>154.5</v>
+        <v>190</v>
       </c>
       <c r="E17" t="n">
-        <v>1.64</v>
+        <v>-0.52</v>
       </c>
       <c r="F17" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.341</v>
+        <v>3.545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68.40000000000001</v>
+        <v>299.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.48</v>
+        <v>0.5</v>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.038</v>
+        <v>7.263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>49.3</v>
+        <v>514</v>
       </c>
       <c r="E19" t="n">
-        <v>1.54</v>
+        <v>-2.1</v>
       </c>
       <c r="F19" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.097</v>
+        <v>21.729</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2585</v>
+        <v>118</v>
       </c>
       <c r="E20" t="n">
-        <v>0.39</v>
+        <v>-1.26</v>
       </c>
       <c r="F20" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>51.598</v>
+        <v>2.994</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28.2</v>
+        <v>1990</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.53</v>
+        <v>-2.93</v>
       </c>
       <c r="F21" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.094</v>
+        <v>21.956</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>298</v>
+        <v>26.55</v>
       </c>
       <c r="E22" t="n">
-        <v>1.36</v>
+        <v>2.31</v>
       </c>
       <c r="F22" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7.265</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41.55</v>
+        <v>155.5</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.84</v>
+        <v>0.65</v>
       </c>
       <c r="F23" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.6860000000000001</v>
+        <v>2.284</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>58.6</v>
+        <v>148.5</v>
       </c>
       <c r="E24" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="F24" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,33 +1252,33 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.771</v>
+        <v>26.892</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>112</v>
+        <v>588</v>
       </c>
       <c r="E25" t="n">
-        <v>0.45</v>
+        <v>-0.68</v>
       </c>
       <c r="F25" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1286,67 +1286,67 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.168</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.15</v>
+        <v>-2.29</v>
       </c>
       <c r="F26" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.656</v>
+        <v>8.507999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>215</v>
+        <v>2585</v>
       </c>
       <c r="E27" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,271 +1354,271 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.413</v>
+        <v>50.535</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>210.5</v>
+        <v>58.1</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.55</v>
+        <v>-0.85</v>
       </c>
       <c r="F28" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.971</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>267</v>
+        <v>18.95</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.93</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.637</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1470</v>
+        <v>335</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.34</v>
+        <v>0.45</v>
       </c>
       <c r="F30" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.595</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>333.5</v>
+        <v>179.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="F31" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.554</v>
+        <v>16.023</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>592</v>
+        <v>49.8</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.74</v>
+        <v>1.01</v>
       </c>
       <c r="F32" t="n">
         <v>71</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>16.319</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.49</v>
       </c>
       <c r="F33" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>22.661</v>
+        <v>1.539</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>25.95</v>
+        <v>68.7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.19</v>
+        <v>0.44</v>
       </c>
       <c r="F34" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.446</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3115</v>
+        <v>209</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.27</v>
+        <v>-0.71</v>
       </c>
       <c r="F35" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.592</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>189.5</v>
+        <v>128.5</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="F36" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>8.551</v>
+        <v>6.886</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>744</v>
+        <v>28.9</v>
       </c>
       <c r="E37" t="n">
-        <v>0.27</v>
+        <v>2.48</v>
       </c>
       <c r="F37" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>11.199</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18.95</v>
+        <v>20.35</v>
       </c>
       <c r="E38" t="n">
-        <v>0.26</v>
+        <v>1.24</v>
       </c>
       <c r="F38" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,101 +1728,101 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.545</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>88.8</v>
+        <v>3015</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.33</v>
+        <v>-3.21</v>
       </c>
       <c r="F39" t="n">
         <v>63</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.312</v>
+        <v>4.203</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>177.5</v>
+        <v>185</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.93</v>
+        <v>-2.37</v>
       </c>
       <c r="F40" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>16.325</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>236.5</v>
+        <v>265</v>
       </c>
       <c r="E41" t="n">
-        <v>0.85</v>
+        <v>-0.75</v>
       </c>
       <c r="F41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,30 +1830,30 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.703</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>755</v>
+        <v>732</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="F42" t="n">
         <v>58</v>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2.059</v>
+        <v>10.368</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>20.1</v>
+        <v>2060</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>-1.44</v>
       </c>
       <c r="F43" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,237 +1898,237 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.299</v>
+        <v>6.284</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>537</v>
+        <v>741</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.1</v>
+        <v>-1.85</v>
       </c>
       <c r="F44" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.569</v>
+        <v>1.972</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>74.3</v>
+        <v>41.95</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.98</v>
+        <v>0.96</v>
       </c>
       <c r="F45" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>9.257999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>59.2</v>
+        <v>1455</v>
       </c>
       <c r="E46" t="n">
-        <v>0.85</v>
+        <v>-1.02</v>
       </c>
       <c r="F46" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.574</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>119.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.65</v>
+        <v>1.46</v>
       </c>
       <c r="F47" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3.064</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>67</v>
+        <v>111.5</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.012</v>
+        <v>1.542</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2090</v>
+        <v>59.1</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.48</v>
+        <v>-0.17</v>
       </c>
       <c r="F49" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>6.471</v>
+        <v>1.554</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>345</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>2.68</v>
+        <v>0.6</v>
       </c>
       <c r="F50" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,33 +2136,33 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.394</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>111.5</v>
+        <v>301.53</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9</v>
+        <v>-2.74</v>
       </c>
       <c r="F51" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,41 +2170,41 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.56</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>284</v>
+        <v>347</v>
       </c>
       <c r="E52" t="n">
-        <v>-2.74</v>
+        <v>0.58</v>
       </c>
       <c r="F52" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5.523</v>
+        <v>1.394</v>
       </c>
     </row>
   </sheetData>
@@ -2280,13 +2280,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>44.15</v>
+        <v>42.54</v>
       </c>
       <c r="F2" t="n">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="G2" t="n">
-        <v>12.81</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="3">
@@ -2311,13 +2311,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>41.51</v>
+        <v>40.74</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="G3" t="n">
-        <v>6.722</v>
+        <v>6.886</v>
       </c>
     </row>
     <row r="4">
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34.08</v>
+        <v>35.02</v>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="G4" t="n">
         <v>1.394</v>
@@ -2373,277 +2373,277 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>31.7</v>
+        <v>30.52</v>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="G5" t="n">
-        <v>16.319</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30.61</v>
+        <v>25.13</v>
       </c>
       <c r="F6" t="n">
-        <v>0.85</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.592</v>
+        <v>14.631</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27.33</v>
+        <v>24.44</v>
       </c>
       <c r="F7" t="n">
-        <v>1.19</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.523</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26.53</v>
+        <v>22.07</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>1.71</v>
       </c>
       <c r="G8" t="n">
-        <v>11.199</v>
+        <v>4.808</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22.83</v>
+        <v>21.79</v>
       </c>
       <c r="F9" t="n">
-        <v>1.51</v>
+        <v>1.12</v>
       </c>
       <c r="G9" t="n">
-        <v>14.221</v>
+        <v>3.545</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.27</v>
+        <v>17.87</v>
       </c>
       <c r="F10" t="n">
-        <v>1.08</v>
+        <v>0.76</v>
       </c>
       <c r="G10" t="n">
-        <v>0.971</v>
+        <v>10.368</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.17</v>
+        <v>17.32</v>
       </c>
       <c r="F11" t="n">
-        <v>1.86</v>
+        <v>0.67</v>
       </c>
       <c r="G11" t="n">
-        <v>4.413</v>
+        <v>4.203</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.74</v>
+        <v>16.76</v>
       </c>
       <c r="F12" t="n">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="G12" t="n">
-        <v>7.265</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13.46</v>
+        <v>13.21</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99</v>
+        <v>1.51</v>
       </c>
       <c r="G13" t="n">
-        <v>28.103</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2652,509 +2652,509 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.33</v>
+        <v>11.8</v>
       </c>
       <c r="F14" t="n">
-        <v>2.42</v>
+        <v>0.97</v>
       </c>
       <c r="G14" t="n">
-        <v>0.47</v>
+        <v>4.488</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.33</v>
+        <v>9.82</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="G15" t="n">
-        <v>22.433</v>
+        <v>4.457</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.3</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.44</v>
+        <v>0.76</v>
       </c>
       <c r="G16" t="n">
-        <v>4.39</v>
+        <v>7.263</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.44</v>
+        <v>9.02</v>
       </c>
       <c r="F17" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="G17" t="n">
-        <v>36.046</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.65</v>
+        <v>7.57</v>
       </c>
       <c r="F18" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="G18" t="n">
-        <v>2.059</v>
+        <v>21.956</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.02</v>
+        <v>5.39</v>
       </c>
       <c r="F19" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="G19" t="n">
-        <v>5.523</v>
+        <v>50.535</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.470000000000001</v>
+        <v>5.26</v>
       </c>
       <c r="F20" t="n">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="G20" t="n">
-        <v>9.257999999999999</v>
+        <v>1.972</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7.58</v>
+        <v>4.01</v>
       </c>
       <c r="F21" t="n">
-        <v>1.07</v>
+        <v>0.92</v>
       </c>
       <c r="G21" t="n">
-        <v>51.598</v>
+        <v>2.284</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.39</v>
+        <v>3.85</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="G22" t="n">
-        <v>4.228</v>
+        <v>26.892</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5.85</v>
+        <v>3.71</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="G23" t="n">
-        <v>22.661</v>
+        <v>9.763</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.94</v>
+        <v>1.93</v>
       </c>
       <c r="F24" t="n">
-        <v>1.25</v>
+        <v>0.77</v>
       </c>
       <c r="G24" t="n">
-        <v>1.656</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.72</v>
+        <v>1.72</v>
       </c>
       <c r="F25" t="n">
-        <v>0.66</v>
+        <v>0.46</v>
       </c>
       <c r="G25" t="n">
-        <v>6.471</v>
+        <v>1.554</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="F26" t="n">
-        <v>0.65</v>
+        <v>0.88</v>
       </c>
       <c r="G26" t="n">
-        <v>0.595</v>
+        <v>33.331</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="F27" t="n">
-        <v>0.88</v>
+        <v>0.58</v>
       </c>
       <c r="G27" t="n">
-        <v>2.341</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.48</v>
+        <v>0.33</v>
       </c>
       <c r="F28" t="n">
-        <v>0.93</v>
+        <v>1.02</v>
       </c>
       <c r="G28" t="n">
-        <v>1.569</v>
+        <v>4.609</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.01</v>
+        <v>0.3</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="G29" t="n">
-        <v>16.325</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.72</v>
+        <v>0.19</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="G30" t="n">
-        <v>1.574</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="31">
@@ -3179,463 +3179,463 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.5</v>
+        <v>-0.21</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="G31" t="n">
-        <v>1.703</v>
+        <v>1.704</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.3</v>
+        <v>-0.26</v>
       </c>
       <c r="F32" t="n">
-        <v>1.11</v>
+        <v>0.87</v>
       </c>
       <c r="G32" t="n">
-        <v>1.012</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="F33" t="n">
-        <v>1.36</v>
+        <v>0.78</v>
       </c>
       <c r="G33" t="n">
-        <v>8.364000000000001</v>
+        <v>16.023</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="G34" t="n">
-        <v>2.038</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.5</v>
+        <v>-0.41</v>
       </c>
       <c r="F35" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="G35" t="n">
-        <v>1.097</v>
+        <v>8.507999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.79</v>
+        <v>-0.49</v>
       </c>
       <c r="F36" t="n">
-        <v>1.35</v>
+        <v>0.7</v>
       </c>
       <c r="G36" t="n">
-        <v>0.545</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.95</v>
+        <v>-0.58</v>
       </c>
       <c r="F37" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>9.720000000000001</v>
+        <v>21.729</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.65</v>
+        <v>-0.8</v>
       </c>
       <c r="F38" t="n">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="G38" t="n">
-        <v>3.064</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.71</v>
+        <v>-0.86</v>
       </c>
       <c r="F39" t="n">
-        <v>0.79</v>
+        <v>1.07</v>
       </c>
       <c r="G39" t="n">
-        <v>0.299</v>
+        <v>0.553</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.93</v>
+        <v>-1.31</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G40" t="n">
-        <v>0.541</v>
+        <v>2.169</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.24</v>
+        <v>-1.56</v>
       </c>
       <c r="F41" t="n">
-        <v>0.95</v>
+        <v>1.41</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6860000000000001</v>
+        <v>8.252000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.61</v>
+        <v>-1.67</v>
       </c>
       <c r="F42" t="n">
-        <v>0.89</v>
+        <v>0.6</v>
       </c>
       <c r="G42" t="n">
-        <v>2.168</v>
+        <v>6.284</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.63</v>
+        <v>-2.04</v>
       </c>
       <c r="F43" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="G43" t="n">
-        <v>0.446</v>
+        <v>1.539</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-2.92</v>
+        <v>-2.62</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G44" t="n">
-        <v>4.718</v>
+        <v>1.542</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.04</v>
+        <v>-3.6</v>
       </c>
       <c r="F45" t="n">
-        <v>0.39</v>
+        <v>0.85</v>
       </c>
       <c r="G45" t="n">
-        <v>1.56</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3644,60 +3644,60 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3.22</v>
+        <v>-4.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="G46" t="n">
-        <v>1.843</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-3.26</v>
+        <v>-5.22</v>
       </c>
       <c r="F47" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="G47" t="n">
-        <v>0.637</v>
+        <v>2.994</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3706,75 +3706,75 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-3.33</v>
+        <v>-6.09</v>
       </c>
       <c r="F48" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="G48" t="n">
-        <v>4.554</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-4.29</v>
+        <v>-6.17</v>
       </c>
       <c r="F49" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="G49" t="n">
-        <v>8.551</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-9.32</v>
+        <v>-7.19</v>
       </c>
       <c r="F50" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G50" t="n">
-        <v>0.094</v>
+        <v>1.833</v>
       </c>
     </row>
     <row r="51">
@@ -3799,13 +3799,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-13.19</v>
+        <v>-12.1</v>
       </c>
       <c r="F51" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="G51" t="n">
-        <v>0.771</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="52">
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-14.6</v>
+        <v>-13.76</v>
       </c>
       <c r="F52" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="G52" t="n">
-        <v>0.312</v>
+        <v>0.317</v>
       </c>
     </row>
   </sheetData>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34.08</v>
+        <v>35.02</v>
       </c>
       <c r="C2" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="D2" t="n">
         <v>1.394</v>
@@ -3902,55 +3902,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.61</v>
+        <v>25.28</v>
       </c>
       <c r="C3" t="n">
-        <v>0.85</v>
+        <v>1.415</v>
       </c>
       <c r="D3" t="n">
-        <v>4.592</v>
+        <v>11.343</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.33</v>
+        <v>23.6</v>
       </c>
       <c r="C4" t="n">
-        <v>1.19</v>
+        <v>1.555</v>
       </c>
       <c r="D4" t="n">
-        <v>3.523</v>
+        <v>19.439</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.905</v>
+        <v>23.125</v>
       </c>
       <c r="C5" t="n">
-        <v>1.52</v>
+        <v>0.8500000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>11.112</v>
+        <v>22.453</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -3959,93 +3959,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.53</v>
+        <v>22.25333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>11.199</v>
+        <v>21.419</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.6</v>
+        <v>21.79</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7</v>
+        <v>1.12</v>
       </c>
       <c r="D7" t="n">
-        <v>22.53</v>
+        <v>3.545</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>17.87</v>
       </c>
       <c r="C8" t="n">
-        <v>1.685</v>
+        <v>0.76</v>
       </c>
       <c r="D8" t="n">
-        <v>18.634</v>
+        <v>10.368</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.47333333333333</v>
+        <v>17.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.43</v>
+        <v>0.67</v>
       </c>
       <c r="D9" t="n">
-        <v>21.017</v>
+        <v>4.203</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.74</v>
+        <v>13.21</v>
       </c>
       <c r="C10" t="n">
-        <v>0.76</v>
+        <v>1.51</v>
       </c>
       <c r="D10" t="n">
-        <v>7.265</v>
+        <v>2.15</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +4054,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.44</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="D11" t="n">
-        <v>36.046</v>
+        <v>7.263</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,20 +4073,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.52</v>
+        <v>9.02</v>
       </c>
       <c r="C12" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>79.70099999999999</v>
+        <v>5.508</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -4096,13 +4096,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9.65</v>
+        <v>5.26</v>
       </c>
       <c r="C13" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="D13" t="n">
-        <v>2.059</v>
+        <v>1.972</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -4111,55 +4111,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.02</v>
+        <v>4.62</v>
       </c>
       <c r="C14" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="D14" t="n">
-        <v>5.523</v>
+        <v>77.42699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.470000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="C15" t="n">
         <v>0.96</v>
       </c>
       <c r="D15" t="n">
-        <v>9.257999999999999</v>
+        <v>26.565</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.85</v>
+        <v>1.58</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="D16" t="n">
-        <v>22.661</v>
+        <v>33.331</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,17 +4168,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.705</v>
+        <v>1.500000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="D17" t="n">
-        <v>27.151</v>
+        <v>1.297</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -4187,17 +4187,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.94</v>
+        <v>1.04</v>
       </c>
       <c r="C18" t="n">
-        <v>1.25</v>
+        <v>0.58</v>
       </c>
       <c r="D18" t="n">
-        <v>1.656</v>
+        <v>0.578</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -4206,36 +4206,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.72</v>
+        <v>0.8039999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.66</v>
+        <v>0.8720000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>6.471</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="C20" t="n">
-        <v>0.65</v>
+        <v>0.95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.595</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.48</v>
+        <v>-0.26</v>
       </c>
       <c r="C21" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="D21" t="n">
-        <v>1.569</v>
+        <v>0.551</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4267,13 +4267,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.01</v>
+        <v>-0.28</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="D22" t="n">
-        <v>16.325</v>
+        <v>16.023</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,36 +4282,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.335</v>
+        <v>-0.3700000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.915</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D23" t="n">
-        <v>1.283</v>
+        <v>4.8</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3</v>
+        <v>-0.41</v>
       </c>
       <c r="C24" t="n">
-        <v>1.11</v>
+        <v>0.95</v>
       </c>
       <c r="D24" t="n">
-        <v>1.012</v>
+        <v>8.507999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -4320,55 +4320,55 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.05999999999999991</v>
+        <v>-0.425</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5666666666666668</v>
+        <v>0.705</v>
       </c>
       <c r="D25" t="n">
-        <v>4.837</v>
+        <v>0.978</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6159999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="C26" t="n">
-        <v>0.876</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>8.09</v>
+        <v>21.729</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.79</v>
+        <v>-1.67</v>
       </c>
       <c r="C27" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.545</v>
+        <v>6.284</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -4377,17 +4377,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.65</v>
+        <v>-2.04</v>
       </c>
       <c r="C28" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="D28" t="n">
-        <v>3.064</v>
+        <v>1.539</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -4396,39 +4396,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.975</v>
+        <v>-4.183333333333334</v>
       </c>
       <c r="C29" t="n">
-        <v>0.87</v>
+        <v>0.9133333333333334</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9850000000000001</v>
+        <v>2.992</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.803333333333333</v>
+        <v>-5.22</v>
       </c>
       <c r="C30" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="D30" t="n">
-        <v>3.021</v>
+        <v>2.994</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-5.2025</v>
+        <v>-5.8375</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9875</v>
+        <v>1.02</v>
       </c>
       <c r="D31" t="n">
-        <v>22.24</v>
+        <v>21.472</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
@@ -4457,13 +4457,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-9.32</v>
+        <v>-6.17</v>
       </c>
       <c r="C32" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="D32" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4572,34 +4572,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2090</v>
+        <v>2060</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.48</v>
+        <v>-1.44</v>
       </c>
       <c r="F2" t="n">
-        <v>3.72</v>
+        <v>-1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>64.22</v>
+        <v>62.5</v>
       </c>
       <c r="H2" t="n">
-        <v>13.6767</v>
+        <v>8.4039</v>
       </c>
       <c r="I2" t="n">
-        <v>53</v>
+        <v>44.3</v>
       </c>
       <c r="J2" t="n">
-        <v>57.6</v>
+        <v>36.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="L2" t="n">
-        <v>-53</v>
+        <v>-42.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,38 +4624,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4920</v>
+        <v>4835</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.74</v>
+        <v>-1.73</v>
       </c>
       <c r="F3" t="n">
-        <v>11.44</v>
+        <v>1.58</v>
       </c>
       <c r="G3" t="n">
-        <v>59.09</v>
+        <v>60.47</v>
       </c>
       <c r="H3" t="n">
-        <v>216.2743</v>
+        <v>190.3007</v>
       </c>
       <c r="I3" t="n">
-        <v>58.6</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>57.3</v>
+        <v>42.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
       <c r="L3" t="n">
-        <v>35.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>❌ EXIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4676,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.33</v>
+        <v>1.46</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.6</v>
+        <v>-13.76</v>
       </c>
       <c r="G4" t="n">
-        <v>57.22</v>
+        <v>59.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.14</v>
+        <v>-4.3216</v>
       </c>
       <c r="I4" t="n">
-        <v>45.3</v>
+        <v>55.5</v>
       </c>
       <c r="J4" t="n">
-        <v>80.3</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="L4" t="n">
-        <v>-36.9</v>
+        <v>-57.8</v>
       </c>
       <c r="M4" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>284</v>
+        <v>301.53</v>
       </c>
       <c r="E5" t="n">
         <v>-2.74</v>
@@ -4740,7 +4740,7 @@
         <v>45.7</v>
       </c>
       <c r="H5" t="n">
-        <v>15.4057</v>
+        <v>15.8573</v>
       </c>
       <c r="I5" t="n">
         <v>25.1</v>
@@ -4752,7 +4752,7 @@
         <v>7.22</v>
       </c>
       <c r="L5" t="n">
-        <v>-70.8</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>0.85</v>
@@ -4780,38 +4780,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.44</v>
+        <v>-1.41</v>
       </c>
       <c r="F6" t="n">
-        <v>7.39</v>
+        <v>11.8</v>
       </c>
       <c r="G6" t="n">
-        <v>56.84</v>
+        <v>58.59</v>
       </c>
       <c r="H6" t="n">
-        <v>30.5205</v>
+        <v>27.5103</v>
       </c>
       <c r="I6" t="n">
-        <v>72.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="J6" t="n">
-        <v>57.1</v>
+        <v>48.4</v>
       </c>
       <c r="K6" t="n">
-        <v>5.4</v>
+        <v>5.46</v>
       </c>
       <c r="L6" t="n">
-        <v>115.4</v>
+        <v>91.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>❌ EXIT</t>
+          <t>👀 WATCH</t>
         </is>
       </c>
     </row>
@@ -4832,34 +4832,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E7" t="n">
-        <v>0.79</v>
+        <v>-1.56</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="G7" t="n">
-        <v>62.71</v>
+        <v>58.73</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2697</v>
+        <v>0.0207</v>
       </c>
       <c r="I7" t="n">
-        <v>91.8</v>
+        <v>57.5</v>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="L7" t="n">
-        <v>194.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>140</v>
+        <v>81.3</v>
       </c>
       <c r="E2" t="n">
-        <v>9.800000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="F2" t="n">
-        <v>428</v>
+        <v>623</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.641</v>
+        <v>3.196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75.40000000000001</v>
+        <v>154</v>
       </c>
       <c r="E3" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>410</v>
+        <v>510</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.15</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>559</v>
+        <v>304.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.41</v>
+        <v>1.67</v>
       </c>
       <c r="F4" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4.488</v>
+        <v>7.932</v>
       </c>
     </row>
     <row r="5">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4190</v>
+        <v>4345</v>
       </c>
       <c r="E5" t="n">
-        <v>0.24</v>
+        <v>3.7</v>
       </c>
       <c r="F5" t="n">
-        <v>152</v>
+        <v>198</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,67 +606,67 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9.763</v>
+        <v>10.793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>365</v>
+        <v>1130</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.35</v>
+        <v>-7</v>
       </c>
       <c r="F6" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.833</v>
+        <v>14.227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>224</v>
+        <v>532</v>
       </c>
       <c r="E7" t="n">
-        <v>4.19</v>
+        <v>3.5</v>
       </c>
       <c r="F7" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,135 +674,135 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.808</v>
+        <v>22.225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>116</v>
       </c>
       <c r="E8" t="n">
-        <v>2.87</v>
+        <v>-1.69</v>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.553</v>
+        <v>2.817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1215</v>
+        <v>325.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.83</v>
+        <v>-2.84</v>
       </c>
       <c r="F9" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>14.631</v>
+        <v>4.113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>113</v>
+        <v>4690</v>
       </c>
       <c r="E10" t="n">
-        <v>0.89</v>
+        <v>-3</v>
       </c>
       <c r="F10" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.169</v>
+        <v>32.551</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>232.5</v>
+        <v>249</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.69</v>
+        <v>-1.19</v>
       </c>
       <c r="F11" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,67 +810,67 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.704</v>
+        <v>8.157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4835</v>
+        <v>2550</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.73</v>
+        <v>-1.35</v>
       </c>
       <c r="F12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>33.331</v>
+        <v>49.296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>252</v>
+        <v>188.5</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.56</v>
+        <v>1.89</v>
       </c>
       <c r="F13" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,33 +878,33 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8.252000000000001</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>300</v>
+        <v>744</v>
       </c>
       <c r="E14" t="n">
-        <v>0.33</v>
+        <v>1.64</v>
       </c>
       <c r="F14" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.609</v>
+        <v>10.625</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8460</v>
+        <v>308</v>
       </c>
       <c r="E15" t="n">
-        <v>1.01</v>
+        <v>0.16</v>
       </c>
       <c r="F15" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,169 +946,169 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12.69</v>
+        <v>4.485</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>307.5</v>
+        <v>49.3</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.97</v>
+        <v>-1</v>
       </c>
       <c r="F16" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4.457</v>
+        <v>1.085</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>190</v>
+        <v>269.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.52</v>
+        <v>1.7</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3.545</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>299.5</v>
+        <v>1490</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5</v>
+        <v>2.41</v>
       </c>
       <c r="F18" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7.263</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>514</v>
+        <v>110</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1</v>
+        <v>-2.65</v>
       </c>
       <c r="F19" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>21.729</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>118</v>
+        <v>72.2</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.26</v>
+        <v>-0.55</v>
       </c>
       <c r="F20" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1116,33 +1116,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.994</v>
+        <v>8.247</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1990</v>
+        <v>216.5</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.93</v>
+        <v>-3.35</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,33 +1150,33 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>21.956</v>
+        <v>4.761</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26.55</v>
+        <v>57.5</v>
       </c>
       <c r="E22" t="n">
-        <v>2.31</v>
+        <v>-1.03</v>
       </c>
       <c r="F22" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.455</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="23">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>155.5</v>
+        <v>153</v>
       </c>
       <c r="E23" t="n">
-        <v>0.65</v>
+        <v>-1.61</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,33 +1218,33 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.284</v>
+        <v>2.264</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>148.5</v>
+        <v>362.5</v>
       </c>
       <c r="E24" t="n">
-        <v>0.68</v>
+        <v>-0.68</v>
       </c>
       <c r="F24" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,101 +1252,101 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>26.892</v>
+        <v>1.658</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>588</v>
+        <v>232.5</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>16.29</v>
+        <v>1.709</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>72.59999999999999</v>
+        <v>18.95</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.29</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8.507999999999999</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2585</v>
+        <v>297.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="F27" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,67 +1354,67 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>50.535</v>
+        <v>4.497</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>58.1</v>
+        <v>177</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.85</v>
+        <v>-1.39</v>
       </c>
       <c r="F28" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.72</v>
+        <v>14.486</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18.95</v>
+        <v>8360</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="F29" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,33 +1422,33 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.551</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>335</v>
+        <v>67.3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.45</v>
+        <v>-2.04</v>
       </c>
       <c r="F30" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,101 +1456,101 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.51</v>
+        <v>1.961</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>179.5</v>
+        <v>531</v>
       </c>
       <c r="E31" t="n">
-        <v>1.13</v>
+        <v>0.38</v>
       </c>
       <c r="F31" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>16.023</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>49.8</v>
+        <v>558</v>
       </c>
       <c r="E32" t="n">
-        <v>1.01</v>
+        <v>-0.18</v>
       </c>
       <c r="F32" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.097</v>
+        <v>4.518</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>529</v>
+        <v>2060</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.49</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1558,33 +1558,33 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.539</v>
+        <v>6.226</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>68.7</v>
+        <v>202</v>
       </c>
       <c r="E34" t="n">
-        <v>0.44</v>
+        <v>-3.35</v>
       </c>
       <c r="F34" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1592,33 +1592,33 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.016</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>209</v>
+        <v>59.7</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.71</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.98</v>
+        <v>1.577</v>
       </c>
     </row>
     <row r="36">
@@ -1646,13 +1646,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>128.5</v>
+        <v>128</v>
       </c>
       <c r="E36" t="n">
-        <v>0.78</v>
+        <v>-0.39</v>
       </c>
       <c r="F36" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,33 +1660,33 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6.886</v>
+        <v>7.006</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28.9</v>
+        <v>41.4</v>
       </c>
       <c r="E37" t="n">
-        <v>2.48</v>
+        <v>-1.31</v>
       </c>
       <c r="F37" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1694,135 +1694,135 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.093</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20.35</v>
+        <v>2915</v>
       </c>
       <c r="E38" t="n">
-        <v>1.24</v>
+        <v>-3.32</v>
       </c>
       <c r="F38" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.298</v>
+        <v>3.873</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3015</v>
+        <v>26.45</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.21</v>
+        <v>-0.38</v>
       </c>
       <c r="F39" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4.203</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>185</v>
+        <v>581</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.37</v>
+        <v>-1.19</v>
       </c>
       <c r="F40" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7.99</v>
+        <v>16.065</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>265</v>
+        <v>111.5</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1830,33 +1830,33 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.606</v>
+        <v>1.523</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>732</v>
+        <v>186.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.61</v>
+        <v>-1.84</v>
       </c>
       <c r="F42" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>10.368</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2060</v>
+        <v>20.15</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.44</v>
+        <v>-0.98</v>
       </c>
       <c r="F43" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,33 +1898,33 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.284</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>741</v>
+        <v>90.3</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.85</v>
+        <v>0.22</v>
       </c>
       <c r="F44" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,67 +1932,67 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1.972</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>41.95</v>
+        <v>1965</v>
       </c>
       <c r="E45" t="n">
-        <v>0.96</v>
+        <v>-1.26</v>
       </c>
       <c r="F45" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.68</v>
+        <v>21.535</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1455</v>
+        <v>749</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.02</v>
+        <v>1.08</v>
       </c>
       <c r="F46" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2000,67 +2000,67 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.578</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>90.09999999999999</v>
+        <v>147.5</v>
       </c>
       <c r="E47" t="n">
-        <v>1.46</v>
+        <v>-0.67</v>
       </c>
       <c r="F47" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.317</v>
+        <v>25.713</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>111.5</v>
+        <v>28.9</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,41 +2068,41 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1.542</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>59.1</v>
+        <v>352.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.17</v>
+        <v>1.59</v>
       </c>
       <c r="F49" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.554</v>
+        <v>1.411</v>
       </c>
     </row>
     <row r="50">
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>67.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="F50" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="51">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>301.53</v>
+        <v>302.13</v>
       </c>
       <c r="E51" t="n">
-        <v>-2.74</v>
+        <v>0.2</v>
       </c>
       <c r="F51" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2170,41 +2170,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5.508</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>6533</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>晶心科</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Andes Tech</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>347</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="F52" t="n">
-        <v>25</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Accumulation (Up)</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>1.394</v>
+        <v>5.346</v>
       </c>
     </row>
   </sheetData>
@@ -2218,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2261,311 +2227,311 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42.54</v>
+        <v>41.75</v>
       </c>
       <c r="F2" t="n">
-        <v>0.68</v>
+        <v>1.26</v>
       </c>
       <c r="G2" t="n">
-        <v>12.69</v>
+        <v>7.006</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40.74</v>
+        <v>40.27</v>
       </c>
       <c r="F3" t="n">
-        <v>1.42</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>6.886</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35.02</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="G4" t="n">
-        <v>1.394</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30.52</v>
+        <v>37.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1.03</v>
+        <v>0.86</v>
       </c>
       <c r="G5" t="n">
-        <v>16.29</v>
+        <v>1.411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25.13</v>
+        <v>31.6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="G6" t="n">
-        <v>14.631</v>
+        <v>16.065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24.44</v>
+        <v>24.88</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.641</v>
+        <v>3.196</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>22.07</v>
+        <v>22.7</v>
       </c>
       <c r="F8" t="n">
-        <v>1.71</v>
+        <v>0.98</v>
       </c>
       <c r="G8" t="n">
-        <v>4.808</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21.79</v>
+        <v>20.39</v>
       </c>
       <c r="F9" t="n">
-        <v>1.12</v>
+        <v>0.85</v>
       </c>
       <c r="G9" t="n">
-        <v>3.545</v>
+        <v>10.625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>17.87</v>
+        <v>20.28</v>
       </c>
       <c r="F10" t="n">
-        <v>0.76</v>
+        <v>1.34</v>
       </c>
       <c r="G10" t="n">
-        <v>10.368</v>
+        <v>4.761</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17.32</v>
+        <v>18.32</v>
       </c>
       <c r="F11" t="n">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>4.203</v>
+        <v>14.227</v>
       </c>
     </row>
     <row r="12">
@@ -2590,215 +2556,215 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>16.76</v>
+        <v>15.43</v>
       </c>
       <c r="F12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.98</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13.21</v>
+        <v>13.41</v>
       </c>
       <c r="F13" t="n">
-        <v>1.51</v>
+        <v>0.99</v>
       </c>
       <c r="G13" t="n">
-        <v>2.15</v>
+        <v>7.932</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>11.8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.97</v>
+        <v>1.52</v>
       </c>
       <c r="G14" t="n">
-        <v>4.488</v>
+        <v>4.485</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9.82</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.41</v>
+        <v>0.89</v>
       </c>
       <c r="G15" t="n">
-        <v>4.457</v>
+        <v>21.535</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.710000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="F16" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="G16" t="n">
-        <v>7.263</v>
+        <v>4.518</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.02</v>
+        <v>8.24</v>
       </c>
       <c r="F17" t="n">
-        <v>0.85</v>
+        <v>0.61</v>
       </c>
       <c r="G17" t="n">
-        <v>5.508</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.57</v>
+        <v>7.82</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9</v>
+        <v>1.26</v>
       </c>
       <c r="G18" t="n">
-        <v>21.956</v>
+        <v>10.793</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2807,91 +2773,91 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.39</v>
+        <v>7.66</v>
       </c>
       <c r="F19" t="n">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="G19" t="n">
-        <v>50.535</v>
+        <v>25.713</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.26</v>
+        <v>6.43</v>
       </c>
       <c r="F20" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>1.972</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.01</v>
+        <v>4.19</v>
       </c>
       <c r="F21" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="G21" t="n">
-        <v>2.284</v>
+        <v>1.577</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2900,556 +2866,556 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="F22" t="n">
-        <v>1.09</v>
+        <v>0.97</v>
       </c>
       <c r="G22" t="n">
-        <v>26.892</v>
+        <v>49.296</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.71</v>
+        <v>3.24</v>
       </c>
       <c r="F23" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
       <c r="G23" t="n">
-        <v>9.763</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.93</v>
+        <v>3.19</v>
       </c>
       <c r="F24" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="G24" t="n">
-        <v>2.016</v>
+        <v>3.873</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.72</v>
+        <v>2.68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.46</v>
+        <v>0.86</v>
       </c>
       <c r="G25" t="n">
-        <v>1.554</v>
+        <v>2.264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="F26" t="n">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
       <c r="G26" t="n">
-        <v>33.331</v>
+        <v>4.497</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="F27" t="n">
-        <v>0.58</v>
+        <v>0.9</v>
       </c>
       <c r="G27" t="n">
-        <v>0.578</v>
+        <v>1.709</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.33</v>
+        <v>1.07</v>
       </c>
       <c r="F28" t="n">
-        <v>1.02</v>
+        <v>0.93</v>
       </c>
       <c r="G28" t="n">
-        <v>4.609</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9429999999999999</v>
+        <v>22.225</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="F30" t="n">
-        <v>0.78</v>
+        <v>1.01</v>
       </c>
       <c r="G30" t="n">
-        <v>0.455</v>
+        <v>8.247</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.21</v>
+        <v>-0.42</v>
       </c>
       <c r="F31" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="G31" t="n">
-        <v>1.704</v>
+        <v>32.551</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-0.26</v>
+        <v>-0.45</v>
       </c>
       <c r="F32" t="n">
-        <v>0.87</v>
+        <v>0.46</v>
       </c>
       <c r="G32" t="n">
-        <v>0.551</v>
+        <v>1.523</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.28</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="G33" t="n">
-        <v>16.023</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.36</v>
+        <v>-0.68</v>
       </c>
       <c r="F34" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="G34" t="n">
-        <v>0.68</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.41</v>
+        <v>-0.76</v>
       </c>
       <c r="F35" t="n">
         <v>0.95</v>
       </c>
       <c r="G35" t="n">
-        <v>8.507999999999999</v>
+        <v>4.113</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.49</v>
+        <v>-0.79</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="G36" t="n">
-        <v>0.298</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.58</v>
+        <v>-0.99</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="G37" t="n">
-        <v>21.729</v>
+        <v>8.157</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="F38" t="n">
-        <v>0.99</v>
+        <v>0.62</v>
       </c>
       <c r="G38" t="n">
-        <v>1.097</v>
+        <v>6.226</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.86</v>
+        <v>-1.32</v>
       </c>
       <c r="F39" t="n">
-        <v>1.07</v>
+        <v>0.74</v>
       </c>
       <c r="G39" t="n">
-        <v>0.553</v>
+        <v>1.961</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3458,323 +3424,323 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.31</v>
+        <v>-1.49</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="G40" t="n">
-        <v>2.169</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.56</v>
+        <v>-2.18</v>
       </c>
       <c r="F41" t="n">
-        <v>1.41</v>
+        <v>0.66</v>
       </c>
       <c r="G41" t="n">
-        <v>8.252000000000001</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-1.67</v>
+        <v>-2.47</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="G42" t="n">
-        <v>6.284</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.04</v>
+        <v>-2.57</v>
       </c>
       <c r="F43" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>1.539</v>
+        <v>1.085</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-2.62</v>
+        <v>-3.08</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4</v>
+        <v>0.89</v>
       </c>
       <c r="G44" t="n">
-        <v>1.542</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.6</v>
+        <v>-3.92</v>
       </c>
       <c r="F45" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G45" t="n">
-        <v>4.51</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-4.5</v>
+        <v>-5.09</v>
       </c>
       <c r="F46" t="n">
-        <v>0.71</v>
+        <v>0.99</v>
       </c>
       <c r="G46" t="n">
-        <v>0.606</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.22</v>
+        <v>-5.85</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="G47" t="n">
-        <v>2.994</v>
+        <v>14.486</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-6.09</v>
+        <v>-7.94</v>
       </c>
       <c r="F48" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G48" t="n">
-        <v>7.99</v>
+        <v>2.817</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-6.17</v>
+        <v>-8.27</v>
       </c>
       <c r="F49" t="n">
-        <v>0.96</v>
+        <v>1.11</v>
       </c>
       <c r="G49" t="n">
-        <v>0.093</v>
+        <v>1.658</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-7.19</v>
+        <v>-10.15</v>
       </c>
       <c r="F50" t="n">
-        <v>0.96</v>
+        <v>0.6</v>
       </c>
       <c r="G50" t="n">
-        <v>1.833</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="51">
@@ -3799,44 +3765,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-12.1</v>
+        <v>-10.16</v>
       </c>
       <c r="F51" t="n">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="G51" t="n">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>8096</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CoAsia</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Design Service</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>-13.76</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.317</v>
+        <v>0.639</v>
       </c>
     </row>
   </sheetData>
@@ -3887,13 +3822,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.02</v>
+        <v>37.7</v>
       </c>
       <c r="C2" t="n">
-        <v>1.62</v>
+        <v>0.86</v>
       </c>
       <c r="D2" t="n">
-        <v>1.394</v>
+        <v>1.411</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3906,13 +3841,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.28</v>
+        <v>26.775</v>
       </c>
       <c r="C3" t="n">
-        <v>1.415</v>
+        <v>1.39</v>
       </c>
       <c r="D3" t="n">
-        <v>11.343</v>
+        <v>11.491</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -3921,58 +3856,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.6</v>
+        <v>26.65</v>
       </c>
       <c r="C4" t="n">
-        <v>1.555</v>
+        <v>1.63</v>
       </c>
       <c r="D4" t="n">
-        <v>19.439</v>
+        <v>21.507</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.125</v>
+        <v>24.88</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8500000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="D5" t="n">
-        <v>22.453</v>
+        <v>3.196</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.25333333333333</v>
+        <v>24.045</v>
       </c>
       <c r="C6" t="n">
-        <v>1.533333333333333</v>
+        <v>1.005</v>
       </c>
       <c r="D6" t="n">
-        <v>21.419</v>
+        <v>23.167</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3982,13 +3917,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.79</v>
+        <v>22.7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.12</v>
+        <v>0.98</v>
       </c>
       <c r="D7" t="n">
-        <v>3.545</v>
+        <v>3.459</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -4001,13 +3936,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.87</v>
+        <v>20.39</v>
       </c>
       <c r="C8" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="D8" t="n">
-        <v>10.368</v>
+        <v>10.625</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -4016,36 +3951,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.32</v>
+        <v>19.3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.67</v>
+        <v>1.315</v>
       </c>
       <c r="D9" t="n">
-        <v>4.203</v>
+        <v>18.988</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.21</v>
+        <v>13.41</v>
       </c>
       <c r="C10" t="n">
-        <v>1.51</v>
+        <v>0.99</v>
       </c>
       <c r="D10" t="n">
-        <v>2.15</v>
+        <v>7.932</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +3989,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.710000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="C11" t="n">
-        <v>0.76</v>
+        <v>0.61</v>
       </c>
       <c r="D11" t="n">
-        <v>7.263</v>
+        <v>1.86</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,17 +4008,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9.02</v>
+        <v>6.43</v>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>5.508</v>
+        <v>0.589</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4092,36 +4027,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.26</v>
+        <v>5.6</v>
       </c>
       <c r="C13" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="D13" t="n">
-        <v>1.972</v>
+        <v>75.009</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.62</v>
+        <v>5.545</v>
       </c>
       <c r="C14" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="D14" t="n">
-        <v>77.42699999999999</v>
+        <v>26.032</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -4130,36 +4065,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.95</v>
+        <v>3.24</v>
       </c>
       <c r="C15" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="D15" t="n">
-        <v>26.565</v>
+        <v>0.914</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.58</v>
+        <v>3.19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="D16" t="n">
-        <v>33.331</v>
+        <v>3.873</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4172,13 +4107,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.500000000000001</v>
+        <v>2.64</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D17" t="n">
-        <v>1.297</v>
+        <v>1.266</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -4187,55 +4122,55 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.04</v>
+        <v>1.756666666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="D18" t="n">
-        <v>0.578</v>
+        <v>4.809</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8039999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8720000000000001</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>8.021000000000001</v>
+        <v>22.225</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3</v>
+        <v>-0.28</v>
       </c>
       <c r="C20" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9429999999999999</v>
+        <v>8.247</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4179,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.26</v>
+        <v>-0.42</v>
       </c>
       <c r="C21" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="D21" t="n">
-        <v>0.551</v>
+        <v>32.551</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4263,17 +4198,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.28</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="D22" t="n">
-        <v>16.023</v>
+        <v>1.55</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,36 +4217,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3700000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.77</v>
       </c>
       <c r="D23" t="n">
-        <v>4.8</v>
+        <v>5.346</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.41</v>
+        <v>-0.79</v>
       </c>
       <c r="C24" t="n">
-        <v>0.95</v>
+        <v>0.78</v>
       </c>
       <c r="D24" t="n">
-        <v>8.507999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -4320,36 +4255,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.425</v>
+        <v>-1.156</v>
       </c>
       <c r="C25" t="n">
-        <v>0.705</v>
+        <v>0.8320000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.978</v>
+        <v>7.859999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.58</v>
+        <v>-1.2</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="D26" t="n">
-        <v>21.729</v>
+        <v>6.226</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4358,74 +4293,74 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.67</v>
+        <v>-2.325</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6</v>
+        <v>0.645</v>
       </c>
       <c r="D27" t="n">
-        <v>6.284</v>
+        <v>0.96</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.04</v>
+        <v>-2.71</v>
       </c>
       <c r="C28" t="n">
-        <v>0.77</v>
+        <v>1.105</v>
       </c>
       <c r="D28" t="n">
-        <v>1.539</v>
+        <v>20.325</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.183333333333334</v>
+        <v>-5.09</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9133333333333334</v>
+        <v>0.99</v>
       </c>
       <c r="D29" t="n">
-        <v>2.992</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-5.22</v>
+        <v>-5.85</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="D30" t="n">
-        <v>2.994</v>
+        <v>14.486</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4434,36 +4369,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-5.8375</v>
+        <v>-6.095</v>
       </c>
       <c r="C31" t="n">
-        <v>1.02</v>
+        <v>1.005</v>
       </c>
       <c r="D31" t="n">
-        <v>21.472</v>
+        <v>2.209</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-6.17</v>
+        <v>-7.94</v>
       </c>
       <c r="C32" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.093</v>
+        <v>2.817</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4575,31 +4510,31 @@
         <v>2060</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.44</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.67</v>
+        <v>-1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>62.5</v>
+        <v>57.58</v>
       </c>
       <c r="H2" t="n">
-        <v>8.4039</v>
+        <v>4.8787</v>
       </c>
       <c r="I2" t="n">
-        <v>44.3</v>
+        <v>44.7</v>
       </c>
       <c r="J2" t="n">
         <v>36.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.23</v>
+        <v>4.13</v>
       </c>
       <c r="L2" t="n">
-        <v>-42.2</v>
+        <v>-26.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4624,34 +4559,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4835</v>
+        <v>4690</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.73</v>
+        <v>-3</v>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>-0.42</v>
       </c>
       <c r="G3" t="n">
-        <v>60.47</v>
+        <v>54.04</v>
       </c>
       <c r="H3" t="n">
-        <v>190.3007</v>
+        <v>158.3203</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>35.9</v>
       </c>
       <c r="J3" t="n">
-        <v>42.7</v>
+        <v>24.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.68</v>
+        <v>4.77</v>
       </c>
       <c r="L3" t="n">
-        <v>9.800000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4676,34 +4611,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>90.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="E4" t="n">
-        <v>1.46</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.76</v>
+        <v>-10.15</v>
       </c>
       <c r="G4" t="n">
-        <v>59.9</v>
+        <v>51.46</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.3216</v>
+        <v>-3.912</v>
       </c>
       <c r="I4" t="n">
-        <v>55.5</v>
+        <v>62.1</v>
       </c>
       <c r="J4" t="n">
         <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="L4" t="n">
-        <v>-57.8</v>
+        <v>-47.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4728,34 +4663,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>301.53</v>
+        <v>302.13</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.74</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>9.02</v>
+        <v>-0.68</v>
       </c>
       <c r="G5" t="n">
-        <v>45.7</v>
+        <v>45.49</v>
       </c>
       <c r="H5" t="n">
-        <v>15.8573</v>
+        <v>13.8488</v>
       </c>
       <c r="I5" t="n">
-        <v>25.1</v>
+        <v>26.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>7.22</v>
+        <v>6.75</v>
       </c>
       <c r="L5" t="n">
-        <v>-72.09999999999999</v>
+        <v>-100</v>
       </c>
       <c r="M5" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4780,34 +4715,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.41</v>
+        <v>-0.18</v>
       </c>
       <c r="F6" t="n">
-        <v>11.8</v>
+        <v>8.35</v>
       </c>
       <c r="G6" t="n">
-        <v>58.59</v>
+        <v>59.64</v>
       </c>
       <c r="H6" t="n">
-        <v>27.5103</v>
+        <v>25.4779</v>
       </c>
       <c r="I6" t="n">
-        <v>63.2</v>
+        <v>60.3</v>
       </c>
       <c r="J6" t="n">
-        <v>48.4</v>
+        <v>33.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="L6" t="n">
-        <v>91.2</v>
+        <v>-23.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4832,34 +4767,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.56</v>
+        <v>-1.19</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.56</v>
+        <v>-0.99</v>
       </c>
       <c r="G7" t="n">
-        <v>58.73</v>
+        <v>51.52</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0207</v>
+        <v>-0.2561</v>
       </c>
       <c r="I7" t="n">
-        <v>57.5</v>
+        <v>29.2</v>
       </c>
       <c r="J7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="L7" t="n">
-        <v>9.800000000000001</v>
+        <v>22.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
         <v>7.82</v>
       </c>
       <c r="F2" t="n">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.196</v>
+        <v>3.193</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.924</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="4">
@@ -564,7 +564,7 @@
         <v>1.67</v>
       </c>
       <c r="F4" t="n">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7.932</v>
+        <v>7.912</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
         <v>3.7</v>
       </c>
       <c r="F5" t="n">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10.793</v>
+        <v>10.674</v>
       </c>
     </row>
     <row r="6">
@@ -632,7 +632,7 @@
         <v>-7</v>
       </c>
       <c r="F6" t="n">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,135 +640,135 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14.227</v>
+        <v>14.172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>116</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5</v>
+        <v>-1.69</v>
       </c>
       <c r="F7" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22.225</v>
+        <v>2.815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>116</v>
+        <v>532</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.69</v>
+        <v>3.5</v>
       </c>
       <c r="F8" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.817</v>
+        <v>22.177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>325.5</v>
+        <v>284.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.84</v>
+        <v>-0.87</v>
       </c>
       <c r="F9" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4.113</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4690</v>
+        <v>325.5</v>
       </c>
       <c r="E10" t="n">
-        <v>-3</v>
+        <v>-2.84</v>
       </c>
       <c r="F10" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>32.551</v>
+        <v>4.101</v>
       </c>
     </row>
     <row r="11">
@@ -802,7 +802,7 @@
         <v>-1.19</v>
       </c>
       <c r="F11" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8.157</v>
+        <v>8.138</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2550</v>
+        <v>188.5</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.35</v>
+        <v>1.89</v>
       </c>
       <c r="F12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -844,67 +844,67 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>49.296</v>
+        <v>7.413</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>188.5</v>
+        <v>49.3</v>
       </c>
       <c r="E13" t="n">
-        <v>1.89</v>
+        <v>-1</v>
       </c>
       <c r="F13" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.416</v>
+        <v>1.084</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>744</v>
+        <v>308</v>
       </c>
       <c r="E14" t="n">
-        <v>1.64</v>
+        <v>0.16</v>
       </c>
       <c r="F14" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,33 +912,33 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>10.625</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>308</v>
+        <v>2550</v>
       </c>
       <c r="E15" t="n">
-        <v>0.16</v>
+        <v>-1.35</v>
       </c>
       <c r="F15" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -946,41 +946,41 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>4.485</v>
+        <v>49.021</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>49.3</v>
+        <v>744</v>
       </c>
       <c r="E16" t="n">
-        <v>-1</v>
+        <v>1.64</v>
       </c>
       <c r="F16" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1.085</v>
+        <v>10.605</v>
       </c>
     </row>
     <row r="17">
@@ -1006,7 +1006,7 @@
         <v>1.7</v>
       </c>
       <c r="F17" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1020,61 +1020,61 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1490</v>
+        <v>110</v>
       </c>
       <c r="E18" t="n">
-        <v>2.41</v>
+        <v>-2.65</v>
       </c>
       <c r="F18" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.589</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>110</v>
+        <v>72.2</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.65</v>
+        <v>-0.55</v>
       </c>
       <c r="F19" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,109 +1082,109 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.109</v>
+        <v>8.244999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72.2</v>
+        <v>216.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.55</v>
+        <v>-3.35</v>
       </c>
       <c r="F20" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>8.247</v>
+        <v>4.755</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>216.5</v>
+        <v>57.5</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.35</v>
+        <v>-1.03</v>
       </c>
       <c r="F21" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4.761</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57.5</v>
+        <v>1490</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.03</v>
+        <v>2.41</v>
       </c>
       <c r="F22" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.639</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="23">
@@ -1218,33 +1218,33 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.264</v>
+        <v>2.263</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>362.5</v>
+        <v>4690</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.68</v>
+        <v>-3</v>
       </c>
       <c r="F24" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.658</v>
+        <v>32.014</v>
       </c>
     </row>
     <row r="25">
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>-0.83</v>
       </c>
       <c r="F27" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,67 +1354,67 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.497</v>
+        <v>4.493</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>177</v>
+        <v>362.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.39</v>
+        <v>-0.68</v>
       </c>
       <c r="F28" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>14.486</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8360</v>
+        <v>177</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.18</v>
+        <v>-1.39</v>
       </c>
       <c r="F29" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>12.374</v>
+        <v>14.481</v>
       </c>
     </row>
     <row r="30">
@@ -1448,7 +1448,7 @@
         <v>-2.04</v>
       </c>
       <c r="F30" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1456,166 +1456,166 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.961</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>531</v>
+        <v>8360</v>
       </c>
       <c r="E31" t="n">
-        <v>0.38</v>
+        <v>-1.18</v>
       </c>
       <c r="F31" t="n">
         <v>78</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.55</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>558</v>
+        <v>531</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.18</v>
+        <v>0.38</v>
       </c>
       <c r="F32" t="n">
         <v>77</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.518</v>
+        <v>1.549</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2060</v>
+        <v>558</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="F33" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6.226</v>
+        <v>4.514</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>202</v>
+        <v>2060</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.35</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.952</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>59.7</v>
+        <v>202</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>-3.35</v>
       </c>
       <c r="F35" t="n">
         <v>68</v>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.577</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>128</v>
+        <v>59.7</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.39</v>
+        <v>1.02</v>
       </c>
       <c r="F36" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,64 +1660,64 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7.006</v>
+        <v>1.577</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>41.4</v>
+        <v>128</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.31</v>
+        <v>-0.39</v>
       </c>
       <c r="F37" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.672</v>
+        <v>7.004</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2915</v>
+        <v>41.4</v>
       </c>
       <c r="E38" t="n">
-        <v>-3.32</v>
+        <v>-1.31</v>
       </c>
       <c r="F38" t="n">
         <v>66</v>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.873</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="39">
@@ -1762,109 +1762,109 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>581</v>
+        <v>2915</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.19</v>
+        <v>-3.32</v>
       </c>
       <c r="F40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>16.065</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>111.5</v>
+        <v>581</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>-1.19</v>
       </c>
       <c r="F41" t="n">
         <v>58</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.523</v>
+        <v>16.056</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>186.5</v>
+        <v>111.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>57</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.459</v>
+        <v>1.522</v>
       </c>
     </row>
     <row r="43">
@@ -1904,27 +1904,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>90.3</v>
+        <v>186.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.22</v>
+        <v>-1.84</v>
       </c>
       <c r="F44" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,33 +1932,33 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.314</v>
+        <v>3.457</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1965</v>
+        <v>90.3</v>
       </c>
       <c r="E45" t="n">
-        <v>-1.26</v>
+        <v>0.22</v>
       </c>
       <c r="F45" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,75 +1966,75 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>21.535</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>749</v>
+        <v>147.5</v>
       </c>
       <c r="E46" t="n">
-        <v>1.08</v>
+        <v>-0.67</v>
       </c>
       <c r="F46" t="n">
         <v>47</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.86</v>
+        <v>25.701</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>147.5</v>
+        <v>749</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.67</v>
+        <v>1.08</v>
       </c>
       <c r="F47" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>25.713</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="48">
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2074,27 +2074,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>352.5</v>
+        <v>1965</v>
       </c>
       <c r="E49" t="n">
-        <v>1.59</v>
+        <v>-1.26</v>
       </c>
       <c r="F49" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.411</v>
+        <v>21.494</v>
       </c>
     </row>
     <row r="50">
@@ -2136,41 +2136,75 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.914</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>晶心科</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Andes Tech</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>352.5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F51" t="n">
+        <v>29</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Accumulation (Up)</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>6173</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>信昌電</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Shinmore</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D52" t="n">
         <v>302.13</v>
       </c>
-      <c r="E51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F51" t="n">
+      <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>5.346</v>
+      <c r="H52" t="n">
+        <v>5.105</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2252,7 +2286,7 @@
         <v>1.26</v>
       </c>
       <c r="G2" t="n">
-        <v>7.006</v>
+        <v>7.004</v>
       </c>
     </row>
     <row r="3">
@@ -2283,7 +2317,7 @@
         <v>0.75</v>
       </c>
       <c r="G3" t="n">
-        <v>12.374</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="4">
@@ -2314,7 +2348,7 @@
         <v>2.87</v>
       </c>
       <c r="G4" t="n">
-        <v>0.924</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="5">
@@ -2345,7 +2379,7 @@
         <v>0.86</v>
       </c>
       <c r="G5" t="n">
-        <v>1.411</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="6">
@@ -2376,7 +2410,7 @@
         <v>0.96</v>
       </c>
       <c r="G6" t="n">
-        <v>16.065</v>
+        <v>16.056</v>
       </c>
     </row>
     <row r="7">
@@ -2407,7 +2441,7 @@
         <v>2.24</v>
       </c>
       <c r="G7" t="n">
-        <v>3.196</v>
+        <v>3.193</v>
       </c>
     </row>
     <row r="8">
@@ -2438,7 +2472,7 @@
         <v>0.98</v>
       </c>
       <c r="G8" t="n">
-        <v>3.459</v>
+        <v>3.457</v>
       </c>
     </row>
     <row r="9">
@@ -2466,10 +2500,10 @@
         <v>20.39</v>
       </c>
       <c r="F9" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="G9" t="n">
-        <v>10.625</v>
+        <v>10.605</v>
       </c>
     </row>
     <row r="10">
@@ -2500,7 +2534,7 @@
         <v>1.34</v>
       </c>
       <c r="G10" t="n">
-        <v>4.761</v>
+        <v>4.755</v>
       </c>
     </row>
     <row r="11">
@@ -2528,10 +2562,10 @@
         <v>18.32</v>
       </c>
       <c r="F11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G11" t="n">
-        <v>14.227</v>
+        <v>14.172</v>
       </c>
     </row>
     <row r="12">
@@ -2562,7 +2596,7 @@
         <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.952</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="13">
@@ -2590,10 +2624,10 @@
         <v>13.41</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="G13" t="n">
-        <v>7.932</v>
+        <v>7.912</v>
       </c>
     </row>
     <row r="14">
@@ -2621,10 +2655,10 @@
         <v>11.8</v>
       </c>
       <c r="F14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G14" t="n">
-        <v>4.485</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="15">
@@ -2652,10 +2686,10 @@
         <v>8.859999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="G15" t="n">
-        <v>21.535</v>
+        <v>21.494</v>
       </c>
     </row>
     <row r="16">
@@ -2686,7 +2720,7 @@
         <v>1.06</v>
       </c>
       <c r="G16" t="n">
-        <v>4.518</v>
+        <v>4.514</v>
       </c>
     </row>
     <row r="17">
@@ -2717,7 +2751,7 @@
         <v>0.61</v>
       </c>
       <c r="G17" t="n">
-        <v>1.86</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="18">
@@ -2745,10 +2779,10 @@
         <v>7.82</v>
       </c>
       <c r="F18" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="G18" t="n">
-        <v>10.793</v>
+        <v>10.674</v>
       </c>
     </row>
     <row r="19">
@@ -2779,7 +2813,7 @@
         <v>1.09</v>
       </c>
       <c r="G19" t="n">
-        <v>25.713</v>
+        <v>25.701</v>
       </c>
     </row>
     <row r="20">
@@ -2807,10 +2841,10 @@
         <v>6.43</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="G20" t="n">
-        <v>0.589</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="21">
@@ -2847,575 +2881,575 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.97</v>
+        <v>0.46</v>
       </c>
       <c r="G22" t="n">
-        <v>49.296</v>
+        <v>5.105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="F23" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="G23" t="n">
-        <v>0.914</v>
+        <v>49.021</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="F24" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="G24" t="n">
-        <v>3.873</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.68</v>
+        <v>3.19</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="G25" t="n">
-        <v>2.264</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.23</v>
+        <v>2.68</v>
       </c>
       <c r="F26" t="n">
-        <v>1.09</v>
+        <v>0.86</v>
       </c>
       <c r="G26" t="n">
-        <v>4.497</v>
+        <v>2.263</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9</v>
+        <v>1.08</v>
       </c>
       <c r="G27" t="n">
-        <v>1.709</v>
+        <v>4.493</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="F28" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="G28" t="n">
-        <v>7.416</v>
+        <v>1.709</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.19</v>
+        <v>1.07</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="G29" t="n">
-        <v>22.225</v>
+        <v>7.413</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.28</v>
+        <v>0.19</v>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="G30" t="n">
-        <v>8.247</v>
+        <v>22.177</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.42</v>
+        <v>-0.28</v>
       </c>
       <c r="F31" t="n">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="G31" t="n">
-        <v>32.551</v>
+        <v>8.244999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-0.45</v>
+        <v>-0.42</v>
       </c>
       <c r="F32" t="n">
-        <v>0.46</v>
+        <v>0.91</v>
       </c>
       <c r="G32" t="n">
-        <v>1.523</v>
+        <v>32.014</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.45</v>
       </c>
       <c r="F33" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="G33" t="n">
-        <v>1.55</v>
+        <v>1.522</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.68</v>
+        <v>-0.52</v>
       </c>
       <c r="F34" t="n">
-        <v>0.77</v>
+        <v>1.22</v>
       </c>
       <c r="G34" t="n">
-        <v>5.346</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.76</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="G35" t="n">
-        <v>4.113</v>
+        <v>1.549</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="F36" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.556</v>
+        <v>4.101</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.99</v>
+        <v>-0.79</v>
       </c>
       <c r="F37" t="n">
-        <v>1.49</v>
+        <v>0.78</v>
       </c>
       <c r="G37" t="n">
-        <v>8.157</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.2</v>
+        <v>-0.99</v>
       </c>
       <c r="F38" t="n">
-        <v>0.62</v>
+        <v>1.48</v>
       </c>
       <c r="G38" t="n">
-        <v>6.226</v>
+        <v>8.138</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.32</v>
+        <v>-1.2</v>
       </c>
       <c r="F39" t="n">
-        <v>0.74</v>
+        <v>0.61</v>
       </c>
       <c r="G39" t="n">
-        <v>1.961</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3424,60 +3458,60 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.49</v>
+        <v>-1.32</v>
       </c>
       <c r="F40" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="G40" t="n">
-        <v>0.441</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.18</v>
+        <v>-1.49</v>
       </c>
       <c r="F41" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="G41" t="n">
-        <v>0.288</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3486,60 +3520,60 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.47</v>
+        <v>-2.18</v>
       </c>
       <c r="F42" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="G42" t="n">
-        <v>0.672</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.57</v>
+        <v>-2.47</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="G43" t="n">
-        <v>1.085</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3548,229 +3582,260 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.08</v>
+        <v>-2.57</v>
       </c>
       <c r="F44" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="G44" t="n">
-        <v>2.109</v>
+        <v>1.084</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.92</v>
+        <v>-3.08</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="G45" t="n">
-        <v>0.551</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-5.09</v>
+        <v>-3.92</v>
       </c>
       <c r="F46" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="G46" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.85</v>
+        <v>-5.09</v>
       </c>
       <c r="F47" t="n">
-        <v>0.86</v>
+        <v>0.99</v>
       </c>
       <c r="G47" t="n">
-        <v>14.486</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-7.94</v>
+        <v>-5.85</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="G48" t="n">
-        <v>2.817</v>
+        <v>14.481</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-8.27</v>
+        <v>-7.94</v>
       </c>
       <c r="F49" t="n">
-        <v>1.11</v>
+        <v>0.9</v>
       </c>
       <c r="G49" t="n">
-        <v>1.658</v>
+        <v>2.815</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-10.15</v>
+        <v>-8.27</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.314</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>8096</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CoAsia</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Design Service</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>-10.15</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.314</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>2356</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>英業達</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Inventec</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>AI Server/OEM</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E52" t="n">
         <v>-10.16</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F52" t="n">
         <v>1.05</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G52" t="n">
         <v>0.639</v>
       </c>
     </row>
@@ -3828,7 +3893,7 @@
         <v>0.86</v>
       </c>
       <c r="D2" t="n">
-        <v>1.411</v>
+        <v>1.41</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3844,10 +3909,10 @@
         <v>26.775</v>
       </c>
       <c r="C3" t="n">
-        <v>1.39</v>
+        <v>1.385</v>
       </c>
       <c r="D3" t="n">
-        <v>11.491</v>
+        <v>11.483</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -3866,7 +3931,7 @@
         <v>1.63</v>
       </c>
       <c r="D4" t="n">
-        <v>21.507</v>
+        <v>21.492</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -3885,7 +3950,7 @@
         <v>2.24</v>
       </c>
       <c r="D5" t="n">
-        <v>3.196</v>
+        <v>3.193</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -3901,10 +3966,10 @@
         <v>24.045</v>
       </c>
       <c r="C6" t="n">
-        <v>1.005</v>
+        <v>0.99</v>
       </c>
       <c r="D6" t="n">
-        <v>23.167</v>
+        <v>23.024</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -3923,7 +3988,7 @@
         <v>0.98</v>
       </c>
       <c r="D7" t="n">
-        <v>3.459</v>
+        <v>3.457</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3939,10 +4004,10 @@
         <v>20.39</v>
       </c>
       <c r="C8" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="D8" t="n">
-        <v>10.625</v>
+        <v>10.605</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -3958,10 +4023,10 @@
         <v>19.3</v>
       </c>
       <c r="C9" t="n">
-        <v>1.315</v>
+        <v>1.31</v>
       </c>
       <c r="D9" t="n">
-        <v>18.988</v>
+        <v>18.927</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -3977,10 +4042,10 @@
         <v>13.41</v>
       </c>
       <c r="C10" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="D10" t="n">
-        <v>7.932</v>
+        <v>7.912</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -3999,7 +4064,7 @@
         <v>0.61</v>
       </c>
       <c r="D11" t="n">
-        <v>1.86</v>
+        <v>1.858</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4015,10 +4080,10 @@
         <v>6.43</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="D12" t="n">
-        <v>0.589</v>
+        <v>0.586</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -4034,10 +4099,10 @@
         <v>5.6</v>
       </c>
       <c r="C13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="D13" t="n">
-        <v>75.009</v>
+        <v>74.72200000000001</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -4053,10 +4118,10 @@
         <v>5.545</v>
       </c>
       <c r="C14" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="D14" t="n">
-        <v>26.032</v>
+        <v>25.987</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -4065,17 +4130,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.24</v>
+        <v>4.05</v>
       </c>
       <c r="C15" t="n">
-        <v>0.88</v>
+        <v>0.46</v>
       </c>
       <c r="D15" t="n">
-        <v>0.914</v>
+        <v>5.105</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4084,17 +4149,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="C16" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="D16" t="n">
-        <v>3.873</v>
+        <v>0.913</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4103,74 +4168,74 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.64</v>
+        <v>3.19</v>
       </c>
       <c r="C17" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="D17" t="n">
-        <v>1.266</v>
+        <v>3.86</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.756666666666667</v>
+        <v>2.64</v>
       </c>
       <c r="C18" t="n">
-        <v>0.62</v>
+        <v>0.745</v>
       </c>
       <c r="D18" t="n">
-        <v>4.809</v>
+        <v>1.265</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.19</v>
+        <v>1.756666666666667</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="D19" t="n">
-        <v>22.225</v>
+        <v>4.808</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.28</v>
+        <v>0.19</v>
       </c>
       <c r="C20" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="D20" t="n">
-        <v>8.247</v>
+        <v>22.177</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4179,17 +4244,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.42</v>
+        <v>-0.28</v>
       </c>
       <c r="C21" t="n">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="D21" t="n">
-        <v>32.551</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4198,17 +4263,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.42</v>
       </c>
       <c r="C22" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="D22" t="n">
-        <v>1.55</v>
+        <v>32.014</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4217,17 +4282,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.68</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="D23" t="n">
-        <v>5.346</v>
+        <v>1.549</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4262,10 +4327,10 @@
         <v>-1.156</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8320000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>7.859999999999999</v>
+        <v>7.856</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
@@ -4281,10 +4346,10 @@
         <v>-1.2</v>
       </c>
       <c r="C26" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="D26" t="n">
-        <v>6.226</v>
+        <v>6.21</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4319,10 +4384,10 @@
         <v>-2.71</v>
       </c>
       <c r="C28" t="n">
-        <v>1.105</v>
+        <v>1.1</v>
       </c>
       <c r="D28" t="n">
-        <v>20.325</v>
+        <v>20.291</v>
       </c>
       <c r="E28" t="n">
         <v>4</v>
@@ -4331,36 +4396,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-5.09</v>
+        <v>-4.236666666666666</v>
       </c>
       <c r="C29" t="n">
-        <v>0.99</v>
+        <v>1.07</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08599999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-5.85</v>
+        <v>-5.09</v>
       </c>
       <c r="C30" t="n">
-        <v>0.86</v>
+        <v>0.99</v>
       </c>
       <c r="D30" t="n">
-        <v>14.486</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4369,20 +4434,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-6.095</v>
+        <v>-5.85</v>
       </c>
       <c r="C31" t="n">
-        <v>1.005</v>
+        <v>0.86</v>
       </c>
       <c r="D31" t="n">
-        <v>2.209</v>
+        <v>14.481</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -4398,7 +4463,7 @@
         <v>0.9</v>
       </c>
       <c r="D32" t="n">
-        <v>2.817</v>
+        <v>2.815</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -4531,10 +4596,10 @@
         <v>4.13</v>
       </c>
       <c r="L2" t="n">
-        <v>-26.4</v>
+        <v>-31.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -4583,10 +4648,10 @@
         <v>4.77</v>
       </c>
       <c r="L3" t="n">
-        <v>25.4</v>
+        <v>-6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4635,10 +4700,10 @@
         <v>3.34</v>
       </c>
       <c r="L4" t="n">
-        <v>-47.5</v>
+        <v>-48.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4666,31 +4731,31 @@
         <v>302.13</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.68</v>
+        <v>4.05</v>
       </c>
       <c r="G5" t="n">
-        <v>45.49</v>
+        <v>33.01</v>
       </c>
       <c r="H5" t="n">
-        <v>13.8488</v>
+        <v>12.1173</v>
       </c>
       <c r="I5" t="n">
-        <v>26.6</v>
+        <v>23.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6.75</v>
+        <v>6.04</v>
       </c>
       <c r="L5" t="n">
         <v>-100</v>
       </c>
       <c r="M5" t="n">
-        <v>0.77</v>
+        <v>0.46</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -4739,7 +4804,7 @@
         <v>5.43</v>
       </c>
       <c r="L6" t="n">
-        <v>-23.2</v>
+        <v>-24.8</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -4791,10 +4856,10 @@
         <v>2.01</v>
       </c>
       <c r="L7" t="n">
-        <v>22.3</v>
+        <v>17.9</v>
       </c>
       <c r="M7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81.3</v>
+        <v>154</v>
       </c>
       <c r="E2" t="n">
-        <v>7.82</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>622</v>
+        <v>507</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.193</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>154</v>
+        <v>304.5</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>1.67</v>
       </c>
       <c r="F3" t="n">
-        <v>507</v>
+        <v>195</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.922</v>
+        <v>7.912</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>304.5</v>
+        <v>4345</v>
       </c>
       <c r="E4" t="n">
-        <v>1.67</v>
+        <v>3.7</v>
       </c>
       <c r="F4" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>7.912</v>
+        <v>10.674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4345</v>
+        <v>1130</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7</v>
+        <v>-7</v>
       </c>
       <c r="F5" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,101 +606,101 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10.674</v>
+        <v>14.172</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1130</v>
+        <v>116</v>
       </c>
       <c r="E6" t="n">
-        <v>-7</v>
+        <v>-1.69</v>
       </c>
       <c r="F6" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14.172</v>
+        <v>2.815</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>116</v>
+        <v>532</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.69</v>
+        <v>3.5</v>
       </c>
       <c r="F7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.815</v>
+        <v>22.177</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>532</v>
+        <v>284.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5</v>
+        <v>-0.87</v>
       </c>
       <c r="F8" t="n">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -708,67 +708,67 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.177</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>284.5</v>
+        <v>325.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.87</v>
+        <v>-2.84</v>
       </c>
       <c r="F9" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.546</v>
+        <v>4.101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>325.5</v>
+        <v>249</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.84</v>
+        <v>-1.19</v>
       </c>
       <c r="F10" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,135 +776,135 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4.101</v>
+        <v>8.138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>249</v>
+        <v>188.5</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.19</v>
+        <v>1.89</v>
       </c>
       <c r="F11" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8.138</v>
+        <v>7.413</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>188.5</v>
+        <v>49.3</v>
       </c>
       <c r="E12" t="n">
-        <v>1.89</v>
+        <v>-1</v>
       </c>
       <c r="F12" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.413</v>
+        <v>1.084</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>49.3</v>
+        <v>308</v>
       </c>
       <c r="E13" t="n">
-        <v>-1</v>
+        <v>0.16</v>
       </c>
       <c r="F13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1.084</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>308</v>
+        <v>744</v>
       </c>
       <c r="E14" t="n">
-        <v>0.16</v>
+        <v>1.64</v>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.479</v>
+        <v>10.605</v>
       </c>
     </row>
     <row r="15">
@@ -952,61 +952,61 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>744</v>
+        <v>269.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="F16" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>10.605</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>269.5</v>
+        <v>110</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7</v>
+        <v>-2.65</v>
       </c>
       <c r="F17" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,33 +1014,33 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.551</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>110</v>
+        <v>72.2</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.65</v>
+        <v>-0.55</v>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,64 +1048,64 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.109</v>
+        <v>8.244999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72.2</v>
+        <v>216.5</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.55</v>
+        <v>-3.35</v>
       </c>
       <c r="F19" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.244999999999999</v>
+        <v>4.755</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>216.5</v>
+        <v>1490</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.35</v>
+        <v>2.41</v>
       </c>
       <c r="F20" t="n">
         <v>96</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.755</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="21">
@@ -1156,27 +1156,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1490</v>
+        <v>153</v>
       </c>
       <c r="E22" t="n">
-        <v>2.41</v>
+        <v>-1.61</v>
       </c>
       <c r="F22" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1184,75 +1184,75 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.586</v>
+        <v>2.263</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>153</v>
+        <v>4690</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.61</v>
+        <v>-3</v>
       </c>
       <c r="F23" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.263</v>
+        <v>32.014</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4690</v>
+        <v>18.95</v>
       </c>
       <c r="E24" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>32.014</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="25">
@@ -1292,27 +1292,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>18.95</v>
+        <v>297.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="F26" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1320,302 +1320,302 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.556</v>
+        <v>4.493</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>297.5</v>
+        <v>362.5</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.83</v>
+        <v>-0.68</v>
       </c>
       <c r="F27" t="n">
         <v>88</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.493</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>362.5</v>
+        <v>177</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.68</v>
+        <v>-1.39</v>
       </c>
       <c r="F28" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.653</v>
+        <v>14.481</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>177</v>
+        <v>67.3</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.39</v>
+        <v>-2.04</v>
       </c>
       <c r="F29" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>14.481</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>67.3</v>
+        <v>8360</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.04</v>
+        <v>-1.18</v>
       </c>
       <c r="F30" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1.96</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8360</v>
+        <v>531</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.18</v>
+        <v>0.38</v>
       </c>
       <c r="F31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>12.35</v>
+        <v>1.549</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="E32" t="n">
-        <v>0.38</v>
+        <v>-0.18</v>
       </c>
       <c r="F32" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1.549</v>
+        <v>4.514</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>558</v>
+        <v>2060</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.514</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2060</v>
+        <v>202</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-3.35</v>
       </c>
       <c r="F34" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6.21</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>202</v>
+        <v>59.7</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.35</v>
+        <v>1.02</v>
       </c>
       <c r="F35" t="n">
         <v>68</v>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.951</v>
+        <v>1.577</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>59.7</v>
+        <v>128</v>
       </c>
       <c r="E36" t="n">
-        <v>1.02</v>
+        <v>-0.39</v>
       </c>
       <c r="F36" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.577</v>
+        <v>7.004</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>128</v>
+        <v>41.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.39</v>
+        <v>-1.31</v>
       </c>
       <c r="F37" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7.004</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>41.4</v>
+        <v>26.45</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.31</v>
+        <v>-0.38</v>
       </c>
       <c r="F38" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.672</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>26.45</v>
+        <v>2915</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.38</v>
+        <v>-3.32</v>
       </c>
       <c r="F39" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,75 +1762,75 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.44</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2915</v>
+        <v>581</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.32</v>
+        <v>-1.19</v>
       </c>
       <c r="F40" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.86</v>
+        <v>16.056</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>581</v>
+        <v>20.15</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.19</v>
+        <v>-0.98</v>
       </c>
       <c r="F41" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>16.056</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="42">
@@ -1870,61 +1870,61 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>20.15</v>
+        <v>186.5</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.98</v>
+        <v>-1.84</v>
       </c>
       <c r="F43" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.288</v>
+        <v>3.457</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>186.5</v>
+        <v>90.3</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.84</v>
+        <v>0.22</v>
       </c>
       <c r="F44" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1932,169 +1932,169 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.457</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>90.3</v>
+        <v>147.5</v>
       </c>
       <c r="E45" t="n">
-        <v>0.22</v>
+        <v>-0.67</v>
       </c>
       <c r="F45" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.314</v>
+        <v>25.701</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>147.5</v>
+        <v>749</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.67</v>
+        <v>1.08</v>
       </c>
       <c r="F46" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>25.701</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>749</v>
+        <v>28.9</v>
       </c>
       <c r="E47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.858</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>28.9</v>
+        <v>1965</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="F48" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.08599999999999999</v>
+        <v>21.494</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1965</v>
+        <v>67</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.26</v>
+        <v>-0.59</v>
       </c>
       <c r="F49" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,33 +2102,33 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>21.494</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>67</v>
+        <v>352.5</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.59</v>
+        <v>1.59</v>
       </c>
       <c r="F50" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2136,74 +2136,40 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.913</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>352.5</v>
+        <v>302.13</v>
       </c>
       <c r="E51" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>6173</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>信昌電</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Shinmore</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>302.13</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
         <v>5.105</v>
       </c>
     </row>
@@ -2218,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,110 +2382,110 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24.88</v>
+        <v>22.7</v>
       </c>
       <c r="F7" t="n">
-        <v>2.24</v>
+        <v>0.98</v>
       </c>
       <c r="G7" t="n">
-        <v>3.193</v>
+        <v>3.457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>22.7</v>
+        <v>20.39</v>
       </c>
       <c r="F8" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="G8" t="n">
-        <v>3.457</v>
+        <v>10.605</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20.39</v>
+        <v>20.28</v>
       </c>
       <c r="F9" t="n">
-        <v>0.84</v>
+        <v>1.34</v>
       </c>
       <c r="G9" t="n">
-        <v>10.605</v>
+        <v>4.755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2528,928 +2494,928 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20.28</v>
+        <v>18.32</v>
       </c>
       <c r="F10" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="G10" t="n">
-        <v>4.755</v>
+        <v>14.172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18.32</v>
+        <v>15.43</v>
       </c>
       <c r="F11" t="n">
-        <v>1.28</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>14.172</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15.43</v>
+        <v>13.41</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="G12" t="n">
-        <v>0.951</v>
+        <v>7.912</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13.41</v>
+        <v>11.8</v>
       </c>
       <c r="F13" t="n">
-        <v>0.98</v>
+        <v>1.51</v>
       </c>
       <c r="G13" t="n">
-        <v>7.912</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>11.8</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.51</v>
+        <v>0.88</v>
       </c>
       <c r="G14" t="n">
-        <v>4.479</v>
+        <v>21.494</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.859999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="F15" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="G15" t="n">
-        <v>21.494</v>
+        <v>4.514</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.35</v>
+        <v>8.24</v>
       </c>
       <c r="F16" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="G16" t="n">
-        <v>4.514</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8.24</v>
+        <v>7.82</v>
       </c>
       <c r="F17" t="n">
-        <v>0.61</v>
+        <v>1.23</v>
       </c>
       <c r="G17" t="n">
-        <v>1.858</v>
+        <v>10.674</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.82</v>
+        <v>7.66</v>
       </c>
       <c r="F18" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="G18" t="n">
-        <v>10.674</v>
+        <v>25.701</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.66</v>
+        <v>6.43</v>
       </c>
       <c r="F19" t="n">
-        <v>1.09</v>
+        <v>0.67</v>
       </c>
       <c r="G19" t="n">
-        <v>25.701</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.43</v>
+        <v>4.19</v>
       </c>
       <c r="F20" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.586</v>
+        <v>1.577</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.19</v>
+        <v>4.05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="G21" t="n">
-        <v>1.577</v>
+        <v>5.105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="F22" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="G22" t="n">
-        <v>5.105</v>
+        <v>49.021</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.54</v>
+        <v>3.24</v>
       </c>
       <c r="F23" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="G23" t="n">
-        <v>49.021</v>
+        <v>0.913</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="F24" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="G24" t="n">
-        <v>0.913</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.19</v>
+        <v>2.68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.65</v>
+        <v>0.86</v>
       </c>
       <c r="G25" t="n">
-        <v>3.86</v>
+        <v>2.263</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.68</v>
+        <v>2.23</v>
       </c>
       <c r="F26" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="G26" t="n">
-        <v>2.263</v>
+        <v>4.493</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="F27" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="G27" t="n">
-        <v>4.493</v>
+        <v>1.709</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.53</v>
+        <v>1.07</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="G28" t="n">
-        <v>1.709</v>
+        <v>7.413</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.07</v>
+        <v>0.19</v>
       </c>
       <c r="F29" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="G29" t="n">
-        <v>7.413</v>
+        <v>22.177</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="F30" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G30" t="n">
-        <v>22.177</v>
+        <v>8.244999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.28</v>
+        <v>-0.42</v>
       </c>
       <c r="F31" t="n">
-        <v>1.01</v>
+        <v>0.91</v>
       </c>
       <c r="G31" t="n">
-        <v>8.244999999999999</v>
+        <v>32.014</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-0.42</v>
+        <v>-0.45</v>
       </c>
       <c r="F32" t="n">
-        <v>0.91</v>
+        <v>0.46</v>
       </c>
       <c r="G32" t="n">
-        <v>32.014</v>
+        <v>1.522</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.45</v>
+        <v>-0.52</v>
       </c>
       <c r="F33" t="n">
-        <v>0.46</v>
+        <v>1.22</v>
       </c>
       <c r="G33" t="n">
-        <v>1.522</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>1.22</v>
+        <v>0.75</v>
       </c>
       <c r="G34" t="n">
-        <v>0.546</v>
+        <v>1.549</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="F35" t="n">
-        <v>0.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>1.549</v>
+        <v>4.101</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.76</v>
+        <v>-0.79</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="G36" t="n">
-        <v>4.101</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.79</v>
+        <v>-0.99</v>
       </c>
       <c r="F37" t="n">
-        <v>0.78</v>
+        <v>1.48</v>
       </c>
       <c r="G37" t="n">
-        <v>0.556</v>
+        <v>8.138</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.99</v>
+        <v>-1.2</v>
       </c>
       <c r="F38" t="n">
-        <v>1.48</v>
+        <v>0.61</v>
       </c>
       <c r="G38" t="n">
-        <v>8.138</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.2</v>
+        <v>-1.32</v>
       </c>
       <c r="F39" t="n">
-        <v>0.61</v>
+        <v>0.74</v>
       </c>
       <c r="G39" t="n">
-        <v>6.21</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3458,60 +3424,60 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.32</v>
+        <v>-1.49</v>
       </c>
       <c r="F40" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="G40" t="n">
-        <v>1.96</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.49</v>
+        <v>-2.18</v>
       </c>
       <c r="F41" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="G41" t="n">
-        <v>0.44</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3520,60 +3486,60 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.18</v>
+        <v>-2.47</v>
       </c>
       <c r="F42" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="G42" t="n">
-        <v>0.288</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.47</v>
+        <v>-2.57</v>
       </c>
       <c r="F43" t="n">
-        <v>0.63</v>
+        <v>0.93</v>
       </c>
       <c r="G43" t="n">
-        <v>0.672</v>
+        <v>1.084</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3582,260 +3548,229 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-2.57</v>
+        <v>-3.08</v>
       </c>
       <c r="F44" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="G44" t="n">
-        <v>1.084</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.08</v>
+        <v>-3.92</v>
       </c>
       <c r="F45" t="n">
         <v>0.89</v>
       </c>
       <c r="G45" t="n">
-        <v>2.109</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-3.92</v>
+        <v>-5.09</v>
       </c>
       <c r="F46" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="G46" t="n">
-        <v>0.551</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.09</v>
+        <v>-5.85</v>
       </c>
       <c r="F47" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="G47" t="n">
-        <v>0.08599999999999999</v>
+        <v>14.481</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-5.85</v>
+        <v>-7.94</v>
       </c>
       <c r="F48" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="G48" t="n">
-        <v>14.481</v>
+        <v>2.815</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-7.94</v>
+        <v>-8.27</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G49" t="n">
-        <v>2.815</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-8.27</v>
+        <v>-10.15</v>
       </c>
       <c r="F50" t="n">
-        <v>1.1</v>
+        <v>0.59</v>
       </c>
       <c r="G50" t="n">
-        <v>1.653</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-10.15</v>
+        <v>-10.16</v>
       </c>
       <c r="F51" t="n">
-        <v>0.59</v>
+        <v>1.05</v>
       </c>
       <c r="G51" t="n">
-        <v>0.314</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Inventec</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>AI Server/OEM</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>-10.16</v>
-      </c>
-      <c r="F52" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="G52" t="n">
         <v>0.639</v>
       </c>
     </row>
@@ -3850,7 +3785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3940,55 +3875,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Plastics</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.88</v>
+        <v>24.045</v>
       </c>
       <c r="C5" t="n">
-        <v>2.24</v>
+        <v>0.99</v>
       </c>
       <c r="D5" t="n">
-        <v>3.193</v>
+        <v>23.024</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.045</v>
+        <v>22.7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="D6" t="n">
-        <v>23.024</v>
+        <v>3.457</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.7</v>
+        <v>20.39</v>
       </c>
       <c r="C7" t="n">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="D7" t="n">
-        <v>3.457</v>
+        <v>10.605</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3997,55 +3932,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20.39</v>
+        <v>19.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.84</v>
+        <v>1.31</v>
       </c>
       <c r="D8" t="n">
-        <v>10.605</v>
+        <v>18.927</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.3</v>
+        <v>13.41</v>
       </c>
       <c r="C9" t="n">
-        <v>1.31</v>
+        <v>0.98</v>
       </c>
       <c r="D9" t="n">
-        <v>18.927</v>
+        <v>7.912</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13.41</v>
+        <v>8.24</v>
       </c>
       <c r="C10" t="n">
-        <v>0.98</v>
+        <v>0.61</v>
       </c>
       <c r="D10" t="n">
-        <v>7.912</v>
+        <v>1.858</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -4054,17 +3989,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.24</v>
+        <v>6.43</v>
       </c>
       <c r="C11" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="D11" t="n">
-        <v>1.858</v>
+        <v>0.586</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4073,36 +4008,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.43</v>
+        <v>5.6</v>
       </c>
       <c r="C12" t="n">
-        <v>0.67</v>
+        <v>1.02</v>
       </c>
       <c r="D12" t="n">
-        <v>0.586</v>
+        <v>74.72200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.6</v>
+        <v>5.545</v>
       </c>
       <c r="C13" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="D13" t="n">
-        <v>74.72200000000001</v>
+        <v>25.987</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -4111,36 +4046,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.545</v>
+        <v>4.05</v>
       </c>
       <c r="C14" t="n">
-        <v>0.98</v>
+        <v>0.46</v>
       </c>
       <c r="D14" t="n">
-        <v>25.987</v>
+        <v>5.105</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.05</v>
+        <v>3.24</v>
       </c>
       <c r="C15" t="n">
-        <v>0.46</v>
+        <v>0.88</v>
       </c>
       <c r="D15" t="n">
-        <v>5.105</v>
+        <v>0.913</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4149,17 +4084,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.88</v>
+        <v>0.65</v>
       </c>
       <c r="D16" t="n">
-        <v>0.913</v>
+        <v>3.86</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4168,74 +4103,74 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.19</v>
+        <v>2.64</v>
       </c>
       <c r="C17" t="n">
-        <v>0.65</v>
+        <v>0.745</v>
       </c>
       <c r="D17" t="n">
-        <v>3.86</v>
+        <v>1.265</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.64</v>
+        <v>1.756666666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>0.745</v>
+        <v>0.62</v>
       </c>
       <c r="D18" t="n">
-        <v>1.265</v>
+        <v>4.808</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.756666666666667</v>
+        <v>0.19</v>
       </c>
       <c r="C19" t="n">
-        <v>0.62</v>
+        <v>0.99</v>
       </c>
       <c r="D19" t="n">
-        <v>4.808</v>
+        <v>22.177</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="C20" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="D20" t="n">
-        <v>22.177</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4244,17 +4179,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.28</v>
+        <v>-0.42</v>
       </c>
       <c r="C21" t="n">
-        <v>1.01</v>
+        <v>0.91</v>
       </c>
       <c r="D21" t="n">
-        <v>8.244999999999999</v>
+        <v>32.014</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4263,17 +4198,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.42</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.91</v>
+        <v>0.75</v>
       </c>
       <c r="D22" t="n">
-        <v>32.014</v>
+        <v>1.549</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -4282,17 +4217,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.79</v>
       </c>
       <c r="C23" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="D23" t="n">
-        <v>1.549</v>
+        <v>0.556</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -4301,131 +4236,131 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.79</v>
+        <v>-1.156</v>
       </c>
       <c r="C24" t="n">
-        <v>0.78</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.556</v>
+        <v>7.856</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.156</v>
+        <v>-1.2</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="D25" t="n">
-        <v>7.856</v>
+        <v>6.21</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.2</v>
+        <v>-2.325</v>
       </c>
       <c r="C26" t="n">
-        <v>0.61</v>
+        <v>0.645</v>
       </c>
       <c r="D26" t="n">
-        <v>6.21</v>
+        <v>0.96</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.325</v>
+        <v>-2.71</v>
       </c>
       <c r="C27" t="n">
-        <v>0.645</v>
+        <v>1.1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.96</v>
+        <v>20.291</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.71</v>
+        <v>-4.236666666666666</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="D28" t="n">
-        <v>20.291</v>
+        <v>2.75</v>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-4.236666666666666</v>
+        <v>-5.09</v>
       </c>
       <c r="C29" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="D29" t="n">
-        <v>2.75</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-5.09</v>
+        <v>-5.85</v>
       </c>
       <c r="C30" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08599999999999999</v>
+        <v>14.481</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4434,38 +4369,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Memory - NOR Flash</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-5.85</v>
+        <v>-7.94</v>
       </c>
       <c r="C31" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="D31" t="n">
-        <v>14.481</v>
+        <v>2.815</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Memory - NOR Flash</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>-7.94</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.815</v>
-      </c>
-      <c r="E32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4584,7 +4500,7 @@
         <v>57.58</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8787</v>
+        <v>-5.949</v>
       </c>
       <c r="I2" t="n">
         <v>44.7</v>
@@ -4636,7 +4552,7 @@
         <v>54.04</v>
       </c>
       <c r="H3" t="n">
-        <v>158.3203</v>
+        <v>145.9217</v>
       </c>
       <c r="I3" t="n">
         <v>35.9</v>
@@ -4688,7 +4604,7 @@
         <v>51.46</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.912</v>
+        <v>-4.0282</v>
       </c>
       <c r="I4" t="n">
         <v>62.1</v>
@@ -4740,7 +4656,7 @@
         <v>33.01</v>
       </c>
       <c r="H5" t="n">
-        <v>12.1173</v>
+        <v>9.4855</v>
       </c>
       <c r="I5" t="n">
         <v>23.7</v>
@@ -4792,7 +4708,7 @@
         <v>59.64</v>
       </c>
       <c r="H6" t="n">
-        <v>25.4779</v>
+        <v>25.4473</v>
       </c>
       <c r="I6" t="n">
         <v>60.3</v>
@@ -4844,7 +4760,7 @@
         <v>51.52</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2561</v>
+        <v>-0.1214</v>
       </c>
       <c r="I7" t="n">
         <v>29.2</v>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>154</v>
+        <v>264</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>13.55</v>
       </c>
       <c r="F2" t="n">
-        <v>507</v>
+        <v>617</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.922</v>
+        <v>2.643</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>304.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>1.67</v>
+        <v>-0.49</v>
       </c>
       <c r="F3" t="n">
-        <v>195</v>
+        <v>292</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,33 +538,33 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7.912</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4345</v>
+        <v>140</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7</v>
+        <v>-9.09</v>
       </c>
       <c r="F4" t="n">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,33 +572,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10.674</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1130</v>
+        <v>121.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-7</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,67 +606,67 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14.172</v>
+        <v>1.707</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>116</v>
+        <v>64.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.69</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.815</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>4055</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5</v>
+        <v>-6.67</v>
       </c>
       <c r="F7" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,67 +674,67 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22.177</v>
+        <v>10.526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>284.5</v>
+        <v>488</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.87</v>
+        <v>-8.27</v>
       </c>
       <c r="F8" t="n">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.546</v>
+        <v>21.807</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>325.5</v>
+        <v>106.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.84</v>
+        <v>-8.19</v>
       </c>
       <c r="F9" t="n">
-        <v>133</v>
+        <v>211</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,67 +742,67 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4.101</v>
+        <v>2.694</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.19</v>
+        <v>6.39</v>
       </c>
       <c r="F10" t="n">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8.138</v>
+        <v>2.199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>188.5</v>
+        <v>1540</v>
       </c>
       <c r="E11" t="n">
-        <v>1.89</v>
+        <v>3.36</v>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,67 +810,67 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7.413</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>49.3</v>
+        <v>2490</v>
       </c>
       <c r="E12" t="n">
-        <v>-1</v>
+        <v>-2.35</v>
       </c>
       <c r="F12" t="n">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.084</v>
+        <v>50.224</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>308</v>
+        <v>43</v>
       </c>
       <c r="E13" t="n">
-        <v>0.16</v>
+        <v>3.86</v>
       </c>
       <c r="F13" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -878,135 +878,135 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.479</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>744</v>
+        <v>1965</v>
       </c>
       <c r="E14" t="n">
-        <v>1.64</v>
+        <v>-4.61</v>
       </c>
       <c r="F14" t="n">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>10.605</v>
+        <v>6.271</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2550</v>
+        <v>276</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.35</v>
+        <v>-2.99</v>
       </c>
       <c r="F15" t="n">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>49.021</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TeamGroup</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>269.5</v>
+        <v>27.2</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7</v>
+        <v>2.84</v>
       </c>
       <c r="F16" t="n">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.551</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>110</v>
+        <v>161.5</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.65</v>
+        <v>-8.76</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.109</v>
+        <v>13.098</v>
       </c>
     </row>
     <row r="18">
@@ -1034,13 +1034,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72.2</v>
+        <v>67.5</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.55</v>
+        <v>-6.51</v>
       </c>
       <c r="F18" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1048,101 +1048,101 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>8.244999999999999</v>
+        <v>7.917</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sino-American</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>216.5</v>
+        <v>305</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.35</v>
+        <v>0.16</v>
       </c>
       <c r="F19" t="n">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4.755</v>
+        <v>8.367000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1490</v>
+        <v>546</v>
       </c>
       <c r="E20" t="n">
-        <v>2.41</v>
+        <v>2.82</v>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.586</v>
+        <v>1.609</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57.5</v>
+        <v>1775</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.03</v>
+        <v>-9.67</v>
       </c>
       <c r="F21" t="n">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,67 +1150,67 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.639</v>
+        <v>20.096</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>153</v>
+        <v>240</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.61</v>
+        <v>-3.61</v>
       </c>
       <c r="F22" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.263</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4690</v>
+        <v>508</v>
       </c>
       <c r="E23" t="n">
-        <v>-3</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1218,135 +1218,135 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>32.014</v>
+        <v>4.328</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18.95</v>
+        <v>160</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="F24" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.556</v>
+        <v>2.391</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>232.5</v>
+        <v>1015</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-10.18</v>
       </c>
       <c r="F25" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.709</v>
+        <v>13.307</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>297.5</v>
+        <v>50.9</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.83</v>
+        <v>3.25</v>
       </c>
       <c r="F26" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.493</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>362.5</v>
+        <v>57.3</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.68</v>
+        <v>-0.35</v>
       </c>
       <c r="F27" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,67 +1354,67 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1.653</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>177</v>
+        <v>740</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.39</v>
+        <v>-0.54</v>
       </c>
       <c r="F28" t="n">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>14.481</v>
+        <v>10.357</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>67.3</v>
+        <v>4525</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.04</v>
+        <v>-3.52</v>
       </c>
       <c r="F29" t="n">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,203 +1422,203 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.96</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8360</v>
+        <v>276</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.18</v>
+        <v>-7.23</v>
       </c>
       <c r="F30" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>12.35</v>
+        <v>4.222</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>531</v>
+        <v>20.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0.38</v>
+        <v>1.74</v>
       </c>
       <c r="F31" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.549</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>558</v>
+        <v>187</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.18</v>
+        <v>-0.8</v>
       </c>
       <c r="F32" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.514</v>
+        <v>7.102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2060</v>
+        <v>114.5</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="F33" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6.21</v>
+        <v>2.174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>202</v>
+        <v>19.15</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.35</v>
+        <v>1.06</v>
       </c>
       <c r="F34" t="n">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.951</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>59.7</v>
+        <v>758</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="F35" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1626,33 +1626,33 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.577</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.39</v>
+        <v>-6.17</v>
       </c>
       <c r="F36" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7.004</v>
+        <v>3.279</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>41.4</v>
+        <v>556</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.31</v>
+        <v>-4.3</v>
       </c>
       <c r="F37" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.672</v>
+        <v>15.082</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>TeamGroup</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>26.45</v>
+        <v>263</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.38</v>
+        <v>-2.41</v>
       </c>
       <c r="F38" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1728,33 +1728,33 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.44</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2915</v>
+        <v>86.2</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.32</v>
+        <v>-4.54</v>
       </c>
       <c r="F39" t="n">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1762,101 +1762,101 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3.86</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>581</v>
+        <v>192</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.19</v>
+        <v>-4.95</v>
       </c>
       <c r="F40" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>16.056</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20.15</v>
+        <v>8095</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.98</v>
+        <v>-3.17</v>
       </c>
       <c r="F41" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.288</v>
+        <v>12.121</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>111.5</v>
+        <v>323</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="F42" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1864,33 +1864,33 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.522</v>
+        <v>3.823</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>186.5</v>
+        <v>296</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.84</v>
+        <v>-3.9</v>
       </c>
       <c r="F43" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1898,67 +1898,67 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.457</v>
+        <v>4.296</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>90.3</v>
+        <v>141.5</v>
       </c>
       <c r="E44" t="n">
-        <v>0.22</v>
+        <v>-4.07</v>
       </c>
       <c r="F44" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.314</v>
+        <v>23.718</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>147.5</v>
+        <v>363</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.67</v>
+        <v>0.14</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1966,67 +1966,67 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>25.701</v>
+        <v>1.589</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>749</v>
+        <v>60.8</v>
       </c>
       <c r="E46" t="n">
-        <v>1.08</v>
+        <v>-9.25</v>
       </c>
       <c r="F46" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.858</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>28.9</v>
+        <v>2810</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>-3.6</v>
       </c>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2034,33 +2034,33 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.08599999999999999</v>
+        <v>3.543</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Sino-American</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1965</v>
+        <v>207</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.26</v>
+        <v>-4.39</v>
       </c>
       <c r="F48" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2068,33 +2068,33 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>21.494</v>
+        <v>4.658</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.59</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2102,74 +2102,108 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.913</v>
+        <v>6.313</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>352.5</v>
+        <v>28.8</v>
       </c>
       <c r="E50" t="n">
-        <v>1.59</v>
+        <v>-0.35</v>
       </c>
       <c r="F50" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Accumulation (Up)</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.41</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>晶心科</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Andes Tech</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>317</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-10.07</v>
+      </c>
+      <c r="F51" t="n">
+        <v>34</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Accumulation (Up)</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1.281</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>6173</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>信昌電</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Shinmore</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D52" t="n">
         <v>302.13</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F52" t="n">
         <v>0</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="H52" t="n">
         <v>5.105</v>
       </c>
     </row>
@@ -2184,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,187 +2261,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ChipMOS</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>41.75</v>
+        <v>36.62</v>
       </c>
       <c r="F2" t="n">
-        <v>1.26</v>
+        <v>0.87</v>
       </c>
       <c r="G2" t="n">
-        <v>7.004</v>
+        <v>12.121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GUC (Global Unichip)</t>
+          <t>ChipMOS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40.27</v>
+        <v>26.78</v>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>1.02</v>
       </c>
       <c r="G3" t="n">
-        <v>12.35</v>
+        <v>6.313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AWSC</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>IP Core (RISC-V)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>25.05</v>
       </c>
       <c r="F4" t="n">
-        <v>2.87</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.922</v>
+        <v>1.281</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Andes Tech</t>
+          <t>AWSC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IP Core (RISC-V)</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>37.7</v>
+        <v>23.35</v>
       </c>
       <c r="F5" t="n">
-        <v>0.86</v>
+        <v>2.79</v>
       </c>
       <c r="G5" t="n">
-        <v>1.41</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Win Semi</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>31.6</v>
+        <v>21.29</v>
       </c>
       <c r="F6" t="n">
-        <v>0.96</v>
+        <v>2.41</v>
       </c>
       <c r="G6" t="n">
-        <v>16.056</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VIS (Vanguard)</t>
+          <t>Win Semi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22.7</v>
+        <v>19.83</v>
       </c>
       <c r="F7" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="G7" t="n">
-        <v>3.457</v>
+        <v>15.082</v>
       </c>
     </row>
     <row r="8">
@@ -2432,13 +2466,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20.39</v>
+        <v>15.62</v>
       </c>
       <c r="F8" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G8" t="n">
-        <v>10.605</v>
+        <v>10.357</v>
       </c>
     </row>
     <row r="9">
@@ -2463,1098 +2497,1098 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20.28</v>
+        <v>14.36</v>
       </c>
       <c r="F9" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="G9" t="n">
-        <v>4.755</v>
+        <v>4.658</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18.32</v>
+        <v>12.96</v>
       </c>
       <c r="F10" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="G10" t="n">
-        <v>14.172</v>
+        <v>8.367000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faraday Tech</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15.43</v>
+        <v>12.82</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>1.79</v>
       </c>
       <c r="G11" t="n">
-        <v>0.951</v>
+        <v>2.643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>VIS (Vanguard)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.41</v>
+        <v>11.46</v>
       </c>
       <c r="F12" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="G12" t="n">
-        <v>7.912</v>
+        <v>3.279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PTI (Powertech)</t>
+          <t>ASMedia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11.8</v>
+        <v>10.39</v>
       </c>
       <c r="F13" t="n">
-        <v>1.51</v>
+        <v>0.88</v>
       </c>
       <c r="G13" t="n">
-        <v>4.479</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2609</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Yang Ming</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8.859999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="F14" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="G14" t="n">
-        <v>21.494</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.35</v>
+        <v>8.84</v>
       </c>
       <c r="F15" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="G15" t="n">
-        <v>4.514</v>
+        <v>2.391</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.24</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="G16" t="n">
-        <v>1.858</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.82</v>
+        <v>7.52</v>
       </c>
       <c r="F17" t="n">
-        <v>1.23</v>
+        <v>0.68</v>
       </c>
       <c r="G17" t="n">
-        <v>10.674</v>
+        <v>1.858</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.66</v>
+        <v>7.51</v>
       </c>
       <c r="F18" t="n">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="G18" t="n">
-        <v>25.701</v>
+        <v>2.199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ASMedia</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.43</v>
+        <v>6.28</v>
       </c>
       <c r="F19" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="G19" t="n">
-        <v>0.586</v>
+        <v>13.307</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yang Ming</t>
+          <t>PTI (Powertech)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.19</v>
+        <v>5.34</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5</v>
+        <v>1.27</v>
       </c>
       <c r="G20" t="n">
-        <v>1.577</v>
+        <v>4.296</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shinmore</t>
+          <t>Wan Hai Lines</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.05</v>
+        <v>4.74</v>
       </c>
       <c r="F21" t="n">
-        <v>0.46</v>
+        <v>0.85</v>
       </c>
       <c r="G21" t="n">
-        <v>5.105</v>
+        <v>1.707</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Shinmore</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95</v>
+        <v>0.46</v>
       </c>
       <c r="G22" t="n">
-        <v>49.021</v>
+        <v>5.105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ennostar Inc</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.24</v>
+        <v>3.84</v>
       </c>
       <c r="F23" t="n">
-        <v>0.88</v>
+        <v>1.51</v>
       </c>
       <c r="G23" t="n">
-        <v>0.913</v>
+        <v>10.526</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>eMemory</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IP Core</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.19</v>
+        <v>3.62</v>
       </c>
       <c r="F24" t="n">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="G24" t="n">
-        <v>3.86</v>
+        <v>2.174</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.68</v>
+        <v>1.31</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="G25" t="n">
-        <v>2.263</v>
+        <v>50.224</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.23</v>
+        <v>1.3</v>
       </c>
       <c r="F26" t="n">
-        <v>1.08</v>
+        <v>0.89</v>
       </c>
       <c r="G26" t="n">
-        <v>4.493</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="F27" t="n">
         <v>0.9</v>
       </c>
       <c r="G27" t="n">
-        <v>1.709</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>IP Core</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="F28" t="n">
-        <v>0.93</v>
+        <v>0.68</v>
       </c>
       <c r="G28" t="n">
-        <v>7.413</v>
+        <v>3.543</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.19</v>
+        <v>1.06</v>
       </c>
       <c r="F29" t="n">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
       <c r="G29" t="n">
-        <v>22.177</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.28</v>
+        <v>0.55</v>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>0.84</v>
       </c>
       <c r="G30" t="n">
-        <v>8.244999999999999</v>
+        <v>1.609</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Design - Mobile/AI</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-0.42</v>
+        <v>0.24</v>
       </c>
       <c r="F31" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="G31" t="n">
-        <v>32.014</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wan Hai Lines</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.46</v>
+        <v>1.18</v>
       </c>
       <c r="G32" t="n">
-        <v>1.522</v>
+        <v>23.718</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>-0.52</v>
       </c>
       <c r="F33" t="n">
-        <v>1.22</v>
+        <v>0.85</v>
       </c>
       <c r="G33" t="n">
-        <v>0.546</v>
+        <v>0.5590000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Wistron</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="F34" t="n">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="G34" t="n">
-        <v>1.549</v>
+        <v>7.102</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Quanta</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.76</v>
+        <v>-1.11</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="G35" t="n">
-        <v>4.101</v>
+        <v>20.096</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>IC Design - Mobile/AI</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.79</v>
+        <v>-2.16</v>
       </c>
       <c r="F36" t="n">
-        <v>0.78</v>
+        <v>1.01</v>
       </c>
       <c r="G36" t="n">
-        <v>0.556</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.99</v>
+        <v>-4</v>
       </c>
       <c r="F37" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="G37" t="n">
-        <v>8.138</v>
+        <v>0.552</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>Ennostar Inc</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.2</v>
+        <v>-4.55</v>
       </c>
       <c r="F38" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>6.21</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Visual Photonics</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.32</v>
+        <v>-4.69</v>
       </c>
       <c r="F39" t="n">
-        <v>0.74</v>
+        <v>1.17</v>
       </c>
       <c r="G39" t="n">
-        <v>1.96</v>
+        <v>4.328</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.49</v>
+        <v>-4.76</v>
       </c>
       <c r="F40" t="n">
-        <v>0.73</v>
+        <v>1.52</v>
       </c>
       <c r="G40" t="n">
-        <v>0.44</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.18</v>
+        <v>-5.56</v>
       </c>
       <c r="F41" t="n">
-        <v>0.66</v>
+        <v>1.01</v>
       </c>
       <c r="G41" t="n">
-        <v>0.288</v>
+        <v>3.823</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Yulon Motor</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.47</v>
+        <v>-5.57</v>
       </c>
       <c r="F42" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="G42" t="n">
-        <v>0.672</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>Lite-On</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.57</v>
+        <v>-5.64</v>
       </c>
       <c r="F43" t="n">
-        <v>0.93</v>
+        <v>1.21</v>
       </c>
       <c r="G43" t="n">
-        <v>1.084</v>
+        <v>4.222</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>Phison (Electronics)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.08</v>
+        <v>-5.76</v>
       </c>
       <c r="F44" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="G44" t="n">
-        <v>2.109</v>
+        <v>6.271</v>
       </c>
     </row>
     <row r="45">
@@ -3579,199 +3613,230 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.92</v>
+        <v>-6.57</v>
       </c>
       <c r="F45" t="n">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="G45" t="n">
-        <v>0.551</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulon Motor</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-5.09</v>
+        <v>-6.69</v>
       </c>
       <c r="F46" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="G46" t="n">
-        <v>0.08599999999999999</v>
+        <v>21.807</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.85</v>
+        <v>-6.77</v>
       </c>
       <c r="F47" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="G47" t="n">
-        <v>14.481</v>
+        <v>7.917</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>ADATA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Memory - NOR Flash</t>
+          <t>Memory - Module</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-7.94</v>
+        <v>-8.26</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9</v>
+        <v>1.13</v>
       </c>
       <c r="G48" t="n">
-        <v>2.815</v>
+        <v>1.589</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ADATA</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Memory - Module</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-8.27</v>
+        <v>-10.89</v>
       </c>
       <c r="F49" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G49" t="n">
-        <v>1.653</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CoAsia</t>
+          <t>Winbond Elec</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Memory - Flash/DRAM</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-10.15</v>
+        <v>-11.75</v>
       </c>
       <c r="F50" t="n">
-        <v>0.59</v>
+        <v>0.99</v>
       </c>
       <c r="G50" t="n">
-        <v>0.314</v>
+        <v>13.098</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>CoAsia</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-10.16</v>
+        <v>-13.71</v>
       </c>
       <c r="F51" t="n">
-        <v>1.05</v>
+        <v>0.67</v>
       </c>
       <c r="G51" t="n">
-        <v>0.639</v>
+        <v>0.294</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Macronix (MXIC)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Memory - NOR Flash</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>-15.81</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.694</v>
       </c>
     </row>
   </sheetData>
@@ -3785,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3822,13 +3887,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.7</v>
+        <v>25.05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>1.41</v>
+        <v>1.281</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -3837,55 +3902,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Memory - Packaging</t>
+          <t>Plastics</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.775</v>
+        <v>21.29</v>
       </c>
       <c r="C3" t="n">
-        <v>1.385</v>
+        <v>2.41</v>
       </c>
       <c r="D3" t="n">
-        <v>11.483</v>
+        <v>3.594</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compound Semi</t>
+          <t>Design Service (AI)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.65</v>
+        <v>20.23</v>
       </c>
       <c r="C4" t="n">
-        <v>1.63</v>
+        <v>1.19</v>
       </c>
       <c r="D4" t="n">
-        <v>21.492</v>
+        <v>22.647</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Design Service (AI)</t>
+          <t>Memory - Packaging</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.045</v>
+        <v>16.06</v>
       </c>
       <c r="C5" t="n">
-        <v>0.99</v>
+        <v>1.145</v>
       </c>
       <c r="D5" t="n">
-        <v>23.024</v>
+        <v>10.609</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -3894,17 +3959,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Foundry - 8inch</t>
+          <t>OSAT (Packaging)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.7</v>
+        <v>15.62</v>
       </c>
       <c r="C6" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="D6" t="n">
-        <v>3.457</v>
+        <v>10.357</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -3913,17 +3978,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OSAT (Packaging)</t>
+          <t>OSAT (Testing)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.39</v>
+        <v>12.96</v>
       </c>
       <c r="C7" t="n">
-        <v>0.84</v>
+        <v>1.14</v>
       </c>
       <c r="D7" t="n">
-        <v>10.605</v>
+        <v>8.367000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3932,36 +3997,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wafer - Material</t>
+          <t>Compound Semi</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.3</v>
+        <v>12.83</v>
       </c>
       <c r="C8" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="D8" t="n">
-        <v>18.927</v>
+        <v>20.349</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OSAT (Testing)</t>
+          <t>Foundry - 8inch</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13.41</v>
+        <v>11.46</v>
       </c>
       <c r="C9" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="D9" t="n">
-        <v>7.912</v>
+        <v>3.279</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -3970,17 +4035,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC Design - Network</t>
+          <t>IC Design - High Speed</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.24</v>
+        <v>10.39</v>
       </c>
       <c r="C10" t="n">
-        <v>0.61</v>
+        <v>0.88</v>
       </c>
       <c r="D10" t="n">
-        <v>1.858</v>
+        <v>0.644</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -3989,93 +4054,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC Design - High Speed</t>
+          <t>Wafer - Material</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.43</v>
+        <v>10.32</v>
       </c>
       <c r="C11" t="n">
-        <v>0.67</v>
+        <v>1.12</v>
       </c>
       <c r="D11" t="n">
-        <v>0.586</v>
+        <v>17.965</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Foundry - Logic</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.6</v>
+        <v>9.273333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>1.02</v>
+        <v>1.163333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>74.72200000000001</v>
+        <v>6.16</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Power Supply</t>
+          <t>IC Design - Network</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.545</v>
+        <v>7.52</v>
       </c>
       <c r="C13" t="n">
-        <v>0.98</v>
+        <v>0.68</v>
       </c>
       <c r="D13" t="n">
-        <v>25.987</v>
+        <v>1.858</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.05</v>
+        <v>4.492</v>
       </c>
       <c r="C14" t="n">
-        <v>0.46</v>
+        <v>0.944</v>
       </c>
       <c r="D14" t="n">
-        <v>5.105</v>
+        <v>8.382999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Compound/LED</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.24</v>
+        <v>4.05</v>
       </c>
       <c r="C15" t="n">
-        <v>0.88</v>
+        <v>0.46</v>
       </c>
       <c r="D15" t="n">
-        <v>0.913</v>
+        <v>5.105</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -4088,13 +4153,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.19</v>
+        <v>1.08</v>
       </c>
       <c r="C16" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="D16" t="n">
-        <v>3.86</v>
+        <v>3.543</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -4103,17 +4168,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Design Service</t>
+          <t>Foundry - Logic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.64</v>
+        <v>0.655</v>
       </c>
       <c r="C17" t="n">
-        <v>0.745</v>
+        <v>1.145</v>
       </c>
       <c r="D17" t="n">
-        <v>1.265</v>
+        <v>73.94199999999999</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -4122,36 +4187,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Airline</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.756666666666667</v>
+        <v>0.65</v>
       </c>
       <c r="C18" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="D18" t="n">
-        <v>4.808</v>
+        <v>1.038</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Memory - DRAM</t>
+          <t>IC Design - Display</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
       <c r="C19" t="n">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
       <c r="D19" t="n">
-        <v>22.177</v>
+        <v>1.609</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -4160,17 +4225,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Foundry - Memory</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.28</v>
+        <v>-0.52</v>
       </c>
       <c r="C20" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="D20" t="n">
-        <v>8.244999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -4183,13 +4248,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.42</v>
+        <v>-2.16</v>
       </c>
       <c r="C21" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="D21" t="n">
-        <v>32.014</v>
+        <v>31.67</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -4198,115 +4263,115 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC Design - Display</t>
+          <t>Design Service</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.465000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.75</v>
+        <v>0.765</v>
       </c>
       <c r="D22" t="n">
-        <v>1.549</v>
+        <v>1.222</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Power Supply</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.79</v>
+        <v>-3.375</v>
       </c>
       <c r="C23" t="n">
-        <v>0.78</v>
+        <v>1.115</v>
       </c>
       <c r="D23" t="n">
-        <v>0.556</v>
+        <v>24.318</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Compound/LED</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.156</v>
+        <v>-4.55</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>7.856</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Memory - Controller</t>
+          <t>AI Server/OEM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-1.2</v>
+        <v>-5.5675</v>
       </c>
       <c r="C25" t="n">
-        <v>0.61</v>
+        <v>1.1525</v>
       </c>
       <c r="D25" t="n">
-        <v>6.21</v>
+        <v>19.706</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Automobile</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.325</v>
+        <v>-5.57</v>
       </c>
       <c r="C26" t="n">
-        <v>0.645</v>
+        <v>0.77</v>
       </c>
       <c r="D26" t="n">
-        <v>0.96</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Server/OEM</t>
+          <t>Memory - Controller</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.71</v>
+        <v>-5.76</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1</v>
+        <v>0.79</v>
       </c>
       <c r="D27" t="n">
-        <v>20.291</v>
+        <v>6.271</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -4316,13 +4381,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-4.236666666666666</v>
+        <v>-6.276666666666666</v>
       </c>
       <c r="C28" t="n">
-        <v>1.07</v>
+        <v>1.176666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -4331,17 +4396,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Automobile</t>
+          <t>Memory - DRAM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-5.09</v>
+        <v>-6.69</v>
       </c>
       <c r="C29" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08599999999999999</v>
+        <v>21.807</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -4350,17 +4415,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Memory - Flash/DRAM</t>
+          <t>Foundry - Memory</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-5.85</v>
+        <v>-6.77</v>
       </c>
       <c r="C30" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="D30" t="n">
-        <v>14.481</v>
+        <v>7.917</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -4369,19 +4434,38 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Memory - Flash/DRAM</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D31" t="n">
+        <v>13.098</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Memory - NOR Flash</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>-7.94</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2.815</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="B32" t="n">
+        <v>-15.81</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="E32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4488,38 +4572,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2060</v>
+        <v>1965</v>
       </c>
       <c r="E2" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="G2" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-5.9208</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>57.58</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-5.949</v>
-      </c>
-      <c r="I2" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>36.7</v>
-      </c>
       <c r="K2" t="n">
-        <v>4.13</v>
+        <v>4.56</v>
       </c>
       <c r="L2" t="n">
-        <v>-31.4</v>
+        <v>69.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>❌ EXIT</t>
         </is>
       </c>
     </row>
@@ -4540,34 +4624,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4690</v>
+        <v>4525</v>
       </c>
       <c r="E3" t="n">
-        <v>-3</v>
+        <v>-3.52</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.42</v>
+        <v>-2.16</v>
       </c>
       <c r="G3" t="n">
-        <v>54.04</v>
+        <v>50.59</v>
       </c>
       <c r="H3" t="n">
-        <v>145.9217</v>
+        <v>107.5118</v>
       </c>
       <c r="I3" t="n">
-        <v>35.9</v>
+        <v>20.8</v>
       </c>
       <c r="J3" t="n">
-        <v>24.2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4.77</v>
+        <v>4.99</v>
       </c>
       <c r="L3" t="n">
-        <v>-6</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -4592,34 +4676,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>90.3</v>
+        <v>86.2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.22</v>
+        <v>-4.54</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.15</v>
+        <v>-13.71</v>
       </c>
       <c r="G4" t="n">
-        <v>51.46</v>
+        <v>44.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.0282</v>
+        <v>-3.5494</v>
       </c>
       <c r="I4" t="n">
-        <v>62.1</v>
+        <v>30.8</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>35.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-48.1</v>
+        <v>-7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -4656,7 +4740,7 @@
         <v>33.01</v>
       </c>
       <c r="H5" t="n">
-        <v>9.4855</v>
+        <v>10.23</v>
       </c>
       <c r="I5" t="n">
         <v>23.7</v>
@@ -4696,34 +4780,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>558</v>
+        <v>508</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.18</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>8.35</v>
+        <v>-4.69</v>
       </c>
       <c r="G6" t="n">
-        <v>59.64</v>
+        <v>44.88</v>
       </c>
       <c r="H6" t="n">
-        <v>25.4473</v>
+        <v>19.7951</v>
       </c>
       <c r="I6" t="n">
-        <v>60.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.43</v>
+        <v>5.95</v>
       </c>
       <c r="L6" t="n">
-        <v>-24.8</v>
+        <v>29.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -4748,38 +4832,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.19</v>
+        <v>-3.61</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.99</v>
+        <v>-4.76</v>
       </c>
       <c r="G7" t="n">
-        <v>51.52</v>
+        <v>36.71</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1214</v>
+        <v>-0.9423</v>
       </c>
       <c r="I7" t="n">
-        <v>29.2</v>
+        <v>-24</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="L7" t="n">
-        <v>17.9</v>
+        <v>32.1</v>
       </c>
       <c r="M7" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>👀 WATCH</t>
+          <t>❌ EXIT</t>
         </is>
       </c>
     </row>

--- a/Taiwan_Market_Data_Latest.xlsx
+++ b/Taiwan_Market_Data_Latest.xlsx
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Evergreen Marine</t>
+          <t>Formosa Plastics</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>264</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>13.55</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>617</v>
+        <v>314</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,33 +504,33 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.643</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Formosa Plastics</t>
+          <t>China Steel</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80.90000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.49</v>
+        <v>1.83</v>
       </c>
       <c r="F3" t="n">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3.594</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="4">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E4" t="n">
-        <v>-9.09</v>
+        <v>0.71</v>
       </c>
       <c r="F4" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.321</v>
       </c>
     </row>
     <row r="5">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>121.5</v>
+        <v>125</v>
       </c>
       <c r="E5" t="n">
-        <v>8.970000000000001</v>
+        <v>2.88</v>
       </c>
       <c r="F5" t="n">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.707</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="6">
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64.5</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>8.039999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="F6" t="n">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,33 +640,33 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.81</v>
+        <v>1.975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alchip</t>
+          <t>KYEC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4055</v>
+        <v>296.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.67</v>
+        <v>-2.79</v>
       </c>
       <c r="F7" t="n">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,101 +674,101 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10.526</v>
+        <v>8.962999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nanya Technology</t>
+          <t>Fubon Financial</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>160.5</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.27</v>
+        <v>0.31</v>
       </c>
       <c r="F8" t="n">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.807</v>
+        <v>2.573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Macronix (MXIC)</t>
+          <t>Novatek</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106.5</v>
+        <v>560</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.19</v>
+        <v>2.56</v>
       </c>
       <c r="F9" t="n">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.694</v>
+        <v>1.693</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CTBC Financial</t>
+          <t>Evergreen Marine</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>71.59999999999999</v>
+        <v>263</v>
       </c>
       <c r="E10" t="n">
-        <v>6.39</v>
+        <v>-0.38</v>
       </c>
       <c r="F10" t="n">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.199</v>
+        <v>3.196</v>
       </c>
     </row>
     <row r="11">
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="E11" t="n">
-        <v>3.36</v>
+        <v>0.32</v>
       </c>
       <c r="F11" t="n">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -810,169 +810,169 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.644</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Macronix (MXIC)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2490</v>
+        <v>110</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.35</v>
+        <v>3.29</v>
       </c>
       <c r="F12" t="n">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>50.224</v>
+        <v>2.822</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EVA Air</t>
+          <t>Nanya Technology</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>480.5</v>
       </c>
       <c r="E13" t="n">
-        <v>3.86</v>
+        <v>-1.54</v>
       </c>
       <c r="F13" t="n">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.737</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phison (Electronics)</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1965</v>
+        <v>2490</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.61</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6.271</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Transcend Info</t>
+          <t>Realtek</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>276</v>
+        <v>778</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.99</v>
+        <v>2.64</v>
       </c>
       <c r="F15" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.552</v>
+        <v>1.894</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TCB Financial</t>
+          <t>Faraday Tech</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27.2</v>
+        <v>211</v>
       </c>
       <c r="E16" t="n">
-        <v>2.84</v>
+        <v>9.9</v>
       </c>
       <c r="F16" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.469</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Winbond Elec</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>161.5</v>
+        <v>4475</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.76</v>
+        <v>-1.1</v>
       </c>
       <c r="F17" t="n">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1014,67 +1014,67 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>13.098</v>
+        <v>31.224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PSMC (Powerchip)</t>
+          <t>Cathay Financial</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67.5</v>
+        <v>114</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.51</v>
+        <v>-0.44</v>
       </c>
       <c r="F18" t="n">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7.917</v>
+        <v>2.218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KYEC</t>
+          <t>Alchip</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>305</v>
+        <v>3940</v>
       </c>
       <c r="E19" t="n">
-        <v>0.16</v>
+        <v>-2.84</v>
       </c>
       <c r="F19" t="n">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1082,67 +1082,67 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.367000000000001</v>
+        <v>9.932</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Novatek</t>
+          <t>Inventec</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>546</v>
+        <v>58.3</v>
       </c>
       <c r="E20" t="n">
-        <v>2.82</v>
+        <v>1.75</v>
       </c>
       <c r="F20" t="n">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.609</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Delta Elec</t>
+          <t>Quanta</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1775</v>
+        <v>323</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.67</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1150,203 +1150,203 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>20.096</v>
+        <v>3.756</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Foxconn</t>
+          <t>EVA Air</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>240</v>
+        <v>43.4</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.61</v>
+        <v>0.93</v>
       </c>
       <c r="F22" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8.15</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Visual Photonics</t>
+          <t>China Airlines</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>508</v>
+        <v>20.65</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.960000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="F23" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Breakout</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.328</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fubon Financial</t>
+          <t>Foxconn</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="E24" t="n">
-        <v>4.58</v>
+        <v>1.25</v>
       </c>
       <c r="F24" t="n">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.391</v>
+        <v>8.496</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GlobalWafers</t>
+          <t>CTBC Financial</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1015</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.18</v>
+        <v>-0.28</v>
       </c>
       <c r="F25" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.307</v>
+        <v>2.291</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mega Financial</t>
+          <t>ASE Tech</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50.9</v>
+        <v>747</v>
       </c>
       <c r="E26" t="n">
-        <v>3.25</v>
+        <v>0.95</v>
       </c>
       <c r="F26" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.15</v>
+        <v>10.053</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inventec</t>
+          <t>PSMC (Powerchip)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>57.3</v>
+        <v>71</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.35</v>
+        <v>5.19</v>
       </c>
       <c r="F27" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1354,67 +1354,67 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.631</v>
+        <v>7.908</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ASE Tech</t>
+          <t>TCB Financial</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>740</v>
+        <v>27.15</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.54</v>
+        <v>-0.18</v>
       </c>
       <c r="F28" t="n">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>10.357</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Delta Elec</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4525</v>
+        <v>1785</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1422,203 +1422,203 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>31.67</v>
+        <v>19.012</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lite-On</t>
+          <t>Mega Financial</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>276</v>
+        <v>51.1</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.23</v>
+        <v>0.39</v>
       </c>
       <c r="F30" t="n">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.222</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Airlines</t>
+          <t>Transcend Info</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20.5</v>
+        <v>278.5</v>
       </c>
       <c r="E31" t="n">
-        <v>1.74</v>
+        <v>0.91</v>
       </c>
       <c r="F31" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.301</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wistron</t>
+          <t>Andes Tech</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>187</v>
+        <v>315.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8</v>
+        <v>-0.47</v>
       </c>
       <c r="F32" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Accumulation (Up)</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7.102</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cathay Financial</t>
+          <t>GlobalWafers</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>114.5</v>
+        <v>1020</v>
       </c>
       <c r="E33" t="n">
-        <v>4.09</v>
+        <v>0.49</v>
       </c>
       <c r="F33" t="n">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.174</v>
+        <v>13.759</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Steel</t>
+          <t>eMemory</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19.15</v>
+        <v>2875</v>
       </c>
       <c r="E34" t="n">
-        <v>1.06</v>
+        <v>2.31</v>
       </c>
       <c r="F34" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Breakout</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.5590000000000001</v>
+        <v>3.584</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Realtek</t>
+          <t>GUC (Global Unichip)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>758